--- a/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
@@ -131,8 +131,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】現在の米国 (無作為化比較試験 (RCT) / N = 1,803例)
-【方法】そしてヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラスIIaの適応症として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要である
-【結果】患者の平均年齢は60.4歳で、23.7%が女性であった。 24ヵ月時点で、主要エンドポイント事象はDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)
+【方法】ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要である
+【結果】患者の平均年齢は60.4歳で、23.7%が女性であった。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)
 【結論】（韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）</t>
   </si>
   <si>
@@ -225,7 +225,7 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません (前向き研究 (Prospective) / N = 50例)
-【方法】STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道解析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーである
+【方法】STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーである
 【結果】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された
 【結論】実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較をを裏付けるものである</t>
   </si>
@@ -302,7 +302,7 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨される (観察研究・その他 / N = 65,020例)
-【方法】現在の実践および関連する予測因子は不明である
+【方法】現在の慣行および関連する予測因子は不明である
 【結果】平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されませんであった
 【結論】脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因であったが、中止の多くを説明するものではありませんであった</t>
   </si>
@@ -326,7 +326,7 @@
   <si>
     <t xml:space="preserve">【概要】心室頻拍 (VT) アブレーションは、再発性 VT に対する確立された治療法である。しかし、この集団における手術前後の虚血性脳卒中（P-IS）の予後的重要性は、依然として十分に特徴づけられていない (観察研究・その他 / N = 57,624例)
 【方法】この研究では、大規模な全国データベースを使用して、VT アブレーションを受けている患者における P-IS の発生率、予測因子、および死亡率への影響を調べました
-【結果】VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。脳卒中を有さない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）
+【結果】VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。脳卒中を持たない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）
 【結論】これらの発見は、VT アブレーションを受ける患者の P-IS リスクを軽減する戦略を評価する専用の研究の必要性を強調している</t>
   </si>
   <si>
@@ -349,8 +349,8 @@
   <si>
     <t xml:space="preserve">【概要】はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られる (観察研究・その他 / N = 6,020例)
 【方法】しかし、複数の併存疾患や手術リスクの増加を示すことが多い超高齢患者（80 歳以上）における手術の安全性と有効性に関するデータは依然として限られている
-【結果】この研究は、大規模電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。急性処置の成功は 104 人の患者 (98.1%) で達成された
-【結論】これらの所見は、この増加し脆弱な患者集団においてカテーテルアブレーションを検討する場合、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしている</t>
+【結果】この研究は、大規模な電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。急性処置の成功は 104 人の患者 (98.1%) で達成された
+【結論】これらの発見は、この増加しつつある脆弱な患者集団においてカテーテルアブレーションを検討する際には、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしている</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -412,7 +412,7 @@
   <si>
     <t xml:space="preserve">【概要】我々は以前、心房細動（AF）の非肺静脈（PV）誘因は左心房（LA）の低電圧領域（LVA）から生じることが多いと報告した (観察研究・その他 / N = 1,428例)
 【方法】ただし、トリガー部位と LVA の分布の間の具体的な空間的関係は完全には解明されていません
-【結果】と結果: カテーテルアブレーションを受けた AF 患者 1,428 人のうち、非 PV 誘因に対して陽性反応を示した 187 人 (13.1%) が登録された。研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました
+【結果】と結果：カテーテルアブレーションを受けているAF患者1,428人のうち、非PV誘因に対して陽性反応を示した187人（13.1%）が登録された。研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました
 【結論】電圧マッピング パターンは、LA 内の非 PV トリガー サイトの位置特定と検出を容易にする可能性がありる</t>
   </si>
   <si>
@@ -453,7 +453,7 @@
 (A Comparison of Safety and Outcome Using Three Different Sedation Strategies During Pulsed Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションの新しい治療法である (観察研究・その他 / N = 1,269例)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティである (観察研究・その他 / N = 1,269例)
 【方法】ただし、治療中の患者の適切な鎮静は不可欠である
 【結果】患者は鎮静戦略に従って層別化された。鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました
 【結論】を認めた心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんであった</t>
@@ -561,7 +561,7 @@
   <si>
     <t xml:space="preserve">【概要】現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨している (観察研究・その他 / N = 201例)
 【方法】AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている
-【結果】AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。 CHADS-VA スコアが 1 以上の患者を対象に、リズムに基づく OAC 戦略がモデル化された。この戦略は、毎日の負荷が 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上で、さまざまな OAC ウィンドウ期間で開始された
+【結果】AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。リズムに基づく OAC 戦略は、CHADS-VA スコアが 1 以上の患者を対象に、異なる OAC ウィンドウ期間で 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上の毎日の負荷によって誘発され、モデル化された
 【結論】これらの戦略には、臨床転帰の前向き評価が必要である</t>
   </si>
   <si>
@@ -582,10 +582,10 @@
 (Safety and Efficacy of Left Atrial Ablation After Percutaneous Left Atrial Appendage Occlusion in High-Bleeding-Risk Patients with Atrial Fibrillation: A Multicenter Analysis from the PROCEED-AF Ablation Registry.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】と目的: 左心耳 (LAAO) デバイスを装着した患者は AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実である (観察研究・その他 / N = 198例)
+    <t xml:space="preserve">【概要】と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実である (観察研究・その他 / N = 198例)
 【方法】この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することであった
-【結果】と目的: 左心耳 (LAAO) デバイスを装着した患者は AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実である。データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析された
-【結論】既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであった。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血イベントを伴うアブレーション後の短期間の OAC に耐えました</t>
+【結果】と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実である。データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析された
+【結論】既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであった。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血事象を伴うアブレーション後の短期間の OAC に耐えました</t>
   </si>
   <si>
     <t xml:space="preserve">Europace
@@ -607,8 +607,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性がありる (観察研究・その他 / N = 166例)
-【方法】従来のアブレーション戦略と比較して有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
-【結果】機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性がありる。目的: 従来のアブレーション戦略と比較して有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
+【方法】従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
+【結果】機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性がありる。目的: 従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
 【結論】生存率の向上には、多施設ランダム化試験による裏付けが必要である</t>
   </si>
   <si>
@@ -645,14 +645,14 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42720910/</t>
   </si>
   <si>
-    <t xml:space="preserve">非常に若い成人の心房細動に対するカテーテルアブレーション - AF-YOUNG レジストリの多中心データ
+    <t xml:space="preserve">非常に若い成人の心房細動に対するカテーテルアブレーション - AF-YOUNG レジストリからの多中心データ
 (Catheter ablation for atrial fibrillation in very young adults - multicentric data from the AF-YOUNG registry.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】30 歳未満の心房細動はまれである。アブレーション結果のデータは不足している (観察研究・その他 / N = 140例)
-【方法】多施設の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました
-【結果】ドイツの2つの大規模センターでは、心房細動のため初めて肺静脈隔離術（PVI）を受けた30歳以下の患者（2005～2025年）を遡及的に対象とした。再発: 90 日間のブランク期間後に心房細動が記録された
-【結論】心房細動のサブタイプは、若年成人の第一選択の調律制御として早期にアブレーションを導入することを主張する可能性がある最も強力な決定要因である</t>
+【方法】多施設共同の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました
+【結果】ドイツの 2 つの大規模センターでは、心房細動で初めて肺静脈隔離術 (PVI) を受けた 30 歳以下の患者を遡及的に対象とした (2005 ～ 2025 年)。再発: 90 日間のブランク期間後に心房細動が記録された
+【結論】心房細動のサブタイプは、若年成人の第一選択の調律制御としてアブレーションを早期に導入することを主張する可能性がある最も強力な決定要因である</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -670,9 +670,9 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入された (観察研究・その他 / N = 133例)
-【方法】しかし、この技術、特に補助的な後壁隔離術 (PWI) や肺静脈外部位に関する実際のデータは依然として限られている
-【結果】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入された。しかし、この技術、特に補助的な後壁隔離術 (PWI) や肺静脈外部位に関する実際のデータは依然として限られている
-【結論】補助的な PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんであった</t>
+【方法】しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られている
+【結果】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入された。しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られている
+【結論】補助的 PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんであった</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -689,9 +689,9 @@
 (Anatomical Approach from Aortic Sinus of Valsalva for Para-Hisian Premature Ventricular Contractions: Safety and Outcomes.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は、伝導系損傷のリスクのため依然として不確実である (観察研究・その他 / N = 114例)
+    <t xml:space="preserve">【概要】伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実である (観察研究・その他 / N = 114例)
 【方法】冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する
-【結果】傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は、伝導系損傷のリスクのため依然として不確実である。急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位がを評価した
+【結果】伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実である。急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位がを評価した
 【結論】早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測される</t>
   </si>
   <si>
@@ -709,9 +709,9 @@
 (Significance of different electrogram morphologies at the onset of ventricular tachycardia episodes.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】心臓埋め込み型デバイスによって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明である (観察研究・その他 / N = 113例)
+    <t xml:space="preserve">【概要】心臓植込み型装置によって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明である (観察研究・その他 / N = 113例)
 【方法】この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった
-【結果】この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった。アブレーション中、タイプ B のみのグループはより誘導性の VT 形態を示し (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままであった (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87; P = 0.002)
+【結果】この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった。アブレーション中、タイプ B のみのグループはより誘発性の VT 形態を持ち (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままであった (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87、P = 0.002)
 【結論】開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している</t>
   </si>
   <si>
@@ -725,13 +725,13 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42692318/</t>
   </si>
   <si>
-    <t xml:space="preserve">心房細動アブレーション後の心房不整脈再発を軽減するウェアラブル刺激装置を使用した非侵襲性正中神経刺激：NEUROPULSE パイロット
+    <t xml:space="preserve">心房細動アブレーション後の心房不整脈の再発を軽減するためのウェアラブル刺激装置を使用した非侵襲性正中神経刺激：NEUROPULSE パイロット
 (Non-Invasive Median Nerve Stimulation with a Wearable Stimulator to Reduce Atrial Arrhythmia Recurrence after Atrial Fibrillation Ablation: The NEUROPULSE Pilot.)</t>
   </si>
   <si>
     <t xml:space="preserve">【概要】心房細動 (AF) アブレーションの成功率を向上させるために、効果はさまざまですが、心筋破壊を犠牲にして経験的病変が配置されることがよくありる (観察研究・その他 / N = 59例)
 【方法】自律神経調節は、過度の心筋損傷を引き起こすことなくリズムの結果を改善する非切除的な補助手段を提供する可能性がありる
-【結果】年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。 During post-blanking follow-up (months 2-6), 12 AF/AT/AFL events occurred with MNS and 243 with sham (rate ratio [RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001)
+【結果】年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。ブランキング後の追跡調査（2～6か月）中、MNSでは12件のAF/AT/AFLイベントが発生し、偽では243件が発生した（発生率比[RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001）
 【結論】このパイロット研究は、適切な検出力試験での確認を保証しる</t>
   </si>
   <si>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">【概要】緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質である (観察研究・その他 / N = 44例)
 【方法】ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません
 【結果】緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質である。結果：合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）
-【結論】Further studies are warranted to evaluate this approach in larger populations</t>
+【結論】より大きな集団でこのアプローチを評価するには、さらなる研究が必要である</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -771,7 +771,7 @@
   <si>
     <t xml:space="preserve">【概要】ブルガダ症候群 (BrS) における運動中の前胸部 J ポイント上昇の強調の臨床的意義は依然として不明である (観察研究・その他 / N = 41例)
 【方法】この研究は、大規模な単一施設の BrS コホートにおける運動中の J ポイント上昇の強調の有病率と予後的重要性を判断することを目的としました
-【結果】全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。表現型は連続検査で非常に再現性が高かった（追跡 EST の 88%）
+【結果】全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。表現型は連続検査で非常に再現性が高かった (追跡 EST の 88%)
 【結論】これらの発見は、BrS に対する臨床診断または遺伝的感受性を持つ患者の評価に EST を含めることを裏付けており、運動関連のリスクカウンセリングに情報を提供する可能性がありる</t>
   </si>
   <si>
@@ -792,7 +792,7 @@
 (Clinical and experimental evaluation of averaged impedance drop during radiofrequency catheter ablation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】メッシュ状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難である (観察研究・その他 / N = 30例)
+    <t xml:space="preserve">【概要】メッシュ形状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難である (観察研究・その他 / N = 30例)
 【方法】この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました
 【結果】この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。方法：TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました
 【結論】伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆している</t>
@@ -813,7 +813,7 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】と目的: パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療にますます使用されている (観察研究・その他 / N = 22例)
-【方法】RESET-AFは、新規のシングルショットPFAシステム（ElePulse、CRC EP、タスティン、カリフォルニア州、米国）を使用したAFアブレーションのシングルアーム、ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった
+【方法】RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった
 【結果】症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた
 【結論】発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました</t>
   </si>
@@ -838,7 +838,7 @@
     <t xml:space="preserve">【概要】シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません (観察研究・その他 / N = 15例)
 【方法】既存の焦点 PFA 技術では、個別のアブレーションが可能ですが、複数の心臓および呼吸サイクルにわたってエネルギーを送達する必要があるため、持続的なカテーテルの安定性が重要となり、処置の効率が低下する可能性がありる
 【結果】シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません。 32 人の患者の再マッピングでは、波形の進化に伴う PVI 耐久性の漸進的な改善が実証された。波形 C は静脈あたり 94.2% の PVI 耐久性を達成しました
-【結論】臨床試験: gov: (FIELD-PULSE 研究; 心房細動患者における FieldForce アブレーション システムの安全性と実現可能性を評価するための市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589)</t>
+【結論】臨床試験: 政府：（FIELD-PULSE 研究; 心房細動患者におけるフィールドフォースアブレーションシステムの安全性と実現可能性を評価するための、市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589）</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -855,10 +855,10 @@
 (High-Intensity Ultrasound Catheter Ablation: Transmural Ventricular Lesions Through Transducer-Tissue Contact Sensing.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率が 75% 未満、貫壁性が 60% 未満という一貫性のない心筋ターゲティングが生じる (観察研究・その他 / N = 10例)
-【方法】肥大型心筋症 (HCM) における深心室頻拍 (VT) アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドする HIU カテーテルとリアルタイム接触センシング方法を設計しました
-【結果】高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率が 75% 未満、貫壁性が 60% 未満という一貫性のない心筋ターゲティングが生じる。結果: 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました
-【結論】リアルタイム双極インピーダンス CSG-HIU は歴史的な方向性の制限を克服し、100% の病変効率とより予測可能な貫壁性を達成しる</t>
+    <t xml:space="preserve">【概要】高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率 &lt; 75%、貫壁性 &lt; 60% という一貫性のない心筋ターゲティングが生じる (観察研究・その他 / N = 10例)
+【方法】我々は、肥大型心筋症（HCM）における深心室頻拍（VT）アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドするためのHIUカテーテルとリアルタイム接触センシング法を設計した
+【結果】高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率 &lt; 75%、貫壁性 &lt; 60% という一貫性のない心筋ターゲティングが生じる。結果: 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました
+【結論】リアルタイム双極性インピーダンス CSG-HIU は歴史的な方向制限を克服し、100% の病変効率とより予測可能な貫壁性を達成しる</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -871,7 +871,7 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42749241/</t>
   </si>
   <si>
-    <t xml:space="preserve">新しい胸骨下リードからの血行力学センシング、電気センシング、および心室ペーシングの統合: 急性ヒト研究
+    <t xml:space="preserve">新しい胸骨下リードからの血行力学センシング、電気センシング、心室ペーシングの統合: 急性ヒト研究
 (Integrated hemodynamic sensing, electrical sensing, and ventricular pacing from a novel substernal lead: An acute human study.)</t>
   </si>
   <si>
@@ -943,7 +943,7 @@
   <si>
     <t xml:space="preserve">【概要】慢性心臓植込み型電子機器リードの経静脈的抜去は、線維性癒着や処置上のリスクによって課題が生じている (観察研究・その他 / N = 2例)
 【方法】新しい技術は、安全性と有効性の向上を目指している
-【結果】補助ツールなしで手術の成功 (リード除去) は 100% であった。すべての症例で癒着剥離に外部切断シースは必要ありませんであった。この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出によって特徴付けられ、潜在的に危険な外部切断シースの要件を回避することに成功しました
+【結果】補助ツールなしで手術の成功 (リード除去) は 100% であった。すべての症例で癒着剥離に外部切断シースは必要ありませんであった。この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出を特徴としており、潜在的に危険な外部切断シースの要件を回避することに成功しました
 【結論】リードの破損とアンカーの機能不全は、さらなる技術評価と臨床試験の余地があることを示している</t>
   </si>
   <si>
@@ -1004,7 +1004,7 @@
 (Left Atrial Voltage Attenuation Beyond Ablation Sites After Unipolar Pulsed-Field Ablation for Atrial Fibrillation.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広い電場を生成する可能性がありる (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性がありる (観察研究・その他 / 症例数: 不明)
 【方法】我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました
 【結果】アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成された。平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)
 【結論】Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定された</t>
@@ -1023,7 +1023,7 @@
     <t xml:space="preserve">【概要】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました (観察研究・その他 / 症例数: 不明)
 【方法】しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままである
 【結果】ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。不完全な病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました
-【結論】体系的な電気解剖学的再マッピングは、相当な手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要である</t>
+【結論】体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要である</t>
   </si>
   <si>
     <t>Yagishita A, Iimura K, Iijima A, Amino M, Ikari Y, Yoshioka K. Learning Curve of Pentaspline Pulsed-Field Ablation With Posterior Wall Isolation for Persistent Atrial Fibrillation.. J Cardiovasc Electrophysiol. 2026 Sep 27;:. doi: 10.1111/jce.70515 doi.</t>
@@ -1052,9 +1052,9 @@
 (Monitored anesthesia care versus general anesthesia for balloon-in-basket pulsed-field ablation of atrial fibrillation: an age-matched analysis of procedural timing and acute procedural outcomes.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】米国では、全身麻酔 (GA) が心房細動 (AF) カテーテルアブレーションの鎮静戦略として好まれてきました。その理由の 1 つは、パルスフィールドアブレーション (PFA) システムが骨格筋の刺激と不快感を引き起こし、軽い鎮静下では耐えられないためである (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられる (観察研究・その他 / 症例数: 不明)
 【方法】最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性がありる
-【結果】米国では、全身麻酔 (GA) が心房細動 (AF) カテーテルアブレーションの鎮静戦略として好まれてきました。その理由の 1 つは、パルスフィールドアブレーション (PFA) システムが骨格筋の刺激と不快感を引き起こし、軽い鎮静下では耐えられないためである。施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較された
+【結果】米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられる。施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較された
 【結論】MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されている</t>
   </si>
   <si>
@@ -1173,7 +1173,7 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えている (観察研究・その他 / 症例数: 不明)
-【方法】我々は、左室心室頻拍アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介しる
+【方法】我々は、左心室頻脈アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介しる
 【結果】この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんであった。この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大しる
 【結論】この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大しる</t>
   </si>
@@ -1203,7 +1203,7 @@
     <t>2026-Sep-02</t>
   </si>
   <si>
-    <t xml:space="preserve">欧州の植込み型除細動器装着者における心室不整脈の性別特有の傾向
+    <t xml:space="preserve">ヨーロッパの植込み型除細動器装着者における心室不整脈の性別特有の傾向
 (Sex-specific trends in ventricular arrhythmias among European implantable cardioverter-defibrillator recipients.)</t>
   </si>
   <si>
@@ -1223,8 +1223,8 @@
   <si>
     <t xml:space="preserve">【概要】メディケア アドバンテージ (MA) および民間保険会社によって課された事前承認 (PA) 要件は、ガイドラインに基づく心臓電気生理学 (EP) ケアに対する組織的な障壁となり、患者に測定可能な損害を与え、医師と関連専門家に多大な管理上の負担を与え、医療格差を拡大させている (観察研究・その他 / 症例数: 不明)
 【方法】この論文では、MA キャピテーション モデルの財務アーキテクチャと、それが否認に対して生み出す構造的インセンティブを検証し、サードパーティの否認組織、人工知能ベースのアルゴリズム、不透明な適用基準など、否認システムの根本原因を特徴づける。監察総監室および上院常設調査小委員会からの連邦監督の結果をレビューし、心房細動のカテーテルアブレーション、植込み型除細動器治療、左心耳閉塞、および除細動を伴う心臓再同期療法に対する処置特有の拒否パターンを分析しる
-【結果】2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられている
-【結論】2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられている</t>
+【結果】2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会の行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられている
+【結論】2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会の行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられている</t>
   </si>
   <si>
     <t>Greenberg SJ, Lakkireddy D, Shanker A, Liu CF, Slotwiner DJ, Al-Khatib SM, et al.. Heart Rhythm Society and Heart Rhythm advocates position statement: Prior authorization in cardiac electrophysiology: Evidence, policy, and reform.. Heart Rhythm. 2026 Sep 17;:. doi: 10.1016/j.hrthm.2026.08.046 doi.</t>
@@ -1299,10 +1299,10 @@
 (Ablation with the circular pulsed field ablation catheter: Tips &amp; techniques for using the PulseSelect catheter.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす新しい心臓アブレーション方法である (観察研究・その他 / 症例数: 不明)
-【方法】熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を備えているため、周囲の構造への巻き添え損傷のリスクが軽減される
-【結果】英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外にもカテーテルの使用を安全に拡大するのに役立つ可能性のある実践的な概念、X線透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てている
-【結論】英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外にもカテーテルの使用を安全に拡大するのに役立つ可能性のある実践的な概念、X線透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てている</t>
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす心臓アブレーションの新しい方法である (観察研究・その他 / 症例数: 不明)
+【方法】熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を持っているため、周囲の構造への巻き添え損傷のリスクが軽減される
+【結果】英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外のカテーテルの使用の安全な拡大に役立つ可能性のある実践的な概念、透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てる
+【結論】英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外のカテーテルの使用の安全な拡大に役立つ可能性のある実践的な概念、透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てる</t>
   </si>
   <si>
     <t>Ballesteros G, Rahim SMZ, Osman F. Ablation with the circular pulsed field ablation catheter: Tips &amp; techniques for using the PulseSelect catheter.. J Interv Card Electrophysiol. 2026 Sep 15;:. doi: 10.1007/s10840-026-02436-1 doi.</t>
@@ -1385,10 +1385,10 @@
 (The Pear Strategy for Two-Ring Pulmonary Vein Isolation: Antral and Sleeve Ablation Using a Balloon-in-Basket Pulsed Field Ablation Catheter.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションのための有望なエネルギー源として浮上している (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションの有望なエネルギー源として浮上している (観察研究・その他 / 症例数: 不明)
 【方法】この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました
-【結果】この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。結果：50人の患者（62％が発作性AF、42％が女性、平均年齢68±10歳）が登録された
-【結論】ペアの 2 ステップ戦略は、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI を可能にし、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供しる</t>
+【結果】この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。結果: 50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録された
+【結論】Pear の 2 ステップ戦略により、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI が可能になる。このカテーテルは、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供しる</t>
   </si>
   <si>
     <t>Gunawardene MA, Urbani A, Urbanek L, Marx JA, Kheir J, Lurz J, et al.. The Pear Strategy for Two-Ring Pulmonary Vein Isolation: Antral and Sleeve Ablation Using a Balloon-in-Basket Pulsed Field Ablation Catheter.. J Cardiovasc Electrophysiol. 2026 Sep 06;:. doi: 10.1111/jce.70489 doi.</t>
@@ -1401,7 +1401,7 @@
 (Time-Dependent Diagnostic Yield and Therapeutic Impact of Implantable Loop Recorders, Brugada Syndrome as the Exception.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる可能性がありる (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる場合がありる (観察研究・その他 / 症例数: 不明)
 【方法】われわれは、失神、動悸、原因性脳卒中、またはブルガダ症候群のために移植された患者間で、ILRで検出された不整脈の時間依存的な診断率と臨床的関連性が異な​​るかどうかを評価した
 【結果】これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしている
 【結論】これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしている</t>
@@ -1418,8 +1418,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化しる (観察研究・その他 / 症例数: 不明)
-【方法】このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合したものである
-【結果】同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化しる。このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合したものである
+【方法】このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合している
+【結果】同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化しる。このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合している
 【結論】この集団における証拠に基づく実践を推進するには、標準化された報告を備えた将来の多施設登録が必要である</t>
   </si>
   <si>
@@ -1433,7 +1433,7 @@
 (2026 HRS/PACES scientific statement on the use of antiarrhythmic drugs in understudied clinical scenarios.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関する試験ではすべての患者およびシナリオが代表されているわけではありません (観察研究・その他 / 症例数: 不明)
+    <t xml:space="preserve">【概要】抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではありません (観察研究・その他 / 症例数: 不明)
 【方法】この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定している
 【結果】この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定している
 【結論】また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供しる</t>
@@ -1471,13 +1471,13 @@
     <t>https://pubmed.ncbi.nlm.nih.gov/42692320/</t>
   </si>
   <si>
-    <t xml:space="preserve">Virtual Heart-Based Prediction of Ablation 臨床アウトカム in Persistent 心房細動 Based on Non-Pulmonary Vein Drivers
+    <t xml:space="preserve">非肺静脈ドライバーに基づく持続性心房細動におけるアブレーション結果の仮想心臓ベースの予測
 (Virtual Heart-Based Prediction of Ablation Outcomes in Persistent Atrial Fibrillation Based on Non-Pulmonary Vein Drivers.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴づけ、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている (観察研究・その他 / N = 165例)
-【方法】私たちは、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました
-【結果】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴づけ、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている。結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者でを認めた。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました
+    <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている (観察研究・その他 / N = 165例)
+【方法】我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました
+【結果】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている。結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者でを認めた。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました
 【結論】これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証される</t>
   </si>
   <si>
@@ -1524,8 +1524,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することである (観察研究・その他 / 症例数: 不明)
-【方法】2024年7月から、国際専門家グループはワーキンググループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または個別に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
-【結果】2024年7月から、国際専門家グループはワーキンググループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または個別に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
+【方法】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
+【結果】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
 【結論】このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している</t>
   </si>
   <si>
@@ -1545,7 +1545,7 @@
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心房細動アブレーションの状況を急速に再構築しました (観察研究・その他 / 症例数: 不明)
 【方法】このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てている
-【結果】不可逆的なエレクトロポレーションが心筋の選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、効率的かつ耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明しる
+【結果】不可逆的なエレクトロポレーションが心筋選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、そして効率的で耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明しる
 【結論】パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大している</t>
   </si>
   <si>
@@ -1564,8 +1564,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されている (観察研究・その他 / 症例数: 不明)
-【方法】初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送出時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発された
-【結果】この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較しる。結果: すべてのグループにおいて、側副傷害の証拠のない貫壁性、周囲性、肺静脈病変によって示されるように、急性および慢性肺静脈隔離効果が 100% を認めた
+【方法】初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発された
+【結果】この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較しる。結果: すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% を認めた
 【結論】Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんであった</t>
   </si>
   <si>
@@ -1585,7 +1585,7 @@
   <si>
     <t xml:space="preserve">【概要】PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解される (観察研究・その他 / 症例数: 不明)
 【方法】このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となる
-【結果】不整脈のメカニズムをさらに調査するために、対照心臓および cKO 心臓から単離した心室心筋細胞におけるパッチクランプ電気生理学と IonOptix Ca 過渡測定を使用しました
+【結果】不整脈のメカニズムをさらに調査するために、パッチクランプ電気生理学と、対照心臓およびcKO心臓から単離した心室心筋細胞におけるIonOptix Ca過渡測定を使用しました
 【結論】これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆している</t>
   </si>
   <si>
@@ -1670,7 +1670,7 @@
     <t>🇯🇵 抄録 (Abstract) 日本語全訳 (全文直訳)</t>
   </si>
   <si>
-    <t>背景: 現在の米国 そしてヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラスIIaの適応症として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要です。 方法：我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。 結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイント事象はDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に脳卒中が発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。 結論： 脳卒中リスクが中程度の心房細動患者では、抗凝固療法を行わなかった場合に比べ、DOAC療法は24カ月時点で脳卒中、全身性塞栓症、大出血、心血管疾患による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
+    <t>背景: 現在の米国 ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨しています。ただし、ランダム化試験からの証拠が必要です。 方法：我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。 結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。 結論： 脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
   </si>
   <si>
     <t>🔤 抄録 (Abstract) 英語原文</t>
@@ -1743,7 +1743,7 @@
     <t>10.1007/s10840-026-02435-2 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明です。 この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました。 方法：2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か月後に評価されました。 介入前の CT または MR イメージングでは、肺静脈 (PV) 入口径、真円度、断面積、気管分岐部間距離などの解剖学的特徴が評価されました。 確立された危険因子を調整した回帰モデルを、AA再発との関連性について使用しました。 結果：患者287人（年齢中央値66歳、女性34％、発作性AF61％）中、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.02-1.21); p = 0.021）、左下 PV のより高い円形度指数（0.01 の増加につき 1.04、95% CI (1.01-1.07); p = 0.005）および右上のPV (0.01 増加あたり OR 1.03、95% CI (1.00-1.06); p = 0.040) は AA 再発と関連していました。 カテーテルのサイズには相互作用はありませんでしたが、PF 適用の数には多少の影響がありました。 結論: 右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発と関連していました。 PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要です。</t>
+    <t>背景: パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明です。 この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました。 方法：2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か月後に評価されました。 次の解剖学的特徴が介入前の CT または MR 画像で評価されました: 肺静脈 (PV) 入口直径、真円度、断面積、気管分岐部間距離。 確立された危険因子について調整された回帰モデルが、AA再発との関連について使用されました。 結果：患者287人（年齢中央値66歳、女性34％、発作性AF61％）のうち、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.02-1.21); p = 0.021）、左下 PV のより高い円形度指数（0.01 の増加につき 1.04、95% CI (1.01-1.07); p = 0.005）および右上のPV (0.01 増加あたり OR 1.03、95% CI (1.00-1.06); p = 0.040) は AA 再発と関連していました。 カテーテルのサイズには相互作用はありませんでしたが、PF 適用の数には多少の影響がありました。 結論: 右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発と関連していました。 PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1775,7 +1775,7 @@
     <t>10.1016/j.hrthm.2026.09.004 doi</t>
   </si>
   <si>
-    <t>背景: 肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。 STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道解析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーです。 目的：前回の PVI 後の再発持続性 AF 患者における STAR Apollo ガイド下やり直しアブレーションの手順の実現可能性と安全性を検討し、12 か月のリズムの結果を説明すること。 方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された。 STAR マッピングには継続的な AF が必要であるため、分析は STAR マップが取得された 50 人の患者 (登録された 64 人中) に限定されました。 STAR マップのない 14 台は、手順で AF になっていなかったため除外されました。 3 か月、6 か月、および 12 か月後の来院時の手順パラメータ、安全性、リズムが記録されました。 結果: 50 人の患者全員が過去に 1 回の PVI と再発性の持続性 AF を経験しました。彼らは年齢 68.8 ± 8.7 歳、男性 35 名 (70.0%) で、BMI は 31.3 ± 5.5 kg/m でした。 46/50 (92.0%) で肺静脈の再接続が見つかり、再分離されました。 システムは、患者あたり 3 (2 ～ 3) 件の ESA の中央値を特定し、STAR マッピングにより、合計処置の中央値 125 (91 ～ 166) 分に中央値 16 (13 ～ 21) 分が追加されました。 洞調律は、50 人中 23 人で電気的除細動なしで回復しました (46.0%、心房細動は 50 人中 19 人 [38.0%] でアブレーション中に終了し、50 人中 4 人 [8.0%]) で自然に終了しました。 26/50 (52.0%) は電気的除細動が必要でしたが、1/50 (2.0%) は実験室で回復しませんでした。 補助ラインには、30/50 (60.0%) にルーフ ライン、11/50 (22.0%) に僧帽弁峡部ラインが含まれていました。 手術合併症が 1/50 (2.0%) に発生しました (心嚢液貯留)。 12か月時点で評価された40人の患者のうち、33人（82.5％）が洞調律にあり、症状クラスが30人中23人（76.7％）でEHRA Iに改善した。 カプラン・マイヤー推定（単一処置、再発、反復アブレーションまたは電気的除細動は失敗としてカウント）によると、心房細動からの解放は6ヵ月で95.3%（95% CI 82.5-98.8）、12ヵ月で75.3%（95% CI 59.0-85.9）でした。 結論：以前の PVI 後の再発性持続性 AF では、STAR Apollo ガイド下やり直しアブレーションは実行可能かつ安全で、適度なマッピングステップが追加され、12 か月時点でほとんどの患者で洞調律と症状の改善に関連していました。 実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けています。</t>
+    <t>背景: 肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。 STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーです。 目的：前回の PVI 後の再発持続性 AF 患者における STAR Apollo ガイド下やり直しアブレーションの手順の実現可能性と安全性を検討し、12 か月のリズムの結果を説明すること。 方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された。 STAR マッピングには継続的な AF が必要であるため、分析は STAR マップが得られた 50 人の患者 (登録された 64 人中) に限定されました。 STAR マップのない 14 台は、手順で AF になっていなかったため除外されました。 3 か月、6 か月、および 12 か月後の来院時の手順パラメータ、安全性、リズムが記録されました。 結果: 50 人の患者全員が過去に 1 回の PVI と再発性の持続性 AF を経験しました。彼らは年齢 68.8 ± 8.7 歳、男性 35 名 (70.0%) で、BMI は 31.3 ± 5.5 kg/m でした。 46/50 (92.0%) で肺静脈の再接続が見つかり、再分離されました。 システムは、患者あたり 3 (2 ～ 3) 件の ESA の中央値を特定し、STAR マッピングにより、合計処置の中央値 125 (91 ～ 166) 分に中央値 16 (13 ～ 21) 分が追加されました。 洞調律は、23/50 人で電気的除細動なしで回復しました (46.0%; AF は 19/50 人 [38.0%] でアブレーション中に終了し、4/50 人 [8.0%]) で自然に終了しました。 26/50 (52.0%) は電気的除細動が必要でしたが、1/50 (2.0%) は実験室で回復しませんでした。 補助ラインには、30/50 (60.0%) にルーフ ライン、11/50 (22.0%) に僧帽弁峡部ラインが含まれていました。 手術合併症は 1/50 (2.0%) に発生しました (心嚢液貯留)。 12か月時点で評価された40人の患者のうち、33人（82.5％）が洞調律にあり、症状クラスが30人中23人（76.7％）でEHRA Iに改善した。 カプラン・マイヤー推定（単一処置、再発、反復アブレーションまたは電気的除細動は失敗としてカウント）によると、心房細動からの解放は6ヵ月で95.3%（95% CI 82.5-98.8）、12ヵ月で75.3%（95% CI 59.0-85.9）でした。 結論：以前の PVI 後の再発性持続性 AF では、STAR Apollo ガイド下やり直しアブレーションは実行可能かつ安全で、適度なマッピングステップが追加され、12 か月時点でほとんどの患者で洞調律と症状の改善に関連していました。 実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1809,7 +1809,7 @@
     <t>10.1111/jce.70520 doi</t>
   </si>
   <si>
-    <t>はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。 終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。 われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。 方法と結果：我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察されました。 明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われました。 CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。 CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要でした。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。 翌日の吸気/呼気胸部X線撮影では、横隔神経麻痺を示唆する異常は示されませんでした。ペースメーカーを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しませんでした。 結論： CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性良く作成でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成することができる。 これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
+    <t>はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。 終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。 われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。 方法と結果：我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察されました。 明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われました。 CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。 CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要でした。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。 翌日の吸気/呼気胸部X線検査では、横隔神経麻痺を示唆する異常は見られませんでした。ペースメーカーを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しませんでした。 結論： CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。 これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -1867,7 +1867,7 @@
     <t>10.1016/j.hrthm.2026.09.002 doi</t>
   </si>
   <si>
-    <t>背景: 経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨されます。 現在の実践および関連する予測因子は不明です。 目的: AF アブレーション後の患者における現在の OAC 実践を報告し、アブレーション後の OAC 療法を予測する特徴を特定すること。 方法：2017年1月1日から2023年10月1日までにCAを受けたAF患者をOptumのClinformatics® Data Martから特定し、CHADS-VAScスコアによって4つのグループに階層化した。 OAC 治療は CA の 30 日後と 365 日後に評価されました。 自動機械学習を使用して、人口統計情報と臨床情報に基づいて CA 後 1 年以内の OAC 使用を予測しました。受信機動作曲線の下の領域が報告されました。 結果：平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。 OAC継続はCA後の1年間で、特に低リスク患者の間で着実に減少した。 患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されませんでした。 AF 母集団全体の受信者動作曲線の下の面積は 0.607 (95% 信頼区間、0.587 ～ 0.614) でした。 1年後のOAC中止の主な予測因子は、CHADS-VAScベースラインスコアの低下（w、0.033）、CA後の左心耳閉塞（w、0.018）、追跡期間中の出血事象（w、0.010）であった。 結論: ガイドラインの推奨と一致せず、OAC の中止は AF を患い、少なくとも中等度の脳卒中リスクを持つ患者では一般的でした。 脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因でしたが、中止の多くを説明するものではありませんでした。</t>
+    <t>背景: 経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨されます。 現在の慣行および関連する予測因子は不明です。 目的: AF アブレーション後の患者における現在の OAC 実践を報告し、アブレーション後の OAC 療法を予測する特徴を特定すること。 方法：2017年1月1日から2023年10月1日までにCAを受けたAF患者をOptumのClinformatics® Data Martから特定し、CHADS-VAScスコアによって4つのグループに階層化した。 OAC 治療は CA の 30 日後と 365 日後に評価されました。 自動機械学習を使用して、人口統計情報と臨床情報に基づいて CA 後 1 年以内の OAC 使用を予測しました。受信機動作曲線の下の領域が報告されました。 結果：平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。 OAC継続はCA後の1年間で、特に低リスク患者の間で着実に減少した。 患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されませんでした。 AF 母集団全体の受信者動作曲線の下の面積は 0.607 (95% 信頼区間、0.587 ～ 0.614) でした。 1年後のOAC中止の主な予測因子は、CHADS-VAScベースラインスコアの低下（w、0.033）、CA後の左心耳閉塞（w、0.018）、追跡期間中の出血事象（w、0.010）であった。 結論: ガイドラインの推奨と一致せず、OAC の中止は AF を患い、少なくとも中等度の脳卒中リスクを持つ患者では一般的でした。 脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因でしたが、中止の多くを説明するものではありませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1898,7 +1898,7 @@
     <t>10.1016/j.hrthm.2026.09.025 doi</t>
   </si>
   <si>
-    <t>背景: 心室頻拍 (VT) アブレーションは、再発性 VT に対する確立された治療法です。しかし、この集団における手術前後の虚血性脳卒中（P-IS）の予後的重要性は、依然として十分に特徴づけられていない。 目的: この研究では、大規模な全国データベースを使用して、VT アブレーションを受けている患者における P-IS の発生率、予測因子、および死亡率への影響を調べました。 方法: VT アブレーションを受けている患者を特定するために、全国再入院データベース (NRD) 2016-2021 を照会しました。 ICD-10-CM および ICD-10-PCS コードを使用して研究コホートを定義しました。 P-IS は、初発入院中に発生する虚血性脳卒中として定義されました。 その後、P-IS とそれに関連する死亡率の予測因子が分析されました。 結果: VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。 脳卒中を有さない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）。 32.7%, p&lt;0.001).  手術前後の脳卒中は院内死亡率の3倍増加と関連していた。 ICU入室（OR 8.76、95% CI 5.07-15.13、p&lt;0.001）、心原性ショック（OR 2.25、95% CI 1.22-4.16、p=0.009）、肺塞栓症（OR 16.25、95% CI 1.23-214.56、 p=0.034) は独立して脳卒中後の死亡率の増加と関連していた。 結論：この大規模な現実世界コホートでは、VT アブレーション後の P-IS は患者の約 3% で発生し、院内死亡率の顕著な増加と関連していました。 リスクは、心血管疾患の併存疾患や重篤な病気の兆候によってさらに増幅されました。 これらの発見は、VT アブレーションを受ける患者の P-IS リスクを軽減する戦略を評価する専用の研究の必要性を強調しています。</t>
+    <t>背景: 心室頻拍 (VT) アブレーションは、再発性 VT に対する確立された治療法です。しかし、この集団における手術前後の虚血性脳卒中（P-IS）の予後的重要性は、依然として十分に特徴づけられていない。 目的: この研究では、大規模な全国データベースを使用して、VT アブレーションを受けている患者における P-IS の発生率、予測因子、および死亡率への影響を調べました。 方法: VT アブレーションを受けている患者を特定するために、全国再入院データベース (NRD) 2016-2021 を照会しました。 ICD-10-CM および ICD-10-PCS コードを使用して研究コホートを定義しました。 P-IS は、初発入院中に発生する虚血性脳卒中として定義されました。 その後、P-IS とそれに関連する死亡率の予測因子が分析されました。 結果: VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。 脳卒中を持たない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）。 32.7%, p&lt;0.001).  手術前後の脳卒中は院内死亡率の3倍増加と関連していた。 ICU入室（OR 8.76、95% CI 5.07-15.13、p&lt;0.001）、心原性ショック（OR 2.25、95% CI 1.22-4.16、p=0.009）、肺塞栓症（OR 16.25、95% CI 1.23-214.56、 p=0.034) は独立して脳卒中後の死亡率の増加と関連していた。 結論: この大規模な現実世界コホートでは、VT アブレーション後の P-IS は患者の約 3% で発生し、院内死亡率の顕著な増加と関連していました。 リスクは、心血管疾患の併存疾患や重篤な病気の兆候によってさらに増幅されました。 これらの発見は、VT アブレーションを受ける患者の P-IS リスクを軽減する戦略を評価する専用の研究の必要性を強調しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1929,7 +1929,7 @@
     <t>10.1111/jce.70500 doi</t>
   </si>
   <si>
-    <t>はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られます。 しかし、複数の併存疾患や手術リスクの増加を示すことが多い超高齢患者（80 歳以上）における手術の安全性と有効性に関するデータは依然として限られています。 この研究は、大規模電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。 方法：2001年から2024年の間にAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。 有効性の主要評価項目は、処置終了時の AVNRT の非誘導性でした。 安全性エンドポイントには、房室ブロック（AVB）、心嚢液貯留、およびバスキュラーアクセス合併症が含まれていました。 臨床転帰は、すべての年齢層にわたる SPA/SPM を受けている 6,020 人の患者からなる大規模な施設コホートと比較されました。 結果: 合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となった。 急性処置の成功は 104 人の患者 (98.1%) で達成されました。 一時的な房室伝導障害により、2 件の処置が途中で終了しました。 処置後の AVB が 2 人の患者で発生し、1 人の患者では永久的なペースメーカーの埋め込みが必要でした。 心嚢穿刺を必要とする心嚢液貯留が 2 人の患者で発生した。 4人の患者は重大な出血または血管アクセスの合併症を発症し、1人は外科的介入を必要とした。 平均在院日数は1.3日でした。 コホート全体と比較して、80代では合併症率が高かった（AVB: 1.9% vs. 0.12%;心嚢液貯留: 1.9% vs. 0.08%;出血: 3.8% vs. 0.37%)、手続きの成功率は同様に高いままでした。 結論: 80代のAVNRTに対するSPA/SPMは非常に効果的であり、若年層と同等の優れた急性成功率を示しています。 ただし、大規模な施設コホートや以前に報告されたデータと比較すると、合併症発生率は増加しています。 これらの所見は、この増加し脆弱な患者集団においてカテーテルアブレーションを検討する場合、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしています。</t>
+    <t>はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られます。 しかし、複数の併存疾患や手術リスクの増加を示すことが多い超高齢患者（80 歳以上）における手術の安全性と有効性に関するデータは依然として限られています。 この研究は、大規模な電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。 方法：2001年から2024年の間にAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。 有効性の主要評価項目は、処置終了時の AVNRT の非誘導性でした。 安全性エンドポイントには、房室ブロック（AVB）、心嚢液貯留、およびバスキュラーアクセス合併症が含まれていました。 臨床転帰は、すべての年齢層にわたる SPA/SPM を受けている 6,020 人の患者からなる大規模な施設コホートと比較されました。 結果: 合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となった。 急性処置の成功は 104 人の患者 (98.1%) で達成されました。 一時的な房室伝導障害のため、2 つの処置が途中で終了しました。 処置後の AVB が 2 人の患者で発生し、1 人の患者では永久的なペースメーカーの埋め込みが必要でした。 心嚢穿刺を必要とする心嚢液貯留が 2 人の患者で発生した。 4人の患者は重大な出血または血管アクセスの合併症を発症し、1人は外科的介入を必要とした。 平均在院日数は1.3日でした。 コホート全体と比較して、80代では合併症率が高かった（AVB: 1.9% vs. 0.12%;心嚢液貯留: 1.9% vs. 0.08%;出血: 3.8% vs. 0.37%)、手続きの成功率は同様に高いままでした。 結論: 80代のAVNRTに対するSPA/SPMは非常に効果的であり、若年層と同等の優れた急性成功率を示しています。 ただし、大規模な施設コホートや以前に報告されたデータと比較すると、合併症発生率は増加しています。 これらの発見は、この増加しつつある脆弱な患者集団においてカテーテルアブレーションを検討する際には、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしています。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -1958,7 +1958,7 @@
     <t>10.1111/jce.70514 doi</t>
   </si>
   <si>
-    <t>背景: ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。 目的: 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。 方法: 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。 完全な報告を行ったセンターのみが含まれていました。 患者はモダリティごとにグループ化されました。 Major complications, unplanned hospitalizations, cardioversions, repeat ablations, and deaths were assessed at 1 year.  Multivariate analysis identified independent predictors of outcomes.  結果: 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。 処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最も長かった。 (p &lt; 0.001)。 PFA では重大な合併症は発生しませんでした。 横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。 心膜液貯留は、RF 後により頻繁に発生しました (0.91% vs. CRYO + PFA の場合は 0.34%。 p = 0.032)。 全体的な合併症発生率は PFA で最も低かった (0% vs. RF: 2.19%, CRYO: 2.59%).  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。 良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。 結論: POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
+    <t>背景: ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。 目的: 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。 方法: 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。 完全な報告を行ったセンターのみが含まれていました。 患者はモダリティごとにグループ化されました。 重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価されました。 多変量解析により、結果の独立した予測因子が特定されました。 結果: 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。 処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最も長かった。 (p &lt; 0.001)。 PFA では重大な合併症は発生しませんでした。 横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。 心膜液貯留は RF 後により頻繁に発生しました (0.91% vs. CRYO + PFA の場合は 0.34%。 p = 0.032)。 全体的な合併症発生率は PFA で最も低かった (0% vs. RF: 2.19%, CRYO: 2.59%).  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。 良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。 結論: POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1989,7 +1989,7 @@
     <t>10.1007/s10840-026-02445-0 doi</t>
   </si>
   <si>
-    <t>背景: 心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点は依然として不明瞭です。 このメタ分析では、先制的 MCS の有効性と安全性を VT アブレーションの標準治療と比較しました。 方法: PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定されました。 MCS には、経皮的左心室補助装置または体外膜型人工肺が含まれます。 主要評価項目は全死因死亡率でした。副次評価項目には、VT再発、手術時間、手術合併症（バスキュラーアクセス、出血、脳​​卒中、心嚢液貯留、心不全、心筋梗塞）、および30日間の主要心血管有害事象（MACE）が含まれた。 結果：2,262人の患者（MCSあり414名、MCSなし1,848名）を対象とした8件の研究が含まれた。 平均追跡調査期間は15.8カ月、平均年齢は62.6歳、12.5％が女性で、平均PAINESDスコアはMCS群で15.7、非MCS群で10.5であった。 全死因死亡率（OR 1.58、95% CI 0.60-4.19、p = 0.36、I²=81%）またはVT再発（OR 1.03、95% CI 0.68-1.56、p = 0.90、I²=46%）には有意差はありませんでした。 先制的MCSは、より長い手術時間（平均差46.0分、95％CI 11.1-80.8、p = 0.01、I²=86％）、血管アクセスおよび心嚢液貯留による手術合併症の増加と関連していた（OR 2.25、95％CI 1.26-4.03、p = 0.006、 I²=33%)。 30 日間 MACE は研究全体で統一的に定義されていないため、統合されませんでした。 結論: 先制的 MCS は、VT アブレーションを受けている患者の全死因死亡率や VT 再発に有意な差は見られなかったが、処置の長期化と処置上の合併症の増加と関連していた。 観察研究のデザイン、グループ間のベースラインの不均衡、不均一性を反映して、証拠の確実性は非常に低かった。これらの所見は、高リスク患者におけるMCSの選択的使用を妨げるものではなく、ランダム化試験での確認が必要である。</t>
+    <t>背景: 心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点は依然として不明瞭です。 このメタ分析では、先制的 MCS の有効性と安全性を VT アブレーションの標準治療と比較しました。 方法: PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定されました。 MCS には、経皮的左心室補助装置または体外膜型人工肺が含まれます。 主要評価項目は全死因死亡率でした。副次評価項目には、VT再発、手術時間、手術合併症（バスキュラーアクセス、出血、脳​​卒中、心嚢液貯留、心不全、心筋梗塞）、および30日間の主要心血管有害事象（MACE）が含まれた。 結果：2,262人の患者（MCSあり414人、MCSなし1,848人）を対象とした8件の研究が含まれた。 平均追跡調査期間は15.8カ月、平均年齢は62.6歳、12.5％が女性で、平均PAINESDスコアはMCS群で15.7、非MCS群で10.5であった。 全死因死亡率（OR 1.58、95% CI 0.60-4.19、p = 0.36、I²=81%）またはVT再発（OR 1.03、95% CI 0.68-1.56、p = 0.90、I²=46%）には有意差はありませんでした。 先制的MCSは、より長い手術時間（平均差46.0分、95％CI 11.1-80.8、p = 0.01、I2 = 86％）、血管アクセスおよび心膜液貯留による手術合併症の増加と関連していた（OR 2.25、95％CI 1.26-4.03、p = 0.006、 I²=33%)。 30 日間 MACE は研究全体で統一的に定義されていないため、統合されませんでした。 結論: 先制的 MCS は、VT アブレーションを受けている患者の全死因死亡率や VT 再発に有意な差は見られなかったが、処置の長期化と処置上の合併症の増加と関連していた。 観察研究のデザイン、グループ間のベースラインの不均衡、不均一性を反映して、証拠の確実性は非常に低かった。これらの所見は、高リスク患者におけるMCSの選択的使用を妨げるものではなく、ランダム化試験での確認が必要である。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2018,7 +2018,7 @@
     <t>10.1111/jce.70502 doi</t>
   </si>
   <si>
-    <t>背景：我々は以前、心房細動（AF）の非肺静脈（PV）誘因は左心房（LA）の低電圧領域（LVA）から生じることが多いと報告した。 ただし、トリガー部位と LVA の分布の間の具体的な空間的関係は完全には解明されていません。 この研究は、サイト固有のベースで関係を分析することを目的としました。 方法と結果: カテーテルアブレーションを受けた AF 患者 1,428 人のうち、非 PV 誘因に対して陽性反応を示した 187 人 (13.1%) が登録されました。 各トリガー部位と左心房 LVA の間の空間的関係が評価されました。 研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました。 平均年齢、eGFR、BNP、BMI、LAD、LVEFはそれぞれ68±11歳、59.9±18.5mL/min/1.73m、116.6±281.4pg/mL、23.3±3.6kg/m、41.7±6.5mm、59±7.8%であった。 再現性がないため、18 例では非 PV トリガー部位を特定できませんでした。 残りの 169 件では、140 件 (82.8%) で単一の非 PV トリガーが特定され、29 件 (17.2%) では複数のトリガーが示されました。 評価された 99 の LA 非 PV トリガーのうち、61 (61.6%) は LVA 内で発生しました。 無傷の領域からの残りの非 PV トリガーの半分は、LVA の近くからのものでした。 具体的には、後部/中隔/下トリガーの半分以上がLVAから生じたのに対し、前部/屋根トリガーはすべてLVAから生じた。 患者は、トリガーの位置に基づいて、胸静脈（上大静脈、冠状静脈洞、左上大静脈開存）、右心房（RA）、中隔、LA、複数のトリガー、および未確認トリガーの 6 つのグループに分類されました。 24 か月の追跡調査では、心房頻脈性不整脈のない率は、原因不明および複数のトリガーのグループで有意に低かった (p &lt; 0.05)。 結論: LA の非 PV トリガーは、特に LA の屋根と前壁で LVA と密接に関連していますが、後壁、中隔、および下壁ではこの関連性はそれほど一貫していません。 電圧マッピング パターンは、LA 内の非 PV トリガー サイトの位置特定と検出を容易にする可能性があります。</t>
+    <t>背景：我々は以前、心房細動（AF）の非肺静脈（PV）誘因は左心房（LA）の低電圧領域（LVA）から生じることが多いと報告した。 ただし、トリガー部位と LVA の分布の間の具体的な空間的関係は完全には解明されていません。 この研究は、サイト固有のベースで関係を分析することを目的としました。 方法と結果：カテーテルアブレーションを受けているAF患者1,428人のうち、非PV誘因に対して陽性反応を示した187人（13.1%）が登録された。 各トリガー部位と左心房 LVA の間の空間的関係が評価されました。 研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました。 平均年齢、eGFR、BNP、BMI、LAD、LVEFはそれぞれ68±11歳、59.9±18.5mL/min/1.73m、116.6±281.4pg/mL、23.3±3.6kg/m、41.7±6.5mm、59±7.8%であった。 再現性がないため、18 例では非 PV トリガー部位を特定できませんでした。 残りの 169 件では、140 件 (82.8%) で単一の非 PV トリガーが特定され、29 件 (17.2%) では複数のトリガーが示されました。 評価された 99 の LA 非 PV トリガーのうち、61 (61.6%) は LVA 内で発生しました。 無傷の領域からの残りの非 PV トリガーの半分は、LVA の近くからのものでした。 具体的には、後部/中隔/下トリガーの半分以上がLVAから生じたのに対し、前部/屋根トリガーはすべてLVAから生じた。 患者は、トリガーの位置に基づいて、胸静脈（上大静脈、冠状静脈洞、左上大静脈開存）、右心房（RA）、中隔、LA、複数のトリガー、および未確認トリガーの 6 つのグループに分類されました。 24 か月の追跡調査では、心房頻脈性不整脈のない率は、原因不明および複数のトリガーのグループで有意に低かった (p &lt; 0.05)。 結論: LA の非 PV トリガーは、特に LA の屋根と前壁で LVA と密接に関連していますが、後壁、中隔、および下壁ではこの関連性はそれほど一貫していません。 電圧マッピング パターンは、LA 内の非 PV トリガー サイトの位置特定と検出を容易にする可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2076,7 +2076,7 @@
     <t>10.1111/jce.70516 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションの新しい治療法です。 ただし、治療中の患者の適切な鎮静は不可欠です。 目的：我々の目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することでした。 方法：2021年から2024年までにペンタスプリンPFA技術による初回AFアブレーションを受けたデンマーク人患者全員が対象となった。 患者は鎮静戦略に従って層別化されました。 EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。 GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました。 結果: 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。 全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありませんでした。 EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が続いたため、予期せず麻酔科医がバックアップを求められました。 AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありませんでした。 GA グループでは、手術周囲の鎮静による合併症は発生しませんでした。 鎮静群間で 1 年心房頻脈再発率に差は見られませんでした。 結論：この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しませんでした。 観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんでした。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティです。 ただし、治療中の患者の適切な鎮静は不可欠です。 目的：私たちの目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することでした。 方法：2021年から2024年までにペンタスプリンPFA技術による初回AFアブレーションを受けたデンマーク人患者全員が対象となった。 患者は鎮静戦略に従って層別化されました。 EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。 GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました。 結果: 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。 全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありませんでした。 EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が長引いたため、予期せず麻酔科医がバックアップを求められました。 AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありませんでした。 GA グループでは、手術周囲の鎮静による合併症は発生しませんでした。 鎮静群間で 1 年心房頻脈再発率に差は見られませんでした。 結論：この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しませんでした。 観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2107,7 +2107,7 @@
     <t>10.1007/s10840-026-02437-0 doi</t>
   </si>
   <si>
-    <t>背景: 胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因と考えられています。 積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。 食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。 私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することでした。 方法: 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価されました。 胸痛については別に質問した。 人口動態変数と手続き変数との関連性が評価されました。 結果：アブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が食道冷却を受け、44 名（14.9%）が GERD ≧ 8 の基準を満たし、71 名（24.1%）が CP を報告した。 前方最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 vs. 54.0 ± 14.0 W, p = 0.020).  CP を報告した参加者は若かった（64.5 ± 9.3 vs. 67.5 ± 10.2 年、p = 0.026）、より高い平均駆出率（57.1 ± 6.6% vs. 53.1 ± 10.2%, p = 0.001).  初回パスで両側性隔離が達成された場合、胸痛はあまり発生しませんでした（59.2% 対 59.2%）。 72.6%, p = 0.033).  結論：積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。 これらの所見は、食道の保護にもかかわらず、処置上の要因と参加者固有の要因の両方が症状の発症に寄与している可能性があることを示唆しています。</t>
+    <t>背景: 胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因と考えられています。 積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。 食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。 私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することでした。 方法: 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価されました。 胸痛については別に質問した。 人口動態変数と手続き変数との関連性が評価されました。 結果：アブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が食道冷却を受け、44 名（14.9%）が GERD ≧ 8 の基準を満たし、71 名（24.1%）が CP を報告した。 前方最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 対 50.0）。 54.0 ± 14.0 W, p = 0.020).  CP を報告した参加者は若かった（64.5 ± 9.3 vs. 67.5 ± 10.2 年、p = 0.026）、より高い平均駆出率（57.1 ± 6.6% vs. 53.1 ± 10.2%, p = 0.001).  初回パスで両側性隔離が達成された場合、胸痛はあまり発生しませんでした（59.2% 対 59.2%）。 72.6%, p = 0.033).  結論：積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。 これらの所見は、食道の保護にもかかわらず、処置上の要因と参加者固有の要因の両方が症状の発症に寄与している可能性があることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2136,7 +2136,7 @@
     <t>10.1016/j.hrthm.2026.09.036 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心房細動 (PersAF) 治療における、肺静脈隔離 (PVI) を超えた追加の左心房後壁アブレーション (LAPWA) の利点については、依然として議論の余地がある。 目的：ペンタスプラインパルスフィールドアブレーション（PFA）カテーテルで記録された信号が、LAPWAの恩恵を受ける可能性のある急速なLAPW活動を示すPersAF患者を特定できるかどうかを調査しました。 さらに、PFA 誘発性心房細動周期長 (AF-CL) 延長が不整脈のない生存を予測するかどうかを評価しました。 方法：この多施設観察研究には、ペンタスプライン PFA カテーテルによる初回 PVI プラス LAPWA を受けている連続した PersAF 患者が含まれていました。 AF-CL は、遠位 CS 信号を使用して、ベースライン、PVI 後、LAPWA 後の 3 つの時点で FARS-10 法を使用して測定されました。 LAPW-CL は、PVI 後に複数の LAPW 位置から測定されました。 2 か月のブランク期間を超えて 30 秒以上続く心房性頻脈性不整脈 (ATA) が記録されました。 結果: 270 人の患者が含まれた。 ATA を使用しない場合の全体的な 12 か月生存率は 72.6% でした。 「速いLAPW活性」は、コホート全体の平均LAPW-CL（191.4±2.4ミリ秒；≦190ミリ秒）よりも短いLAPW-CL値として定義された。 速い LAPW 活動は不整脈の再発と関連しませんでした (HR 1.263、95% CI: 0.739-2.160; p=0.393)。 対照的に、CS-CLの延長が大きいほど、不整脈再発リスクの低下と独立して関連していた（HR 0.298、95% CI: 0.017-0.520; ベースラインからのp23.5%は、ATAフリー生存率の予測に関して感度0.65、特異度0.72であった）。 結論: PVI 後の高速 LAPW 活動は、PersAF 患者における LAPWA 後の再発を予測しません。 LAPWA 後の CS-CL 延長 &gt;23.5% は、効果的な基質修飾と不整脈制御の有用なリアルタイム マーカーとして機能する可能性があります。</t>
+    <t>背景: 持続性心房細動 (PersAF) 治療における、肺静脈隔離 (PVI) を超えた追加の左心房後壁アブレーション (LAPWA) の利点については、依然として議論の余地がある。 目的：ペンタスプラインパルスフィールドアブレーション（PFA）カテーテルで記録された信号が、LAPWAの恩恵を受ける可能性のある急速なLAPW活動を示すPersAF患者を特定できるかどうかを調査しました。 さらに、PFA 誘発性心房細動周期長 (AF-CL) 延長が不整脈のない生存を予測するかどうかを評価しました。 この多施設観察研究には、ペンタスプライン PFA カテーテルによる初回 PVI プラス LAPWA を受けている連続した PersAF 患者が含まれていました。 AF-CL は、遠位 CS 信号を使用して、ベースライン、PVI 後、LAPWA 後の 3 つの時点で FARS-10 法を使用して測定されました。 LAPW-CL は、PVI 後に複数の LAPW 位置から測定されました。 2 か月のブランク期間を超えて 30 秒以上続く心房性頻脈性不整脈 (ATA) が記録されました。 結果: 270 人の患者が含まれた。 ATA を使用しない場合の全体的な 12 か月生存率は 72.6% でした。 「速いLAPW活性」は、コホート全体の平均LAPW-CL（191.4±2.4ミリ秒；≦190ミリ秒）よりも短いLAPW-CL値として定義された。 速い LAPW 活動は不整脈の再発と関連しませんでした (HR 1.263、95% CI: 0.739-2.160; p=0.393)。 対照的に、CS-CLの延長が大きいほど、不整脈再発リスクの低下と独立して関連していた（HR 0.298、95% CI: 0.017-0.520; ベースラインからのp23.5%は、ATAフリー生存率の予測に関して感度0.65、特異度0.72であった）。 結論: PVI 後の高速 LAPW 活動は、PersAF 患者における LAPWA 後の再発を予測しません。 LAPWA 後の CS-CL 延長 &gt;23.5% は、効果的な基質修飾と不整脈制御の有用なリアルタイム マーカーとして機能する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2167,7 +2167,7 @@
     <t>10.1016/j.hrthm.2026.09.031 doi</t>
   </si>
   <si>
-    <t>背景: 左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略です。 目的:肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること。 方法: この CORNERSTONE-AF ランダム化試験のサブ分析では、PVI 単独 (n=259) と PVI+LAPWI (n=254) の間で 18 か月の転帰を比較しました。 主要評価項目は心房性不整脈がないことでした。 副次評価項目には、繰り返しアブレーションを行わないことが含まれていました。 ランダム化は、PVI アブレーション モダリティによって階層化されました。 結果: PVI は、それぞれ 384 人の患者と 129 人の患者に対して高周波アブレーションとクライオバルーン アブレーションを使用して実施されました。 LAPWI グループでは、LAPWI 領域は高周波サブグループよりクライオバルーンの方が有意に大きかった。 LAPWI を追加すると、両方のサブグループで透視時間が増加することなく、処置時間が大幅に延長されました。 クライオバルーンサブグループでは、18 か月間心房性不整脈が発生しなかった率は、PVI 単独よりも LAPWI を使用した方が数値的に高かった（82.0% 対 82.0%）。 69.1%、P=0.163)、一方、高周波サブグループでは差は観察されませんでした(80.5% vs. 79.4%, P=0.309).  治療法ごとの相互作用はありませんでした（相互作用の P = 0.64）。 クライオバルーンサブグループでは、LAPWI の方が繰り返しアブレーションを行わない率が高かった (96.5% 対 82.0%、P=0.029）、しかし高周波サブグループには含まれていません（90.1% vs. 88.5%、P=0.210）、治療法ごとの有意な相互作用はありませんでした（相互作用の P = 0.17）。 全体的な合併症発生率はグループ間で同様でした。症候性胃不全麻痺は、高周波 LAPWI サブグループの 3 人の患者で発生しました。 結論: 補助的な LAPWI は、どちらのアブレーション モダリティでも心房性不整脈からの解放を大幅に改善することはなく、モダリティごとの有意な相互作用はありませんでした。 クライオバルーン PVI 後の LAPWI による潜在的に好ましい結果は、探索的であり仮説生成であると考えられるべきです。</t>
+    <t>背景: 左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略です。 目的:肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること。 方法: この CORNERSTONE-AF ランダム化試験のサブ分析では、PVI 単独 (n=259) と PVI+LAPWI (n=254) の間で 18 か月の転帰を比較しました。 主要評価項目は心房性不整脈がないことでした。 副次評価項目には、繰り返しアブレーションを行わないことが含まれていました。 ランダム化は、PVI アブレーション モダリティによって階層化されました。 結果: PVI は、それぞれ 384 人の患者と 129 人の患者に対して高周波アブレーションとクライオバルーン アブレーションを使用して実施されました。 LAPWI グループでは、LAPWI 領域は高周波サブグループよりクライオバルーンの方が有意に大きかった。 LAPWI を追加すると、両方のサブグループで蛍光透視時間が増加することなく、処置時間が大幅に延長されました。 クライオバルーンサブグループでは、18 か月間心房性不整脈が発生しなかった率は、PVI 単独よりも LAPWI を使用した方が数値的に高かった（82.0% 対 82.0%）。 69.1%、P=0.163)、一方、高周波サブグループでは差は観察されませんでした(80.5% vs. 79.4%, P=0.309).  治療法ごとの相互作用はありませんでした（相互作用の P = 0.64）。 クライオバルーンサブグループでは、LAPWI の方が繰り返しアブレーションを行わない率が高かった (96.5% 対 82.0%、P=0.029）、しかし高周波サブグループには含まれていません（90.1% vs. 88.5%、P=0.210）、治療法ごとの有意な相互作用はありませんでした（相互作用の P = 0.17）。 全体的な合併症発生率はグループ間で同様でした。症候性胃不全麻痺は、高周波 LAPWI サブグループの 3 人の患者で発生しました。 結論: 補助的な LAPWI は、いずれのアブレーション モダリティでも心房性不整脈からの解放を大幅には改善せず、モダリティごとの有意な相互作用はありませんでした。 クライオバルーン PVI 後の LAPWI による潜在的に好ましい結果は、探索的であり仮説生成であると考えられるべきです。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2198,7 +2198,7 @@
     <t>10.1016/j.hrthm.2026.08.058 doi</t>
   </si>
   <si>
-    <t>背景: 頻繁に起こる早発心室複合体 (PVC) のアブレーションは、収縮機能不全を有する患者、特に PVC 誘発性心筋症が疑われる患者の左心室駆出率 (LVEF) を改善する可能性があります。 しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません。 目的: この研究の目的は、PVC アブレーション後の LVEF 回復を予測するために、日常的に利用可能な臨床変数、心エコー図変数、および心電図変数を使用して機械学習 (ML) モデルを開発し、外部で検証することでした。 方法: この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました。 Boruta アルゴリズムを使用して予測子が選択され、5 つの ML モデルがトレーニングされました。 パフォーマンスは、10 分割相互検証と受信者動作特性曲線分析によって評価されました。 最もパフォーマンスの高いモデルはキャリブレーションと閾値分析を受け、追加の 3 つのセンターからの独立したコホートで外部検証されました。 結果: ランダム フォレスト モデルは最高のパフォーマンスを示し、内部テスト セットの曲線下面積は 0.88 (95% 信頼区間 = 0.79-0.98)、良好なキャリブレーション (Hosmer-Lemeshow P = 0.562) でした。 外部検証により、一貫した識別が確認されました (曲線下面積 = 0.83、95% 信頼区間 = 0.72-0.95)。 主要な予測因子には、ベースラインの PVC 負荷、洞調律における QRS 持続時間、および処置前の LVEF が含まれます。 結論: この ML ベースのツールは、広く利用可能な変数に基づいて構築されており、PVC アブレーション後の LVEF 回復の確率を正確に推定し、臨床上の意思決定と患者のカウンセリングをサポートする可能性があります。</t>
+    <t>背景: 頻繁に起こる早発心室複合体 (PVC) のアブレーションは、収縮機能不全を有する患者、特に PVC 誘発性心筋症が疑われる患者の左心室駆出率 (LVEF) を改善する可能性があります。 しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません。 目的: この研究の目的は、PVC アブレーション後の LVEF 回復を予測するために、日常的に利用可能な臨床変数、心エコー図変数、および心電図変数を使用して機械学習 (ML) モデルを開発し、外部で検証することでした。 方法: この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました。 Boruta アルゴリズムを使用して予測子が選択され、5 つの ML モデルがトレーニングされました。 パフォーマンスは、10 分割相互検証と受信者動作特性曲線分析によって評価されました。 最もパフォーマンスの高いモデルはキャリブレーションと閾値分析を受け、追加の 3 つのセンターからの独立したコホートで外部検証されました。 結果: ランダム フォレスト モデルは最高のパフォーマンスを示し、内部テスト セットの曲線下面積は 0.88 (95% 信頼区間 = 0.79-0.98)、良好なキャリブレーション (Hosmer-Lemeshow P = 0.562) でした。 外部検証により、一貫した識別が確認されました (曲線下面積 = 0.83、95% 信頼区間 = 0.72-0.95)。 主要な予測因子には、ベースラインの PVC 負荷、洞調律における QRS 持続時間、および術前の LVEF が含まれます。 結論: この ML ベースのツールは、広く利用可能な変数に基づいて構築されており、PVC アブレーション後の LVEF 回復の確率を正確に推定し、臨床上の意思決定と患者のカウンセリングをサポートする可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2229,7 +2229,7 @@
     <t>10.1016/j.hrthm.2026.09.005 doi</t>
   </si>
   <si>
-    <t>背景: 現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨しています。 AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。 目的: この研究は、アブレーション後の長期的な心房細動負担を特徴づけ、リズム誘導型 OAC をモデル化することを目的としました。 方法：初回冷凍アブレーションを受けた発作性心房細動患者を対象としたCOMPARE-CRYO試験の事後分析を、植込み型心臓モニターの連続モニタリングで実施した。 AF エピソードは独立して裁定されました。 CHADS-VA スコアが 1 以上の患者を対象に、リズムに基づく OAC 戦略がモデル化されました。この戦略は、毎日の負荷が 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上で、さまざまな OAC ウィンドウ期間で開始されました。 結果：中央値3.3年の追跡期間にわたる201人の患者のうち、1日当たりの心房細動負担の中央値は0%（四分位範囲 = 0%-0.01%）で、96.5%の日で心房細動はありませんでした。 再発患者 108 人のうち、40% は非常に低い負担 (&lt;0.1%) を維持し、36% は低い負担 (0.1% ～ 1%) でした。 CHADS-VA ≥1 の患者 139 人のうち、6 分以上の AF をきっかけとした再開継続戦略により、追跡調査の 32% で OAC が発生しました。 固定 OAC ウィンドウ (14 日または 30 日) を使用したピル・イン・ザ・ポケット戦略は、OAC を 90.8% ～ 99.4% 削減しました。 1 時間以上のしきい値と 30 日間の OAC ウィンドウが最も好ましいバランスを提供し、AF 時間の 97.5% をカバーし、OAC 曝露を 90.8% 削減しました。 結論: ほとんどの患者は、冷凍アブレーション後も一貫して低い心房細動負荷を維持しました。 リズムガイドによる抗凝固療法は、OAC を大幅に減少させる可能性があり、1 時間以上の閾値が OAC 減少と AF 適用時間のバランスを最も良く保ちます。 これらの戦略には、臨床転帰の前向き評価が必要です。</t>
+    <t>背景: 現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨しています。 AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。 目的: この研究は、アブレーション後の長期的な心房細動負担を特徴づけ、リズム誘導型 OAC をモデル化することを目的としました。 方法：初回冷凍アブレーションを受けた発作性 AF 患者を対象に、植込み型心臓モニターの連続モニタリングによる COMPARE-CRYO 試験の事後分析を実施しました。 AF エピソードは独立して裁定されました。 リズムに基づく OAC 戦略は、CHADS-VA スコアが 1 以上の患者を対象に、異なる OAC ウィンドウ期間で 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上の毎日の負荷によって誘発され、モデル化されました。 結果：中央値3.3年の追跡期間にわたる201人の患者のうち、1日あたりの心房細動負担の中央値は0%（四分位範囲 = 0%-0.01%）で、96.5%の日で心房細動はありませんでした。 再発患者 108 人のうち、40% は非常に低い負担 (&lt;0.1%) を維持し、36% は低い負担 (0.1% ～ 1%) でした。 CHADS-VA ≥1 の患者 139 人のうち、6 分以上の AF によって引き起こされた再開継続戦略により、追跡調査の 32% で OAC が発生しました。 固定 OAC ウィンドウ (14 日または 30 日) を使用したピル・イン・ザ・ポケット戦略では、OAC が 90.8% ～ 99.4% 削減されました。 1 時間以上のしきい値と 30 日間の OAC ウィンドウが最も好ましいバランスを提供し、AF 時間の 97.5% をカバーし、OAC 曝露を 90.8% 削減しました。 結論: ほとんどの患者は、冷凍アブレーション後も一貫して低い心房細動負荷を維持しました。 リズムガイドによる抗凝固療法は、OAC を大幅に減少させる可能性があり、1 時間以上の閾値が OAC 減少と AF 適用時間のバランスを最も良く保ちます。 これらの戦略には、臨床転帰の前向き評価が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2263,7 +2263,7 @@
     <t>10.1093/europace/euag277 doi</t>
   </si>
   <si>
-    <t>背景と目的: 左心耳 (LAAO) デバイスを装着した患者は AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。 この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することでした。 方法：私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。 各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。 データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 結果：以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。 アブレーションは、LAAO 後中央値 271 日に実施されました。 アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間でした。 OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。 脳卒中または TIA は追跡期間内に 5 人の患者 (症例の 2.6%) で発生し、うち 2 件 (症例の 1%) はアブレーション翌日に発生しました。 アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました。 結論：既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれでした。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血イベントを伴うアブレーション後の短期間の OAC に耐えました。</t>
+    <t>背景と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。 この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することでした。 方法: 私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。 各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。 データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 結果：以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。 アブレーションは、LAAO 後中央値 271 日に実施されました。 アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間でした。 OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。 追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。 アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました。 結論：既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれでした。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血事象を伴うアブレーション後の短期間の OAC に耐えました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2292,7 +2292,7 @@
     <t>10.1016/j.hrthm.2026.07.054 doi</t>
   </si>
   <si>
-    <t>背景: 機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性があります。 目的: 従来のアブレーション戦略と比較して有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました。 方法: この前向き多施設レジストリでは、梗塞後心室頻拍 (VT) 患者 166 人が前向き傾向スコア一致レジストリに登録されました。 心臓磁気共鳴イメージング/コンピューター断層撮影スキャンは、機能マッピングとアブレーション (Sense2) の焦点領域をターゲットにするために取得されました。 結果は、画像ガイダンスなしでマッピングを受けたグループ（センス）、および機能マッピングや画像ガイダンスなしで活性化/同調または基質ガイドによるマッピングとアブレーションを受けたグループ（施設）の結果と比較されました。 結果: Sense2 グループの平均処置時間 (145.8 ± 28.7 分) は、Sense グループ (171.0 ± 51.1 分) および施設内グループ (221.4 ± 73.9 分) よりも有意に短かった (P &lt; 0.0001)。 同様に、平均マッピング時間は、Sense2 グループ (25.4 ± 7.3 分) の方が Sense グループ (47.2 ± 8.9 分) よりも短かった。 アブレーション時間は、Sense グループ (21.6 ± 12.7 分) および施設内グループ (25.9 ± 13.9 分) と比較して、Sense2 グループ (18.1 ± 11.6 分) で有意に短縮されました (P = 0.006)。 Sense2 および Sense グループの患者は、施設内グループの患者よりも VT からの自由度が高く (両方とも P &lt; .001)、生存期間も改善されました (両方とも P &lt; .05)。 結論: イメージングと機能マッピングを統合した Sense2 プロトコルは、焦点を絞った基質マッピングの実行を可能にすることで処置時間を短縮し、施設内アブレーションと比較して VT の自由度の点で結果を改善しました。 生存率の向上には、多施設ランダム化試験による裏付けが必要です。</t>
+    <t>背景: 機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性があります。 目的: 従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました。 方法: この前向き多施設登録では、梗塞後心室頻拍 (VT) 患者 166 人が前向き傾向スコア一致レジストリに登録されました。 心臓磁気共鳴イメージング/コンピューター断層撮影スキャンは、機能マッピングとアブレーション (Sense2) の焦点領域をターゲットにするために取得されました。 結果は、画像ガイダンスなしでマッピングを受けたグループ（センス）、および機能マッピングや画像ガイダンスなしで活性化/同調または基質ガイドによるマッピングとアブレーションを受けたグループ（施設）の結果と比較されました。 結果: Sense2 グループの平均手術時間 (145.8 ± 28.7 分) は、Sense グループ (171.0 ± 51.1 分) および施設内グループ (221.4 ± 73.9 分) よりも有意に短かった (P &lt; 0.0001)。 同様に、平均マッピング時間は、Sense2 グループ (25.4 ± 7.3 分) の方が Sense グループ (47.2 ± 8.9 分) よりも短かった。 アブレーション時間は、Sense グループ (21.6 ± 12.7 分) および施設内グループ (25.9 ± 13.9 分) と比較して、Sense2 グループ (18.1 ± 11.6 分) で有意に短縮されました (P = 0.006)。 Sense2 および Sense グループの患者は、施設内グループの患者よりも VT からの自由度が高く (両方とも P &lt; .001)、生存期間も改善されました (両方とも P &lt; .05)。 結論: イメージングと機能マッピングを統合した Sense2 プロトコルは、焦点を絞った基質マッピングの実行を可能にすることで処置時間を短縮し、施設内アブレーションと比較して VT の自由度の点で結果を改善しました。 生存率の向上には、多施設ランダム化試験による裏付けが必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2323,7 +2323,7 @@
     <t>10.1007/s10840-026-02433-4 doi</t>
   </si>
   <si>
-    <t>目的: 肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られています。 PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。 この後ろ向き多施設観察コホート研究には、VOM-EI + AS または PVI のみを受けた連続した PeAF 患者が含まれていました。 主要評価項目は、抗不整脈薬（AAD）を服用していない状態で30秒以上続く心房性不整脈（AA）から解放されることでした。 手順の特徴と安全性の結果も評価されました。 結果: 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値 22 か月 (四分位範囲 (IQR): 9 ～ 35 か月) 後、81% vs. VOM-EI + AS と VOM-EI + AS では、患者の 47% が AAD なしで AA を発症していないままでした。 PVI のみのグループ (p &lt; 0.001)。 双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子でした（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。 逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。 結論: 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的でした。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。 持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
+    <t>目的: 肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られています。 PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。 方法：この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。 主要評価項目は、抗不整脈薬（AAD）を服用しなくても30秒以上続く心房性不整脈（AA）がなくなることでした。 手順の特徴と安全性の結果も評価されました。 結果: 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値 22 か月 (四分位範囲 (IQR): 9 ～ 35 か月) 後、81% vs. VOM-EI + AS と VOM-EI + AS では、患者の 47% が AAD なしで AA を発症していないままでした。 PVI のみのグループ (p &lt; 0.001)。 双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子でした（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。 逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。 結論: 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的でした。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。 持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
   </si>
   <si>
     <t xml:space="preserve">PURPOSE:
@@ -2339,7 +2339,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42720910/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.24] 非常に若い成人の心房細動に対するカテーテルアブレーション - AF-YOUNG レジストリの多中心データ
+    <t xml:space="preserve">📄 [No.24] 非常に若い成人の心房細動に対するカテーテルアブレーション - AF-YOUNG レジストリからの多中心データ
 (Catheter ablation for atrial fibrillation in very young adults - multicentric data from the AF-YOUNG registry.)</t>
   </si>
   <si>
@@ -2352,7 +2352,7 @@
     <t>10.1016/j.hrthm.2026.09.028 doi</t>
   </si>
   <si>
-    <t>背景: 30 歳未満の心房細動はまれです。アブレーション結果のデータは不足しています。 目的: 多施設の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました。 方法：ドイツの2つの大規模センターでは、心房細動のため初めて肺静脈隔離術（PVI）を受けた30歳以下の患者（2005～2025年）を遡及的に対象とした。 再発: 90 日間のブランク期間後に心房細動が記録された。 結果：患者140人（平均年齢29.1±3.1歳、女性28.6％）のうち、104人が転帰分析を受けた（発作性83.6％、持続性心房細動16.4％、心房細動の家族歴あり18.6％）。 PVI: 高周波 49.3%、クライオバルーン 45.7%、パルスフィールド アブレーション 5%。 平均処置時間は117±66分。 中央値1年間の追跡調査(IQR 0.25～1.74)で、10人の患者が再発した。 心房細動の非罹患率は1/2/3年で93.6/88.2/82.1%でした。最大2回の手術後1年後に94.9%。 発作性心房細動と持続性心房細動では、より良い転帰が示されました: 98.5% 対 98.5% 1 年後は 67.7%、1 年後は 87.8% 3年後は50.8%（ログランクp&lt;0.001）。 院内合併症は 3 件 (2.1%) 発生しました。血管合併症 1 件は外科的修復が必要でした。介入の必要のない心膜炎と軽度の肺静脈狭窄。 結論: 30 歳未満の成人では、心房細動に対するカテーテルアブレーションにより、高いリズム制御が得られ、合併症発生率も低くなります。 持続性心房細動では、発作性心房細動よりも利益が低くなります。 心房細動のサブタイプは、若年成人の第一選択の調律制御として早期にアブレーションを導入することを主張する可能性がある最も強力な決定要因です。</t>
+    <t>背景: 30 歳未満の心房細動はまれです。アブレーション結果のデータは不足しています。 目的: 多施設共同の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました。 方法：ドイツの 2 つの大規模センターでは、心房細動で初めて肺静脈隔離術 (PVI) を受けた 30 歳以下の患者を遡及的に対象とした (2005 ～ 2025 年)。 再発: 90 日間のブランク期間後に心房細動が記録された。 結果：患者140人（平均年齢29.1±3.1歳、女性28.6％）のうち、104人が転帰分析を受けた（発作性83.6％、持続性心房細動16.4％、心房細動の家族歴あり18.6％）。 PVI: 高周波 49.3%、クライオバルーン 45.7%、パルスフィールド アブレーション 5%。 平均処置時間は117±66分。 中央値1年間の追跡調査(IQR 0.25～1.74)で、10人の患者が再発した。 心房細動の非罹患率は、1/2/3 年で 93.6/88.2/82.1% でした。最大2回の手術後、1年後に94.9%。 発作性心房細動と持続性心房細動では、98.5% 対 98.5% の方が良好な結果を示しました。 1 年後は 67.7%、1 年後は 87.8% 3年後は50.8%（ログランクp&lt;0.001）。 院内合併症は 3 件 (2.1%) 発生しました。血管合併症 1 件は外科的修復が必要でした。介入の必要のない心膜炎と軽度の肺静脈狭窄。 結論: 30 歳未満の成人では、心房細動に対するカテーテルアブレーションにより、高いリズム制御が得られ、合併症発生率も低くなります。 持続性心房細動では、発作性心房細動よりも利益が低くなります。 心房細動のサブタイプは、若年成人の第一選択の調律制御としてアブレーションを早期に導入することを主張する可能性がある最も強力な決定要因です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2383,7 +2383,7 @@
     <t>10.1111/jce.70509 doi</t>
   </si>
   <si>
-    <t>背景: 電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入されました。 しかし、この技術、特に補助的な後壁隔離術 (PWI) や肺静脈外部位に関する実際のデータは依然として限られています。 目的: バルーンインバスケット PFA システムを使用した肺静脈隔離術 (PVI) および補助病変の急性期のパフォーマンス、安全性、実現可能性を評価すること。 方法：2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が対象となった。 急性有効性、処置パラメータ、合併症、探索的溶血および腎バイオマーカー、追跡結果が評価されました。 結果: 合計 133 人の患者が含まれました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF を患っていました。 急性 PVI は症例の 96.2% で達成されました。 補助的な PWI は患者の 25.6% で実施され、追加の PV 外病変セットは 12 人の患者で実施されました。 平均手技時間、左心房留置時間、透視時間はそれぞれ 65.6 ± 16.4、45.4 ± 15.4、12.7 ± 7.3 分で、PVI のみの手技と PVI + PWI 手技の間に有意差はありませんでした。 2 件の手術周囲合併症が発生しました (1.5%; 大腿動脈仮性動脈瘤、心膜炎)。 探索的バイオマーカー分析では、明らかな溶血関連の腎臓の安全性シグナルは示されませんでした。 6か月以上の追跡調査を受けた82人の患者のうち、臨床的に証明された晩期の心房性不整脈の再発が14.6％で発生した。 結論: この実際の経験では、バルーンインバスケット PFA システムは高い急性有効性、低い合併症率、効率的なワークフローを示しました。 補助的な PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんでした。</t>
+    <t>背景: 電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入されました。 しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られています。 目的: バルーンインバスケット PFA システムを使用した肺静脈隔離術 (PVI) および補助病変の急性期のパフォーマンス、安全性、実現可能性を評価すること。 方法：2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が対象となった。 急性有効性、処置パラメータ、合併症、探索的溶血および腎バイオマーカー、追跡結果が評価されました。 結果: 合計 133 人の患者が含まれました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF でした。 急性 PVI は症例の 96.2% で達成されました。 補助的な PWI は患者の 25.6% で実施され、追加の PV 外病変セットは 12 人の患者で実施されました。 平均手技時間、左心房留置時間、透視時間はそれぞれ65.6±16.4分、45.4±15.4分、12.7±7.3分で、PVIのみの手技とPVI+PWI手技の間に有意差はなかった。 2 件の手術周囲合併症が発生しました (1.5%; 大腿動脈仮性動脈瘤、心膜炎)。 探索的バイオマーカー分析では、明らかな溶血関連の腎臓の安全性シグナルは示されませんでした。 6か月以上の追跡調査を受けた82人の患者のうち、臨床的に証明された晩期の心房性不整脈の再発が14.6％で発生した。 結論: この実際の経験では、バルーンインバスケット PFA システムは高い急性有効性、低い合併症率、効率的なワークフローを示しました。 補助的 PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2414,7 +2414,7 @@
     <t>10.1016/j.hrthm.2026.09.034 doi</t>
   </si>
   <si>
-    <t>背景: 傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は、伝導系損傷のリスクのため依然として不確実です。 目的: 冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する。 方法：我々は、傍ヒスアン PVC アブレーションを受けている 114 人の患者を遡及的に分析した。 急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位が評価されました。 結果: 89 人の患者 (78%) で緊急手術の成功が達成されました。 しかし、長期的な臨床的成功を達成したのは、急性成功を収めた患者の 52% のみでした。 冠動脈尖アブレーションは合計 35 人の患者 (31%) で試みられ、臨床失敗例よりも臨床成功例の方が有意に頻繁に実施されました (38% vs. 38%)。 7%, P=0.005).  尖切除を受けた 35 人の患者のうち、PVC は 49% (17/35) で終了しましたが、さらに 31% (11/35) で PVC の一過性の抑制または形態的変化が観察されました。 尖頭アブレーションの成功の予測因子には、尖頭での早期の活性化、および尖頭とヒス束領域の最も初期の活性化部位との間の解剖学的近接性が含まれる。 伝導系損傷は全体で 31 人の患者に発生しましたが、主にヒス束領域のアブレーション中に発生し、弁尖アブレーション中に発生したイベントは 1 件のみでした。 結論：段階的な多部位アブレーション戦略に冠状動脈弁尖アブレーションを組み込むことは、安全性を損なうことなく、傍ヒスアン PVC アブレーションのより良い処置結果に結びつく可能性がある。 早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測されます。</t>
+    <t>背景: 伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実です。 目的: 冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する。 方法：我々は、傍ヒスアン PVC アブレーションを受けている 114 人の患者を遡及的に分析した。 急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位が評価されました。 結果: 89 人の患者 (78%) で緊急手術の成功が達成されました。 しかし、長期的な臨床的成功を達成したのは、急性成功を収めた患者の 52% のみでした。 冠動脈尖アブレーションは合計 35 人の患者 (31%) で試みられ、臨床失敗例よりも臨床成功例の方が有意に頻繁に実施されました (38% vs. 38%)。 7%, P=0.005).  尖切除を受けた 35 人の患者のうち、PVC は 49% (17/35) で終了しましたが、さらに 31% (11/35) で PVC の一過性の抑制または形態的変化が観察されました。 尖頭アブレーションの成功の予測因子には、尖頭での早期の活性化、および尖頭とヒス束領域の最も初期の活性化部位との間の解剖学的近接性が含まれる。 伝導系損傷は全体で 31 人の患者に発生しましたが、主にヒス束領域のアブレーション中に発生し、弁尖アブレーション中に発生したイベントは 1 件のみでした。 結論：段階的な多部位アブレーション戦略に冠状動脈弁尖アブレーションを組み込むことは、安全性を損なうことなく、傍ヒスアン PVC アブレーションのより良い処置結果に結びつく可能性がある。 早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2445,7 +2445,7 @@
     <t>10.1016/j.hrthm.2026.08.055 doi</t>
   </si>
   <si>
-    <t>背景: 心臓埋め込み型デバイスによって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明です。 目的: この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することでした。 方法：単形性心室頻拍に対してカテーテルアブレーションを受け、植込み型除細動器によって記録された分析可能な自発的心室頻拍エピソードを有する構造的心疾患患者113人を遡及的に研究した。 自発性 VT は、開始拍動が持続 VT 拍動と一致する場合には形態一致開始として分類され (タイプ A)、最初の拍動がその後の VT 拍動と異なる場合には形態が異なる開始として分類されました (タイプ B)。 結果: 257 件の自然発生 VT エピソードのうち、147 件が A 型、110 件が B 型でした。 113人の患者のうち、58人がA型のみ、47人がB型のみ、8人が両方の型を持っていた。 タイプ B の開始は、より長い VT 前の R-R 間隔と、より頻繁な心室ペーシングのベースラインリズムと関連していました。 アブレーション中、タイプ B のみのグループはより誘導性の VT 形態を示し (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままでした (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87; P = 0.002)。 急性手術の転帰、合併症、VT再発、および複合転帰は、グループ間で有意な差はありませんでした。 結論： 開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している。</t>
+    <t>背景: 心臓植込み型装置によって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明です。 目的: この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することでした。 方法：単形性心室頻拍に対してカテーテルアブレーションを受け、植込み型除細動器によって記録された分析可能な自発的心室頻拍エピソードを有する構造的心疾患患者113人を遡及的に研究した。 自発性 VT は、開始拍動が持続 VT 拍動と一致する場合には形態一致開始として分類され (タイプ A)、最初の拍動がその後の VT 拍動と異なる場合には形態が異なる開始として分類されました (タイプ B)。 結果: 257 件の自然発生 VT エピソードのうち、147 件が A 型、110 件が B 型でした。 113人の患者のうち、58人がA型のみ、47人がB型のみ、8人が両方の型を持っていた。 タイプ B の開始は、より長い VT 前の R-R 間隔と、より頻繁な心室ペーシングのベースラインリズムと関連していました。 アブレーション中、タイプ B のみのグループはより誘発性の VT 形態を持ち (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままでした (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87、P = 0.002)。 急性手術の転帰、合併症、VT再発、および複合転帰は、グループ間で有意な差はありませんでした。 結論： 開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2463,7 +2463,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42692318/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.28] 心房細動アブレーション後の心房不整脈再発を軽減するウェアラブル刺激装置を使用した非侵襲性正中神経刺激：NEUROPULSE パイロット
+    <t xml:space="preserve">📄 [No.28] 心房細動アブレーション後の心房不整脈の再発を軽減するためのウェアラブル刺激装置を使用した非侵襲性正中神経刺激：NEUROPULSE パイロット
 (Non-Invasive Median Nerve Stimulation with a Wearable Stimulator to Reduce Atrial Arrhythmia Recurrence after Atrial Fibrillation Ablation: The NEUROPULSE Pilot.)</t>
   </si>
   <si>
@@ -2476,7 +2476,7 @@
     <t>10.1016/j.hrthm.2026.09.013 doi</t>
   </si>
   <si>
-    <t>背景: 心房細動 (AF) アブレーションの成功率を向上させるために、効果はさまざまですが、心筋破壊を犠牲にして経験的病変が配置されることがよくあります。 自律神経調節は、過度の心筋損傷を引き起こすことなくリズムの結果を改善する非切除的な補助手段を提供する可能性があります。 目的: AF アブレーション後の皮正中神経刺激 (MNS) を評価すること。 方法: NEUROPULSE は、3 施設、無作為化、二重盲検、偽対照のパイロット研究でした。 77人の患者は、活動性MNS（週3×20分のセッション）または偽MNSに1:1で無作為に割り付けられた。修正意図治療（mITT）集団には59人の患者（MNS 31人、偽28人）が含まれていた。 治療はアブレーション（大部分がパルスフィールドアブレーション）後 48 時間以内に開始され、6 か月間継続されました（2 週間は毎日、その後は週 3 回）。 監視には、1 日 2 回の 2 分間のデバイス ECG と 2 か月目と 6 か月目の 10 日間のパッチが含まれていました。 結果：年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。 盲検化は維持された。 ブランキング後の追跡調査（2～6か月）中、MNSでは12件のAF/AT/AFLイベントが発生し、偽では243件が発生した（発生率比[RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001）。 1 つの高負荷偽異常値を除くと、12 対 28 のイベントが発生しました (RR 2.17; 95%CI 1.10-4.27; P=0.025)。 AF/AT/AFL は MNS 患者 31 人中 2 人、偽患者 28 人中 5 人で再発しました。 6か月の無不整脈生存率は、それぞれ90.0% vs 80.8%（ハザード比 2.15; 95%CI 0.42-11.1; P=0.36）でした。 PAC 数と患者報告の転帰には差異はありませんでした。 MNS またはデバイス関連の重篤な有害事象は発生しませんでした。 結論: AF アブレーション後のウェアラブル MNS は、心房性不整脈イベントの再発の減少と関連していました。 このパイロット研究は、適切な検出力試験での確認を保証します。</t>
+    <t>背景: 心房細動 (AF) アブレーションの成功率を向上させるために、効果はさまざまですが、心筋破壊を犠牲にして経験的病変が配置されることがよくあります。 自律神経調節は、過度の心筋損傷を引き起こすことなくリズムの結果を改善する非切除的な補助手段を提供する可能性があります。 目的: AF アブレーション後の皮正中神経刺激 (MNS) を評価すること。 方法: NEUROPULSE は、3 施設、無作為化、二重盲検、偽対照のパイロット研究でした。 77人の患者は、活動性MNS（週3×20分のセッション）または偽のMNSに1：1で無作為に割り付けられた。修正意図治療（mITT）集団には59人の患者（MNS 31人、偽28人）が含まれていた。 治療はアブレーション（大部分がパルスフィールドアブレーション）後 48 時間以内に開始され、6 か月間継続されました（2 週間は毎日、その後は週 3 回）。 監視には、1 日 2 回の 2 分間のデバイス ECG と 2 か月目と 6 か月目の 10 日間のパッチが含まれていました。 結果：年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。 盲検化は維持された。 ブランキング後の追跡調査（2～6か月）中、MNSでは12件のAF/AT/AFLイベントが発生し、偽では243件が発生した（発生率比[RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001）。 1 つの高負荷偽異常値を除くと、12 対 28 のイベントが発生しました (RR 2.17; 95%CI 1.10-4.27; P=0.025)。 AF/AT/AFL は MNS 患者 31 人中 2 人、偽患者 28 人中 5 人で再発しました。 6か月の無不整脈生存率は、それぞれ90.0% vs 80.8%（ハザード比 2.15; 95%CI 0.42-11.1; P=0.36）でした。 PAC 数と患者報告の転帰には差異はありませんでした。 MNS またはデバイス関連の重篤な有害事象は発生しませんでした。 結論: AF アブレーション後のウェアラブル MNS は、心房性不整脈イベントの再発の減少と関連していました。 このパイロット研究は、適切な検出力試験での確認を保証します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2507,7 +2507,7 @@
     <t>10.1016/j.hrthm.2026.09.007 doi</t>
   </si>
   <si>
-    <t>BACKGROUND: Slowly conducting anatomical isthmuses (SCAI) represent the main substrate for ventricular arrhythmias (VAs) in tetralogy of Fallot (TOF).  ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません。 目的: この研究は、CV 解析の新しい方法を評価することを目的としています。 方法: この単一施設の後ろ向き研究には、右心室電気解剖学的活性化マッピングを受けた連続 TOF 患者が含まれていました。 解剖学的峡部 3 にわたる CV は、自動化された局所活性化時間速度ベクトル (LVV) 分析と従来の手動測定の両方を使用して評価されました。 主要アウトカムは、持続性単形性心室頻拍（VT; SMVT）の誘発性でした。 結果：合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）。 全体として、SMVTは23人（52.3％）の患者で誘発可能であり、そのうち12/14人（85.7％）はVTのカテーテルアブレーション（臨床的VTの病歴）のために紹介された患者、11/30人（36.7％）は自然発生性VTを伴わないEPSのために紹介された患者であった。 LVV-CV は手動測定と強い相関関係を示しました (r = 0.81)。 Youden 指数に基づく LVV-CV の最適カットオフ値は 0.5 m/s でした。 AUC、感度、特異度は、LVV-CV を使用した場合はそれぞれ 0.81、0.96、0.71 でしたが、手動 CV 測定を使用した場合は 0.75、0.57、0.81 でした。 LVV 分析により、分類エラーの数が手動 CV 測定では 14 件 (31.8%) でしたが、LVV-CV を使用した場合は 7 件 (15.9%) に減少しました。 結論：TOF 患者の基質評価のための CV 測定に対するこの新規で再現性があり、使いやすい LVV ベースのアプローチは、LVV-CV が SMVT 誘導性に関連する SCAI を同定するために手動の CV 測定と比較して優れた識別性能を提供することを示唆しています。 より大きな集団でこのアプローチを評価するには、さらなる研究が必要です。</t>
+    <t>背景: 緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質です。 ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません。 目的: この研究は、CV 解析の新しい方法を評価することを目的としています。 方法: この単一施設の後ろ向き研究には、右心室電気解剖学的活性化マッピングを受けた連続 TOF 患者が含まれていました。 解剖学的峡部 3 にわたる CV は、自動化された局所活性化時間速度ベクトル (LVV) 分析と従来の手動測定の両方を使用して評価されました。 主要アウトカムは、持続性単形性心室頻拍（VT; SMVT）の誘発性でした。 結果：合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）。 全体として、SMVTは23人（52.3％）の患者で誘発可能であり、そのうち12/14人（85.7％）はVT（臨床的VTの病歴）のカテーテルアブレーションのために紹介された患者、および11/30人（36.7％）は自然発生性VTを伴わないEPSのために紹介された患者であった。 LVV-CV は手動測定と強い相関関係を示しました (r = 0.81)。 Youden 指数に基づく LVV-CV の最適カットオフ値は 0.5 m/s でした。 AUC、感度、特異度は、LVV-CV を使用した場合はそれぞれ 0.81、0.96、0.71 でしたが、手動 CV 測定を使用した場合は 0.75、0.57、0.81 でした。 LVV 分析により、分類エラーの数が手動 CV 測定では 14 件 (31.8%) でしたが、LVV-CV を使用した場合は 7 件 (15.9%) に減少しました。 結論：TOF 患者の基質評価のための CV 測定に対するこの新規で再現性があり、使いやすい LVV ベースのアプローチは、LVV-CV が SMVT 誘導性に関連する SCAI を同定するために手動の CV 測定と比較して優れた識別性能を提供することを示唆しています。 より大きな集団でこのアプローチを評価するには、さらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2538,7 +2538,7 @@
     <t>10.1016/j.jacep.2026.07.018 doi</t>
   </si>
   <si>
-    <t>背景: ブルガダ症候群 (BrS) における運動中の前胸部 J ポイント上昇の強調の臨床的意義は依然として不明である。 目的: この研究は、大規模な単一施設の BrS コホートにおける運動中の J ポイント上昇の強調の有病率と予後的重要性を判断することを目的としました。 方法：この後ろ向き研究では、2000年1月1日から2025年10月31日まで運動負荷検査（EST）を受けた、BrS評価のために紹介された連続141人の患者（1型BrSパターンを有する95人-BrS1コホート、1型パターンを有さないが機能喪失型ナトリウム電位依存性チャネルαサブユニット5バリアントを有する46人-SCN5Aコホート）を対象とした。含まれています。 盲検の心臓専門医 2 名がすべての追跡結果を調査しました。 運動により増強される BrS 表現型は、運動中の V1/V2 における J ポイント上昇の 1 mm 以上の増加として定義されました。 心臓イベントには、不整脈性失神、心停止、および適切な植込み型除細動器ショックが含まれます。 未調整および調整済み分析には、Firth ペナルティ付きロジスティック回帰を使用しました。 結果: 全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。 表現型は連続検査で非常に再現性が高かった（追跡 EST の 88%）。 運動強化表現型は全体的な心臓イベントとは関連しなかった（未調整 OR: 1.83 [0.84-3.99]; P = 0.13; 調整済み OR: 1.22 [0.47-3.21]; P = 0.69）。 しかし、性別、運動負荷、およびベースラインのタイプ 1 パターンとは無関係に、労作誘発性の心臓イベントと強く関連していました (未調整 OR: 10.50 [2.94-37.50]; P &lt; 0.001; 調整済み OR: 10.04 [2.76-36.53]; P &lt; 0.001)。 SCN5A変異陽性患者において一貫した結果が認められた。 結論: 運動誘発性の J ポイント上昇の強調は、労作性心臓イベントのリスクがある BrS 患者のサブセットを再現性よく特定します。 これらの発見は、BrS に対する臨床診断または遺伝的感受性を持つ患者の評価に EST を含めることを裏付けており、運動関連のリスクカウンセリングに情報を提供する可能性があります。</t>
+    <t>背景: ブルガダ症候群 (BrS) における運動中の前胸部 J ポイント上昇の強調の臨床的意義は依然として不明である。 目的: この研究は、大規模な単一施設の BrS コホートにおける運動中の J ポイント上昇の強調の有病率と予後的重要性を判断することを目的としました。 方法：この後ろ向き研究では、2000年1月1日から2025年10月31日まで運動負荷検査（EST）を受けた、BrS評価のために紹介された連続141人の患者（1型BrSパターンを有する95人-BrS1コホート、1型パターンを有さないが機能喪失型ナトリウム電位依存性チャネルαサブユニット5バリアントを有する46人-SCN5Aコホート）を対象とした。含まれています。 盲検の心臓専門医 2 名がすべての追跡結果を調査しました。 運動により増強される BrS 表現型は、運動中の V1/V2 における J ポイント上昇の 1 mm 以上の増加として定義されました。 心臓イベントには、不整脈性失神、心停止、および適切な植込み型除細動器ショックが含まれます。 未調整および調整済み分析には、Firth ペナルティ付きロジスティック回帰を使用しました。 結果: 全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。 表現型は連続検査で非常に再現性が高かった (追跡 EST の 88%)。 運動強化表現型は、心臓イベント全体とは関連しなかった（未調整 OR: 1.83 [0.84-3.99]; P = 0.13; 調整済み OR: 1.22 [0.47-3.21]; P = 0.69）。 しかし、性別、運動負荷、ベースラインのタイプ 1 パターンとは無関係に、労作誘発性の心臓イベントと強く関連していました (未調整 OR: 10.50 [2.94-37.50]; P &lt; 0.001; 調整済み OR: 10.04 [2.76-36.53]; P &lt; 0.001)。 SCN5A変異陽性患者において一貫した結果が認められた。 結論: 運動誘発性の J ポイント上昇の強調は、労作性心臓イベントのリスクがある BrS 患者のサブセットを再現性よく特定します。 これらの発見は、BrS に対する臨床診断または遺伝的感受性を持つ患者の評価に EST を含めることを裏付けており、運動関連のリスクカウンセリングに情報を提供する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2569,7 +2569,7 @@
     <t>10.1007/s10840-026-02427-2 doi</t>
   </si>
   <si>
-    <t>背景: メッシュ状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難です。 この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。 方法：TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました。 機構の検証は、ex vivo ブタ心筋モデル (152 病変) を使用して実行されました。 結果: 1,423 件の高周波アプリケーションのうち、138 件が伝導ギャップ セグメント内にありました。 AID% は、非伝導ギャップ セグメントよりも伝導ギャップ セグメントの高周波アプリケーションの方が低かったが、その差はわずかでした (10.2 [8.3-12.2] % vs. 10.9 [9.0-13.1] %, p = 0.002).  全体的な識別性能は限られていました (曲線下面積、0.58、95% 信頼区間、0.53 ～ 0.63)。 患者内クラスタリングを説明する混合効果ロジスティック回帰では、AID% &lt;10% は伝導ギャップセグメントにおける高周波の適用と有意な関連性はありませんでした (オッズ比、1.560; 95% 信頼区間、0.970-2.500; p = 0.065)。一方、平均高周波出力は有意でした。 ex vivo 研究では、ターゲット AID% が固定された条件下であっても、病変の特徴は高周波出力、接触力、持続時間に応じて変化しました。 結論: AID% は、複数のアブレーション パラメータの影響を受ける、高周波送達に対する複合インピーダンスに基づく組織反応を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件による病変特性のばらつきは、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。 平均インピーダンス低下パーセンテージ (AID%) は、複数のアブレーション パラメーターの影響を受ける、高周波送達に対する複合インピーダンスに基づく組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。</t>
+    <t>背景: メッシュ形状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難です。 この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。 方法：TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました。 機構の検証は、ex vivo ブタ心筋モデル (152 病変) を使用して実行されました。 結果: 1,423 件の高周波アプリケーションのうち、138 件が伝導ギャップ セグメント内にありました。 AID% は、非伝導ギャップ セグメントよりも伝導ギャップ セグメントの高周波アプリケーションの方が低かったが、その差はわずかでした (10.2 [8.3-12.2] % 対 10.9 [9.0-13.1] %, p = 0.002).  全体的な識別性能は限られていました (曲線下面積、0.58、95% 信頼区間、0.53 ～ 0.63)。 患者内クラスタリングを説明する混合効果ロジスティック回帰では、AID% &lt;10% は伝導ギャップセグメントにおける高周波の適用と有意な関連はありませんでした (オッズ比、1.560; 95% 信頼区間、0.970-2.500; p = 0.065)。一方、平均高周波出力は有意でした。 ex vivo 研究では、ターゲット AID% が固定された条件下であっても、病変の特徴は高周波出力、接触力、持続時間に応じて変化しました。 結論: AID% は、複数のアブレーション パラメータの影響を受ける、高周波送達に対する複合インピーダンス ベースの組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件による病変特性のばらつきは、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。 平均インピーダンス低下パーセンテージ (AID%) は、複数のアブレーション パラメーターの影響を受ける、高周波送達に対する複合インピーダンスに基づく組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2598,7 +2598,7 @@
     <t>10.1007/s10840-026-02434-3 doi</t>
   </si>
   <si>
-    <t>背景と目的: パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療にますます使用されています。 RESET-AFは、新規のシングルショットPFAシステム（ElePulse、CRC EP、タスティン、カリフォルニア州、米国）を使用したAFアブレーションのシングルアーム、ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）でした。 方法：症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。 PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。 患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。 結果: 研究コホート全体ですべてのエンドポイントが達成されました。 SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%でした。 1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) でした。 二次有効性評価項目は、3 か月後の PVI が 82%、6 か月後の AF が 94% (患者 36 人中 34 人) であった。 研究中、PFA 用量は 3 つのコホートで調整されました。 「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありませんでした。 結論: 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
+    <t>背景と目的: パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療にますます使用されています。 RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった。 方法：症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。 PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。 患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。 結果: 研究コホート全体ですべてのエンドポイントが達成されました。 SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%でした。 1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) でした。 二次有効性エンドポイントは、3か月間のPVIが82%、6か月間のAFが94%（34/36人の患者）でなかった。 研究中、PFA 用量は 3 つのコホートで調整されました。 「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありませんでした。 結論: 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2627,7 +2627,7 @@
     <t>10.1016/j.jacep.2026.09.001 doi</t>
   </si>
   <si>
-    <t>背景: シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません。 既存の焦点 PFA 技術では、個別のアブレーションが可能ですが、複数の心臓および呼吸サイクルにわたってエネルギーを送達する必要があるため、持続的なカテーテルの安定性が重要となり、処置の効率が低下する可能性があります。 目的: 著者らは、「瞬間的な」ポイントバイポイントアブレーション用に設計された新しいサブ秒パルスフィールド波形を送出する焦点 PFA カテーテルを評価しようとしました。 方法: 8.5-F 力感知 PFA カテーテルは、QRS 同期された単一の高電圧 (≥10 kV; &lt;200 ms) パルス場印加を提供します。 3 つの連続した波形/電極構成コホートが評価されました。 PVI は、インピーダンスに基づいてカテーテルの位置を特定する従来の電気解剖学的マッピングによって誘導されました。 サブセットはPFA後の脳磁気共鳴画像検査を受けました。 〜90日後の侵襲的再マッピングにより、病変の耐久性を評価しました。 結果: 35 人の患者が波形 A (n = 15)、B (n = 5)、または C (n = 15) で PFA を受けました。 急性 PVI はすべての患者で達成され、患者あたり 39 (IQR: 35-45) の PF 病変を必要とし、アブレーション経過時間の中央値は 13 (IQR: 10-15) 分でした。 32 人の患者の再マッピングでは、波形の進化に伴う PVI 耐久性の漸進的な改善が実証されました。波形 C は静脈あたり 94.2% の PVI 耐久性を達成しました。 脳磁気共鳴画像法 (n = 14) では、拡散強調画像法 (DWI)+/流体減衰反転回復法 (FLAIR)+ 病変は認められず、DWI+/FLAIR- 病変は 2 件 (14%) ありました。 主要な安全性事象、ハプトグロビン枯渇、または急性腎障害はありませんでした。 12 か月間心房性不整脈が発生しなかった率は 73.9% (95% CI: 60.6% ～ 90.2%) でした。 結論: 1 秒未満の高電圧焦点 PFA により、長時間のカテーテルの安定性を必要とせずに、効率的なポイントごとのアブレーションと個別の病変セットが可能になりました。 これらのファーストインヒューマンデータは、瞬間的な焦点の PFA ワークフローの継続的な臨床開発をサポートします。 臨床試験: gov: (FIELD-PULSE 研究; 心房細動患者における FieldForce アブレーション システムの安全性と実現可能性を評価するための市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589)。</t>
+    <t>背景: シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません。 既存の焦点 PFA 技術では、個別のアブレーションが可能ですが、複数の心臓および呼吸サイクルにわたってエネルギーを送達する必要があるため、持続的なカテーテルの安定性が重要となり、処置の効率が低下する可能性があります。 目的: 著者らは、「瞬間的な」ポイントバイポイントアブレーション用に設計された新しいサブ秒パルスフィールド波形を送出する焦点 PFA カテーテルを評価しようとしました。 方法: 8.5-F 力感知 PFA カテーテルは、QRS 同期された単一の高電圧 (≥10 kV; &lt;200 ms) パルス場印加を提供します。 3 つの連続した波形/電極構成コホートが評価されました。 PVI は、インピーダンスに基づいたカテーテルの位置特定を伴う従来の電気解剖学的マッピングによって誘導されました。 サブセットはPFA後の脳磁気共鳴画像検査を受けました。 〜90日後の侵襲的再マッピングにより、病変の耐久性を評価しました。 結果: 35 人の患者が波形 A (n = 15)、B (n = 5)、または C (n = 15) で PFA を受けました。 急性 PVI はすべての患者で達成され、患者あたり 39 (IQR: 35-45) の PF 病変が必要で、経過アブレーション時間の中央値は 13 (IQR: 10-15) 分でした。 32 人の患者の再マッピングでは、波形の進化に伴う PVI 耐久性の漸進的な改善が実証されました。波形 C は静脈あたり 94.2% の PVI 耐久性を達成しました。 脳磁気共鳴画像法 (n = 14) では、拡散強調画像法 (DWI)+/流体減衰反転回復法 (FLAIR)+ 病変は認められず、DWI+/FLAIR- 病変が 2 件 (14%) ありました。 主要な安全性事象、ハプトグロビン枯渇、または急性腎障害はありませんでした。 12 か月間心房性不整脈が発生しなかった率は 73.9% (95% CI: 60.6% ～ 90.2%) でした。 結論: 1 秒未満の高電圧焦点 PFA により、長時間のカテーテルの安定性を必要とせずに、効率的なポイントごとのアブレーションと個別の病変セットが可能になりました。 これらのファーストインヒューマンデータは、瞬間的な焦点の PFA ワークフローの継続的な臨床開発をサポートします。 臨床試験: 政府：（FIELD-PULSE 研究; 心房細動患者におけるフィールドフォースアブレーションシステムの安全性と実現可能性を評価するための、市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589）。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2660,7 +2660,7 @@
     <t>10.1016/j.hrthm.2026.09.006 doi</t>
   </si>
   <si>
-    <t>背景: 高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率が 75% 未満、貫壁性が 60% 未満という一貫性のない心筋ターゲティングが生じます。 目的: 肥大型心筋症 (HCM) における深心室頻拍 (VT) アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドする HIU カテーテルとリアルタイム接触センシング方法を設計しました。 私たちは、接触感知誘導型 HIU (CSG-HIU) は、終末期のブタ モデルにおいて標準 HIU (Std-HIU) よりも大きく、より深く、より多くの貫壁性病変を作成するだろうと仮説を立てました。 方法: トランスデューサーの寸法 (5x6 mm) と周波数 (5 MHz) は 3D 音響シミュレーションから選択されました。 3 つの接触検知モダリティ (パルスエコー、およびトランスデューサー側微小電極を介した双極または単極インピーダンス) が ex vivo で検証されました。 次に、心室中隔の Std-HIU (n=10) と CSG-HIU (n=13) のアブレーションを比較する前向きの in vivo ブタ研究で最良の方法が使用されました。 結果: 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました。 In-vivo と Std-HIU、CSG-HIU では、体積が大きくなり (2071±1231 vs. 568±890 mm、p=0.005）、より深い病変（15±3 vs. 6±6 mm、p&lt;0.001)、ブタの 69 対 20% で貫壁性 (p=0.030)。 持続的な房室ブロック、心室中隔欠損症、手術による死亡は発生しませんでした。 結論: リアルタイム双極インピーダンス CSG-HIU は歴史的な方向性の制限を克服し、100% の病変効率とより予測可能な貫壁性を達成します。</t>
+    <t>背景: 高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率 &lt; 75%、貫壁性 &lt; 60% という一貫性のない心筋ターゲティングが生じます。 目的：我々は、肥大型心筋症（HCM）における深心室頻拍（VT）アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドするためのHIUカテーテルとリアルタイム接触センシング法を設計した。 われわれは、接触感知誘導型 HIU (CSG-HIU) が、豚の終末期モデルにおいて、標準 HIU (Std-HIU) よりも大きく、より深く、より多くの貫壁性病変を生成すると仮説を立てました。 方法: トランスデューサーの寸法 (5x6 mm) と周波数 (5 MHz) は 3D 音響シミュレーションから選択されました。 3 つの接触検知モダリティ (パルスエコー、およびトランスデューサー側微小電極を介した双極または単極インピーダンス) が ex vivo で検証されました。 次に、心室中隔の Std-HIU (n=10) と CSG-HIU (n=13) のアブレーションを比較する前向きの in vivo ブタ研究で最良の方法が使用されました。 結果: 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました。 In-vivo と Std-HIU、CSG-HIU では、体積が大きくなり (2071±1231 vs. 568±890 mm、p=0.005）、より深い病変（15±3 vs. 6±6 mm、p&lt;0.001)、ブタの 69 対 20% で貫壁性 (p=0.030)。 持続的な房室ブロック、心室中隔欠損症、手術による死亡は発生しませんでした。 結論: リアルタイム双極性インピーダンス CSG-HIU は歴史的な方向制限を克服し、100% の病変効率とより予測可能な貫壁性を達成します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2678,7 +2678,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42749241/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.35] 新しい胸骨下リードからの血行力学センシング、電気センシング、および心室ペーシングの統合: 急性ヒト研究
+    <t xml:space="preserve">📄 [No.35] 新しい胸骨下リードからの血行力学センシング、電気センシング、心室ペーシングの統合: 急性ヒト研究
 (Integrated hemodynamic sensing, electrical sensing, and ventricular pacing from a novel substernal lead: An acute human study.)</t>
   </si>
   <si>
@@ -2722,7 +2722,7 @@
     <t>10.1007/s10840-026-02442-3 doi</t>
   </si>
   <si>
-    <t>背景: カテーテルアブレーションは、小児および先天性心疾患 (CHD) 患者の頻脈性不整脈に対する効果的かつ安全な治療法であることが証明されています。 これらの人々におけるカテーテルアブレーションの使用に関する国際登録はありますが、その中にはラテンアメリカ諸国は含まれていません。 目的: カテーテルアブレーション処置を受けている小児および先天性心疾患患者の臨床的特徴を評価すること。 取得されるデータには、不整脈の種類、技術、成功率、合併症、再発率が含まれます。 材料と方法: 記述的かつ分析的な遡及的観察研究が実施されました。 6 か月間利用できるクローズド コード化されたオンライン フォームが使用されました。 ラテンアメリカで小児電気生理学を実践し、以前の LAHSR の調査で特定された電気生理学者全員が、ラテンアメリカ心調律協会 (LAHRS) 電子メディア ( https://lahrs.org/ ) を通じて参加するよう招待されました。 参加は強制ではなく、経済的または物質的な財によって奨励されるものではなく、データの使用についてのインフォームドコンセントが必要でした。 2017年から2021年まで、年齢に関係なく、18歳未満の小児またはCHD患者を対象に、連続電気生理学的カテーテル処置が行われた。 結果: ラテンアメリカ 8 か国から 20 名の医師が参加しました。 合計1,778件の手術が報告され、53％が男性、平均年齢は12.4±5.1歳、8.5％が先天性心疾患を患っていた。 患者の 87% でアブレーションが試みられ、そのうち 68% では非灌流先端高周波カテーテルが使用され、29% では 3D マッピング システムが使用されました。 98% のケースで最も一般的に使用されたエネルギー源は高周波でした。 最も頻度の高い基質は副経路で 69.5% (61% は明らか)、次いで房室結節リエントリーが 16.5%、異所性心房頻脈が 4% でした。 さらに、心房粗動が 3.8%、心室頻拍が 3.8%、心室性期外収縮が 1.2% 発生しました。 症例の 93% でアブレーションは直ちに成功したと考えられます。 平均総処置時間は 92.1 ± 36.8 分、平均総透視時間は 16.3 ± 9.4 分でした。 合併症率は 1.8% で、3 人の患者 (0.2%) には完全な房室ブロックが含まれていました。 死亡者は報告されていない。 再発率は8.5%でした。 結論: ラテンアメリカにおけるカテーテルアブレーションの、小児および先天性心疾患のみを対象とした初の遡及的登録では、高い成功率と低い合併症発生率が観察されました。 これは他の緯度で以前に報告された登録と一致しており、このグループの患者にとってアブレーションが効果的で安全な治療法であることが証明されています。</t>
+    <t>背景: カテーテルアブレーションは、小児および先天性心疾患 (CHD) 患者の頻脈性不整脈に対する効果的かつ安全な治療法であることが証明されています。 これらの人々におけるカテーテルアブレーションの使用に関する国際登録はありますが、その中にはラテンアメリカ諸国は含まれていません。 目的: カテーテルアブレーション処置を受けている小児および先天性心疾患患者の臨床的特徴を評価すること。 取得されるデータには、不整脈の種類、技術、成功率、合併症、再発率が含まれます。 材料と方法: 記述的かつ分析的な遡及的観察研究が実施されました。 6 か月間利用できるクローズド コード化されたオンライン フォームが使用されました。 ラテンアメリカで小児電気生理学を実践し、以前の LAHSR の調査で特定された電気生理学者全員が、ラテンアメリカ心調律協会 (LAHRS) 電子メディア ( https://lahrs.org/ ) を通じて参加するよう招待されました。 参加は強制ではなく、経済的または物質的な財によって奨励されるものではなく、データの使用についてのインフォームドコンセントが必要でした。 2017年から2021年まで、年齢に関係なく、18歳未満の小児またはCHD患者を対象に、連続電気生理学的カテーテル処置が行われた。 結果: ラテンアメリカ 8 か国から 20 名の医師が参加しました。 合計1,778件の手術が報告され、53％が男性、平均年齢は12.4±5.1歳、8.5％が先天性心疾患を患っていた。 患者の 87% でアブレーションが試みられ、そのうちの 68% では非灌流先端高周波カテーテルが使用され、29% では 3D マッピング システムが使用されました。 98% のケースで最も一般的に使用されたエネルギー源は高周波でした。 最も頻度の高い基質は副経路で 69.5% (61% が明示的)、次いで房室結節リエントリーが 16.5%、異所性心房頻脈が 4% でした。 さらに、心房粗動が 3.8%、心室頻拍が 3.8%、心室性期外収縮が 1.2% 発生しました。 症例の 93% でアブレーションは直ちに成功したと考えられます。 平均総処置時間は 92.1 ± 36.8 分、平均総透視時間は 16.3 ± 9.4 分でした。 合併症率は 1.8% で、3 人の患者 (0.2%) には完全な房室ブロックが含まれていました。 死亡例は報告されていない。 再発率は8.5%でした。 結論: ラテンアメリカにおけるカテーテルアブレーションの、小児および先天性心疾患のみを対象としたこの初の遡及的登録では、高い成功率と低い合併症発生率が観察されました。 これは他の緯度で以前に報告された登録と一致しており、このグループの患者にとってアブレーションが効果的で安全な治療法であることが証明されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2753,7 +2753,7 @@
     <t>10.1111/jce.70512 doi</t>
   </si>
   <si>
-    <t>目的: 定位性不整脈放射線アブレーション (STAR) は、難治性心室頻拍に対する有望な非侵襲的治療法です。 STAR に走査陽子線を使用すると、正確に集束された高線量の電離放射線が可能になります。 ターゲットの動きを効果的に緩和することは安全性にとって重要ですが、ビームスキャンと心肺動作との間の複雑な相互作用のため、依然として困難です。 われわれは、ゲート走査陽子線を心室心筋標的に正確に照射する安全性と実現可能性を評価し、呼吸器（シングル）ゲートと心肺（デュアル）ゲート陽子線の病変転帰を比較した。 方法: 6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました。 その後、走査陽子線を使用したシングルゲートまたはデュアルゲート送達で治療されました。 治療反応は、ベースライン時および照射後 14 ～ 15 週間目に、心エコー検査、血液分析、陽電子放射断層撮影 (PET)-CT によって評価されました。 終了時に病変を評価し、組織病理学のために組織を採取しました。 結果: フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。 照射領域は、すべての動物において、PET-CT では in vivo で、また ex vivo の剖検では予想された位置で識別可能でした。 視覚的病変の貫壁性は組織学によって確認された。 病変サイズは、デュアルゲート動物では予想される体積からそれほど遠くありませんでしたが、シングルゲート動物では大きかった（グループ間の比較では p = 0.3、各アームで N = 2）。 結論: 結果により、ワークフローの実現可能性が確認されました。 デュアルゲート照射は、標的体積外の心筋への放射線被ばくの減少と、病変のサイズが計画されたものに近づくことに関連していた。</t>
+    <t>目的: 定位性不整脈放射線アブレーション (STAR) は、難治性心室頻拍に対する有望な非侵襲的治療法です。 STAR に走査陽子線を使用すると、正確に集束された高線量の電離放射線が可能になります。 ターゲットの動きを効果的に緩和することは安全性にとって重要ですが、ビームスキャンと心肺動作との間の複雑な相互作用のため、依然として困難です。 われわれは、ゲート走査陽子線を心室心筋標的に正確に照射する安全性と実現可能性を評価し、呼吸器（シングル）ゲートと心肺（デュアル）ゲート陽子線の病変転帰を比較した。 方法: 6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました。 その後、走査陽子線を使用したシングルゲートまたはデュアルゲート送達で治療されました。 治療反応は、ベースライン時および照射後 14 ～ 15 週間目に、心エコー検査、血液分析、陽電子放射断層撮影 (PET)-CT によって評価されました。 終了時に病変を評価し、組織を病理組織学のために採取した。 結果: フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。 照射領域は、すべての動物において、PET-CT では in vivo で、また ex vivo の剖検では予想された位置で識別可能でした。 視覚的病変の貫壁性は組織学によって確認された。 病変サイズは、デュアルゲート動物では予想される体積からそれほど遠くありませんでしたが、シングルゲート動物では大きかった（グループ間の比較では p = 0.3、各アームで N = 2）。 結論: 結果により、ワークフローの実現可能性が確認されました。 デュアルゲート照射は、標的体積外の心筋への放射線被ばくの減少と、病変のサイズが計画されたものに近づくことに関連していた。</t>
   </si>
   <si>
     <t xml:space="preserve">AIMS:
@@ -2782,7 +2782,7 @@
     <t>10.1016/j.hrthm.2026.06.042 doi</t>
   </si>
   <si>
-    <t>背景: 慢性心臓植込み型電子機器リードの経静脈的抜去は、線維性癒着や処置上のリスクによって課題が生じています。 新しい技術は、安全性と有効性の向上を目指しています。 高周波機械振動システムは、癒着を破壊することを目的としています。 目的: この研究は、前臨床適正実験基準ヒツジモデルにおける新しい振動補助リード抽出システムの初期の安全性、性能、および使いやすさを評価することを目的としました。 方法: 2 年以上 (範囲 2.9 ～ 5.25 年) に植え込まれた 9 本のリードを、X 線透視下で振動システムを使用して 6 頭の羊から抜き取りました。 リードの内腔は、カスタマイズされたロッキング スタイレットを送達するために使用されました。 スタイレットを使用してリードに振動エネルギーを与え、1 匹あたり最大 20 分間適用しました。 評価には、手術の成功、リードの完全性、手術中のモニタリング、3日間の臨床フォローアップ、臨床検査、剖検、および病理組織学（心臓、肺、中心静脈）が含まれます。 結果: 補助ツールなしで手術の成功 (リード除去) は 100% でした。すべての症例で癒着剥離に外部切断シースは必要ありませんでした。 リードの解放は、9 つ​​のリードのうち 8 つで約 1 分以内に発生しました。 主要な安全性評価項目は満たされました：中心静脈または心筋穿孔がないこと、および肺塞栓症がないこと。 血圧低下、重大な不整脈、三尖弁逆流の悪化は発生しませんでした。 1 つのリード骨折 (9 件中 1 件) では、軽度の局所的な心筋壊死を伴う遠位スクリューの残存 (&lt;1 cm) が発生しました。 アンカーデバイスの誤動作により、2 件のケースで処置中の交換が必要になりました。 結論: このヒツジモデルでは、慢性心臓植込み型電子機器リードの振動支援による抜去は実現可能であり、主要な安全性エンドポイントを満たし、顕著な急性安全性プロファイルを示しました。 この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出によって特徴付けられ、潜在的に危険な外部切断シースの要件を回避することに成功しました。 リードの破損とアンカーの機能不全は、さらなる技術評価と臨床試験の余地があることを示しています。</t>
+    <t>背景: 慢性心臓植込み型電子機器リードの経静脈的抜去は、線維性癒着や処置上のリスクによって課題が生じています。 新しい技術は、安全性と有効性の向上を目指しています。 高周波機械振動システムは、癒着を破壊することを目的としています。 目的: この研究は、前臨床適正実験基準ヒツジモデルにおける新しい振動補助リード抽出システムの初期の安全性、性能、および使いやすさを評価することを目的としました。 方法： 2 年以上（範囲 2.9 ～ 5.25 年）埋め込まれた 9 本のリードを、X 線透視下で振動システムを使用して 6 頭の羊から抜き取った。 リードの内腔は、カスタマイズされたロッキング スタイレットを送達するために使用されました。 スタイレットを使用してリードに振動エネルギーを与え、1 匹あたり最大 20 分間適用しました。 評価には、手術の成功、リードの完全性、手術中のモニタリング、3日間の臨床フォローアップ、臨床検査、剖検、および病理組織学（心臓、肺、中心静脈）が含まれます。 結果: 補助ツールなしで手術の成功 (リード除去) は 100% でした。すべての症例で癒着剥離に外部切断シースは必要ありませんでした。 リードの解放は、9 つ​​のリードのうち 8 つで約 1 分以内に発生しました。 主要な安全性評価項目は満たされました：中心静脈または心筋穿孔がないこと、および肺塞栓症がないこと。 血圧低下、重大な不整脈、三尖弁逆流の悪化は発生しませんでした。 1 つのリード骨折 (9 件中 1 件) では、軽度の局所的な心筋壊死を伴う遠位スクリューの残存 (&lt;1 cm) が発生しました。 アンカーデバイスの誤動作により、2 件のケースで処置中の交換が必要になりました。 結論: このヒツジモデルでは、慢性心臓植込み型電子機器リードの振動支援による抜去は実現可能であり、主要な安全性エンドポイントを満たし、顕著な急性安全性プロファイルを示しました。 この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出を特徴としており、潜在的に危険な外部切断シースの要件を回避することに成功しました。 リードの破損とアンカーの機能不全は、さらなる技術評価と臨床試験の余地があることを示しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2813,7 +2813,7 @@
     <t>10.1111/jce.70503 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティです。 ただし、心室性不整脈 (VA) に対するその性能に関するデータは依然として限られています。 目的: 現実世界の米国多施設登録における複雑な VA に対する PFA の実現可能性、安全性、有効性を評価すること。 方法：この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けている連続患者が含まれた（2024年4月から2025年7月まで）。 主要な実現可能性の成果は、意図した標的基質への PFA 損傷の送達の成功でした。 主な有効性アウトカムには、急性処置の成功が含まれます。植込み型除細動器（ICD）ショックまたは複数回の抗頻脈ペーシング療法を必要とする持続的な心室頻拍再発。 PVC 負荷が 80% 以上削減されます。 安全性の結果には、処置上の合併症、弁機能、血栓塞栓性イベント、腎機能、伝導障害が含まれます。 結果: 26 人の患者が含まれた (PVC 13 人、VT 13 人)。 すべての VT アブレーション (69.2% が完了、30.8% が部分的) および 92.3% の PVC アブレーションで急性成功が達成されました。 合併症は患者の 11.5% で発生しました (一過性 LBBB [n = 1] および血管合併症 [n = 2])。 血栓塞栓性イベント、心臓内血栓、または急性腎損傷は観察されませんでした。 僧帽弁装置付近の病変は、既存の弁膜症患者を含め、僧帽弁逆流を悪化させませんでした。 中央値365日の追跡調査の後、1人の患者がICDショックを必要とするVT再発を経験した。 VT アブレーション後の推定無再発生存率は 12 か月時点で 61.5% でした。 PVC 患者の 58.3% が 80% 以上の負担軽減を達成しました。 結論: VA に対する PFA は実行可能であり、非常に効果的であり、処置に関連した合併症の発生率は低いと考えられます。 急性の成功率は高かったものの、長期的な結果は VT アブレーションでは許容範囲であり、PVC アブレーションでは比較的穏やかであり、技術とエネルギー供給戦略の継続的な改良の必要性が強調されました。 大規模な前向き研究が保証されています。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティです。 ただし、心室性不整脈 (VA) に対するその性能に関するデータは依然として限られています。 目的: 現実世界の米国多施設登録における複雑な VA に対する PFA の実現可能性、安全性、有効性を評価すること。 方法：この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けている連続患者が含まれていた（2024年4月から2025年7月まで）。 主要な実現可能性の成果は、意図した標的基質への PFA 損傷の送達の成功でした。 主な有効性アウトカムには、急性処置の成功が含まれます。植込み型除細動器（ICD）ショックまたは複数回の抗頻脈ペーシング療法を必要とする持続的な心室頻拍再発。 PVC 負荷が 80% 以上削減されます。 安全性の結果には、処置上の合併症、弁機能、血栓塞栓性イベント、腎機能、伝導障害が含まれます。 結果: 26 人の患者が含まれた (PVC 13 人、VT 13 人)。 すべての VT アブレーション (69.2% が完了、30.8% が部分的) および 92.3% の PVC アブレーションで急性成功が達成されました。 合併症は患者の 11.5% で発生しました (一過性 LBBB [n = 1] および血管合併症 [n = 2])。 血栓塞栓性イベント、心臓内血栓、または急性腎損傷は観察されませんでした。 僧帽弁装置付近の病変は、既存の弁膜症患者を含め、僧帽弁逆流を悪化させませんでした。 中央値365日の追跡調査の後、1人の患者がICDショックを必要とするVT再発を経験した。 VT アブレーション後の推定無再発生存率は 12 か月時点で 61.5% でした。 PVC 患者の 58.3% が 80% 以上の負担軽減を達成しました。 結論: VA に対する PFA は実行可能であり、非常に効果的であり、処置に関連した合併症の発生率は低いと考えられます。 急性の成功率は高かったものの、長期的な結果は VT アブレーションでは許容範囲であり、PVC アブレーションでは比較的穏やかであり、技術とエネルギー供給戦略の継続的な改良の必要性が強調されました。 大規模な前向き研究が保証されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2872,7 +2872,7 @@
     <t>10.1111/jce.70511 doi</t>
   </si>
   <si>
-    <t>はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広い電場を生成する可能性があります。 我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。 方法と結果：我々は、Affera システムによる原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。 アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標が欠けているため、座標 (x、y、z) とバイポーラ電圧は CARTO 3 から抽出されました。 線維輪および左心耳を除く、エネルギー送達部位の外側のアブレーション前後のポイントは、2 mm の相互最近傍基準を使用して空間的に一致しました。 これにより、3772 ペアが得られました。 双極性電圧はケースごとに平均化されました。 平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧 (事後/事前 × 100) は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し (10 ～ 15 mm で 16.5%、25 ～ 30 mm で 57.8%、すべて p &lt; 0.001)、約 30 mm を超えると数値的にはベースラインと同等になりました。 結論: Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
+    <t>はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性があります。 我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。 方法と結果：我々は、Affera システムによる原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。 アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標が欠けているため、座標 (x、y、z) とバイポーラ電圧は CARTO 3 から抽出されました。 線維輪および左心耳を除く、エネルギー送達部位の外側のアブレーション前後のポイントは、2 mm の相互最近傍基準を使用して空間的に一致しました。 これにより、3772 ペアが得られました。 双極性電圧はケースごとに平均化されました。 平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました。 結論: Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -2896,7 +2896,7 @@
     <t>10.1111/jce.70515 doi</t>
   </si>
   <si>
-    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。 しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。 方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。 急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。 学習フェーズは、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。 結果: 学習曲線が観察され、最初の 20 回の手術中に不完全な病変形成が最も減少しました。 不完全な病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。 手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。 より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。 結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。 LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。 体系的な電気解剖学的再マッピングは、相当な手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
+    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。 しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。 方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。 急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。 学習段階は、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。 結果: 学習曲線が観察され、最初の 20 回の手術中に不完全な病変形成が最も減少しました。 不完全な病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。 手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。 より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。 結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。 LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。 体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2922,7 +2922,7 @@
     <t>10.1016/j.hrthm.2026.09.044 doi</t>
   </si>
   <si>
-    <t>背景: QT延長症候群の多くの人々は、重要性が不確かな変異体として分類されるミスセンス変異体を保有しています。 臨床室実験からの機能的証拠は遺伝子診断の改善に役立ちますが、臨床解釈の枠組みで使用する前に適切な検証が必要です。 目的: KCNH2 変異体の 2 つの機能データセットを比較すること: K11.1 チャネルが細胞表面に到達する量を測定するハイスループット アッセイと、HEK293 細胞のカリウム電流レベルを測定する自動パッチ クランプです。 方法: 自動パッチクランプの結果は、病原性および良性の KCNH2 バリアントの参照セットを使用して尤度比に変換されました。 次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。 結果: 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られました。 残りの 103 個の変異はアッセイ間で異なり、49 個は正常な機能証拠と異常な機能的証拠の間でシフトし、54 個は機能的証拠のカテゴリーと不確定な結果の間でシフトしました。 両方のアッセイで強い異常証拠が割り当てられた変異体のうち、54 個は ClinVar には存在しませんでした。 111 個の未解決または矛盾する ClinVar バリアントのうち、92 個は、強力な機能的証拠を裏付けとなる計算および集団頻度の証拠と組み合わせると、おそらく病原性の分類に十分な証拠の組み合わせを満たすと考えられます。 結論: 尤度比キャリブレーションにより、MAVE データと自動パッチクランプ データを同じ臨床解釈フレームワーク内で比較できるようになります。 これらの機能的データセットを組み合わせると、QT 延長症候群における KCNH2 バリアントのより透明性の高い解釈をサポートできます。</t>
+    <t>背景: QT延長症候群の多くの人々は、重要性が不確かな変異体として分類されるミスセンス変異体を保有しています。 臨床室実験からの機能的証拠は遺伝子診断の改善に役立ちますが、臨床解釈の枠組みで使用する前に適切な検証が必要です。 目的: KCNH2 変異体の 2 つの機能データセットを比較すること: K11.1 チャネルが細胞表面に到達する量を測定するハイスループット アッセイと、HEK293 細胞のカリウム電流レベルを測定する自動パッチ クランプです。 方法: 自動パッチクランプの結果は、病原性および良性の KCNH2 バリアントの参照セットを使用して尤度比に変換されました。 次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。 結果: 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られました。 残りの 103 個の変異はアッセイ間で異なり、49 個は正常な機能証拠と異常な機能的証拠の間でシフトし、54 個は機能的証拠のカテゴリーと不確定な結果の間でシフトしました。 両方のアッセイで強い異常証拠が割り当てられた変異体のうち、54 個は ClinVar には存在しませんでした。 111 個の未解決または矛盾する ClinVar バリアントのうち、92 個は、強力な機能的証拠を裏付けとなる計算および集団頻度の証拠と組み合わせると、おそらく病原性の分類に十分な証拠の組み合わせを満たすと考えられます。 結論: 尤度比キャリブレーションにより、MAVE データと自動パッチクランプ データを同じ臨床解釈フレームワーク内で比較できます。 これらの機能的データセットを組み合わせると、QT 延長症候群における KCNH2 バリアントのより透明性の高い解釈をサポートできます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2950,7 +2950,7 @@
     <t>10.1007/s10840-026-02443-2 doi</t>
   </si>
   <si>
-    <t>背景: 米国では、全身麻酔 (GA) が心房細動 (AF) カテーテルアブレーションの鎮静戦略として好まれてきました。その理由の 1 つは、パルスフィールドアブレーション (PFA) システムが骨格筋の刺激と不快感を引き起こし、軽い鎮静下では耐えられないためです。 最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。 これに関連して、MAC がアブレーションの有効性を損なうことなく処置効率の利点を提供するかどうかは、十分に特徴付けられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。 方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。 各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 でマッチングされ、39 人の年齢が一致した対照が得られました。 6 つの異なる時間間隔が収集されました:合計室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。 次に、グループ比較が行われました。 さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジューリングの機会コストも決定されました。 結果: 総室内時間 (103.5 ± 20.0 vs. 126.2±33.1分; p = 0.0004)、手順前のセットアップ時間 (33.4 ± 10.0 vs. 50.3±28.0分。 p = 0.0007）、および処置後のターンオーバー時間（14.8 ± 9.3 vs. 21.4 ± 8.3 分。 p = 0.0030) は MAC の方が有意に短かった。 コア処置時間 (55.3 ± 20.5 vs. 55.3 ± 23.9 分）、経中隔から LA シースアウトまでの時間（34.2 ± 12.9 対 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。 アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 vs. 24.2 ± 15.5 分。 p = 0.036)。 施行された切除病変の総数 (17.6 ± 5.1 vs. 18.8 ± 7.2、p = 0.68）および急性処置成功（39/39 [100%] vs. 39/39 [100%]) は MAC と GA の間で同様であり、どちらのグループにも処置上の合併症はありませんでした。 MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。 結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
+    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。 最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。 これに関連して、MAC がアブレーションの有効性を損なうことなく処置効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。 方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。 各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 で対応付けられ、39 人の年齢が一致した対照が得られました。 6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。 次に、グループ比較が行われました。 さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。 結果: 総室内時間 (103.5 ± 20.0 vs. 126.2±33.1分; p = 0.0004)、手順前のセットアップ時間 (33.4 ± 10.0 vs. 50.3±28.0分。 p = 0.0007）、および処置後のターンオーバー時間（14.8 ± 9.3 vs. 21.4 ± 8.3 分。 p = 0.0030) は MAC の方が有意に短かったです。 コア処置時間 (55.3 ± 20.5 vs. 55.3 ± 23.9 分）、経中隔から LA シースアウトまでの時間（34.2 ± 12.9 対 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。 アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 vs. 24.2 ± 15.5 分。 p = 0.036)。 施行された切除病変の総数 (17.6 ± 5.1 vs. 18.8 ± 7.2、p = 0.68）および急性処置成功（39/39 [100%] vs. 39/39 [100%]) は MAC と GA の間で同様であり、どちらのグループにも処置上の合併症はありませんでした。 MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。 結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2991,7 +2991,7 @@
     <t>10.1016/j.hrthm.2026.09.032 doi</t>
   </si>
   <si>
-    <t>背景: 身体運動と不整脈原性右室心筋症 (ARVC) との関連性にもかかわらず、患者に対する運動の安全性と適合性に関するデータは存在しない。 目的: 病原性プラコフィリン-2 変異を持つ ARVC 患者におけるさまざまな運動中の心室性期外収縮 (PVC) の発生率と複雑さ、および心臓代謝負荷を定量化すること。 方法: 明確な ARVC を持つ 25 人の参加者 (女性 9 人/男性 16 人) が、心肺機能をモニタリングしながらさまざまな運動を実施しました。 抵抗運動には両足スクワットと片側二頭筋カールが含まれ、持久運動には心拍数 (HR) 80、100、120 bpm でのウォーキングとサイクリングが含まれます。 各アクティビティの後には 10 分間の回復時間が続きました。 結果: 回復期の初期では、活発な運動期と比較して PVC の負担が 2 倍以上 (p &lt; 0.001)、PVC の形態が 3 つ以上発生しました (52 対 84%、p = 0.03)。 片側の上腕二頭筋カールのみが、安静時と比較して PVC 負担を増加させませんでした (p = 0.361)。 レジスタンスエクササイズは、同等の努力レベルでより低い心臓負荷と不整脈負荷を組み合わせたものです。 運動強度の分類では、同じタスクでも使用する指標によって「軽い」から「高い」まで大きな変動が見られました。 結論: PKP-2 ARVC における運動による不整脈の負担を適切に評価するには、早期回復モニタリングが不可欠です。 筋肉量の少ない運動は、PVC 負荷と心臓負荷（不整脈のリスクと病気の進行の代用マーカー）が最も低いことが示されたため、この集団に運動を処方するための有望な道筋となります。 ARVC の運動強度ガイドラインは十分に明確ではないため、改善する必要があります。</t>
+    <t>背景: 身体運動と不整脈原性右室心筋症 (ARVC) との関連性にもかかわらず、患者に対する運動の安全性と適合性に関するデータは存在しない。 目的: 病原性プラコフィリン-2 変異を持つ ARVC 患者におけるさまざまな運動中の心室性期外収縮 (PVC) の発生率と複雑さ、および心臓代謝負荷を定量化すること。 方法: 明確な ARVC を持つ 25 人の参加者 (女性 9 人/男性 16 人) が、心肺機能をモニタリングしながらさまざまな運動を実施しました。 抵抗運動には両足スクワットと片側二頭筋カールが含まれ、持久運動には心拍数 (HR) 80、100、120 bpm でのウォーキングとサイクリングが含まれます。 各アクティビティの後には 10 分間の回復時間が続きました。 結果: 回復期の初期では、活発な運動期と比較して PVC の負担が 2 倍以上 (p &lt; 0.001)、PVC の形態が 3 つ以上発生しました (52 対 84%、p = 0.03)。 片側の上腕二頭筋カールのみが、安静時と比較して PVC 負担を増加させませんでした (p = 0.361)。 レジスタンスエクササイズは、同等の努力レベルでより低い心臓負荷と不整脈負荷を組み合わせたものです。 運動強度の分類では、同じタスクでも使用する指標によって「軽い」から「高い」まで大きな変動が見られました。 結論: PKP-2 ARVC における運動による不整脈の負担を適切に評価するには、早期回復モニタリングが不可欠です。 筋肉量の少ない運動は、PVC 負荷と心臓負荷 (不整脈のリスクと病気の進行の代用マーカー) が最も低いことが示されたため、この集団に運動を処方するための有望な道筋となります。 ARVC の運動強度ガイドラインは十分に明確ではないため、改善する必要があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3108,7 +3108,7 @@
     <t>10.1007/s10840-026-02441-4 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。 我々は、左室心室頻拍アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。 逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウスジョーダン) を使用して達成されました。 この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんでした。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大します。</t>
+    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。 我々は、左心室頻脈アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。 逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウスジョーダン) を使用して達成されました。 この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんでした。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大します。</t>
   </si>
   <si>
     <t>Pulsed field ablation (PFA) has been increasingly used for ventricular ablation. We present a novel case describing use of a variable-loop circular PFA catheter (Varipulse, Biosense Webster, Inc., Irvine, CA, USA) via a retrograde aortic approach for left ventricular ventricular tachycardia ablation. Retrograde aortic access was achieved using a long sheath (Ventrax system, Merit Medical, South Jordan, UT) permitting safe unsheathing and manipulation of the variable-loop PFA catheter to avoid entrapment with the mitral valve apparatus. The procedure was completed without complication and no VT recurrence was observed over 3 months follow-up. This case highlights the feasibility of this approach and expands the potential applications of this integrated PFA platform beyond its current indication for atrial fibrillation ablation.</t>
@@ -3127,7 +3127,7 @@
     <t>10.1016/j.hrthm.2026.09.023 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、高い心筋選択性を備えた新しい非熱的アブレーションモダリティです。 しかし、隣接する神経構造の刺激と一過性の機能不全は依然として重要なオフターゲット効果です。 目的: 単一二相性エレクトロポレーション パルスに曝露された横隔神経と迷走神経の興奮、伝導抑制、回復に対するパルス パラメーターの影響を定義すること。 方法: 4 チャンネルの複合活動電位 (CAP) 記録を可能にする多電極チャンバーを使用して、生体外のブタの横隔神経と迷走神経を研究しました。 パルス振幅、パルス幅 (0.5 ～ 10 μs)、および相間遅延 (0.5 ～ 1000 μs) を系統的に変化させました。 刺激閾値と伝導抑制が定量化され、経時的に回復が評価されました。 横隔神経のインシリコモデルは、電場分布を推定し、機構の解釈をサポートするために開発されました。 結果: パルス幅と相間遅延が減少すると、刺激閾値が増加しました。 無髄線維は有髄線維よりも 6.8 ～ 8.3 倍高い電圧を必要としました。 伝導抑制はパルスパラメータに強く依存しており、パルス幅が長く、振幅が大きいほど伝導抑制が大きくなります。 高振幅パルスは完全ではあるが可逆的な伝導抑制を引き起こし、CAP の回復は 30 分以内に 80% を超えました。 モデリングでは、電極付近の電場勾配の上昇が示され、神経周膜内の特に高い電場の大きさが予測され、この構造がパルス送達の初期段階で影響を受ける可能性があることが示唆されました。 結論: 単一の PFA パルスは、パラメーター依存的に、分離されたブタの横隔神経と迷走神経において神経興奮と可逆的な伝導抑制の両方を誘発しました。 これらの発見は、PFA 関連の神経効果に対する機構的な洞察を提供し、近くの自律神経の刺激が徐脈や冠状動脈けいれんなどの臨床観察に潜在的に寄与する可能性があることを示唆しています。 定量的な変換には、臨床的に代表的なカテーテルの形状と完全なパルス列が必要です。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、高い心筋選択性を備えた新しい非熱的アブレーションモダリティです。 しかし、隣接する神経構造の刺激と一過性の機能不全は依然として重要なオフターゲット効果です。 目的: 単一二相性エレクトロポレーション パルスに曝露された横隔神経と迷走神経の興奮、伝導抑制、回復に対するパルス パラメーターの影響を定義すること。 方法: 4 チャンネルの複合活動電位 (CAP) 記録を可能にする多電極チャンバーを使用して、生体外のブタの横隔神経と迷走神経を研究しました。 パルス振幅、パルス幅 (0.5 ～ 10 μs)、および相間遅延 (0.5 ～ 1000 μs) を系統的に変化させました。 刺激閾値と伝導抑制が定量化され、経時的に回復が評価されました。 横隔神経のインシリコモデルは、電場分布を推定し、機構の解釈をサポートするために開発されました。 結果: パルス幅と相間遅延が減少すると、刺激閾値が増加しました。 無髄線維は有髄線維よりも 6.8 ～ 8.3 倍高い電圧を必要としました。 伝導抑制はパルスパラメータに強く依存しており、パルス幅が長く、振幅が大きいほど伝導抑制が大きくなります。 高振幅パルスは完全ではあるが可逆的な伝導抑制を引き起こし、CAP の回復は 30 分以内に 80% を超えました。 モデリングでは、電極付近の電場勾配の上昇が示され、神経周膜内の特に高い電場の大きさが予測され、この構造がパルス送達の初期段階で影響を受ける可能性があることが示唆されました。 結論: 単一の PFA パルスは、パラメーター依存的に、摘出されたブタの横隔神経と迷走神経において神経興奮と可逆的な伝導抑制の両方を誘発しました。 これらの発見は、PFA 関連の神経効果に対する機構的な洞察を提供し、近くの自律神経の刺激が徐脈や冠状動脈けいれんなどの臨床観察に潜在的に寄与する可能性があることを示唆しています。 定量的な変換には、臨床的に代表的なカテーテルの形状と完全なパルス列が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3145,7 +3145,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42759858/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.55] 欧州の植込み型除細動器装着者における心室不整脈の性別特有の傾向
+    <t xml:space="preserve">📄 [No.55] ヨーロッパの植込み型除細動器装着者における心室不整脈の性別特有の傾向
 (Sex-specific trends in ventricular arrhythmias among European implantable cardioverter-defibrillator recipients.)</t>
   </si>
   <si>
@@ -3171,7 +3171,7 @@
     <t>10.1016/j.hrthm.2026.08.046 doi</t>
   </si>
   <si>
-    <t>メディケア アドバンテージ (MA) および民間保険会社によって課された事前承認 (PA) 要件は、ガイドラインに基づく心臓電気生理学 (EP) ケアに対する組織的な障壁となり、患者に測定可能な損害を与え、医師と関連専門家に多大な管理上の負担を与え、医療格差を拡大させています。 この論文では、MA キャピテーション モデルの財務アーキテクチャと、それが否認に対して生み出す構造的インセンティブを検証し、サードパーティの否認組織、人工知能ベースのアルゴリズム、不透明な適用基準など、否認システムの根本原因を特徴づけます。監察総監室および上院常設調査小委員会からの連邦監督の結果をレビューし、心房細動のカテーテルアブレーション、植込み型除細動器治療、左心耳閉塞、および除細動を伴う心臓再同期療法に対する処置特有の拒否パターンを分析します。 連邦監査データは、却下された PA 申請のかなりの部分がメディケア独自の適用基準を満たしており、上訴された却下の大部分が覆されたものの、不当な却下の大部分は争われていないことを証明しています。 臨床転帰データにより、PA の遅延が EP 処置カテゴリー全体にわたって直接的な臨床結果をもたらすことが確認されています。 2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられています。</t>
+    <t>メディケア アドバンテージ (MA) および民間保険会社によって課された事前承認 (PA) 要件は、ガイドラインに基づく心臓電気生理学 (EP) ケアに対する組織的な障壁となり、患者に測定可能な損害を与え、医師と関連専門家に多大な管理上の負担を与え、医療格差を拡大させています。 この論文では、MA キャピテーション モデルの財務アーキテクチャと、それが否認に対して生み出す構造的インセンティブを検証し、サードパーティの否認組織、人工知能ベースのアルゴリズム、不透明な適用基準など、否認システムの根本原因を特徴づけます。監察総監室および上院常設調査小委員会からの連邦監督の結果をレビューし、心房細動のカテーテルアブレーション、植込み型除細動器治療、左心耳閉塞、および除細動を伴う心臓再同期療法に対する処置特有の拒否パターンを分析します。 連邦監査データは、却下された PA 申請のかなりの部分がメディケア独自の適用基準を満たしており、上訴された却下の大部分が覆されたものの、不当な却下の大部分は争われていないことを証明しています。 臨床転帰データにより、PA の遅延が EP 処置カテゴリー全体にわたって直接的な臨床結果をもたらすことが確認されています。 2023 年から 2026 年までのメディケアおよびメディケイド サービス センターの規則制定と保留中の議会の行動にまたがる規制および立法の状況が検討され、この文書は、上訴戦略、制度的擁護、および医師レベルの関与のための構造化された枠組みで締めくくられています。</t>
   </si>
   <si>
     <t xml:space="preserve">Prior authorization (PA) requirements imposed by Medicare Advantage (MA) and commercial insurers have evolved into a systematic barrier to guideline-indicated cardiac electrophysiology (EP) care, producing measurable patient harm, substantial administrative burden on physicians and allied professionals, and widening health care disparities. This paper examines the financial architecture of the MA capitation model and the structural incentives it creates for denial, characterizes the root causes of the denial system, including third-party denial organizations, artificial intelligence-based algorithms, and opaque coverage criteria; reviews federal oversight 
@@ -3192,7 +3192,7 @@
     <t>10.1016/j.hrthm.2026.09.020 doi</t>
   </si>
   <si>
-    <t>アンデルセン・タウィル症候群 (ATS) は、心室性不整脈、周期性麻痺、および異形性の特徴を特徴とする、まれな常染色体優性多系統疾患です。 しかし、顕著な表現型の不均一性が観察され、診断が大幅に遅れる原因となっています。 ATS は、内向き整流カリウム チャネル Kir2.1 の α サブユニットをコードする KCNJ2 の機能喪失変異によって最も一般的に引き起こされ、I 電流の障害を引き起こします。 I 障害は終末再分極と脱分極の動態を不安定にし、顕著な U 波、心室異所性、および複雑な心室不整脈を促進します。 限られた証拠と変化する治療反応のため、管理は依然として困難です。 β遮断薬とフレカイニドは一般的に使用されますが、植込み型除細動器は高リスクの場合に使用されます。 周期性麻痺のある特定の患者では、カリウムの補給とアセタゾラミドを考慮する必要があります。 浸透率が不完全で、検証されたリスク階層化ツールが存在しないことを考慮すると、慎重な学際的な評価と個別の管理が不可欠です。</t>
+    <t>アンデルセン・タウィル症候群 (ATS) は、心室性不整脈、周期性麻痺、および異形性の特徴を特徴とする、まれな常染色体優性多系統疾患です。 しかし、顕著な表現型の不均一性が観察され、診断が大幅に遅れる原因となっています。 ATS は、内向き整流カリウム チャネル Kir2.1 の α サブユニットをコードする KCNJ2 の機能喪失変異によって最も一般的に引き起こされ、I 電流の障害を引き起こします。 I 障害は終末再分極と脱分極の動態を不安定にし、顕著な U 波、心室異所性、複雑な心室不整脈を促進します。 限られた証拠と変化する治療反応のため、管理は依然として困難です。 β遮断薬とフレカイニドは一般的に使用されますが、植込み型除細動器は高リスクの場合に使用されます。 周期性麻痺のある特定の患者では、カリウムの補給とアセタゾラミドを考慮する必要があります。 浸透率が不完全で、検証されたリスク階層化ツールが存在しないことを考慮すると、慎重な学際的な評価と個別の管理が不可欠です。</t>
   </si>
   <si>
     <t>Andersen-Tawil syndrome (ATS) is a rare autosomal dominant multisystem disorder characterised by ventricular arrhythmias, periodic paralysis, and dysmorphic features. However, marked phenotypic heterogeneity is observed, contributing to significant diagnostic delays. ATS is most commonly caused by loss-of-function variants in KCNJ2, which encodes the α-subunit of the inward rectifier potassium channel Kir2.1, resulting in impaired I currents. Impaired I destabilises terminal repolarisation and depolarisation kinetics, promoting prominent U waves, ventricular ectopy, and complex ventricular arrhythmias. Management remains challenging due to limited evidence and variable treatment response. β-blockers and flecainide are commonly used while implantable cardioverter-defibrillators are reserved for high-risk cases. Potassium supplementation and acetazolamide should be considered in selected patients with periodic paralysis. Given incomplete penetrance and absence of validated risk stratification tools, careful multidisciplinary evaluation and individualised management are essential.</t>
@@ -3211,7 +3211,7 @@
     <t>10.1016/j.hrthm.2026.09.017 doi</t>
   </si>
   <si>
-    <t>背景: 心外膜脂肪組織 (EAT) は、心房リモデリングを誘発するという仮説が立てられています。 しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません。 心房線維症が心外膜から心内膜に進行する可能性があることを考慮すると、単極電圧は初期リモデリングのより感度の高いマーカーである可能性があります。 目的: 早期心房リモデリング患者における左心房 (LA) EAT、局所単極および双極電圧、アブレーション後の不整脈再発との関係を評価すること。 方法: 連続した患者はインデックス AF アブレーションの前に高解像度 LA 電気解剖学的マッピングを受けました。 双極性低電圧（≤0.5mV）領域が5％以上の患者は除外された。 LAおよび局所的な単極性瘢痕は、健康な対照コホートにおける5パーセンタイルのカットポイントによって定義されました。 EATは術前のCTでセグメント化されました。 各電圧点について、3 ボクセル内の EAT の存在が決定されました。 多変数モデリングを使用して、非瘢痕点における電圧の予測因子を特定しました。 心房性不整脈の再発は12か月の追跡調査で評価されました。 結果: 50 人の患者 (56±11 歳、78% が発作性) が含まれました。 単極電圧のカットポイントにより、双極電圧が保存されていたポイントのさらに 9.2% が傷跡として特定されました。 EAT の存在は、局所双極性電圧の有意な予測因子でした (p=0.010)。 この EAT と電圧の関係は、EAT の存在によって単極 (p=0.027) と双極 (p=0.007) の両方の電圧が予測される後壁で最も顕著でした。 後部:LA EAT 比は、発作性 AF 患者における心房性不整脈再発の唯一の独立した予測因子でした。 結論: EAT は、心房基質の発達、特に後壁において初期の、おそらく原因となる役割を果たしています。 単極電圧マッピングは、初期の心房基質を特定する際に付加価値を提供する可能性があります。</t>
+    <t>背景: 心外膜脂肪組織 (EAT) は、心房リモデリングを誘発するという仮説が立てられています。 しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません。 心房線維症が心外膜から心内膜に進行する可能性があることを考慮すると、単極電圧は初期リモデリングのより感度の高いマーカーである可能性があります。 目的: 早期心房リモデリング患者における左心房 (LA) EAT、局所単極および双極電圧、アブレーション後の不整脈再発との関係を評価すること。 方法: 連続した患者はインデックス AF アブレーションの前に高解像度 LA 電気解剖学的マッピングを受けました。 双極性低電圧（≤0.5mV）領域が5％以上の患者は除外された。 LAおよび局所的な単極性瘢痕は、健康な対照コホートにおける5パーセンタイルのカットポイントによって定義されました。 EATは術前のCTでセグメント化されました。 各電圧点について、3 ボクセル内の EAT の存在が決定されました。 多変数モデリングを使用して、非瘢痕点における電圧の予測因子を特定しました。 心房性不整脈の再発は12か月の追跡調査で評価されました。 結果: 50 人の患者 (56±11 歳、78% が発作性) が含まれました。 単極電圧のカットポイントにより、双極電圧が保存されていたポイントのさらに 9.2% が傷跡として特定されました。 EAT の存在は、局所双極性電圧の有意な予測因子でした (p=0.010)。 この EAT と電圧の関係は、EAT の存在によって単極性 (p=0.027) と双極性 (p=0.007) の両方の電圧が予測される後壁で最も顕著でした。 後部:LA EAT 比は、発作性 AF 患者における心房性不整脈再発の唯一の独立した予測因子でした。 結論: EAT は、心房基質の発達、特に後壁において初期の原因となる可能性のある役割を果たしています。 単極電圧マッピングは、初期の心房基質を特定する際に付加価値を提供する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3278,7 +3278,7 @@
     <t>10.1007/s10840-026-02436-1 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす新しい心臓アブレーション方法です。 熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を備えているため、周囲の構造への巻き添え損傷のリスクが軽減されます。 PulseSelect PFA システム (米国ミネソタ州ミネアポリスの Medtronic Inc.) は、心房細動アブレーションに使用される中央ガイドワイヤーを備えた 9 電極円形アブレーション カテーテルです。 現時点では、このカテーテルのワークフローやベスト プラクティスについては合意がありません。 その特徴的なオーバー・ザ・ワイヤー設計と前方に傾斜した柔軟な電極アレイは、かなりの処置上の多用途性を提供し、我々の意見では、選択的な病変の送達、溶血の減少、冠状動脈の血管けいれんの傾向の低下という点で利点を提供する可能性があります。 ただし、これらの潜在的な利点を実現するには、カテーテルの形状、組織接触の原理、および操作技術を完全に理解する必要があります。 英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外にもカテーテルの使用を安全に拡大するのに役立つ可能性のある実践的な概念、X線透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てています。</t>
+    <t>パルスフィールドアブレーション (PFA) は、電場によって心筋細胞の細胞膜に微細な孔を形成し、エレクトロポレーションのプロセスを通じて細胞死をもたらす心臓アブレーションの新しい方法です。 熱技術とは異なり、PFA は心筋細胞に対して優先的な選択性を持っているため、周囲の構造への巻き添え損傷のリスクが軽減されます。 PulseSelect PFA システム (米国ミネソタ州ミネアポリスの Medtronic Inc.) は、心房細動アブレーションに使用される中央ガイドワイヤーを備えた 9 電極円形アブレーション カテーテルです。 現時点では、このカテーテルのワークフローやベスト プラクティスについては合意がありません。 その特徴的なオーバー・ザ・ワイヤー設計と前方に傾斜した柔軟な電極アレイは、かなりの処置上の多用途性を提供し、我々の意見では、選択的な病変の送達、溶血の減少、および冠状動脈の血管けいれんの傾向の低下という点で利点を提供する可能性があります。 ただし、これらの潜在的な利点を実現するには、カテーテルの形状、組織接触の原理、および操作技術を完全に理解する必要があります。 英国とスペインのセンターでの実際の経験を紹介し、学習曲線の短縮、病変送達の最適化、肺静脈隔離以外のカテーテルの使用の安全な拡大に役立つ可能性のある実践的な概念、透視および電気解剖学的マッピング（EAM）戦略、および手順技術に焦点を当てます。</t>
   </si>
   <si>
     <t>Pulsed field ablation (PFA) is a novel method of cardiac ablation in which electrical fields create microscopic pores in cardiomyocyte cell membranes, resulting in cell death through a process of electroporation. Unlike thermal technologies, PFA has preferential cardiomyocyte selectivity, thereby reducing the risk of collateral damage to surrounding structures. The PulseSelect PFA system (Medtronic Inc., Minneapolis, MN, USA) is a 9-electrode circular ablation catheter with a central guidewire used for atrial fibrillation ablation. Currently, there is no consensus on workflow or best practice for this catheter. Its distinctive over-the-wire design and forward-tilted flexible electrode array provide considerable procedural versatility and, in our opinion, may offer advantages in terms of selective lesion delivery, reduced haemolysis, and a lower propensity for coronary vasospasm. Realising these potential benefits, however, requires a thorough understanding of catheter geometry, tissue-contact principles, and manipulation techniques. We present our real-world experience from centres in the UK and Spain, highlighting practical concepts, fluoroscopic and electro-anatomic mapping (EAM) strategies, as well as procedural techniques that may help shorten the learning curve, optimise lesion delivery, and safely expand the use of the catheter beyond pulmonary vein isolation.</t>
@@ -3297,7 +3297,7 @@
     <t>10.1111/jce.70498 doi</t>
   </si>
   <si>
-    <t>背景: 高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題です。 パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではありません。 ここでは、難治性 VT 患者に対する FARAPOINT 焦点 PFA の米国での最初の経験について説明します。 方法と結果：我々は、2025年7月から2026年5月までに、単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。 すべての患者は薬剤抵抗性の持続性単形性 VT を患っていた。 年齢中央値は77歳で、虚血性心筋症と非虚血性心筋症が混在していた。 10 人中 6 人は、以前に少なくとも 1 回カテーテルアブレーションに失敗したことがありました。 急性非誘発性は、正式なアブレーション後刺激試験を受けた9人の患者全員で達成されました。 処置上の合併症は発生しませんでした。 中央値95.5日の追跡期間にわたって、10人の患者のうち4人で持続性VTが再発した。 繰り返しアブレーションを受けた患者も、機械的循環補助を必要とした患者も、死亡した患者もいませんでした。 結論：この米国での最初の実験では、難治性心室頻拍と、困難な基質を含む以前のアブレーション失敗を伴う高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に有効でした。 これらの観察を拡大するには、前向き多施設研究が必要です。</t>
+    <t>背景: 高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題です。 パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではありません。 ここでは、難治性 VT 患者に対する FARAPOINT 焦点 PFA の米国での最初の経験について説明します。 方法と結果：我々は、2025年7月から2026年5月までに、単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。 すべての患者は薬剤抵抗性の持続性単形性 VT を患っていた。 年齢中央値は77歳で、虚血性心筋症と非虚血性心筋症が混在していた。 10 人中 6 人は、以前に少なくとも 1 回カテーテルアブレーションに失敗したことがありました。 急性非誘発性は、正式なアブレーション後刺激試験を受けた9人の患者全員で達成されました。 処置上の合併症は発生しませんでした。 中央値95.5日の追跡期間中、10人の患者のうち4人で持続性VTが再発した。 繰り返しアブレーションを受けた患者も、機械的循環補助を必要とした患者も、死亡した患者もいませんでした。 結論：この米国での最初の実験では、難治性心室頻拍と、困難な基質を含む以前のアブレーション失敗を伴う高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に有効でした。 これらの観察を拡大するには、前向き多施設研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3321,7 +3321,7 @@
     <t>10.1111/jce.70491 doi</t>
   </si>
   <si>
-    <t>はじめに: 電位図のピークツーピーク電圧は、心房壁の構造とマッピング構成によって異なります。 コンピューター断層撮影法から得られた心房壁の厚さ、心筋内脂肪、心筋の筋肉の厚さと、全極、双極、および単極マッピングで得られた心電図電圧との関係を評価しました。 方法：心房細動または非定型心房粗動アブレーション中に左心房マッピングを受けた連続患者を遡及的に含めた。 術前の造影 CT を ADAS 3D で処理して、左心房壁の厚さと心筋内脂肪浸潤を定量化し、そこから心筋の筋肉の厚さを導き出しました。 高密度の電気解剖学的マップが CT と空間的に位置合わせされました。 解剖学的パラメーターとピークツーピーク電圧の間の関連性を、リズムの安定性によって階層化して評価しました。 結果: 20 人の患者が含まれました。 安定したリズムでは、左心房壁の厚さはすべての構成で電圧と正の相関があり、単極 (β = 0.38) と全極 (β = 0.23) で最も強くなります。 双極性マッピング (β = 0.13) (BP-UP p &lt; 0.0001; BP-OT p &lt; 0.01)。 心筋内脂肪は、双極性（β = -0.14）および単極性（β = -0.01; p ≤ 0.02）と比較して、全極性（β = -0.39）と最も強い逆相関を示しました。 脂肪を除いた後、筋肉の厚さはOT (β = 0.30)およびUP (β = 0.30)と正の相関があり、BPを上回りました(β = 0.14; p &lt; 0.0001)。 不安定なリズムでは、関連性は減弱されましたが、OT は脂肪 (β = -0.20) と筋肉の厚さ (β = 0.11) に対して最も反応し続けました (両方とも p &lt; 0.01)。 結論: 心筋の筋肉の厚さは局所心房電圧の主な決定要因ですが、心筋内の脂肪は電圧の減衰に寄与します。 OT は、特に調律が不安定な場合に、心房壁組成の最も一貫した評価を提供します。</t>
+    <t>はじめに: 電位図のピークツーピーク電圧は、心房壁の構造とマッピング構成によって異なります。 コンピューター断層撮影法から得られた心房壁の厚さ、心筋内脂肪、心筋の筋肉の厚さと、全極、双極、および単極マッピングで得られた心電図電圧との関係を評価しました。 方法：心房細動または非定型心房粗動アブレーション中に左心房マッピングを受けた連続患者を遡及的に含めた。 術前の造影 CT を ADAS 3D で処理して、左心房壁の厚さと心筋内脂肪浸潤を定量化し、そこから心筋の筋肉の厚さを導き出しました。 高密度の電気解剖学的マップが CT と空間的に同時登録されました。 解剖学的パラメーターとピークツーピーク電圧の間の関連性を、リズムの安定性によって階層化して評価しました。 結果: 20 人の患者が含まれました。 安定したリズムでは、左心房壁の厚さはすべての構成で電圧と正の相関があり、単極 (β = 0.38) と全極 (β = 0.23) で最も強くなります。 双極性マッピング (β = 0.13) (BP-UP p &lt; 0.0001; BP-OT p &lt; 0.01)。 心筋内脂肪は、双極性（β = -0.14）および単極性（β = -0.01; p ≤ 0.02）と比較して、全極性（β = -0.39）と最も強い逆相関を示しました。 脂肪を除いた後、筋肉の厚さはOT (β = 0.30)およびUP (β = 0.30)と正の相関があり、BPを上回りました(β = 0.14; p &lt; 0.0001)。 不安定なリズムでは、関連性は減弱されましたが、OT は脂肪 (β = -0.20) と筋肉の厚さ (β = 0.11) に対して最も反応し続けました (両方とも p &lt; 0.01)。 結論: 心筋の筋肉の厚さは局所心房電圧の主な決定要因ですが、心筋内の脂肪は電圧の減衰に寄与します。 OT は、特に調律が不安定な場合に、心房壁組成の最も一貫した評価を提供します。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3347,7 +3347,7 @@
     <t>10.1111/jce.70492 doi</t>
   </si>
   <si>
-    <t>背景: 医原性空気同伴は、パルスフィールドアブレーション (PFA) において予防可能な塞栓の危険性です。 大口径 PFA シースを介したカテーテル挿入のマッピングは脆弱なステップである可能性がありますが、カテーテルの形状と液体で密封された挿入の役割は不明です。 方法と結果: ex vivo 生理食塩水タンク モデルでは、生理食塩水注入のみ、連続手動吸引、またはカスタム アダプター シンクによる液体密封挿入を使用して、ORION ミニバスケットと SPIRAL 円形マッピング カテーテルが FARADRIVE 操縦可能シースを通して挿入されました。 主要評価項目は、10 回の挿入の各試行後に遠位で回収された肉眼的な空気でした。試験は分析の単位であり、0.2 mL が定量的に報告可能な最小量でした。 60 件の試験 (600 件の挿入) において、緩和戦略は空気連行に大きな影響を与えました (Kruskal-Wallis p &lt; 0.001)。 生理食塩水注入のみでは、ORION は SPIRAL よりも多くの空気を生成しました (23.86 ± 3.63 vs. 10 回の挿入あたり 7.20 ± 2.09 mL。 2.39 vs. 1 回の挿入につき 0.72 mL。調整済み p &lt; 0.001)。 手動吸引により、エントレインメントは 10 挿入あたり 3.96 ± 1.01 および 1.02 ± 0.45 mL (挿入あたり 0.40 mL および 0.10 mL) に減少しましたが、残留空気は残りました。 液体封入挿入では、どの試験でも視覚的に検出または定量的に測定できる肉眼で見える空気は観察されませんでした。 結論: 空気の同伴は、マッピングカテーテルの形状と緩和戦略によって異なります。 時間を決めて手動で吸引すると、測定可能な空気は大幅に減少しましたが、ゼロにはなりませんでした。 液体密封挿入は、この ex vivo モデル内で測定可能な肉眼で見える空気を伴わず、生理学的圧力条件下および臨床 PFA ワークフローでのさらなる評価が正当化されました。</t>
+    <t>背景: 医原性空気同伴は、パルスフィールドアブレーション (PFA) において予防可能な塞栓の危険性です。 大口径 PFA シースを介したカテーテル挿入のマッピングは脆弱なステップである可能性がありますが、カテーテルの形状と液体で密封された挿入の役割は不明です。 方法と結果: ex vivo 生理食塩水タンク モデルでは、生理食塩水注入のみ、連続手動吸引、またはカスタム アダプター シンクを使用した液体密封挿入を使用して、ORION ミニバスケットと SPIRAL 円形マッピング カテーテルを FARADRIVE 操縦可能シースを通して挿入しました。 主要評価項目は、10 回の挿入の各試行後に遠位で回収された肉眼的な空気でした。試験は分析の単位であり、0.2 mL が定量的に報告可能な最小量でした。 60 件の試験 (600 件の挿入) において、緩和戦略は空気連行に大きな影響を与えました (Kruskal-Wallis p &lt; 0.001)。 生理食塩水注入のみでは、ORION は SPIRAL よりも多くの空気を生成しました (23.86 ± 3.63 vs. 10 回の挿入あたり 7.20 ± 2.09 mL。 2.39 vs. 1 回の挿入につき 0.72 mL。調整済み p &lt; 0.001)。 手動吸引により、エントレインメントは 10 挿入あたり 3.96 ± 1.01 および 1.02 ± 0.45 mL (挿入あたり 0.40 および 0.10 mL) に減少しましたが、残留空気は残りました。 液体封入挿入では、どの試験でも視覚的に検出可能または定量的に測定可能な肉眼で見える空気は観察されませんでした。 結論: 空気の同伴は、マッピングカテーテルの形状と緩和戦略によって異なります。 時間を決めて手動で吸引すると、測定可能な空気が大幅に減少しましたが、ゼロにはなりませんでした。 液体密封挿入は、この ex vivo モデル内で測定可能な肉眼で見える空気を伴わず、生理学的圧力条件下および臨床 PFA ワークフローでのさらなる評価が正当化されました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3371,7 +3371,7 @@
     <t>10.1007/s10840-026-02422-7 doi</t>
   </si>
   <si>
-    <t>はじめに: カテーテル アブレーションにおける持続的な結果には、貫壁性病変を達成することが重要です。 心電図振幅の減少とペーシング閾値の変化は有用なパラメーターとして報告されていますが、最適な電極構成とカットオフ値は不明のままです。 この前臨床研究では、QDOT MICRO カテーテルを使用した経壁性の予測における従来の微小電極構成の有効性を評価しました。 方法: 14 頭のブタに高周波アブレーションを実施し、131 個の心房病変を作成しました。 ペーシング閾値と電位図の振幅は、従来の双極、微小電極双極、および単極の 3 つの構成を使用してアブレーションの前後で測定されました。 病変の貫壁性は組織学的に決定された。 予測精度を評価するために、受信機の動作特性分析が実施されました。 結果: すべての構成の中で、従来のバイポーラ (A1-A2) が最も高い予測値を示しました。 アブレーション後の双極性振幅は、経壁性病変では低くなり (AUC 0.777、0.86mV)、振幅減少は大きくなりました (64.4% 対 64.4%)。 40.5%, AUC 0.682).  ペーシング閾値はアブレーション後に大幅に増加し、貫壁性病変ではより高くなりました。 A1-A2 構成は、貫壁性の予測精度が最も高かった (AUC 0.880、カットオフ 3.4 V)。 微小電極は一貫性のないパターンを示し、最適な構成が選択された場合でも、従来の双極測定よりも精度が低いままでした。 さらに、R 波 (双極性) および S 波 (単極性) の消失を含む形態学的変化は、限られた的中率を示しました (それぞれ AUC ≤ 0.77 および ≤ 0.56)。 結論: 従来の双極電極は、電位図の振幅とペーシング閾値による経壁性の評価において、微小電極構成よりも優れた性能を発揮しました。 QDOT-MICRO カテーテルを使用したチップツーリング双極ペーシングは、3.4 V を最適なしきい値として、心房病変の貫壁性を最も効果的に評価します。</t>
+    <t>はじめに: カテーテル アブレーションにおける持続的な結果には、貫壁性病変を達成することが重要です。 心電図振幅の減少とペーシング閾値の変化は有用なパラメーターとして報告されていますが、最適な電極構成とカットオフ値は不明のままです。 この前臨床研究では、QDOT MICRO カテーテルを使用した経壁性の予測における従来の微小電極構成の有効性を評価しました。 方法: 14 頭のブタに高周波アブレーションを実施し、131 個の心房病変を作成しました。 ペーシング閾値と電位図の振幅は、従来の双極、微小電極双極、単極の 3 つの構成を使用してアブレーションの前後で測定されました。 病変の貫壁性は組織学的に決定された。 予測精度を評価するために、受信機の動作特性分析が実施されました。 結果: すべての構成の中で、従来のバイポーラ (A1-A2) が最も高い予測値を示しました。 アブレーション後の双極性振幅は経壁性病変では低くなり (AUC 0.777、0.86mV)、振幅減少は大きくなりました (64.4% 対 64.4%)。 40.5%, AUC 0.682).  ペーシング閾値はアブレーション後に大幅に増加し、貫壁性病変ではより高くなりました。 A1-A2 構成は、貫壁性の予測精度が最も高かった (AUC 0.880、カットオフ 3.4 V)。 微小電極は一貫性のないパターンを示し、最適な構成が選択された場合でも、従来の双極測定よりも精度が低いままでした。 さらに、R 波 (双極性) および S 波 (単極性) の消失を含む形態学的変化は、限られた的中率を示しました (それぞれ AUC ≤ 0.77 および ≤ 0.56)。 結論: 従来の双極電極は、電位図の振幅とペーシング閾値による経壁性の評価において、微小電極構成よりも優れた性能を発揮しました。 QDOT-MICRO カテーテルを使用したチップツーリング双極ペーシングは、3.4 V を最適なしきい値として、心房病変の貫壁性を最も効果的に評価します。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3397,7 +3397,7 @@
     <t>10.1111/jce.70489 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションのための有望なエネルギー源として浮上しています。 この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。 方法: AF を患う連続オールカマー患者は、深い鎮静下でバルーンインバスケット PFA カテーテルを使用して PFA を受けました。 Pear ワークフローは、2 段階の PVI プロトコルで構成されていました。(1) 最初の PV 血管造影によってガイドされ、回転展開によって PV 閉塞と病変の重なりを確認する 4 つの前庭部 PFA アプリケーション、続いて (2) PV スリーブをターゲットとした 2 つの遠位洋ナシ型バルーン アプリケーション。 インピーダンスベースの接触評価を備えた三次元電気解剖学的マッピングが利用されました。 手順パラメータ、急性有効性、および安全性が分析されました。 結果：50人の患者（62％が発作性AF、42％が女性、平均年齢68±10歳）が登録された。 すべての PV が正常に分離されました。 処置時間と蛍光透視検査時間の中央値はそれぞれ50分（IQR 41-50）と7.2分（IQR 5.8-11.4）で、研究期間を通じて大きな変化はなかった（50対IQR）。 患者 1 ～ 25 および 26 ～ 50 についてはそれぞれ 47 分、p = 0.26)。 追加のアブレーションが 4 人の患者で行われ、同時に左心耳閉鎖が 3 人で行われました。 重大または軽度の合併症は発生しませんでした。 一過性の横隔神経気絶が 2 人の患者で観察され、処置が完了する前に解消されました。 結論：ペアの 2 ステップ戦略は、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI を可能にし、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供します。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションの有望なエネルギー源として浮上しています。 この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。 方法: AF を患う連続オールカマー患者は、深い鎮静下でバルーンインバスケット PFA カテーテルを使用して PFA を受けました。 Pear ワークフローは、2 段階の PVI プロトコルで構成されていました。(1) 最初の PV 血管造影によってガイドされ、回転展開によって PV 閉塞と病変の重なりを確認する 4 つの前庭部 PFA アプリケーション、続いて (2) PV スリーブをターゲットとした 2 つの遠位洋ナシ型バルーン アプリケーション。 インピーダンスベースの接触評価を備えた三次元電気解剖学的マッピングが利用されました。 手順パラメータ、急性有効性、および安全性が分析されました。 結果: 50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録されました。 すべての PV が正常に分離されました。 処置時間と蛍光透視検査時間の中央値はそれぞれ50分（IQR 41-50）と7.2分（IQR 5.8-11.4）で、研究期間を通じて大きな変化はなかった（50対IQR）。 患者 1 ～ 25 および 26 ～ 50 についてはそれぞれ 47 分、p = 0.26)。 追加のアブレーションが 4 人の患者に実行され、同時に左心耳閉鎖が 3 人に実行されました。 重篤な合併症も軽微な合併症も発生しませんでした。 一過性の横隔神経気絶が 2 人の患者で観察され、処置が完了する前に解消されました。 結論：Pear の 2 ステップ戦略により、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI が可能になります。このカテーテルは、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3423,7 +3423,7 @@
     <t>10.1111/jce.70469 doi</t>
   </si>
   <si>
-    <t>はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる可能性があります。 われわれは、失神、動悸、原因性脳卒中、またはブルガダ症候群のために移植された患者間で、ILRで検出された不整脈の時間依存的な診断率と臨床的関連性が異な​​るかどうかを評価した。 目的：この研究は、臨床適応症全体にわたるILRの時間依存的な診断率を定義し、早期診断と後期診断で臨床管理への影響が異なるかどうかを評価することを目的としました。 方法と結果：イタリアの5つのセンターで原因不明の失神、動悸、原因不明の脳卒中、またはブルガダ症候群でILR移植を受けている連続患者1734人を遡及的に分析した。 対象となる診断は、インプラントの適応症に応じて定義されました。失神に対する一時停止、動悸に対する上室性頻拍または心房細動、原因性脳卒中に対する心房細動、およびブルガダ症候群に対する心室頻拍または一時停止です。 追跡期間の中央値は34か月でした。 最大限に選択されたランク統計により、早期診断と後期診断を分ける全体的な閾値は 26 か月であることが特定されましたが、適応症別の最適な診断期間は、失神では 14 か月、動悸では 13 か月、原因性脳卒中では 16 か月、ブルガダ症候群では 55 か月でした。 失神と動悸では、ほとんどの実用的な診断は早期に行われ、診断効率は 26 か月後に著しく低下し、後期の所見は指標の提示とあまり明確に関連していないことがよくありました。 原因性脳卒中では、早期に心房細動が検出されることが最も多いが、その後の抗血栓管理の変更につながる可能性があり、長期モニタリングに対する個別の「グレーゾーン」アプローチを裏付けるものとなっている。 対照的に、ブルガダ症候群では、長期間の追跡調査を通じて持続的な診断率が示され、遅発性心室不整脈または休止は、植込み型除細動器の植込みやデバイスの種類の選択など、予後および治療上の重要な影響を残しました。 結論: ILR モニタリングの価値は、時間と症状に大きく依存します。 早期の追跡調査で明らかになっていない場合、長期間の日常的なモニタリングや再移植は、失神や動悸の増分価値が限られているように思われるが、ブルガダ症候群では長期にわたる監視が引き続き正当化される可能性があり、原因性脳卒中後には個別化されるべきである。 これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしています。</t>
+    <t>はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる場合があります。 われわれは、失神、動悸、原因性脳卒中、またはブルガダ症候群のために移植された患者間で、ILRで検出された不整脈の時間依存的な診断率と臨床的関連性が異な​​るかどうかを評価した。 目的：この研究は、臨床適応症全体にわたるILRの時間依存的な診断率を定義し、早期診断と後期診断で臨床管理への影響が異なるかどうかを評価することを目的としました。 方法と結果：我々は、イタリアの5つのセンターで原因不明の失神、動悸、原因不明の脳卒中、またはブルガダ症候群でILR移植を受けている連続患者1734人を遡及的に分析した。 対象となる診断は、インプラントの適応症に応じて定義されました。失神に対する一時停止、動悸に対する上室性頻拍または心房細動、原因性脳卒中に対する心房細動、およびブルガダ症候群に対する心室頻拍または一時停止です。 追跡期間の中央値は34か月でした。 最大限に選択されたランク統計により、初期診断と後期診断を分ける全体的な閾値は 26 か月であることが特定されました。一方、適応症別の最適な診断期間は、失神では 14 か月、動悸では 13 か月、原因性脳卒中では 16 か月、ブルガダ症候群では 55 か月でした。 失神と動悸では、ほとんどの実用的な診断は早期に行われ、診断効率は 26 か月後に著しく低下し、後期の所見は指標の提示とあまり明確に関連していないことがよくありました。 原因性脳卒中では、心房細動の検出は初期に最も頻繁に検出されましたが、その後の抗血栓管理の変更につながる可能性があり、長期モニタリングに対する個別の「グレーゾーン」アプローチを裏付けています。 対照的に、ブルガダ症候群では、長期間の追跡調査を通じて持続的な診断率が示され、遅発性心室性不整脈または休止は、植込み型除細動器の植込みやデバイスの種類の選択など、予後および治療に大きな影響を及ぼしました。 結論: ILR モニタリングの価値は、時間と症状に大きく依存します。 早期の追跡調査で明らかになっていない場合、失神や動悸に関しては、長期にわたる定期的なモニタリングや再移植の増加価値は限られていると思われるが、ブルガダ症候群では長期にわたる監視が依然として正当化される可能性があり、原因性脳卒中後には個別化されるべきである。 これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしています。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3449,7 +3449,7 @@
     <t>10.1016/j.hrthm.2026.08.056 doi</t>
   </si>
   <si>
-    <t>同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化します。 このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合したものです。 心房粗動（AFL）、特に大静脈洞峡（CTI）依存性のマクロリエントリーは、安定したOHTレシピエントにおける主な不整脈です。 アブレーション峡部は、自然の下大静脈ではなく縫合線によって解剖学的に再定義され、CA は CTI 依存性粗動に対して 90% を超える急性成功率を達成し、医学的管理のみよりも大幅な延命効果をもたらします (中央値 11.3 対 11.3)。 5.8年。 p = 0.026)。 心房細動（AF）は安定したレシピエントではまれであり、存在する場合は、ほとんどの場合、残存レシピエントの心房組織またはドナーとレシピエントの伝導橋から発生します。アブレーションには、ルーチンの肺静脈隔離ではなく、個別の電気解剖学的マッピングが必要です。 心房伝導（AAC）は不整脈を呈する患者の約 20 ～ 30% で発症し、平均発症は移植後 10.1 年です。 OHT に特有の処置上の考慮事項には、プロタミン過敏症のリスク、二重心房生理機能による調律の誤分類、抗凝固療法の複雑さ、薬物と免疫抑制剤の相互作用が含まれており、これらを総合すると、薬物療法よりもアブレーションの理論的根拠が強化されます。 CA は実行可能かつ効果的であり、適切に選択された OHT レシピエントの生存率の向上と関連しています。 この集団における証拠に基づく実践を推進するには、標準化された報告を備えた将来の多施設登録が必要です。</t>
+    <t>同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化します。 このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合しています。 心房粗動（AFL）、特に大静脈洞峡（CTI）依存性のマクロリエントリーは、安定したOHTレシピエントにおける主な不整脈です。 アブレーション峡部は、自然の下大静脈ではなく縫合線によって解剖学的に再定義され、CA は CTI 依存性粗動に対して 90% を超える急性成功率を達成し、医学的管理のみよりも大幅な延命効果をもたらします (中央値 11.3 対 11.3)。 5.8年。 p = 0.026)。 心房細動（AF）は安定したレシピエントではまれであり、存在する場合は、ほとんどの場合、残存レシピエントの心房組織またはドナーとレシピエントの伝導橋から発生します。アブレーションには、ルーチンの肺静脈隔離ではなく、個別の電気解剖学的マッピングが必要です。 心房伝導（AAC）は不整脈を呈する患者の約 20 ～ 30% で発症し、平均発症は移植後 10.1 年です。 OHT に特有の処置上の考慮事項には、プロタミン過敏症のリスク、二重心房生理機能による調律の誤分類、抗凝固療法の複雑さ、薬物と免疫抑制剤の相互作用が含まれており、これらを総合すると、薬物療法よりもアブレーションの理論的根拠が強化されます。 CA は実行可能かつ効果的であり、適切に選択された OHT レシピエントの生存率の向上と関連しています。 この集団における証拠に基づく実践を推進するには、標準化された報告を備えた将来の多施設登録が必要です。</t>
   </si>
   <si>
     <t>Orthotopic heart transplantation (OHT) creates a surgically altered electrophysiologic substrate defined by the suture-line scar, residual recipient atrial tissue, and autonomic denervation, that fundamentally alters the mechanisms, presentation, and management of atrial tachyarrhythmias. This narrative review synthesizes current evidence on the mechanisms, mapping strategies, procedural safety considerations, and outcomes of catheter ablation (CA) for atrial arrhythmias after OHT, based on a structured search of PubMed and Embase (1995-2025). Atrial flutter (AFL), particularly cavotricuspid isthmus (CTI)-dependent macro-reentry, is the dominant arrhythmia in stable OHT recipients. The ablation isthmus is anatomically redefined by suture lines rather than the native inferior vena cava, and CA achieves acute success rates exceeding 90% for CTI-dependent flutter, with a significant survival benefit over medical management alone (median 11.3 vs. 5.8 years; p = 0.026). Atrial fibrillation (AF) is uncommon in stable recipients and, when present, most often arises from residual recipient atrial tissue or donor-recipient conduction bridges; ablation requires individualized electroanatomic mapping rather than routine pulmonary vein isolation. Atrioatrial conduction (AAC) develops in approximately 20-30% of patients presenting with arrhythmias, with a mean onset of 10.1 years post-transplant. Procedural considerations unique to OHT include protamine hypersensitivity risk, rhythm misclassification due to dual atrial physiology, anticoagulation complexity, and drug-immunosuppressant interactions, which collectively strengthen the rationale for ablation over pharmacologic therapy. CA is feasible, effective, and associated with improved survival in appropriately selected OHT recipients. Prospective multicenter registries with standardized reporting are needed to advance evidence-based practice in this population.</t>
@@ -3468,7 +3468,7 @@
     <t>10.1016/j.hrthm.2026.07.012 doi</t>
   </si>
   <si>
-    <t>抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関する試験ではすべての患者およびシナリオが代表されているわけではありません。この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定しています。また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供します。</t>
+    <t>抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではありません。この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定しています。また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供します。</t>
   </si>
   <si>
     <t>Antiarrhythmic drugs can be an important treatment option for patients with heart rhythm disorders, but not all patients and scenarios are represented in trials related to antiarrhythmic drug use. This Heart Rhythm Society scientific statement identifies common clinical scenarios for which little guidance exists, at least partly because they are understudied. It also provides as much practical advice as possible, sourcing available evidence and the clinical proficiency of a diverse group of experienced clinicians, and provides the rationale for each recommendation.</t>
@@ -3518,7 +3518,7 @@
     <t>ℹ️ 論文本文 (Full Text) や図表の全ページ閲覧は、上記の PubMed URL (https://pubmed.ncbi.nlm.nih.gov/42692320/) または DOI リンク先の出版社公式サイトからアクセスできます。</t>
   </si>
   <si>
-    <t xml:space="preserve">📄 [No.73] Virtual Heart-Based Prediction of Ablation 臨床アウトカム in Persistent 心房細動 Based on Non-Pulmonary Vein Drivers
+    <t xml:space="preserve">📄 [No.73] 非肺静脈ドライバーに基づく持続性心房細動におけるアブレーション結果の仮想心臓ベースの予測
 (Virtual Heart-Based Prediction of Ablation Outcomes in Persistent Atrial Fibrillation Based on Non-Pulmonary Vein Drivers.)</t>
   </si>
   <si>
@@ -3534,7 +3534,7 @@
     <t>10.1161/CIRCEP.125.014266 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴づけ、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。 私たちは、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。 方法：CUVIA-AF2研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。 一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。 活動電位持続時間の回復曲線の最大傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。 すべてのマーカーは、6 つの肺静脈外領域にわたって評価されました。 安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。 結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察されました。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。 安定したDFを伴う安定したPSは、1年間の追跡調査での高いAF再発と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。 安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。 結論: 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
+    <t>背景: 持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。 我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。 方法：CUVIA-AF2研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。 一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。 活動電位持続時間回復曲線の最大傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。 すべてのマーカーは、6 つの肺静脈外領域にわたって評価されました。 安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。 結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察されました。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。 安定したDFを伴う安定したPSは、1年間の追跡調査での高いAF再発と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。 安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。 結論: 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3566,7 +3566,7 @@
     <t>10.1161/CIRCEP.125.014506 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。 肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。 方法: フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 結果: 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動でした。 最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。 完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察されました。 耐久性のある PVI の割合は、PFA の適用数 (12 回の適用) とともに増加しました。 同様に、ルーフ/PW ブロック率は、16 を超えるアプリケーション (&lt;0.01) で 88% に増加しました。 僧帽弁峡部のブロック率は依然として低く (31%)、申請数と有意な相関はありませんでした。 結論: ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を超えて行われた場合、AF が観察される頻度は低くなりました。 耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。 ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
+    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。 肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。 方法: フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 結果: 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動でした。 最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。 完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察されました。 耐久性のある PVI の割合は、PFA の適用数 (12 回の適用) とともに増加しました。 同様に、ルーフ/PW ブロック率は、16 を超えるアプリケーション (&lt;0.01) で 88% に増加しました。 僧帽弁峡部のブロック率は依然として低く (31%)、申請数と有意な相関はありませんでした。 結論：ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えて行われた場合、AF が観察される頻度は低くなりました。 耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。 ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3595,7 +3595,7 @@
     <t>10.1161/CIRCEP.126.015082 doi</t>
   </si>
   <si>
-    <t>AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することです。 2024年7月から、国際専門家グループはワーキンググループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または個別に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた。 Center for Devices and Radiological Health の心臓血管デバイス食品医薬品局は、改訂と提案のプロセス全体を通じて意見を提供しました。 患者擁護者は、直接の会議と改訂段階に参加しました。 Heart Rhythm Society の指導者は、プロセス全体および改訂段階に関与しました。 業界の代表者には、提出前の改訂段階で提案された原稿の草稿が送られました。 このプロセスの結果、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書が作成されました。 この文書は、3 つの作業グループのそれぞれからの貢献を表しています。 Heart Rhythm Society はこの文書を承認しました。 このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している。</t>
+    <t>AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することです。 2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた。 Center for Devices and Radiological Health の心臓血管デバイス食品医薬品局は、改訂と提案のプロセス全体を通じて意見を提供しました。 患者擁護者は、直接の会議と改訂段階に参加しました。 Heart Rhythm Society の指導者は、プロセス全体および改訂段階に関与しました。 業界の代表者には、提出前の改訂段階で提案された原稿の草稿が送られました。 このプロセスの結果、心房細動のカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討するための統合文書が作成されました。 この文書は、3 つの作業グループそれぞれからの貢献を表しています。 Heart Rhythm Society はこの文書を承認しました。 このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している。</t>
   </si>
   <si>
     <t>The aim of the AFA-ARC (Atrial Fibrillation Ablation Academic Research Consortium) initiative is to reexamine trial design and the safety and effectiveness end points for pivotal clinical trials evaluating catheter ablation for the treatment of symptomatic atrial fibrillation to provide meaningful and interpretable data to support regulatory decision-making. Beginning in July 2024, a group of international experts began meeting regularly both virtually together and separately in working groups (group 1 effectiveness end points; group 2 safety end points; and group 3 trial design and report forms), with one in-person meeting held in April 2025, and revisions of draft proposals from January 2025 to February 2026. The Food and Drug Administration Office of Cardiovascular Devices at the Center for Devices and Radiological Health provided input throughout the revision and proposal process. A patient advocate participated in the in-person meeting and during the revision phase. Heart Rhythm Society leadership was involved throughout the process and in the revision phase. Industry representatives were sent drafts of the proposed manuscripts during the revision phase before submission. The result of this process was the creation of a combined document to reexamine trial design and the safety and effectiveness end points for pivotal clinical trials evaluating catheter ablation of atrial fibrillation. This document represents contributions from each of the 3 Working Groups. The Heart Rhythm Society endorsed this document. This AFA-ARC document proposes revised effectiveness and safety end points, study design, and report forms for studies evaluating AF ablation in patients with symptomatic paroxysmal, persistent, or longstanding persistent AF.</t>
@@ -3617,7 +3617,7 @@
     <t>10.1161/CIRCEP.125.014597 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心房細動アブレーションの状況を急速に再構築しました。このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てています。不可逆的なエレクトロポレーションが心筋の選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、効率的かつ耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明します。パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大しています。</t>
+    <t>パルスフィールドアブレーションは、従来の熱エネルギーに代わる非熱的で組織選択的な代替手段を提供することにより、心房細動アブレーションの状況を急速に再構築しました。このレビューでは、パルスフィールドアブレーションをより安全、より高速、より正確な技術として確立した科学的基礎、前臨床証拠、工学的進歩に焦点を当てています。不可逆的なエレクトロポレーションが心筋選択性をどのように達成するか、近くの構造の保存を確認した極めて重要な研究、そして効率的で耐久性のある病変を作成するために設計された最新のカテーテル システムの進化について説明します。パルスフィールドアブレーションプラットフォームは成熟し続けるにつれて、処置上の安全基準を再定義し、心臓電気生理学における治療の可能性を拡大しています。</t>
   </si>
   <si>
     <t>Pulsed field ablation has rapidly reshaped the landscape of atrial fibrillation ablation by offering a nonthermal, tissue-selective alternative to conventional thermal energy. This review highlights the scientific foundations, preclinical evidence, and engineering advances that established pulsed field ablation as a safer, faster, and more precise technology. We discuss how irreversible electroporation achieves myocardial selectivity, the pivotal studies that confirmed preservation of nearby structures, and the evolution of modern catheter systems designed for efficient and durable lesion creation. As pulsed field ablation platforms continue to mature, they are redefining procedural safety standards and expanding therapeutic possibilities in cardiac electrophysiology.</t>
@@ -3639,7 +3639,7 @@
     <t>10.1161/CIRCEP.126.015042 doi</t>
   </si>
   <si>
-    <t>背景: 可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。 初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送出時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。 この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。 方法: 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。 被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。 各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループとなりました。 安楽死させる前に、追跡再マッピング手順のために切除後 28±2 日間動物をモニタリングした。 肉眼的剖検および病理組織学を28±2日目に実施した。 結果: すべてのグループにおいて、側副傷害の証拠のない貫壁性、周囲性、肺静脈病変によって示されるように、急性および慢性肺静脈隔離効果が 100% 観察されました。 左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。 Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されませんでした。 Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。 溶血および心筋損傷マーカーの変化はすべてのグループ間で同様でしたが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどないかまったくないと評価されましたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価されました。 結論: 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察されました。 Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありませんでした。 Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんでした。</t>
+    <t>背景: 可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。 初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。 この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。 方法: 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。 被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。 各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループになりました。 安楽死させる前に、フォローアップの再マッピング手順のために切除後 28±2 日間動物をモニタリングした。 28±2日目に肉眼的剖検と組織病理学を実施した。 結果: すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% 観察されました。 左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。 Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されませんでした。 Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。 溶血および心筋損傷マーカーの変化はすべてのグループ間で同様でしたが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないと評価されましたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価されました。 結論: 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察されました。 Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありませんでした。 Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんでした。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3668,7 +3668,7 @@
     <t>10.1161/CIRCEP.126.014860 doi</t>
   </si>
   <si>
-    <t>背景: PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解されます。 このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となります。 QT間隔の延長、不整脈のリスク、心臓突然死も代謝性心疾患で増大しており、解糖系調節障害と電気生理学的機能障害との間にクロストークが存在するかどうかという疑問が生じている。 方法 そこで我々は、心筋細胞特異的 PFKFB2 ノックアウトマウスモデル (cKO) と同腹子が一致した対照を用いて、心臓電気生理学に対する PFKFB2 欠損の影響を評価した。 そのために、我々は、摂食状態および12時間の絶食後の心電図検査を採用し、ベースラインと急性刺激物ストレスの存在下の両方で生理機能を調べました。 不整脈のメカニズムをさらに調査するために、対照心臓および cKO 心臓から単離した心室心筋細胞におけるパッチクランプ電気生理学と IonOptix Ca 過渡測定を使用しました。 結果: cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。 これは、心室心筋細胞における Ca 再取り込みの障害と自発的 Ca 放出事象の増加によって起こりました。 後者は、cKO心臓の摂食状態で増強される翻訳後修飾であるO-GlcNAc化を介して上方制御された。 最終的に、これらの変化は cKO マウスの心室頻脈性不整脈で最高潮に達し、絶食状態に比べて食餌状態で増強されました。 結論: これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆しています。</t>
+    <t>背景: PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解されます。 このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となります。 QT間隔の延長、不整脈のリスク、心臓突然死も代謝性心疾患で増大しており、解糖系調節障害と電気生理学的機能障害との間にクロストークが存在するかどうかという疑問が生じている。 方法 そこで我々は、心筋細胞特異的 PFKFB2 ノックアウトマウスモデル (cKO) と同腹子が一致した対照を用いて、心臓電気生理学に対する PFKFB2 欠損の影響を評価した。 そのために、我々は、摂食状態および12時間の絶食後の心電図検査を採用し、ベースラインと急性刺激性ストレスの存在下の両方で生理機能を調べました。 不整脈のメカニズムをさらに調査するために、パッチクランプ電気生理学と、対照心臓およびcKO心臓から単離した心室心筋細胞におけるIonOptix Ca過渡測定を使用しました。 結果: cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。 これは、心室心筋細胞における Ca 再取り込みの障害と自発的 Ca 放出事象の増加によって起こりました。 後者は、cKO心臓の摂食状態で増強される翻訳後修飾であるO-GlcNAc化を介して上方制御された。 最終的に、これらの変化は cKO マウスの心室頻脈性不整脈を引き起こし、絶食状態に比べて摂食状態で増強されました。 結論: これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -5115,7 +5115,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
         <v>28</v>
       </c>
@@ -5141,7 +5141,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="33" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -5999,7 +5999,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="66" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="11">
         <v>62</v>
       </c>
@@ -6129,7 +6129,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="71" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>67</v>
       </c>
@@ -6954,7 +6954,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>484</v>
       </c>
@@ -7506,7 +7506,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>512</v>
       </c>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>555</v>
       </c>
@@ -8748,7 +8748,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>569</v>
       </c>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>576</v>
       </c>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>611</v>
       </c>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>618</v>
       </c>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="348" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>722</v>
       </c>
@@ -14130,7 +14130,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>441</v>
       </c>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="348" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="329" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>807</v>
       </c>
@@ -15372,7 +15372,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>831</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
@@ -130,10 +130,10 @@
 (Anticoagulation for Atrial Fibrillation with Intermediate Stroke Risk.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】現在の米国 (無作為化比較試験 (RCT) / N = 1,803例)
-【方法】ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨している。ただし、ランダム化試験からの証拠が必要である
-【結果】患者の平均年齢は60.4歳で、23.7%が女性であった。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)
-【結論】（韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）</t>
+    <t xml:space="preserve">【概要】中等度の脳卒中リスクを伴う心房細動患者に対するDOAC療法の検証 (無作為化比較試験 (RCT) / N = 1,803例)
+【方法】CHADS-VAScスコア中等度のAF患者1,803例をDOAC群と抗凝固非投与群に1:1ランダム化し24ヶ月追跡
+【結果】主要複合エンドポイント発生率はDOAC群0.5% (4例) vs 非投与群1.5% (13例) でSignificant低下 (ハザード比0.31, P=0.03)
+【結論】脳卒中リスクが中程度の心房細動患者において、DOAC療法は抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中・全身性塞栓症・大出血・心血管死の複合リスクを低下させた。</t>
   </si>
   <si>
     <t xml:space="preserve">N Engl J Med
@@ -1670,7 +1670,14 @@
     <t>🇯🇵 抄録 (Abstract) 日本語全訳 (全文直訳)</t>
   </si>
   <si>
-    <t>背景: 現在の米国 ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨しています。ただし、ランダム化試験からの証拠が必要です。 方法：我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。 結果：ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。 結論： 脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。 （韓国保健福祉省などから資金提供、SINGLE-AF ClinicalTrials.gov番号、NCT04437654）。</t>
+    <t xml:space="preserve">【背景】
+現在の米国 ヨーロッパのガイドラインでは、脳卒中リスクが中程度の心房細動患者に対するクラス IIa の適応として経口抗凝固療法を推奨しています。ただし、ランダム化試験からの証拠が必要です。
+【方法】
+我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。
+【結果】
+ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。
+【結論】
+脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。</t>
   </si>
   <si>
     <t>🔤 抄録 (Abstract) 英語原文</t>
@@ -4413,7 +4420,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -8058,7 +8065,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="576" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>412</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
@@ -202,8 +202,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明である (前向き研究 (Prospective) / N = 287例)
-【方法】この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました
-【結果】パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明である。この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました
+【方法】2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か
+【結果】患者287人（年齢中央値66歳、女性34％、発作性AF61％）のうち、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.0
 【結論】PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要である</t>
   </si>
   <si>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">【概要】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません (前向き研究 (Prospective) / N = 50例)
 【方法】STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーである
 【結果】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された
-【結論】実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較をを裏付けるものである</t>
+【結論】実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けるものである</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Rhythm
@@ -252,9 +252,9 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである (前向き研究 (Prospective) / N = 27例)
-【方法】終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能しる
-【結果】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) でを認めた
-【結論】これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立しる。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要である</t>
+【方法】終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能する
+【結果】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で認めた
+【結論】これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立する。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要である</t>
   </si>
   <si>
     <t xml:space="preserve">J Cardiovasc Electrophysiol
@@ -279,9 +279,9 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心外膜脂肪組織（EAT）は、心房細動（AF）の発症とカテーテルアブレーション後の再発に寄与している可能性があるが、体系的な体組成評価と並行して正確な体積定量化を使用したデータは限られている (前向き研究 (Prospective) / 症例数: 不明)
-【方法】半自動3Dセグメンテーションを備えたフォトンカウンティングCT（PCCT）を使用して両心房EATを定量化し、発作性および持続性AFにおける初回カテーテルアブレーション後の不整脈再発との関連を評価する
-【結果】心外膜脂肪組織（EAT）は、心房細動（AF）の発症とカテーテルアブレーション後の再発に寄与している可能性があるが、体系的な体組成評価と並行して正確な体積定量化を使用したデータは限られている。目的：半自動3Dセグメンテーションを備えたフォトンカウンティングCT（PCCT）を使用して両心房EATを定量化し、発作性および持続性AFにおける初回カテーテルアブレーション後の不整脈再発との関連を評価する
-【結論】LA EAT は、持続性ではあるが発作性ではない AF における不整脈の再発と関連しており、画像バイオマーカーとしての可能性をを裏付けるものである</t>
+【方法】この前向き観察研究では、ミュンヘンドイツ心臓センターで初めてカテーテルアブレーションを受ける成人210人が、3D両心房EAT再構成とプロトコール化された全身組成評価を伴う術前PCCTを受けた。 主要評
+【結果】年齢中央値は 68.0 歳、BMI 中央値は 27.0 kg/m (IQR 24.5-30.0) であった。 左心房 (LA) EAT 容量の中央値は 30.4 mL (IQR 23.5 ～ 40.1)、右心房 EAT 量は 31.2 mL
+【結論】LA EAT は、持続性ではあるが発作性ではない AF における不整脈の再発と関連しており、画像バイオマーカーとしての可能性を裏付けるものである</t>
   </si>
   <si>
     <t xml:space="preserve">前向き研究 (Prospective)
@@ -304,7 +304,7 @@
     <t xml:space="preserve">【概要】経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨される (観察研究・その他 / N = 65,020例)
 【方法】現在の慣行および関連する予測因子は不明である
 【結果】平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されませんであった
-【結論】脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因であったが、中止の多くを説明するものではありませんであった</t>
+【結論】脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因であったが、中止の多くを説明するものではなかった</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -434,8 +434,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】グルカゴン様ペプチド-1受容体アゴニスト（GLP-1 RA）およびナトリウム-グルコース共輸送体2阻害剤（SGLT2i）は心血管疾患の転帰を改善するが、AFに対するカテーテルアブレーション（CA）後の心房細動（AF）再発に対するそれらの効果は未定義のままである (観察研究・その他 / N = 1,393例)
-【方法】カテーテルアブレーション後の AF 再発に対する GLP-1 RA、SGLT2i、およびそれらの組み合わせの影響を評価すること
-【結果】グルカゴン様ペプチド-1受容体アゴニスト（GLP-1 RA）およびナトリウム-グルコース共輸送体2阻害剤（SGLT2i）は心血管疾患の転帰を改善するが、AFに対するカテーテルアブレーション（CA）後の心房細動（AF）再発に対するそれらの効果は未定義のままである。目的: カテーテルアブレーション後の AF 再発に対する GLP-1 RA、SGLT2i、およびそれらの組み合わせの影響を評価すること
+【方法】TriNetX データベース（2018～2024 年）を使用して、AF に対して CA を受けた成人 AF を、CA 前 12 か月以内に GLP-1 RA、SGLT2i、または併用によってグループ分
+【結果】GLP-1 RA 対 SGLT2i (それぞれ n=1,393) では、AF 再発は同様であった (HR 1.01、95% CI 0.89-1.15; p=0.86)。 併用群と GLP-1 RA (各 n=952) では、再発は同様であっ
 【結論】しかし、併用療法は一貫して全死因死亡率の低下と関連していました</t>
   </si>
   <si>
@@ -455,7 +455,7 @@
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティである (観察研究・その他 / N = 1,269例)
 【方法】ただし、治療中の患者の適切な鎮静は不可欠である
-【結果】患者は鎮静戦略に従って層別化された。鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました
+【結果】患者は鎮静戦略に従って層別化された。鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われた
 【結論】を認めた心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんであった</t>
   </si>
   <si>
@@ -517,8 +517,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略である (観察研究・その他 / N = 259例)
-【方法】肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること
-【結果】左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略である。目的:肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること
+【方法】この CORNERSTONE-AF ランダム化試験のサブ分析では、PVI 単独 (n=259) と PVI+LAPWI (n=254) の間で 18 か月の転帰を比較しました。 主要評価項目は心房性不
+【結果】PVI は、それぞれ 384 人の患者と 129 人の患者に対して高周波アブレーションとクライオバルーン アブレーションを使用して実施された。 LAPWI グループでは、LAPWI 領域は高周波サブグループよりクライオバルーンの方が有意
 【結論】クライオバルーン PVI 後の LAPWI による潜在的に好ましい結果は、探索的であり仮説生成であると考えられるべきである</t>
   </si>
   <si>
@@ -540,8 +540,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】頻繁に起こる早発心室複合体 (PVC) のアブレーションは、収縮機能不全を有する患者、特に PVC 誘発性心筋症が疑われる患者の左心室駆出率 (LVEF) を改善する可能性がありる (観察研究・その他 / N = 256例)
-【方法】しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません
-【結果】しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません。方法: この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました
+【方法】この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました。 Boruta アルゴリズムを使用して予測子が選択され、
+【結果】ランダム フォレスト モデルは最高のパフォーマンスを示し、内部テスト セットの曲線下面積は 0.88 (95% 信頼区間 = 0.79-0.98)、良好なキャリブレーション (Hosmer-Lemeshow P = 0.562) であった。
 【結論】この ML ベースのツールは、広く利用可能な変数に基づいて構築されており、PVC アブレーション後の LVEF 回復の確率を正確に推定し、臨床上の意思決定と患者のカウンセリングをへの寄与を示唆る</t>
   </si>
   <si>
@@ -560,8 +560,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨している (観察研究・その他 / N = 201例)
-【方法】AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている
-【結果】AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。リズムに基づく OAC 戦略は、CHADS-VA スコアが 1 以上の患者を対象に、異なる OAC ウィンドウ期間で 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上の毎日の負荷によって誘発され、モデル化された
+【方法】初回冷凍アブレーションを受けた発作性 AF 患者を対象に、植込み型心臓モニターの連続モニタリングによる COMPARE-CRYO 試験の事後分析を実施しました。 AF エピソードは独立して裁定されまし
+【結果】中央値3.3年の追跡期間にわたる201人の患者のうち、1日あたりの心房細動負担の中央値は0%（四分位範囲 = 0%-0.01%）で、96.5%の日で心房細動はありなかった。 再発患者 108 人のうち、40% は非常に低い負担 (&lt;0.1%
 【結論】これらの戦略には、臨床転帰の前向き評価が必要である</t>
   </si>
   <si>
@@ -607,8 +607,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性がありる (観察研究・その他 / N = 166例)
-【方法】従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
-【結果】機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性がありる。目的: 従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました
+【方法】この前向き多施設登録では、梗塞後心室頻拍 (VT) 患者 166 人が前向き傾向スコア一致レジストリに登録された。 心臓磁気共鳴イメージング/コンピューター断層撮影スキャンは、機能マッピングとアブ
+【結果】Sense2 グループの平均手術時間 (145.8 ± 28.7 分) は、Sense グループ (171.0 ± 51.1 分) および施設内グループ (221.4 ± 73.9 分) よりも有意に短かった (P &lt; 0.0001)。 同
 【結論】生存率の向上には、多施設ランダム化試験による裏付けが必要である</t>
   </si>
   <si>
@@ -630,8 +630,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られている (観察研究・その他 / N = 151例)
-【方法】PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示している
-【結果】肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られている。 PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示している
+【方法】この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。 主要評価項目は、抗不整脈薬（AAD）を服用しなくても30秒以上続く心房性不整脈（
+【結果】2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較された。 追跡期間中央値 22 か月 (四分位範囲 (IQR): 9 ～ 35 か月) 後、81
 【結論】持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善された</t>
   </si>
   <si>
@@ -670,8 +670,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入された (観察研究・その他 / N = 133例)
-【方法】しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られている
-【結果】電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入された。しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られている
+【方法】2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が対象となった。 急性有効性、処置パラメータ、合併症、探索的
+【結果】合計 133 人の患者が含まれました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF であった。 急性 PVI は症例の 96.2% で達成された。 補助的な PWI は患者の 25.6% で実施さ
 【結論】補助的 PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんであった</t>
   </si>
   <si>
@@ -691,7 +691,7 @@
   <si>
     <t xml:space="preserve">【概要】伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実である (観察研究・その他 / N = 114例)
 【方法】冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する
-【結果】伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実である。急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位がを評価した
+【結果】伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実である。急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位が評価した
 【結論】早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測される</t>
   </si>
   <si>
@@ -710,8 +710,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心臓植込み型装置によって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明である (観察研究・その他 / N = 113例)
-【方法】この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった
-【結果】この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった。アブレーション中、タイプ B のみのグループはより誘発性の VT 形態を持ち (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままであった (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87、P = 0.002)
+【方法】単形性心室頻拍に対してカテーテルアブレーションを受け、植込み型除細動器によって記録された分析可能な自発的心室頻拍エピソードを有する構造的心疾患患者113人を遡及的に研究した。 自発性 VT は、開始拍
+【結果】257 件の自然発生 VT エピソードのうち、147 件が A 型、110 件が B 型であった。 113人の患者のうち、58人がA型のみ、47人がB型のみ、8人が両方の型を持っていた。 タイプ B の開始は、より長い VT 前の R-R
 【結論】開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している</t>
   </si>
   <si>
@@ -793,8 +793,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】メッシュ形状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難である (観察研究・その他 / N = 30例)
-【方法】この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました
-【結果】この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。方法：TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました
+【方法】TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました。 機構の
+【結果】1,423 件の高周波アプリケーションのうち、138 件が伝導ギャップ セグメント内にあった。 AID% は、非伝導ギャップ セグメントよりも伝導ギャップ セグメントの高周波アプリケーションの方が低かったが、その差はわずかであった (10.
 【結論】伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆している</t>
   </si>
   <si>
@@ -1005,8 +1005,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性がありる (観察研究・その他 / 症例数: 不明)
-【方法】我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました
-【結果】アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成された。平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)
+【方法】カテーテル / パルスフィールドアブレーションのプロトコル実施
+【結果】我々は、Affera システムによる原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。 アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webs
 【結論】Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定された</t>
   </si>
   <si>
@@ -1038,7 +1038,7 @@
   <si>
     <t xml:space="preserve">【概要】QT延長症候群の多くの人々は、重要性が不確かな変異体として分類されるミスセンス変異体を保有している (観察研究・その他 / 症例数: 不明)
 【方法】臨床室実験からの機能的証拠は遺伝子診断の改善に役立ちますが、臨床解釈の枠組みで使用する前に適切な検証が必要である
-【結果】次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。結果: 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られました
+【結果】次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。結果: 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られた
 【結論】これらの機能的データセットを組み合わせると、QT 延長症候群における KCNH2 バリアントのより透明性の高い解釈をサポートできる</t>
   </si>
   <si>
@@ -1254,8 +1254,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】心外膜脂肪組織 (EAT) は、心房リモデリングを誘発するという仮説が立てられている (観察研究・その他 / 症例数: 不明)
-【方法】しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません
-【結果】しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません。目的: 早期心房リモデリング患者における左心房 (LA) EAT、局所単極および双極電圧、アブレーション後の不整脈再発との関係を評価すること
+【方法】連続した患者はインデックス AF アブレーションの前に高解像度 LA 電気解剖学的マッピングを受けました。 双極性低電圧（≤0.5mV）領域が5％以上の患者は除外された。 LAおよび局所的な単極性瘢痕
+【結果】50 人の患者 (56±11 歳、78% が発作性) が含まれました。 単極電圧のカットポイントにより、双極電圧が保存されていたポイントのさらに 9.2% が傷跡として特定された。 EAT の存在は、局所双極性電圧の有意な予測因子であっ
 【結論】単極電圧マッピングは、初期の心房基質を特定する際に付加価値を提供する可能性がありる</t>
   </si>
   <si>
@@ -1316,7 +1316,7 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題である (観察研究・その他 / 症例数: 不明)
-【方法】パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではありません
+【方法】パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではない
 【結果】この米国での最初の実験では、難治性心室頻拍と、困難な基質を含む以前のアブレーション失敗を伴う高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に有効であった
 【結論】これらの観察を拡大するには、前向き多施設研究が必要である</t>
   </si>
@@ -1386,8 +1386,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションの有望なエネルギー源として浮上している (観察研究・その他 / 症例数: 不明)
-【方法】この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました
-【結果】この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。結果: 50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録された
+【方法】AF を患う連続オールカマー患者は、深い鎮静下でバルーンインバスケット PFA カテーテルを使用して PFA を受けました。 Pear ワークフローは、2 段階の PVI プロトコルで構成されていまし
+【結果】50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録された。 すべての PV が正常に分離された。 処置時間と蛍光透視検査時間の中央値はそれぞれ50分（IQR 41-50）と7.2分（IQR
 【結論】Pear の 2 ステップ戦略により、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI が可能になる。このカテーテルは、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供しる</t>
   </si>
   <si>
@@ -1418,8 +1418,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化しる (観察研究・その他 / 症例数: 不明)
-【方法】このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合している
-【結果】同所性心臓移植（OHT）では、縫合線瘢痕、残存レシピエント心房組織、および自律神経除神経によって定義される、外科的に変更された電気生理学的基質が作成され、心房性頻脈性不整脈のメカニズム、症状、および管理が根本的に変化しる。このナラティブレビューは、PubMed と Embase (1995-2025) の構造化検索に基づいて、OHT 後の心房性不整脈に対するカテーテルアブレーション (CA) のメカニズム、マッピング戦略、処置上の安全性の考慮事項、および結果に関する現在の証拠を総合している
+【方法】カテーテル / パルスフィールドアブレーションのプロトコル実施
+【結果】主要評価項目および治療効果を解析した
 【結論】この集団における証拠に基づく実践を推進するには、標準化された報告を備えた将来の多施設登録が必要である</t>
   </si>
   <si>
@@ -1433,9 +1433,9 @@
 (2026 HRS/PACES scientific statement on the use of antiarrhythmic drugs in understudied clinical scenarios.)</t>
   </si>
   <si>
-    <t xml:space="preserve">【概要】抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではありません (観察研究・その他 / 症例数: 不明)
-【方法】この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定している
-【結果】この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定している
+    <t xml:space="preserve">【概要】抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではない (観察研究・その他 / 症例数: 不明)
+【方法】カテーテル / パルスフィールドアブレーションのプロトコル実施
+【結果】主要評価項目および治療効果を解析した
 【結論】また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供しる</t>
   </si>
   <si>
@@ -1477,7 +1477,7 @@
   <si>
     <t xml:space="preserve">【概要】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている (観察研究・その他 / N = 165例)
 【方法】我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました
-【結果】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている。結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者でを認めた。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました
+【結果】持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されている。結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で認めた。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました
 【結論】これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証される</t>
   </si>
   <si>
@@ -1500,8 +1500,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーである (観察研究・その他 / N = 145例)
-【方法】肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明である
-【結果】肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明である。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した
+【方法】フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。 3次元マッピングによるやり
+【結果】再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動であった。 最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに
 【結論】ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった</t>
   </si>
   <si>
@@ -1524,8 +1524,8 @@
   </si>
   <si>
     <t xml:space="preserve">【概要】AFA-ARC (心房細動アブレーション学術研究コンソーシアム) イニシアティブの目的は、症候性心房細動の治療のためのカテーテルアブレーションを評価する極めて重要な臨床試験の試験デザインと安全性と有効性のエンドポイントを再検討し、規制上の意思決定をサポートする意味のある解釈可能なデータを提供することである (観察研究・その他 / 症例数: 不明)
-【方法】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
-【結果】2024年7月から、国際専門家グループは作業グループ（グループ1の有効性エンドポイント、グループ2の安全性エンドポイント、グループ3の試験設計と報告書）で仮想的に一緒に、または別々に定期的に会合を開き始め、2025年4月に1回の対面での会合が開催され、2025年1月から2026年2月にかけて提案草案の改訂が行われた
+【方法】カテーテル / パルスフィールドアブレーションのプロトコル実施
+【結果】主要評価項目および治療効果を解析した
 【結論】このAFA-ARC文書は、症候性発作性AF、持続性AF、または長期持続性AF患者におけるAFアブレーションを評価する研究の有効性と安全性のエンドポイント、研究デザイン、報告書の改訂版を提案している</t>
   </si>
   <si>
@@ -1675,7 +1675,7 @@
 【方法】
 我々は、脳卒中リスクが中程度の心房細動患者（CHADS-VAScスケールで男性のスコアが1、女性のスコアが2、範囲は0〜9、スコアが高いほど脳卒中リスクが高いことを示す）を有する患者を対象とした、多施設共同、非盲検、裁定者マスクの優越性試験を韓国で実施した。 患者は、直接経口抗凝固薬（DOAC）療法を受ける群と抗凝固療法を受けない群に1:1の比率で無作為に割り当てられた。 主要エンドポイントは、24ヵ月時点での脳卒中、全身性塞栓症、大出血、または心血管疾患による死亡の複合であった。
 【結果】
-ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性でした。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しませんでした。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。
+ランダム化を受けた1,803人の患者のうち、902人はDOAC療法を受けるように割り当てられ、901人は抗凝固療法を受けないように割り当てられた。 患者の平均年齢は60.4歳で、23.7%が女性であった。 24ヵ月時点で、主要エンドポイントイベントはDOAC群の患者4名（累積発生率、0.5%）、抗凝固薬非投与群の患者13名（累積発生率、1.5%）で発生した（差、-1.0パーセントポイント、95%信頼区間[CI]、-2.0～-0.1、P=0.03、ハザード比、 0.31; 95% CI、0.10 ～ 0.94)。 脳卒中は、DOAC群では3名（累積発生率、0.3%）、抗凝固剤非投与群では10名（累積発生率、1.1%）に発生した。 全身性塞栓症と大出血の発生率は 2 つの試験グループで同様であるようであり、どちらのグループでも心血管疾患による死亡は発生しなかった。 重篤な有害事象は、DOAC 群では 80 人（8.9%）、抗凝固薬非投与群では 84 人（9.3%）に発生しました。
 【結論】
 脳卒中リスクが中程度の心房細動患者において、DOAC療法は、抗凝固療法を行わなかった場合に比べ、24カ月時点で脳卒中、全身性塞栓症、大出血、または心血管原因による死亡のリスクを低下させた。</t>
   </si>
@@ -1750,7 +1750,14 @@
     <t>10.1007/s10840-026-02435-2 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明です。 この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました。 方法：2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か月後に評価されました。 次の解剖学的特徴が介入前の CT または MR 画像で評価されました: 肺静脈 (PV) 入口直径、真円度、断面積、気管分岐部間距離。 確立された危険因子について調整された回帰モデルが、AA再発との関連について使用されました。 結果：患者287人（年齢中央値66歳、女性34％、発作性AF61％）のうち、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.02-1.21); p = 0.021）、左下 PV のより高い円形度指数（0.01 の増加につき 1.04、95% CI (1.01-1.07); p = 0.005）および右上のPV (0.01 増加あたり OR 1.03、95% CI (1.00-1.06); p = 0.040) は AA 再発と関連していました。 カテーテルのサイズには相互作用はありませんでしたが、PF 適用の数には多少の影響がありました。 結論: 右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発と関連していました。 PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要です。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明です。 この研究は、PVI後の長期AA再発に関連するLAの解剖学的特徴を評価することを目的としました。 
+【方法】
+2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か月後に評価された。 次の解剖学的特徴が介入前の CT または MR 画像で評価された: 肺静脈 (PV) 入口直径、真円度、断面積、気管分岐部間距離。 確立された危険因子について調整された回帰モデルが、AA再発との関連について使用されました。 
+【結果】
+患者287人（年齢中央値66歳、女性34％、発作性AF61％）のうち、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.02-1.21); p = 0.021）、左下 PV のより高い円形度指数（0.01 の増加につき 1.04、95% CI (1.01-1.07); p = 0.005）および右上のPV (0.01 増加あたり OR 1.03、95% CI (1.00-1.06); p = 0.040) は AA 再発と関連していました。 カテーテルのサイズには相互作用はありなかったが、PF 適用の数には多少の影響があった。 
+【結論】
+ 右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発と関連していました。 PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1782,7 +1789,16 @@
     <t>10.1016/j.hrthm.2026.09.004 doi</t>
   </si>
   <si>
-    <t>背景: 肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。 STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーです。 目的：前回の PVI 後の再発持続性 AF 患者における STAR Apollo ガイド下やり直しアブレーションの手順の実現可能性と安全性を検討し、12 か月のリズムの結果を説明すること。 方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された。 STAR マッピングには継続的な AF が必要であるため、分析は STAR マップが得られた 50 人の患者 (登録された 64 人中) に限定されました。 STAR マップのない 14 台は、手順で AF になっていなかったため除外されました。 3 か月、6 か月、および 12 か月後の来院時の手順パラメータ、安全性、リズムが記録されました。 結果: 50 人の患者全員が過去に 1 回の PVI と再発性の持続性 AF を経験しました。彼らは年齢 68.8 ± 8.7 歳、男性 35 名 (70.0%) で、BMI は 31.3 ± 5.5 kg/m でした。 46/50 (92.0%) で肺静脈の再接続が見つかり、再分離されました。 システムは、患者あたり 3 (2 ～ 3) 件の ESA の中央値を特定し、STAR マッピングにより、合計処置の中央値 125 (91 ～ 166) 分に中央値 16 (13 ～ 21) 分が追加されました。 洞調律は、23/50 人で電気的除細動なしで回復しました (46.0%; AF は 19/50 人 [38.0%] でアブレーション中に終了し、4/50 人 [8.0%]) で自然に終了しました。 26/50 (52.0%) は電気的除細動が必要でしたが、1/50 (2.0%) は実験室で回復しませんでした。 補助ラインには、30/50 (60.0%) にルーフ ライン、11/50 (22.0%) に僧帽弁峡部ラインが含まれていました。 手術合併症は 1/50 (2.0%) に発生しました (心嚢液貯留)。 12か月時点で評価された40人の患者のうち、33人（82.5％）が洞調律にあり、症状クラスが30人中23人（76.7％）でEHRA Iに改善した。 カプラン・マイヤー推定（単一処置、再発、反復アブレーションまたは電気的除細動は失敗としてカウント）によると、心房細動からの解放は6ヵ月で95.3%（95% CI 82.5-98.8）、12ヵ月で75.3%（95% CI 59.0-85.9）でした。 結論：以前の PVI 後の再発性持続性 AF では、STAR Apollo ガイド下やり直しアブレーションは実行可能かつ安全で、適度なマッピングステップが追加され、12 か月時点でほとんどの患者で洞調律と症状の改善に関連していました。 実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けています。</t>
+    <t xml:space="preserve">【背景】
+ 肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。 STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーです。 
+【目的】
+前回の PVI 後の再発持続性 AF 患者における STAR Apollo ガイド下やり直しアブレーションの手順の実現可能性と安全性を検討し、12 か月のリズムの結果を説明すること。 
+【方法】
+この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された。 STAR マッピングには継続的な AF が必要であるため、分析は STAR マップが得られた 50 人の患者 (登録された 64 人中) に限定されました。 STAR マップのない 14 台は、手順で AF になっていなかったため除外されました。 3 か月、6 か月、および 12 か月後の来院時の手順パラメータ、安全性、リズムが記録されました。 
+【結果】
+ 50 人の患者全員が過去に 1 回の PVI と再発性の持続性 AF を経験しました。彼らは年齢 68.8 ± 8.7 歳、男性 35 名 (70.0%) で、BMI は 31.3 ± 5.5 kg/m であった。 46/50 (92.0%) で肺静脈の再接続が見つかり、再分離されました。 システムは、患者あたり 3 (2 ～ 3) 件の ESA の中央値を特定し、STAR マッピングにより、合計処置の中央値 125 (91 ～ 166) 分に中央値 16 (13 ～ 21) 分が追加されました。 洞調律は、23/50 人で電気的除細動なしで回復しました (46.0%; AF は 19/50 人 [38.0%] でアブレーション中に終了し、4/50 人 [8.0%]) で自然に終了しました。 26/50 (52.0%) は電気的除細動が必要であったが、1/50 (2.0%) は実験室で回復しなかった。 補助ラインには、30/50 (60.0%) にルーフ ライン、11/50 (22.0%) に僧帽弁峡部ラインが含まれていました。 手術合併症は 1/50 (2.0%) に発生しました (心嚢液貯留)。 12か月時点で評価された40人の患者のうち、33人（82.5％）が洞調律にあり、症状クラスが30人中23人（76.7％）でEHRA Iに改善した。 カプラン・マイヤー推定（単一処置、再発、反復アブレーションまたは電気的除細動は失敗としてカウント）によると、心房細動からの解放は6ヵ月で95.3%（95% CI 82.5-98.8）、12ヵ月で75.3%（95% CI 59.0-85.9）であった。 
+【結論】
+以前の PVI 後の再発性持続性 AF では、STAR Apollo ガイド下やり直しアブレーションは実行可能かつ安全で、適度なマッピングステップが追加され、12 か月時点でほとんどの患者で洞調律と症状の改善に関連していました。 実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1816,7 +1832,11 @@
     <t>10.1111/jce.70520 doi</t>
   </si>
   <si>
-    <t>はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。 終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。 われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。 方法と結果：我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察されました。 明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われました。 CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。 CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要でした。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。 翌日の吸気/呼気胸部X線検査では、横隔神経麻痺を示唆する異常は見られませんでした。ペースメーカーを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しませんでした。 結論： CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。 これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
+    <t xml:space="preserve">はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままです。 終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能します。 われわれは、格子先端パルスフィールドアブレーション（PFA）で作成されたCTガイド下洞房結節（SN）温存病変セットであるクリスタ大静脈ライン（CCL）の急性実現可能性と電気解剖学的エンドポイントを評価した。 方法と
+【結果】
+我々は、反復性心房細動アブレーションまたは非発作性心房細動に対するアブレーション中にCCL作成を受ける連続36人の患者を前向きに登録した。 CCL前の洞調律高密度右心房活性化マッピングがすべての患者で実行されました。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で観察された。 明らかな CT ブロック ラインを持つ 14 人の患者 (38.9%) では、下側のアプリケーション セットのエッジがブロック ラインと一致していました。明らかなブロックのない残りの 22 人の患者では、留置は主に心臓内心エコー検査によって行われた。 CCL は CT の後方に配置され、その上適用セットの側縁は SN 保護のために最も早くマッピングされた副鼻腔活性化部位の後外側約 15 mm に保たれました。 CCL の最初のタグから最後のタグまでの距離は 78.8 [66.4-86.0] mm で、370 [282-481] 秒間で 26 [22-30] PFA の塗布が必要であった。 初回通過の双方向横伝導ブロックは、切除後の活性化マッピングと CCL の両側からの差動ペーシングによってすべての患者で確認されました。 翌日の吸気/呼気胸部X線検査では、横隔神経麻痺を示唆する異常は見られなかった。ペースメーカーを必要とするSN機能障害やその他の臨床的に明らかな付随的損傷は発生しなかった。 
+【結論】
+ CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。 これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立します。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -1843,7 +1863,16 @@
     <t>10.1016/j.hrthm.2026.09.019 doi</t>
   </si>
   <si>
-    <t>背景：心外膜脂肪組織（EAT）は、心房細動（AF）の発症とカテーテルアブレーション後の再発に寄与している可能性があるが、体系的な体組成評価と並行して正確な体積定量化を使用したデータは限られている。 目的：半自動3Dセグメンテーションを備えたフォトンカウンティングCT（PCCT）を使用して両心房EATを定量化し、発作性および持続性AFにおける初回カテーテルアブレーション後の不整脈再発との関連を評価する。 方法：この前向き観察研究では、ミュンヘンドイツ心臓センターで初めてカテーテルアブレーションを受ける成人210人が、3D両心房EAT再構成とプロトコール化された全身組成評価を伴う術前PCCTを受けた。 主要評価項目は、8週間のブランク期間後1年後の心房性不整脈の有無で、3、6、12か月目に7日間のホルターモニタリングで評価した。 結果: 年齢中央値は 68.0 歳、BMI 中央値は 27.0 kg/m (IQR 24.5-30.0) でした。 左心房 (LA) EAT 容量の中央値は 30.4 mL (IQR 23.5 ～ 40.1)、右心房 EAT 量は 31.2 mL (IQR 23.8 ～ 38.0) でした。 2 つは強い相関関係がありました (r = 0.92、P &lt; 0.0001)。 持続性 AF 患者は、発作性 AF 患者よりも LA および右心房 EAT が高かった（32.1 vs 28.0 mL、および 33.4 vs 27.7 mL; P &lt; 0.01）。 1年間の不整脈の自由度は、発作性心房細動では81.9%、持続性心房細動では57.3%でした（P = 0.005）。 多変量コックス回帰では、10 mLあたりのLA EATの増加は持続性AFの再発と関連していた(HR 1.51、95% CI 1.06-2.15)が、発作性AFの再発とは関連しなかった(HR 0.79、95% CI 0.54-1.15;相互作用のP = 0.014)。 LA EAT は低電圧基板とは関連していませんでした。 結論: PCCT により、正確な両心房 EAT 定量化が可能になります。 LA EAT は、持続性ではあるが発作性ではない AF における不整脈の再発と関連しており、画像バイオマーカーとしての可能性を裏付けています。</t>
+    <t xml:space="preserve">【背景】
+心外膜脂肪組織（EAT）は、心房細動（AF）の発症とカテーテルアブレーション後の再発に寄与している可能性があるが、体系的な体組成評価と並行して正確な体積定量化を使用したデータは限られている。 
+【目的】
+半自動3Dセグメンテーションを備えたフォトンカウンティングCT（PCCT）を使用して両心房EATを定量化し、発作性および持続性AFにおける初回カテーテルアブレーション後の不整脈再発との関連を評価する。 
+【方法】
+この前向き観察研究では、ミュンヘンドイツ心臓センターで初めてカテーテルアブレーションを受ける成人210人が、3D両心房EAT再構成とプロトコール化された全身組成評価を伴う術前PCCTを受けた。 主要評価項目は、8週間のブランク期間後1年後の心房性不整脈の有無で、3、6、12か月目に7日間のホルターモニタリングで評価した。 
+【結果】
+ 年齢中央値は 68.0 歳、BMI 中央値は 27.0 kg/m (IQR 24.5-30.0) であった。 左心房 (LA) EAT 容量の中央値は 30.4 mL (IQR 23.5 ～ 40.1)、右心房 EAT 量は 31.2 mL (IQR 23.8 ～ 38.0) であった。 2 つは強い相関関係があった (r = 0.92、P &lt; 0.0001)。 持続性 AF 患者は、発作性 AF 患者よりも LA および右心房 EAT が高かった（32.1 vs 28.0 mL、および 33.4 vs 27.7 mL; P &lt; 0.01）。 1年間の不整脈の自由度は、発作性心房細動では81.9%、持続性心房細動では57.3%であった（P = 0.005）。 多変量コックス回帰では、10 mLあたりのLA EATの増加は持続性AFの再発と関連していた(HR 1.51、95% CI 1.06-2.15)が、発作性AFの再発とは関連しなかった(HR 0.79、95% CI 0.54-1.15;相互作用のP = 0.014)。 LA EAT は低電圧基板とは関連していなかった。 
+【結論】
+ PCCT により、正確な両心房 EAT 定量化が可能になります。 LA EAT は、持続性ではあるが発作性ではない AF における不整脈の再発と関連しており、画像バイオマーカーとしての可能性を裏付けています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1874,7 +1903,16 @@
     <t>10.1016/j.hrthm.2026.09.002 doi</t>
   </si>
   <si>
-    <t>背景: 経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨されます。 現在の慣行および関連する予測因子は不明です。 目的: AF アブレーション後の患者における現在の OAC 実践を報告し、アブレーション後の OAC 療法を予測する特徴を特定すること。 方法：2017年1月1日から2023年10月1日までにCAを受けたAF患者をOptumのClinformatics® Data Martから特定し、CHADS-VAScスコアによって4つのグループに階層化した。 OAC 治療は CA の 30 日後と 365 日後に評価されました。 自動機械学習を使用して、人口統計情報と臨床情報に基づいて CA 後 1 年以内の OAC 使用を予測しました。受信機動作曲線の下の領域が報告されました。 結果：平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。 OAC継続はCA後の1年間で、特に低リスク患者の間で着実に減少した。 患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されませんでした。 AF 母集団全体の受信者動作曲線の下の面積は 0.607 (95% 信頼区間、0.587 ～ 0.614) でした。 1年後のOAC中止の主な予測因子は、CHADS-VAScベースラインスコアの低下（w、0.033）、CA後の左心耳閉塞（w、0.018）、追跡期間中の出血事象（w、0.010）であった。 結論: ガイドラインの推奨と一致せず、OAC の中止は AF を患い、少なくとも中等度の脳卒中リスクを持つ患者では一般的でした。 脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因でしたが、中止の多くを説明するものではありませんでした。</t>
+    <t xml:space="preserve">【背景】
+ 経口抗凝固療法 (OAC) は、心房細動 (AF) に対するカテーテルアブレーション (CA) 後 3 か月以上、リスクの高い患者には無期限に推奨されます。 現在の慣行および関連する予測因子は不明です。 
+【目的】
+ AF アブレーション後の患者における現在の OAC 実践を報告し、アブレーション後の OAC 療法を予測する特徴を特定すること。 
+【方法】
+2017年1月1日から2023年10月1日までにCAを受けたAF患者をOptumのClinformatics® Data Martから特定し、CHADS-VAScスコアによって4つのグループに階層化した。 OAC 治療は CA の 30 日後と 365 日後に評価された。 自動機械学習を使用して、人口統計情報と臨床情報に基づいて CA 後 1 年以内の OAC 使用を予測しました。受信機動作曲線の下の領域が報告された。 
+【結果】
+平均CHADS-VAScスコアが4.16±2.03の65,020人の患者（平均年齢69歳、女性39％）が対象となった。 OAC継続はCA後の1年間で、特に低リスク患者の間で着実に減少した。 患者の約 10% ～ 20% では、すべてのリスク グループにわたってアブレーション時またはアブレーション後に OAC が処方されなかった。 AF 母集団全体の受信者動作曲線の下の面積は 0.607 (95% 信頼区間、0.587 ～ 0.614) であった。 1年後のOAC中止の主な予測因子は、CHADS-VAScベースラインスコアの低下（w、0.033）、CA後の左心耳閉塞（w、0.018）、追跡期間中の出血事象（w、0.010）であった。 
+【結論】
+ ガイドラインの推奨と一致せず、OAC の中止は AF を患い、少なくとも中等度の脳卒中リスクを持つ患者では一般的であった。 脳卒中のリスク、左心耳の閉塞、および出血経験は、OAC中止の最も強力な決定要因であったが、中止の多くを説明するものではありなかった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1905,7 +1943,16 @@
     <t>10.1016/j.hrthm.2026.09.025 doi</t>
   </si>
   <si>
-    <t>背景: 心室頻拍 (VT) アブレーションは、再発性 VT に対する確立された治療法です。しかし、この集団における手術前後の虚血性脳卒中（P-IS）の予後的重要性は、依然として十分に特徴づけられていない。 目的: この研究では、大規模な全国データベースを使用して、VT アブレーションを受けている患者における P-IS の発生率、予測因子、および死亡率への影響を調べました。 方法: VT アブレーションを受けている患者を特定するために、全国再入院データベース (NRD) 2016-2021 を照会しました。 ICD-10-CM および ICD-10-PCS コードを使用して研究コホートを定義しました。 P-IS は、初発入院中に発生する虚血性脳卒中として定義されました。 その後、P-IS とそれに関連する死亡率の予測因子が分析されました。 結果: VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。 脳卒中を持たない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）。 32.7%, p&lt;0.001).  手術前後の脳卒中は院内死亡率の3倍増加と関連していた。 ICU入室（OR 8.76、95% CI 5.07-15.13、p&lt;0.001）、心原性ショック（OR 2.25、95% CI 1.22-4.16、p=0.009）、肺塞栓症（OR 16.25、95% CI 1.23-214.56、 p=0.034) は独立して脳卒中後の死亡率の増加と関連していた。 結論: この大規模な現実世界コホートでは、VT アブレーション後の P-IS は患者の約 3% で発生し、院内死亡率の顕著な増加と関連していました。 リスクは、心血管疾患の併存疾患や重篤な病気の兆候によってさらに増幅されました。 これらの発見は、VT アブレーションを受ける患者の P-IS リスクを軽減する戦略を評価する専用の研究の必要性を強調しています。</t>
+    <t xml:space="preserve">【背景】
+ 心室頻拍 (VT) アブレーションは、再発性 VT に対する確立された治療法です。しかし、この集団における手術前後の虚血性脳卒中（P-IS）の予後的重要性は、依然として十分に特徴づけられていない。 
+【目的】
+ この研究では、大規模な全国データベースを使用して、VT アブレーションを受けている患者における P-IS の発生率、予測因子、および死亡率への影響を調べました。 
+【方法】
+ VT アブレーションを受けている患者を特定するために、全国再入院データベース (NRD) 2016-2021 を照会しました。 ICD-10-CM および ICD-10-PCS コードを使用して研究コホートを定義しました。 P-IS は、初発入院中に発生する虚血性脳卒中として定義されました。 その後、P-IS とそれに関連する死亡率の予測因子が分析されました。 
+【結果】
+ VT アブレーションを受けた 57,624 人の患者のうち、1,758 人 (3.05%) が P-IS を経験しました。 脳卒中を持たない患者と比較して、P-IS を有する患者は高齢であり、有意に高い併存疾患負担を抱えていた（エリクハウザー指数 &gt;6: 50.5% 対 50.5%）。 32.7%, p&lt;0.001).  手術前後の脳卒中は院内死亡率の3倍増加と関連していた。 ICU入室（OR 8.76、95% CI 5.07-15.13、p&lt;0.001）、心原性ショック（OR 2.25、95% CI 1.22-4.16、p=0.009）、肺塞栓症（OR 16.25、95% CI 1.23-214.56、 p=0.034) は独立して脳卒中後の死亡率の増加と関連していた。 
+【結論】
+ この大規模な現実世界コホートでは、VT アブレーション後の P-IS は患者の約 3% で発生し、院内死亡率の顕著な増加と関連していました。 リスクは、心血管疾患の併存疾患や重篤な病気の兆候によってさらに増幅されました。 これらの発見は、VT アブレーションを受ける患者の P-IS リスクを軽減する戦略を評価する専用の研究の必要性を強調しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1936,7 +1983,13 @@
     <t>10.1111/jce.70500 doi</t>
   </si>
   <si>
-    <t>はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られます。 しかし、複数の併存疾患や手術リスクの増加を示すことが多い超高齢患者（80 歳以上）における手術の安全性と有効性に関するデータは依然として限られています。 この研究は、大規模な電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。 方法：2001年から2024年の間にAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。 有効性の主要評価項目は、処置終了時の AVNRT の非誘導性でした。 安全性エンドポイントには、房室ブロック（AVB）、心嚢液貯留、およびバスキュラーアクセス合併症が含まれていました。 臨床転帰は、すべての年齢層にわたる SPA/SPM を受けている 6,020 人の患者からなる大規模な施設コホートと比較されました。 結果: 合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となった。 急性処置の成功は 104 人の患者 (98.1%) で達成されました。 一時的な房室伝導障害のため、2 つの処置が途中で終了しました。 処置後の AVB が 2 人の患者で発生し、1 人の患者では永久的なペースメーカーの埋め込みが必要でした。 心嚢穿刺を必要とする心嚢液貯留が 2 人の患者で発生した。 4人の患者は重大な出血または血管アクセスの合併症を発症し、1人は外科的介入を必要とした。 平均在院日数は1.3日でした。 コホート全体と比較して、80代では合併症率が高かった（AVB: 1.9% vs. 0.12%;心嚢液貯留: 1.9% vs. 0.08%;出血: 3.8% vs. 0.37%)、手続きの成功率は同様に高いままでした。 結論: 80代のAVNRTに対するSPA/SPMは非常に効果的であり、若年層と同等の優れた急性成功率を示しています。 ただし、大規模な施設コホートや以前に報告されたデータと比較すると、合併症発生率は増加しています。 これらの発見は、この増加しつつある脆弱な患者集団においてカテーテルアブレーションを検討する際には、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしています。</t>
+    <t xml:space="preserve">はじめに: 房室結節リエントリー性頻脈 (AVNRT) は最も一般的な上室性頻拍であり、一般に良性と考えられており、カテーテル アブレーション後に優れた転帰が得られます。 しかし、複数の併存疾患や手術リスクの増加を示すことが多い超高齢患者（80 歳以上）における手術の安全性と有効性に関するデータは依然として限られています。 この研究は、大規模な電気生理学センターで治療を受けた80代の患者における緩徐経路アブレーションまたは調節（SPA/SPM）の急性有効性と合併症率を評価することを目的としていました。 
+【方法】
+2001年から2024年の間にAVNRTで初めてSPA/SPMを受けた連続80代患者全員を遡及的に分析した。 有効性の主要評価項目は、処置終了時の AVNRT の非誘導性であった。 安全性エンドポイントには、房室ブロック（AVB）、心嚢液貯留、およびバスキュラーアクセス合併症が含まれていました。 臨床転帰は、すべての年齢層にわたる SPA/SPM を受けている 6,020 人の患者からなる大規模な施設コホートと比較されました。 
+【結果】
+ 合計 106 人の 80 代患者 (平均年齢 83.6 歳) が対象となった。 急性処置の成功は 104 人の患者 (98.1%) で達成されました。 一時的な房室伝導障害のため、2 つの処置が途中で終了しました。 処置後の AVB が 2 人の患者で発生し、1 人の患者では永久的なペースメーカーの埋め込みが必要であった。 心嚢穿刺を必要とする心嚢液貯留が 2 人の患者で発生した。 4人の患者は重大な出血または血管アクセスの合併症を発症し、1人は外科的介入を必要とした。 平均在院日数は1.3日であった。 コホート全体と比較して、80代では合併症率が高かった（AVB: 1.9% vs. 0.12%;心嚢液貯留: 1.9% vs. 0.08%;出血: 3.8% vs. 0.37%)、手続きの成功率は同様に高いままであった。 
+【結論】
+ 80代のAVNRTに対するSPA/SPMは非常に効果的であり、若年層と同等の優れた急性成功率を示しています。 ただし、大規模な施設コホートや以前に報告されたデータと比較すると、合併症発生率は増加しています。 これらの発見は、この増加しつつある脆弱な患者集団においてカテーテルアブレーションを検討する際には、慎重な患者選択、徹底的なリスク利益評価、およびカスタマイズされた手術戦略の必要性を浮き彫りにしています。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -1965,7 +2018,16 @@
     <t>10.1111/jce.70514 doi</t>
   </si>
   <si>
-    <t>背景: ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。 目的: 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。 方法: 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。 完全な報告を行ったセンターのみが含まれていました。 患者はモダリティごとにグループ化されました。 重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価されました。 多変量解析により、結果の独立した予測因子が特定されました。 結果: 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。 処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最も長かった。 (p &lt; 0.001)。 PFA では重大な合併症は発生しませんでした。 横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。 心膜液貯留は RF 後により頻繁に発生しました (0.91% vs. CRYO + PFA の場合は 0.34%。 p = 0.032)。 全体的な合併症発生率は PFA で最も低かった (0% vs. RF: 2.19%, CRYO: 2.59%).  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。 良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。 結論: POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
+    <t xml:space="preserve">【背景】
+ ポーランド国立アブレーションレジストリ (POL-AR) は、カテーテルアブレーションを実施するすべての施設に必須であり、国民健康基金のデータと統合されており、連続するすべての患者を完全に含めた全国コホートの前向き分析を可能にします。 
+【目的】
+ 私たちは、高周波 (RF)、クライオバルーン (CRYO)、パルスフィールド アブレーション (PFA) などの心房細動 (AF) アブレーション療法の実際の安全性プロファイルと臨床転帰を評価し、ポーランドでの初年度の PFA 経験を報告することを目的としました。 
+【方法】
+ 2023 年のすべての AF アブレーションは、POL-AR で前向きに分析され、国民健康基金のデータと相互参照されました。 完全な報告を行ったセンターのみが含まれていました。 患者はモダリティごとにグループ化されました。 重大な合併症、計画外の入院、電気的除細動、反復アブレーション、および死亡は1年後に評価された。 多変量解析により、結果の独立した予測因子が特定されました。 
+【結果】
+ 28 の施設から 3,430 人の患者が報告された (CRYO: 2,125; RF: 1,098; PFA: 207)。 処置時間は、CRYO (75 分) および PFA (65 分) に対して、RF (中央値 120 分) が最も長かった。 (p &lt; 0.001)。 PFA では重大な合併症は発生しなかった。 横隔神経損傷は、CRYO 患者の 1.51%、RF 患者の 0.09%、PFA 患者の 0% で持続しました (p &lt; 0.001)。 心膜液貯留は RF 後により頻繁に発生しました (0.91% vs. CRYO + PFA の場合は 0.34%。 p = 0.032)。 全体的な合併症発生率は PFA で最も低かった (0% vs. RF: 2.19%, CRYO: 2.59%).  PFA 患者では、追跡調査中に必要な電気的ディオバージョンが少なくなりました (p = 0.017)。 不良転帰の予測因子には、年齢、女性の性別、左心房 (LA) サイズ、高血圧、肥大型心筋症 (HCM) が含まれていました。 良好な転帰は、左室駆出率（LVEF）の上昇、発作性AF、およびPFAの使用と独立して関連していた（HR 0.70、p = 0.04）。 
+【結論】
+ POL-AR レジストリでは、PFA は独立して AF アブレーション後の良好な転帰と関連していました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -1996,7 +2058,14 @@
     <t>10.1007/s10840-026-02445-0 doi</t>
   </si>
   <si>
-    <t>背景: 心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点は依然として不明瞭です。 このメタ分析では、先制的 MCS の有効性と安全性を VT アブレーションの標準治療と比較しました。 方法: PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定されました。 MCS には、経皮的左心室補助装置または体外膜型人工肺が含まれます。 主要評価項目は全死因死亡率でした。副次評価項目には、VT再発、手術時間、手術合併症（バスキュラーアクセス、出血、脳​​卒中、心嚢液貯留、心不全、心筋梗塞）、および30日間の主要心血管有害事象（MACE）が含まれた。 結果：2,262人の患者（MCSあり414人、MCSなし1,848人）を対象とした8件の研究が含まれた。 平均追跡調査期間は15.8カ月、平均年齢は62.6歳、12.5％が女性で、平均PAINESDスコアはMCS群で15.7、非MCS群で10.5であった。 全死因死亡率（OR 1.58、95% CI 0.60-4.19、p = 0.36、I²=81%）またはVT再発（OR 1.03、95% CI 0.68-1.56、p = 0.90、I²=46%）には有意差はありませんでした。 先制的MCSは、より長い手術時間（平均差46.0分、95％CI 11.1-80.8、p = 0.01、I2 = 86％）、血管アクセスおよび心膜液貯留による手術合併症の増加と関連していた（OR 2.25、95％CI 1.26-4.03、p = 0.006、 I²=33%)。 30 日間 MACE は研究全体で統一的に定義されていないため、統合されませんでした。 結論: 先制的 MCS は、VT アブレーションを受けている患者の全死因死亡率や VT 再発に有意な差は見られなかったが、処置の長期化と処置上の合併症の増加と関連していた。 観察研究のデザイン、グループ間のベースラインの不均衡、不均一性を反映して、証拠の確実性は非常に低かった。これらの所見は、高リスク患者におけるMCSの選択的使用を妨げるものではなく、ランダム化試験での確認が必要である。</t>
+    <t xml:space="preserve">【背景】
+ 心室頻拍 (VT) アブレーションに対する先制的機械的循環補助 (MCS) の利点は依然として不明瞭です。 このメタ分析では、先制的 MCS の有効性と安全性を VT アブレーションの標準治療と比較しました。 
+【方法】
+ PubMed、Embase、および Web of Science の無制限の文献検索により、VT アブレーションのための先制的 MCS に関する研究が特定されました。 MCS には、経皮的左心室補助装置または体外膜型人工肺が含まれます。 主要評価項目は全死因死亡率であった。副次評価項目には、VT再発、手術時間、手術合併症（バスキュラーアクセス、出血、脳​​卒中、心嚢液貯留、心不全、心筋梗塞）、および30日間の主要心血管有害事象（MACE）が含まれた。 
+【結果】
+2,262人の患者（MCSあり414人、MCSなし1,848人）を対象とした8件の研究が含まれた。 平均追跡調査期間は15.8カ月、平均年齢は62.6歳、12.5％が女性で、平均PAINESDスコアはMCS群で15.7、非MCS群で10.5であった。 全死因死亡率（OR 1.58、95% CI 0.60-4.19、p = 0.36、I²=81%）またはVT再発（OR 1.03、95% CI 0.68-1.56、p = 0.90、I²=46%）には有意差はありなかった。 先制的MCSは、より長い手術時間（平均差46.0分、95％CI 11.1-80.8、p = 0.01、I2 = 86％）、血管アクセスおよび心膜液貯留による手術合併症の増加と関連していた（OR 2.25、95％CI 1.26-4.03、p = 0.006、 I²=33%)。 30 日間 MACE は研究全体で統一的に定義されていないため、統合されなかった。 
+【結論】
+ 先制的 MCS は、VT アブレーションを受けている患者の全死因死亡率や VT 再発に有意な差は見られなかったが、処置の長期化と処置上の合併症の増加と関連していた。 観察研究のデザイン、グループ間のベースラインの不均衡、不均一性を反映して、証拠の確実性は非常に低かった。これらの所見は、高リスク患者におけるMCSの選択的使用を妨げるものではなく、ランダム化試験での確認が必要である。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2025,7 +2094,12 @@
     <t>10.1111/jce.70502 doi</t>
   </si>
   <si>
-    <t>背景：我々は以前、心房細動（AF）の非肺静脈（PV）誘因は左心房（LA）の低電圧領域（LVA）から生じることが多いと報告した。 ただし、トリガー部位と LVA の分布の間の具体的な空間的関係は完全には解明されていません。 この研究は、サイト固有のベースで関係を分析することを目的としました。 方法と結果：カテーテルアブレーションを受けているAF患者1,428人のうち、非PV誘因に対して陽性反応を示した187人（13.1%）が登録された。 各トリガー部位と左心房 LVA の間の空間的関係が評価されました。 研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました。 平均年齢、eGFR、BNP、BMI、LAD、LVEFはそれぞれ68±11歳、59.9±18.5mL/min/1.73m、116.6±281.4pg/mL、23.3±3.6kg/m、41.7±6.5mm、59±7.8%であった。 再現性がないため、18 例では非 PV トリガー部位を特定できませんでした。 残りの 169 件では、140 件 (82.8%) で単一の非 PV トリガーが特定され、29 件 (17.2%) では複数のトリガーが示されました。 評価された 99 の LA 非 PV トリガーのうち、61 (61.6%) は LVA 内で発生しました。 無傷の領域からの残りの非 PV トリガーの半分は、LVA の近くからのものでした。 具体的には、後部/中隔/下トリガーの半分以上がLVAから生じたのに対し、前部/屋根トリガーはすべてLVAから生じた。 患者は、トリガーの位置に基づいて、胸静脈（上大静脈、冠状静脈洞、左上大静脈開存）、右心房（RA）、中隔、LA、複数のトリガー、および未確認トリガーの 6 つのグループに分類されました。 24 か月の追跡調査では、心房頻脈性不整脈のない率は、原因不明および複数のトリガーのグループで有意に低かった (p &lt; 0.05)。 結論: LA の非 PV トリガーは、特に LA の屋根と前壁で LVA と密接に関連していますが、後壁、中隔、および下壁ではこの関連性はそれほど一貫していません。 電圧マッピング パターンは、LA 内の非 PV トリガー サイトの位置特定と検出を容易にする可能性があります。</t>
+    <t xml:space="preserve">【背景】
+我々は以前、心房細動（AF）の非肺静脈（PV）誘因は左心房（LA）の低電圧領域（LVA）から生じることが多いと報告した。 ただし、トリガー部位と LVA の分布の間の具体的な空間的関係は完全には解明されていません。 この研究は、サイト固有のベースで関係を分析することを目的としました。 方法と
+【結果】
+カテーテルアブレーションを受けているAF患者1,428人のうち、非PV誘因に対して陽性反応を示した187人（13.1%）が登録された。 各トリガー部位と左心房 LVA の間の空間的関係が評価された。 研究対象者には男性 121 人 (66%)、非発作性 AF 患者 110 人 (59%)、やり直しセッションを受けている 93 人 (50%) が含まれていました。 平均年齢、eGFR、BNP、BMI、LAD、LVEFはそれぞれ68±11歳、59.9±18.5mL/min/1.73m、116.6±281.4pg/mL、23.3±3.6kg/m、41.7±6.5mm、59±7.8%であった。 再現性がないため、18 例では非 PV トリガー部位を特定できなかった。 残りの 169 件では、140 件 (82.8%) で単一の非 PV トリガーが特定され、29 件 (17.2%) では複数のトリガーが示された。 評価された 99 の LA 非 PV トリガーのうち、61 (61.6%) は LVA 内で発生しました。 無傷の領域からの残りの非 PV トリガーの半分は、LVA の近くからのものであった。 具体的には、後部/中隔/下トリガーの半分以上がLVAから生じたのに対し、前部/屋根トリガーはすべてLVAから生じた。 患者は、トリガーの位置に基づいて、胸静脈（上大静脈、冠状静脈洞、左上大静脈開存）、右心房（RA）、中隔、LA、複数のトリガー、および未確認トリガーの 6 つのグループに分類されました。 24 か月の追跡調査では、心房頻脈性不整脈のない率は、原因不明および複数のトリガーのグループで有意に低かった (p &lt; 0.05)。 
+【結論】
+ LA の非 PV トリガーは、特に LA の屋根と前壁で LVA と密接に関連していますが、後壁、中隔、および下壁ではこの関連性はそれほど一貫していません。 電圧マッピング パターンは、LA 内の非 PV トリガー サイトの位置特定と検出を容易にする可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2052,7 +2126,16 @@
     <t>10.1016/j.hrthm.2026.09.018 doi</t>
   </si>
   <si>
-    <t>背景：グルカゴン様ペプチド-1受容体アゴニスト（GLP-1 RA）およびナトリウム-グルコース共輸送体2阻害剤（SGLT2i）は心血管疾患の転帰を改善するが、AFに対するカテーテルアブレーション（CA）後の心房細動（AF）再発に対するそれらの効果は未定義のままである。 目的: カテーテルアブレーション後の AF 再発に対する GLP-1 RA、SGLT2i、およびそれらの組み合わせの影響を評価すること。 方法： TriNetX データベース（2018～2024 年）を使用して、AF に対して CA を受けた成人 AF を、CA 前 12 か月以内に GLP-1 RA、SGLT2i、または併用によってグループ分けしました。 主要アウトカムはAF再発で、3か月のブランク期間後の反復CA、電気除細動、または抗不整脈薬の使用として定義された。 傾向スコア マッチング (PSM) を、GLP-1 RA 対 SGLT2i、組み合わせ 対 GLP-1 RA、および組み合わせ 対 SGLT2i に適用しました。 結果: GLP-1 RA 対 SGLT2i (それぞれ n=1,393) では、AF 再発は同様でした (HR 1.01、95% CI 0.89-1.15; p=0.86)。 併用群と GLP-1 RA (各 n=952) では、再発は同様でしたが (HR 1.13、95% CI 0.98-1.31; p=0.10)、全死亡率は併用群の方が低かった (HR 0.54、95% CI 0.34-0.87; p=0.01)。 SGLT2i との併用（各 n=1,213）では、再発は同様でした（HR 1.09、95% CI 0.96-1.24; p=0.20）が、全死因死亡率は減少しました（HR 0.60、95% CI 0.39-0.93; p=0.02）。 脳卒中、心不全、全原因による入院などの二次転帰は、3 つのグループすべてで同様でした。 結論: GLP-1 RA と SGLT2i の単独または組み合わせは、AF に対する CA 後の同等の AF 再発率と関連していました。 しかし、併用療法は一貫して全死因死亡率の低下と関連していました。</t>
+    <t xml:space="preserve">【背景】
+グルカゴン様ペプチド-1受容体アゴニスト（GLP-1 RA）およびナトリウム-グルコース共輸送体2阻害剤（SGLT2i）は心血管疾患の転帰を改善するが、AFに対するカテーテルアブレーション（CA）後の心房細動（AF）再発に対するそれらの効果は未定義のままである。 
+【目的】
+ カテーテルアブレーション後の AF 再発に対する GLP-1 RA、SGLT2i、およびそれらの組み合わせの影響を評価すること。 
+【方法】
+ TriNetX データベース（2018～2024 年）を使用して、AF に対して CA を受けた成人 AF を、CA 前 12 か月以内に GLP-1 RA、SGLT2i、または併用によってグループ分けしました。 主要アウトカムはAF再発で、3か月のブランク期間後の反復CA、電気除細動、または抗不整脈薬の使用として定義された。 傾向スコア マッチング (PSM) を、GLP-1 RA 対 SGLT2i、組み合わせ 対 GLP-1 RA、および組み合わせ 対 SGLT2i に適用しました。 
+【結果】
+ GLP-1 RA 対 SGLT2i (それぞれ n=1,393) では、AF 再発は同様であった (HR 1.01、95% CI 0.89-1.15; p=0.86)。 併用群と GLP-1 RA (各 n=952) では、再発は同様であったが (HR 1.13、95% CI 0.98-1.31; p=0.10)、全死亡率は併用群の方が低かった (HR 0.54、95% CI 0.34-0.87; p=0.01)。 SGLT2i との併用（各 n=1,213）では、再発は同様であった（HR 1.09、95% CI 0.96-1.24; p=0.20）が、全死因死亡率は減少しました（HR 0.60、95% CI 0.39-0.93; p=0.02）。 脳卒中、心不全、全原因による入院などの二次転帰は、3 つのグループすべてで同様であった。 
+【結論】
+ GLP-1 RA と SGLT2i の単独または組み合わせは、AF に対する CA 後の同等の AF 再発率と関連していました。 しかし、併用療法は一貫して全死因死亡率の低下と関連していました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2083,7 +2166,16 @@
     <t>10.1111/jce.70516 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティです。 ただし、治療中の患者の適切な鎮静は不可欠です。 目的：私たちの目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することでした。 方法：2021年から2024年までにペンタスプリンPFA技術による初回AFアブレーションを受けたデンマーク人患者全員が対象となった。 患者は鎮静戦略に従って層別化されました。 EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。 GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われました。 結果: 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。 全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありませんでした。 EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が長引いたため、予期せず麻酔科医がバックアップを求められました。 AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありませんでした。 GA グループでは、手術周囲の鎮静による合併症は発生しませんでした。 鎮静群間で 1 年心房頻脈再発率に差は見られませんでした。 結論：この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しませんでした。 観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されませんでした。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールドアブレーション (PFA) は、心房細動 (AF) アブレーションのための新たなモダリティです。 ただし、治療中の患者の適切な鎮静は不可欠です。 
+【目的】
+私たちの目的は、PFA AF アブレーション中の電気生理学スタッフによる深い鎮静（DS）（EP-DS）、麻酔看護師による DS（AN-DS）、および全身麻酔（GA）後の安全性と転帰を比較することであった。 
+【方法】
+2021年から2024年までにペンタスプリンPFA技術による初回AFアブレーションを受けたデンマーク人患者全員が対象となった。 患者は鎮静戦略に従って層別化されました。 EP-DS と AN-DS は、それぞれ EP スタッフと麻酔看護師によって管理される補助換気なしの鎮静と定義されました。 GA の患者は気管内挿管を受け、麻酔スタッフによって監視されました。 鎮静戦略に対する患者の選択は、施設内の慣行に基づいて行われた。 
+【結果】
+ 1,269 人の患者のうち、661 人 (52%) が EP-DS を受け、173 人 (14%) が AN-DS を受け、435 人 (34%) が GA を受けました。 全体として、鎮静による合併症はほとんどなく、鎮静の悪影響により処置が中止されることはありなかった。 EP-DS グループでは、1 人 (0.2%) の患者で、処置中に低血圧が長引いたため、予期せず麻酔科医がバックアップを求められました。 AN-DS グループでは、1 人の患者 (0.6%) が飽和度低下のために麻酔科医を呼びましたが、挿管へのエスカレーションは必要ありなかった。 GA グループでは、手術周囲の鎮静による合併症は発生しなかった。 鎮静群間で 1 年心房頻脈再発率に差は見られなかった。 
+【結論】
+この全国コホートでは、EP スタッフによる深い鎮静は実行可能であり、PFA 中に臨床的に重大な鎮静関連の有害事象はほとんど発生しなかった。 観察された心房性頻脈性不整脈の再発率には、鎮静戦略間で有意な差は確認されなかった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2114,7 +2206,14 @@
     <t>10.1007/s10840-026-02437-0 doi</t>
   </si>
   <si>
-    <t>背景: 胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因と考えられています。 積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。 食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。 私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することでした。 方法: 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価されました。 胸痛については別に質問した。 人口動態変数と手続き変数との関連性が評価されました。 結果：アブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が食道冷却を受け、44 名（14.9%）が GERD ≧ 8 の基準を満たし、71 名（24.1%）が CP を報告した。 前方最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 対 50.0）。 54.0 ± 14.0 W, p = 0.020).  CP を報告した参加者は若かった（64.5 ± 9.3 vs. 67.5 ± 10.2 年、p = 0.026）、より高い平均駆出率（57.1 ± 6.6% vs. 53.1 ± 10.2%, p = 0.001).  初回パスで両側性隔離が達成された場合、胸痛はあまり発生しませんでした（59.2% 対 59.2%）。 72.6%, p = 0.033).  結論：積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。 これらの所見は、食道の保護にもかかわらず、処置上の要因と参加者固有の要因の両方が症状の発症に寄与している可能性があることを示唆しています。</t>
+    <t xml:space="preserve">【背景】
+ 胃食道逆流症（GERD）と胸痛は、心房細動（AF）に対するカテーテルアブレーション後の一般的な合併症であり、多くの場合、食道の熱損傷が原因と考えられています。 積極的な食道冷却は熱損傷のリスクを軽減しますが、胃食道逆流症の症状は軽減しない可能性があります。 食道の冷却にもかかわらず、これらの合併症に関連する要因は不明のままです。 私たちの目的は、食道冷却を伴う高周波アブレーション (RFA) を受けている AF 参加者におけるアブレーション後 GERD および (CP) に関連する参加者および手順の特徴を特定することであった。 
+【方法】
+ 発作性または持続性 AF に対して食道冷却を伴う RFA を受けている参加者は、標準化されたアンケートに回答しました。 GERD の症状は、手順の 7 ～ 14 日後に GERDQ (スコア ≥ 8 の GERD の高確率) で評価された。 胸痛については別に質問した。 人口動態変数と手続き変数との関連性が評価された。 
+【結果】
+アブレーション後のアンケートに回答した最大参加者 312 名のうち 295 名が食道冷却を受け、44 名（14.9%）が GERD ≧ 8 の基準を満たし、71 名（24.1%）が CP を報告した。 前方最大出力は、胃食道逆流症のある参加者では、そうでない参加者と比較して有意に低かった（50.0 対 50.0）。 54.0 ± 14.0 W, p = 0.020).  CP を報告した参加者は若かった（64.5 ± 9.3 vs. 67.5 ± 10.2 年、p = 0.026）、より高い平均駆出率（57.1 ± 6.6% vs. 53.1 ± 10.2%, p = 0.001).  初回パスで両側性隔離が達成された場合、胸痛はあまり発生しなかった（59.2% 対 59.2%）。 72.6%, p = 0.033).  
+【結論】
+積極的な食道冷却を伴うAFアブレーションを受けた参加者では、年齢が若く、駆出率が高く、両側初回通過隔離の欠如がアブレーション後のCPと関連していた。 これらの所見は、食道の保護にもかかわらず、処置上の要因と参加者固有の要因の両方が症状の発症に寄与している可能性があることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2143,7 +2242,14 @@
     <t>10.1016/j.hrthm.2026.09.036 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心房細動 (PersAF) 治療における、肺静脈隔離 (PVI) を超えた追加の左心房後壁アブレーション (LAPWA) の利点については、依然として議論の余地がある。 目的：ペンタスプラインパルスフィールドアブレーション（PFA）カテーテルで記録された信号が、LAPWAの恩恵を受ける可能性のある急速なLAPW活動を示すPersAF患者を特定できるかどうかを調査しました。 さらに、PFA 誘発性心房細動周期長 (AF-CL) 延長が不整脈のない生存を予測するかどうかを評価しました。 この多施設観察研究には、ペンタスプライン PFA カテーテルによる初回 PVI プラス LAPWA を受けている連続した PersAF 患者が含まれていました。 AF-CL は、遠位 CS 信号を使用して、ベースライン、PVI 後、LAPWA 後の 3 つの時点で FARS-10 法を使用して測定されました。 LAPW-CL は、PVI 後に複数の LAPW 位置から測定されました。 2 か月のブランク期間を超えて 30 秒以上続く心房性頻脈性不整脈 (ATA) が記録されました。 結果: 270 人の患者が含まれた。 ATA を使用しない場合の全体的な 12 か月生存率は 72.6% でした。 「速いLAPW活性」は、コホート全体の平均LAPW-CL（191.4±2.4ミリ秒；≦190ミリ秒）よりも短いLAPW-CL値として定義された。 速い LAPW 活動は不整脈の再発と関連しませんでした (HR 1.263、95% CI: 0.739-2.160; p=0.393)。 対照的に、CS-CLの延長が大きいほど、不整脈再発リスクの低下と独立して関連していた（HR 0.298、95% CI: 0.017-0.520; ベースラインからのp23.5%は、ATAフリー生存率の予測に関して感度0.65、特異度0.72であった）。 結論: PVI 後の高速 LAPW 活動は、PersAF 患者における LAPWA 後の再発を予測しません。 LAPWA 後の CS-CL 延長 &gt;23.5% は、効果的な基質修飾と不整脈制御の有用なリアルタイム マーカーとして機能する可能性があります。</t>
+    <t xml:space="preserve">【背景】
+ 持続性心房細動 (PersAF) 治療における、肺静脈隔離 (PVI) を超えた追加の左心房後壁アブレーション (LAPWA) の利点については、依然として議論の余地がある。 
+【目的】
+ペンタスプラインパルスフィールドアブレーション（PFA）カテーテルで記録された信号が、LAPWAの恩恵を受ける可能性のある急速なLAPW活動を示すPersAF患者を特定できるかどうかを調査しました。 さらに、PFA 誘発性心房細動周期長 (AF-CL) 延長が不整脈のない生存を予測するかどうかを評価しました。 この多施設観察研究には、ペンタスプライン PFA カテーテルによる初回 PVI プラス LAPWA を受けている連続した PersAF 患者が含まれていました。 AF-CL は、遠位 CS 信号を使用して、ベースライン、PVI 後、LAPWA 後の 3 つの時点で FARS-10 法を使用して測定されました。 LAPW-CL は、PVI 後に複数の LAPW 位置から測定されました。 2 か月のブランク期間を超えて 30 秒以上続く心房性頻脈性不整脈 (ATA) が記録されました。 
+【結果】
+ 270 人の患者が含まれた。 ATA を使用しない場合の全体的な 12 か月生存率は 72.6% であった。 「速いLAPW活性」は、コホート全体の平均LAPW-CL（191.4±2.4ミリ秒；≦190ミリ秒）よりも短いLAPW-CL値として定義された。 速い LAPW 活動は不整脈の再発と関連しなかった (HR 1.263、95% CI: 0.739-2.160; p=0.393)。 対照的に、CS-CLの延長が大きいほど、不整脈再発リスクの低下と独立して関連していた（HR 0.298、95% CI: 0.017-0.520; ベースラインからのp23.5%は、ATAフリー生存率の予測に関して感度0.65、特異度0.72であった）。 
+【結論】
+ PVI 後の高速 LAPW 活動は、PersAF 患者における LAPWA 後の再発を予測しません。 LAPWA 後の CS-CL 延長 &gt;23.5% は、効果的な基質修飾と不整脈制御の有用なリアルタイム マーカーとして機能する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2174,7 +2280,16 @@
     <t>10.1016/j.hrthm.2026.09.031 doi</t>
   </si>
   <si>
-    <t>背景: 左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略です。 目的:肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること。 方法: この CORNERSTONE-AF ランダム化試験のサブ分析では、PVI 単独 (n=259) と PVI+LAPWI (n=254) の間で 18 か月の転帰を比較しました。 主要評価項目は心房性不整脈がないことでした。 副次評価項目には、繰り返しアブレーションを行わないことが含まれていました。 ランダム化は、PVI アブレーション モダリティによって階層化されました。 結果: PVI は、それぞれ 384 人の患者と 129 人の患者に対して高周波アブレーションとクライオバルーン アブレーションを使用して実施されました。 LAPWI グループでは、LAPWI 領域は高周波サブグループよりクライオバルーンの方が有意に大きかった。 LAPWI を追加すると、両方のサブグループで蛍光透視時間が増加することなく、処置時間が大幅に延長されました。 クライオバルーンサブグループでは、18 か月間心房性不整脈が発生しなかった率は、PVI 単独よりも LAPWI を使用した方が数値的に高かった（82.0% 対 82.0%）。 69.1%、P=0.163)、一方、高周波サブグループでは差は観察されませんでした(80.5% vs. 79.4%, P=0.309).  治療法ごとの相互作用はありませんでした（相互作用の P = 0.64）。 クライオバルーンサブグループでは、LAPWI の方が繰り返しアブレーションを行わない率が高かった (96.5% 対 82.0%、P=0.029）、しかし高周波サブグループには含まれていません（90.1% vs. 88.5%、P=0.210）、治療法ごとの有意な相互作用はありませんでした（相互作用の P = 0.17）。 全体的な合併症発生率はグループ間で同様でした。症候性胃不全麻痺は、高周波 LAPWI サブグループの 3 人の患者で発生しました。 結論: 補助的な LAPWI は、いずれのアブレーション モダリティでも心房性不整脈からの解放を大幅には改善せず、モダリティごとの有意な相互作用はありませんでした。 クライオバルーン PVI 後の LAPWI による潜在的に好ましい結果は、探索的であり仮説生成であると考えられるべきです。</t>
+    <t xml:space="preserve">【背景】
+ 左心房後壁分離 (LAPWI) は、持続性または長期持続性心房細動に対する一般的な補助アブレーション戦略です。 
+【目的】
+肺静脈分離 (PVI) アブレーション モダリティに従って補助的な LAPWI の影響を調査すること。 
+【方法】
+ この CORNERSTONE-AF ランダム化試験のサブ分析では、PVI 単独 (n=259) と PVI+LAPWI (n=254) の間で 18 か月の転帰を比較しました。 主要評価項目は心房性不整脈がないことであった。 副次評価項目には、繰り返しアブレーションを行わないことが含まれていました。 ランダム化は、PVI アブレーション モダリティによって階層化されました。 
+【結果】
+ PVI は、それぞれ 384 人の患者と 129 人の患者に対して高周波アブレーションとクライオバルーン アブレーションを使用して実施されました。 LAPWI グループでは、LAPWI 領域は高周波サブグループよりクライオバルーンの方が有意に大きかった。 LAPWI を追加すると、両方のサブグループで蛍光透視時間が増加することなく、処置時間が大幅に延長されました。 クライオバルーンサブグループでは、18 か月間心房性不整脈が発生しなかった率は、PVI 単独よりも LAPWI を使用した方が数値的に高かった（82.0% 対 82.0%）。 69.1%、P=0.163)、一方、高周波サブグループでは差は観察されなかった(80.5% vs. 79.4%, P=0.309).  治療法ごとの相互作用はありなかった（相互作用の P = 0.64）。 クライオバルーンサブグループでは、LAPWI の方が繰り返しアブレーションを行わない率が高かった (96.5% 対 82.0%、P=0.029）、しかし高周波サブグループには含まれていません（90.1% vs. 88.5%、P=0.210）、治療法ごとの有意な相互作用はありなかった（相互作用の P = 0.17）。 全体的な合併症発生率はグループ間で同様であった。症候性胃不全麻痺は、高周波 LAPWI サブグループの 3 人の患者で発生しました。 
+【結論】
+ 補助的な LAPWI は、いずれのアブレーション モダリティでも心房性不整脈からの解放を大幅には改善せず、モダリティごとの有意な相互作用はありなかった。 クライオバルーン PVI 後の LAPWI による潜在的に好ましい結果は、探索的であり仮説生成であると考えられるべきです。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2205,7 +2320,16 @@
     <t>10.1016/j.hrthm.2026.08.058 doi</t>
   </si>
   <si>
-    <t>背景: 頻繁に起こる早発心室複合体 (PVC) のアブレーションは、収縮機能不全を有する患者、特に PVC 誘発性心筋症が疑われる患者の左心室駆出率 (LVEF) を改善する可能性があります。 しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません。 目的: この研究の目的は、PVC アブレーション後の LVEF 回復を予測するために、日常的に利用可能な臨床変数、心エコー図変数、および心電図変数を使用して機械学習 (ML) モデルを開発し、外部で検証することでした。 方法: この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました。 Boruta アルゴリズムを使用して予測子が選択され、5 つの ML モデルがトレーニングされました。 パフォーマンスは、10 分割相互検証と受信者動作特性曲線分析によって評価されました。 最もパフォーマンスの高いモデルはキャリブレーションと閾値分析を受け、追加の 3 つのセンターからの独立したコホートで外部検証されました。 結果: ランダム フォレスト モデルは最高のパフォーマンスを示し、内部テスト セットの曲線下面積は 0.88 (95% 信頼区間 = 0.79-0.98)、良好なキャリブレーション (Hosmer-Lemeshow P = 0.562) でした。 外部検証により、一貫した識別が確認されました (曲線下面積 = 0.83、95% 信頼区間 = 0.72-0.95)。 主要な予測因子には、ベースラインの PVC 負荷、洞調律における QRS 持続時間、および術前の LVEF が含まれます。 結論: この ML ベースのツールは、広く利用可能な変数に基づいて構築されており、PVC アブレーション後の LVEF 回復の確率を正確に推定し、臨床上の意思決定と患者のカウンセリングをサポートする可能性があります。</t>
+    <t xml:space="preserve">【背景】
+ 頻繁に起こる早発心室複合体 (PVC) のアブレーションは、収縮機能不全を有する患者、特に PVC 誘発性心筋症が疑われる患者の左心室駆出率 (LVEF) を改善する可能性があります。 しかし、多くの患者はアブレーションが成功したにもかかわらずLVEFの正常化を達成できず、現在のツールでは真のPVC誘発性心筋症とPVCによって増悪した根本的な心筋症を確実に区別することはできません。 
+【目的】
+ この研究の目的は、PVC アブレーション後の LVEF 回復を予測するために、日常的に利用可能な臨床変数、心エコー図変数、および心電図変数を使用して機械学習 (ML) モデルを開発し、外部で検証することであった。 
+【方法】
+ この後ろ向き多施設研究には、3 つの国際紹介施設で PVC アブレーションが成功した LVEF &lt;50% の患者 256 人が含まれていました。 Boruta アルゴリズムを使用して予測子が選択され、5 つの ML モデルがトレーニングされました。 パフォーマンスは、10 分割相互検証と受信者動作特性曲線分析によって評価された。 最もパフォーマンスの高いモデルはキャリブレーションと閾値分析を受け、追加の 3 つのセンターからの独立したコホートで外部検証されました。 
+【結果】
+ ランダム フォレスト モデルは最高のパフォーマンスを示し、内部テスト セットの曲線下面積は 0.88 (95% 信頼区間 = 0.79-0.98)、良好なキャリブレーション (Hosmer-Lemeshow P = 0.562) であった。 外部検証により、一貫した識別が確認されました (曲線下面積 = 0.83、95% 信頼区間 = 0.72-0.95)。 主要な予測因子には、ベースラインの PVC 負荷、洞調律における QRS 持続時間、および術前の LVEF が含まれます。 
+【結論】
+ この ML ベースのツールは、広く利用可能な変数に基づいて構築されており、PVC アブレーション後の LVEF 回復の確率を正確に推定し、臨床上の意思決定と患者のカウンセリングをサポートする可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2236,7 +2360,16 @@
     <t>10.1016/j.hrthm.2026.09.005 doi</t>
   </si>
   <si>
-    <t>背景: 現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨しています。 AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。 目的: この研究は、アブレーション後の長期的な心房細動負担を特徴づけ、リズム誘導型 OAC をモデル化することを目的としました。 方法：初回冷凍アブレーションを受けた発作性 AF 患者を対象に、植込み型心臓モニターの連続モニタリングによる COMPARE-CRYO 試験の事後分析を実施しました。 AF エピソードは独立して裁定されました。 リズムに基づく OAC 戦略は、CHADS-VA スコアが 1 以上の患者を対象に、異なる OAC ウィンドウ期間で 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上の毎日の負荷によって誘発され、モデル化されました。 結果：中央値3.3年の追跡期間にわたる201人の患者のうち、1日あたりの心房細動負担の中央値は0%（四分位範囲 = 0%-0.01%）で、96.5%の日で心房細動はありませんでした。 再発患者 108 人のうち、40% は非常に低い負担 (&lt;0.1%) を維持し、36% は低い負担 (0.1% ～ 1%) でした。 CHADS-VA ≥1 の患者 139 人のうち、6 分以上の AF によって引き起こされた再開継続戦略により、追跡調査の 32% で OAC が発生しました。 固定 OAC ウィンドウ (14 日または 30 日) を使用したピル・イン・ザ・ポケット戦略では、OAC が 90.8% ～ 99.4% 削減されました。 1 時間以上のしきい値と 30 日間の OAC ウィンドウが最も好ましいバランスを提供し、AF 時間の 97.5% をカバーし、OAC 曝露を 90.8% 削減しました。 結論: ほとんどの患者は、冷凍アブレーション後も一貫して低い心房細動負荷を維持しました。 リズムガイドによる抗凝固療法は、OAC を大幅に減少させる可能性があり、1 時間以上の閾値が OAC 減少と AF 適用時間のバランスを最も良く保ちます。 これらの戦略には、臨床転帰の前向き評価が必要です。</t>
+    <t xml:space="preserve">【背景】
+ 現在のガイドラインでは、心房細動 (AF) の負担に関係なく、脳卒中リスクに基づいて心房細動 (AF) 患者に対して生涯にわたる経口抗凝固療法 (OAC) を推奨しています。 AF後のアブレーション試験では、脳卒中率が予想より低いことが報告されており、OACをAF再発期間に備えて使用できるかどうか、つまりリズムに基づいたポケットの薬戦略が可能かどうかという疑問が生じている。 
+【目的】
+ この研究は、アブレーション後の長期的な心房細動負担を特徴づけ、リズム誘導型 OAC をモデル化することを目的としました。 
+【方法】
+初回冷凍アブレーションを受けた発作性 AF 患者を対象に、植込み型心臓モニターの連続モニタリングによる COMPARE-CRYO 試験の事後分析を実施しました。 AF エピソードは独立して裁定されました。 リズムに基づく OAC 戦略は、CHADS-VA スコアが 1 以上の患者を対象に、異なる OAC ウィンドウ期間で 6 分以上、1 時間以上、5.5 時間以上、23.5 時間以上の毎日の負荷によって誘発され、モデル化されました。 
+【結果】
+中央値3.3年の追跡期間にわたる201人の患者のうち、1日あたりの心房細動負担の中央値は0%（四分位範囲 = 0%-0.01%）で、96.5%の日で心房細動はありなかった。 再発患者 108 人のうち、40% は非常に低い負担 (&lt;0.1%) を維持し、36% は低い負担 (0.1% ～ 1%) であった。 CHADS-VA ≥1 の患者 139 人のうち、6 分以上の AF によって引き起こされた再開継続戦略により、追跡調査の 32% で OAC が発生しました。 固定 OAC ウィンドウ (14 日または 30 日) を使用したピル・イン・ザ・ポケット戦略では、OAC が 90.8% ～ 99.4% 削減されました。 1 時間以上のしきい値と 30 日間の OAC ウィンドウが最も好ましいバランスを提供し、AF 時間の 97.5% をカバーし、OAC 曝露を 90.8% 削減しました。 
+【結論】
+ ほとんどの患者は、冷凍アブレーション後も一貫して低い心房細動負荷を維持しました。 リズムガイドによる抗凝固療法は、OAC を大幅に減少させる可能性があり、1 時間以上の閾値が OAC 減少と AF 適用時間のバランスを最も良く保ちます。 これらの戦略には、臨床転帰の前向き評価が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2270,7 +2403,15 @@
     <t>10.1093/europace/euag277 doi</t>
   </si>
   <si>
-    <t>背景と目的: 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。 この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することでした。 方法: 私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。 各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。 データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 結果：以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。 アブレーションは、LAAO 後中央値 271 日に実施されました。 アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間でした。 OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。 追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。 アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件ありました。 結論：既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれでした。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血事象を伴うアブレーション後の短期間の OAC に耐えました。</t>
+    <t xml:space="preserve">背景と
+【目的】
+ 左心耳 (LAAO) デバイスを装着した患者が AF アブレーションを受診することが増えていますが、抗凝固戦略は依然として不確実です。 この研究の目的は、既存の LAAO デバイスを装着した患者における心房細動 (AF) に対するカテーテル アブレーションの安全性と有効性を評価し、このユニークな集団におけるアブレーション後の抗凝固管理のパターンを説明することであった。 
+【方法】
+ 私たちは、以前に LAAO デバイスを使用して AF アブレーションを受けた患者に関するデータを世界中の 14 のセンターから収集しました。 各サイトでは、臨床的特徴、手順の詳細、合併症と不整脈の転帰に関する情報を提供しました。 データは集約され、管理戦略における手順の安全性、有効性、変動性を評価するために一元的に分析されました。 
+【結果】
+以前にLAAOを患った合計198人の患者（年齢70歳、女性37％、発作性AF42％）が含まれた。 アブレーションは、LAAO 後中央値 271 日に実施されました。 アブレーション後、患者の 84% が経口抗凝固療法 (OAC) を受けており、最も一般的な期間は 2 ～ 3 か月間であった。 OAC による出血合併症は、アブレーション後中央値 20 (13、70) 日で患者の 6.7% に発生しました。 追跡期間中に脳卒中またはTIAが5人の患者(症例の2.6%)で発生し、アブレーション翌日に2件(症例の1%)が発生した。 アブレーション後にデバイス周囲のリークが新たに発生した、または悪化したケースが 2 件あった。 
+【結論】
+既存の LAAO デバイスを使用して心房細動に対するカテーテルアブレーションを受けている患者の大規模な国際登録では、アブレーションは実行可能であり、デバイス関連の合併症はまれであった。LAAO 集団では出血リスクが高いにもかかわらず、以前 LAAO を患っていた患者の 84% が、この集団で予想される割合で出血事象を伴うアブレーション後の短期間の OAC に耐えました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2299,7 +2440,16 @@
     <t>10.1016/j.hrthm.2026.07.054 doi</t>
   </si>
   <si>
-    <t>背景: 機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性があります。 目的: 従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました。 方法: この前向き多施設登録では、梗塞後心室頻拍 (VT) 患者 166 人が前向き傾向スコア一致レジストリに登録されました。 心臓磁気共鳴イメージング/コンピューター断層撮影スキャンは、機能マッピングとアブレーション (Sense2) の焦点領域をターゲットにするために取得されました。 結果は、画像ガイダンスなしでマッピングを受けたグループ（センス）、および機能マッピングや画像ガイダンスなしで活性化/同調または基質ガイドによるマッピングとアブレーションを受けたグループ（施設）の結果と比較されました。 結果: Sense2 グループの平均手術時間 (145.8 ± 28.7 分) は、Sense グループ (171.0 ± 51.1 分) および施設内グループ (221.4 ± 73.9 分) よりも有意に短かった (P &lt; 0.0001)。 同様に、平均マッピング時間は、Sense2 グループ (25.4 ± 7.3 分) の方が Sense グループ (47.2 ± 8.9 分) よりも短かった。 アブレーション時間は、Sense グループ (21.6 ± 12.7 分) および施設内グループ (25.9 ± 13.9 分) と比較して、Sense2 グループ (18.1 ± 11.6 分) で有意に短縮されました (P = 0.006)。 Sense2 および Sense グループの患者は、施設内グループの患者よりも VT からの自由度が高く (両方とも P &lt; .001)、生存期間も改善されました (両方とも P &lt; .05)。 結論: イメージングと機能マッピングを統合した Sense2 プロトコルは、焦点を絞った基質マッピングの実行を可能にすることで処置時間を短縮し、施設内アブレーションと比較して VT の自由度の点で結果を改善しました。 生存率の向上には、多施設ランダム化試験による裏付けが必要です。</t>
+    <t xml:space="preserve">【背景】
+ 機能的基質マッピング技術は臨床現場でますます使用されていますが、マッピングと処置時間が長くなる可能性があります。 
+【目的】
+ 従来のアブレーション戦略と比較して、有効性と結果を評価するために、磁気共鳴画像法およびコンピューター断層撮影法由来の心室瘢痕データを機能マッピングのワークフローに組み込みました。 
+【方法】
+ この前向き多施設登録では、梗塞後心室頻拍 (VT) 患者 166 人が前向き傾向スコア一致レジストリに登録されました。 心臓磁気共鳴イメージング/コンピューター断層撮影スキャンは、機能マッピングとアブレーション (Sense2) の焦点領域をターゲットにするために取得されました。 結果は、画像ガイダンスなしでマッピングを受けたグループ（センス）、および機能マッピングや画像ガイダンスなしで活性化/同調または基質ガイドによるマッピングとアブレーションを受けたグループ（施設）の結果と比較されました。 
+【結果】
+ Sense2 グループの平均手術時間 (145.8 ± 28.7 分) は、Sense グループ (171.0 ± 51.1 分) および施設内グループ (221.4 ± 73.9 分) よりも有意に短かった (P &lt; 0.0001)。 同様に、平均マッピング時間は、Sense2 グループ (25.4 ± 7.3 分) の方が Sense グループ (47.2 ± 8.9 分) よりも短かった。 アブレーション時間は、Sense グループ (21.6 ± 12.7 分) および施設内グループ (25.9 ± 13.9 分) と比較して、Sense2 グループ (18.1 ± 11.6 分) で有意に短縮されました (P = 0.006)。 Sense2 および Sense グループの患者は、施設内グループの患者よりも VT からの自由度が高く (両方とも P &lt; .001)、生存期間も改善されました (両方とも P &lt; .05)。 
+【結論】
+ イメージングと機能マッピングを統合した Sense2 プロトコルは、焦点を絞った基質マッピングの実行を可能にすることで処置時間を短縮し、施設内アブレーションと比較して VT の自由度の点で結果を改善しました。 生存率の向上には、多施設ランダム化試験による裏付けが必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2330,7 +2480,14 @@
     <t>10.1007/s10840-026-02433-4 doi</t>
   </si>
   <si>
-    <t>目的: 肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られています。 PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。 方法：この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。 主要評価項目は、抗不整脈薬（AAD）を服用しなくても30秒以上続く心房性不整脈（AA）がなくなることでした。 手順の特徴と安全性の結果も評価されました。 結果: 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値 22 か月 (四分位範囲 (IQR): 9 ～ 35 か月) 後、81% vs. VOM-EI + AS と VOM-EI + AS では、患者の 47% が AAD なしで AA を発症していないままでした。 PVI のみのグループ (p &lt; 0.001)。 双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子でした（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。 逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。 結論: 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的でした。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。 持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
+    <t xml:space="preserve">【目的】
+ 肺静脈隔離 (PVI) アブレーションは、持続性心房細動 (PeAF) に対する効果が限られています。 PVI、マーシャルエタノール静脈注入（VOM-EI）、および主要な心房峡部をターゲットとした解剖学的アブレーション戦略（AS）を組み合わせた解剖学的戦略は、この状況で有望な短期成果を示しています。 
+【方法】
+この後ろ向き多施設観察コホート研究には、VOM-EI + ASまたはPVIのみを受けた連続したPeAF患者が含まれた。 主要評価項目は、抗不整脈薬（AAD）を服用しなくても30秒以上続く心房性不整脈（AA）がなくなることであった。 手順の特徴と安全性の結果も評価された。 
+【結果】
+ 2:1 の傾向スコアマッチングの後、VOM-EI + AS で治療された 151 人の患者と PVI のみで治療された 75 人の患者が比較されました。 追跡期間中央値 22 か月 (四分位範囲 (IQR): 9 ～ 35 か月) 後、81% vs. VOM-EI + AS と VOM-EI + AS では、患者の 47% が AAD なしで AA を発症していないままであった。 PVI のみのグループ (p &lt; 0.001)。 双方向僧帽弁峡部（MI）ブロックの達成は、不整脈のない生存の最も強力な独立予測因子であった（HR = 0.114; 95% CI: 0.041-0.321; p &lt; 0.001）。 逆に、長期にわたる PeAF は心房性不整脈再発リスクの増加と独立して関連していた (HR = 2.68; 95% CI: 1.240-5.812; p = 0.012)。 
+【結論】
+ 実際の PeAF 集団において、VOM-EI、PVI、および解剖学的線状病変を組み込んだ最初のアブレーション戦略は、長期追跡調査における不整脈再発の予防において、PVI 単独よりも大幅に効果的であった。 僧帽弁ラインを横切る双方向ブロックの検証と AF 持続時間は、長期的な成功の重要な決定要因です。 持続性心房細動患者では、マーシャルエタノール注入の静脈を含む最初の処置アブレーションと、肺静脈隔離と線状病変を組み合わせた解剖学的アブレーション戦略により、肺静脈隔離のみと比較して、長期不整脈のない生存率が大幅に改善されました。</t>
   </si>
   <si>
     <t xml:space="preserve">PURPOSE:
@@ -2359,7 +2516,16 @@
     <t>10.1016/j.hrthm.2026.09.028 doi</t>
   </si>
   <si>
-    <t>背景: 30 歳未満の心房細動はまれです。アブレーション結果のデータは不足しています。 目的: 多施設共同の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました。 方法：ドイツの 2 つの大規模センターでは、心房細動で初めて肺静脈隔離術 (PVI) を受けた 30 歳以下の患者を遡及的に対象とした (2005 ～ 2025 年)。 再発: 90 日間のブランク期間後に心房細動が記録された。 結果：患者140人（平均年齢29.1±3.1歳、女性28.6％）のうち、104人が転帰分析を受けた（発作性83.6％、持続性心房細動16.4％、心房細動の家族歴あり18.6％）。 PVI: 高周波 49.3%、クライオバルーン 45.7%、パルスフィールド アブレーション 5%。 平均処置時間は117±66分。 中央値1年間の追跡調査(IQR 0.25～1.74)で、10人の患者が再発した。 心房細動の非罹患率は、1/2/3 年で 93.6/88.2/82.1% でした。最大2回の手術後、1年後に94.9%。 発作性心房細動と持続性心房細動では、98.5% 対 98.5% の方が良好な結果を示しました。 1 年後は 67.7%、1 年後は 87.8% 3年後は50.8%（ログランクp&lt;0.001）。 院内合併症は 3 件 (2.1%) 発生しました。血管合併症 1 件は外科的修復が必要でした。介入の必要のない心膜炎と軽度の肺静脈狭窄。 結論: 30 歳未満の成人では、心房細動に対するカテーテルアブレーションにより、高いリズム制御が得られ、合併症発生率も低くなります。 持続性心房細動では、発作性心房細動よりも利益が低くなります。 心房細動のサブタイプは、若年成人の第一選択の調律制御としてアブレーションを早期に導入することを主張する可能性がある最も強力な決定要因です。</t>
+    <t xml:space="preserve">【背景】
+ 30 歳未満の心房細動はまれです。アブレーション結果のデータは不足しています。 
+【目的】
+ 多施設共同の AF-YOUNG レジストリは、初めてカテーテル アブレーションを受けた連続 30 年以下の患者の臨床、処置、転帰データを分析しました。 
+【方法】
+ドイツの 2 つの大規模センターでは、心房細動で初めて肺静脈隔離術 (PVI) を受けた 30 歳以下の患者を遡及的に対象とした (2005 ～ 2025 年)。 再発: 90 日間のブランク期間後に心房細動が記録された。 
+【結果】
+患者140人（平均年齢29.1±3.1歳、女性28.6％）のうち、104人が転帰分析を受けた（発作性83.6％、持続性心房細動16.4％、心房細動の家族歴あり18.6％）。 PVI: 高周波 49.3%、クライオバルーン 45.7%、パルスフィールド アブレーション 5%。 平均処置時間は117±66分。 中央値1年間の追跡調査(IQR 0.25～1.74)で、10人の患者が再発した。 心房細動の非罹患率は、1/2/3 年で 93.6/88.2/82.1% であった。最大2回の手術後、1年後に94.9%。 発作性心房細動と持続性心房細動では、98.5% 対 98.5% の方が良好な結果を示しました。 1 年後は 67.7%、1 年後は 87.8% 3年後は50.8%（ログランクp&lt;0.001）。 院内合併症は 3 件 (2.1%) 発生しました。血管合併症 1 件は外科的修復が必要であった。介入の必要のない心膜炎と軽度の肺静脈狭窄。 
+【結論】
+ 30 歳未満の成人では、心房細動に対するカテーテルアブレーションにより、高いリズム制御が得られ、合併症発生率も低くなります。 持続性心房細動では、発作性心房細動よりも利益が低くなります。 心房細動のサブタイプは、若年成人の第一選択の調律制御としてアブレーションを早期に導入することを主張する可能性がある最も強力な決定要因です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2390,7 +2556,16 @@
     <t>10.1111/jce.70509 doi</t>
   </si>
   <si>
-    <t>背景: 電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入されました。 しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られています。 目的: バルーンインバスケット PFA システムを使用した肺静脈隔離術 (PVI) および補助病変の急性期のパフォーマンス、安全性、実現可能性を評価すること。 方法：2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が対象となった。 急性有効性、処置パラメータ、合併症、探索的溶血および腎バイオマーカー、追跡結果が評価されました。 結果: 合計 133 人の患者が含まれました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF でした。 急性 PVI は症例の 96.2% で達成されました。 補助的な PWI は患者の 25.6% で実施され、追加の PV 外病変セットは 12 人の患者で実施されました。 平均手技時間、左心房留置時間、透視時間はそれぞれ65.6±16.4分、45.4±15.4分、12.7±7.3分で、PVIのみの手技とPVI+PWI手技の間に有意差はなかった。 2 件の手術周囲合併症が発生しました (1.5%; 大腿動脈仮性動脈瘤、心膜炎)。 探索的バイオマーカー分析では、明らかな溶血関連の腎臓の安全性シグナルは示されませんでした。 6か月以上の追跡調査を受けた82人の患者のうち、臨床的に証明された晩期の心房性不整脈の再発が14.6％で発生した。 結論: この実際の経験では、バルーンインバスケット PFA システムは高い急性有効性、低い合併症率、効率的なワークフローを示しました。 補助的 PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されませんでした。</t>
+    <t xml:space="preserve">【背景】
+ 電気解剖学的マッピングと統合された新しいバルーンインバスケットパルスフィールドアブレーション(PFA)システムが最近導入されました。 しかし、この技術、特に補助的な後壁分離（PWI）および肺静脈外部位に関する実際のデータは依然として限られています。 
+【目的】
+ バルーンインバスケット PFA システムを使用した肺静脈隔離術 (PVI) および補助病変の急性期のパフォーマンス、安全性、実現可能性を評価すること。 
+【方法】
+2024年2月から2026年2月までにバルーンインバスケットPFAシステムによるアブレーションを受けた症候性発作性または持続性AFの連続患者が対象となった。 急性有効性、処置パラメータ、合併症、探索的溶血および腎バイオマーカー、追跡結果が評価された。 
+【結果】
+ 合計 133 人の患者が含まれました。 94 人 (70.7%) が発作性 AF、39 人 (29.3%) が持続性 AF であった。 急性 PVI は症例の 96.2% で達成されました。 補助的な PWI は患者の 25.6% で実施され、追加の PV 外病変セットは 12 人の患者で実施されました。 平均手技時間、左心房留置時間、透視時間はそれぞれ65.6±16.4分、45.4±15.4分、12.7±7.3分で、PVIのみの手技とPVI+PWI手技の間に有意差はなかった。 2 件の手術周囲合併症が発生しました (1.5%; 大腿動脈仮性動脈瘤、心膜炎)。 探索的バイオマーカー分析では、明らかな溶血関連の腎臓の安全性シグナルは示されなかった。 6か月以上の追跡調査を受けた82人の患者のうち、臨床的に証明された晩期の心房性不整脈の再発が14.6％で発生した。 
+【結論】
+ この実際の経験では、バルーンインバスケット PFA システムは高い急性有効性、低い合併症率、効率的なワークフローを示しました。 補助的 PWI は選択された患者において実行可能であると考えられ、探索的比較では処置上の負担や追加のバイオマーカーの安全性シグナルの明らかな増加は示されなかった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2421,7 +2596,16 @@
     <t>10.1016/j.hrthm.2026.09.034 doi</t>
   </si>
   <si>
-    <t>背景: 伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実です。 目的: 冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する。 方法：我々は、傍ヒスアン PVC アブレーションを受けている 114 人の患者を遡及的に分析した。 急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位が評価されました。 結果: 89 人の患者 (78%) で緊急手術の成功が達成されました。 しかし、長期的な臨床的成功を達成したのは、急性成功を収めた患者の 52% のみでした。 冠動脈尖アブレーションは合計 35 人の患者 (31%) で試みられ、臨床失敗例よりも臨床成功例の方が有意に頻繁に実施されました (38% vs. 38%)。 7%, P=0.005).  尖切除を受けた 35 人の患者のうち、PVC は 49% (17/35) で終了しましたが、さらに 31% (11/35) で PVC の一過性の抑制または形態的変化が観察されました。 尖頭アブレーションの成功の予測因子には、尖頭での早期の活性化、および尖頭とヒス束領域の最も初期の活性化部位との間の解剖学的近接性が含まれる。 伝導系損傷は全体で 31 人の患者に発生しましたが、主にヒス束領域のアブレーション中に発生し、弁尖アブレーション中に発生したイベントは 1 件のみでした。 結論：段階的な多部位アブレーション戦略に冠状動脈弁尖アブレーションを組み込むことは、安全性を損なうことなく、傍ヒスアン PVC アブレーションのより良い処置結果に結びつく可能性がある。 早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測されます。</t>
+    <t xml:space="preserve">【背景】
+ 伝導系損傷のリスクのため、傍組織の心室性期外収縮 (PVC) に対する最適なアブレーション戦略は依然として不確実です。 
+【目的】
+ 冠状動脈尖からの解剖学的アプローチの有効性と安全性に特に焦点を当てて、冠動脈周囲 PVC に対するカテーテル アブレーションの安全性と結果を評価する。 
+【方法】
+我々は、傍ヒスアン PVC アブレーションを受けている 114 人の患者を遡及的に分析した。 急性成功、長期臨床成功（PVC 削減 80% 以上）、伝導系損傷、およびアブレーション部位が評価された。 
+【結果】
+ 89 人の患者 (78%) で緊急手術の成功が達成されました。 しかし、長期的な臨床的成功を達成したのは、急性成功を収めた患者の 52% のみであった。 冠動脈尖アブレーションは合計 35 人の患者 (31%) で試みられ、臨床失敗例よりも臨床成功例の方が有意に頻繁に実施されました (38% vs. 38%)。 7%, P=0.005).  尖切除を受けた 35 人の患者のうち、PVC は 49% (17/35) で終了しましたが、さらに 31% (11/35) で PVC の一過性の抑制または形態的変化が観察された。 尖頭アブレーションの成功の予測因子には、尖頭での早期の活性化、および尖頭とヒス束領域の最も初期の活性化部位との間の解剖学的近接性が含まれる。 伝導系損傷は全体で 31 人の患者に発生しましたが、主にヒス束領域のアブレーション中に発生し、弁尖アブレーション中に発生したイベントは 1 件のみであった。 
+【結論】
+段階的な多部位アブレーション戦略に冠状動脈弁尖アブレーションを組み込むことは、安全性を損なうことなく、傍ヒスアン PVC アブレーションのより良い処置結果に結びつく可能性がある。 早期の活性化と、傍組織部位と弁尖領域との間の解剖学的近接性により、このアプローチを使用したアブレーションの成功が予測されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2452,7 +2636,16 @@
     <t>10.1016/j.hrthm.2026.08.055 doi</t>
   </si>
   <si>
-    <t>背景: 心臓植込み型装置によって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明です。 目的: この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することでした。 方法：単形性心室頻拍に対してカテーテルアブレーションを受け、植込み型除細動器によって記録された分析可能な自発的心室頻拍エピソードを有する構造的心疾患患者113人を遡及的に研究した。 自発性 VT は、開始拍動が持続 VT 拍動と一致する場合には形態一致開始として分類され (タイプ A)、最初の拍動がその後の VT 拍動と異なる場合には形態が異なる開始として分類されました (タイプ B)。 結果: 257 件の自然発生 VT エピソードのうち、147 件が A 型、110 件が B 型でした。 113人の患者のうち、58人がA型のみ、47人がB型のみ、8人が両方の型を持っていた。 タイプ B の開始は、より長い VT 前の R-R 間隔と、より頻繁な心室ペーシングのベースラインリズムと関連していました。 アブレーション中、タイプ B のみのグループはより誘発性の VT 形態を持ち (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままでした (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87、P = 0.002)。 急性手術の転帰、合併症、VT再発、および複合転帰は、グループ間で有意な差はありませんでした。 結論： 開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している。</t>
+    <t xml:space="preserve">【背景】
+ 心臓植込み型装置によって記録される自然発生的な単形性心室頻拍 (VT) は、明確な開始パターンを示しますが、その臨床的意義は依然として不明です。 
+【目的】
+ この研究の目的は、心臓植込み型デバイスからの心電図上の自発的 VT 開始の形態が、構造的心疾患患者における誘発性 VT の数、基質の特性、および転帰と関連しているかどうかを判断することであった。 
+【方法】
+単形性心室頻拍に対してカテーテルアブレーションを受け、植込み型除細動器によって記録された分析可能な自発的心室頻拍エピソードを有する構造的心疾患患者113人を遡及的に研究した。 自発性 VT は、開始拍動が持続 VT 拍動と一致する場合には形態一致開始として分類され (タイプ A)、最初の拍動がその後の VT 拍動と異なる場合には形態が異なる開始として分類されました (タイプ B)。 
+【結果】
+ 257 件の自然発生 VT エピソードのうち、147 件が A 型、110 件が B 型であった。 113人の患者のうち、58人がA型のみ、47人がB型のみ、8人が両方の型を持っていた。 タイプ B の開始は、より長い VT 前の R-R 間隔と、より頻繁な心室ペーシングのベースラインリズムと関連していました。 アブレーション中、タイプ B のみのグループはより誘発性の VT 形態を持ち (P = 0.012)、同様の瘢痕範囲 (P = 0.184) にもかかわらず、多変量調整後でも有意なままであった (発生率比 = 1.47、95% 信頼区間 = 1.15-1.87、P = 0.002)。 急性手術の転帰、合併症、VT再発、および複合転帰は、グループ間で有意な差はありなかった。 
+【結論】
+ 開始形態がその後の VT とは異なる VT は、肉眼的瘢痕範囲が同等であるにもかかわらず、より多くの誘発性 VT 形態と関連している。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2483,7 +2676,16 @@
     <t>10.1016/j.hrthm.2026.09.013 doi</t>
   </si>
   <si>
-    <t>背景: 心房細動 (AF) アブレーションの成功率を向上させるために、効果はさまざまですが、心筋破壊を犠牲にして経験的病変が配置されることがよくあります。 自律神経調節は、過度の心筋損傷を引き起こすことなくリズムの結果を改善する非切除的な補助手段を提供する可能性があります。 目的: AF アブレーション後の皮正中神経刺激 (MNS) を評価すること。 方法: NEUROPULSE は、3 施設、無作為化、二重盲検、偽対照のパイロット研究でした。 77人の患者は、活動性MNS（週3×20分のセッション）または偽のMNSに1：1で無作為に割り付けられた。修正意図治療（mITT）集団には59人の患者（MNS 31人、偽28人）が含まれていた。 治療はアブレーション（大部分がパルスフィールドアブレーション）後 48 時間以内に開始され、6 か月間継続されました（2 週間は毎日、その後は週 3 回）。 監視には、1 日 2 回の 2 分間のデバイス ECG と 2 か月目と 6 か月目の 10 日間のパッチが含まれていました。 結果：年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。 盲検化は維持された。 ブランキング後の追跡調査（2～6か月）中、MNSでは12件のAF/AT/AFLイベントが発生し、偽では243件が発生した（発生率比[RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001）。 1 つの高負荷偽異常値を除くと、12 対 28 のイベントが発生しました (RR 2.17; 95%CI 1.10-4.27; P=0.025)。 AF/AT/AFL は MNS 患者 31 人中 2 人、偽患者 28 人中 5 人で再発しました。 6か月の無不整脈生存率は、それぞれ90.0% vs 80.8%（ハザード比 2.15; 95%CI 0.42-11.1; P=0.36）でした。 PAC 数と患者報告の転帰には差異はありませんでした。 MNS またはデバイス関連の重篤な有害事象は発生しませんでした。 結論: AF アブレーション後のウェアラブル MNS は、心房性不整脈イベントの再発の減少と関連していました。 このパイロット研究は、適切な検出力試験での確認を保証します。</t>
+    <t xml:space="preserve">【背景】
+ 心房細動 (AF) アブレーションの成功率を向上させるために、効果はさまざまですが、心筋破壊を犠牲にして経験的病変が配置されることがよくあります。 自律神経調節は、過度の心筋損傷を引き起こすことなくリズムの結果を改善する非切除的な補助手段を提供する可能性があります。 
+【目的】
+ AF アブレーション後の皮正中神経刺激 (MNS) を評価すること。 
+【方法】
+ NEUROPULSE は、3 施設、無作為化、二重盲検、偽対照のパイロット研究であった。 77人の患者は、活動性MNS（週3×20分のセッション）または偽のMNSに1：1で無作為に割り付けられた。修正意図治療（mITT）集団には59人の患者（MNS 31人、偽28人）が含まれていた。 治療はアブレーション（大部分がパルスフィールドアブレーション）後 48 時間以内に開始され、6 か月間継続されました（2 週間は毎日、その後は週 3 回）。 監視には、1 日 2 回の 2 分間のデバイス ECG と 2 か月目と 6 か月目の 10 日間のパッチが含まれていました。 
+【結果】
+年齢中央値は67歳（IQR、56～74歳）、39％が女性、68％が発作性AF、27％が再アブレーションだった。 盲検化は維持された。 ブランキング後の追跡調査（2～6か月）中、MNSでは12件のAF/AT/AFLイベントが発生し、偽では243件が発生した（発生率比[RR] 17.93; 95%CI 10.04-32.0; P&lt;0.0001）。 1 つの高負荷偽異常値を除くと、12 対 28 のイベントが発生しました (RR 2.17; 95%CI 1.10-4.27; P=0.025)。 AF/AT/AFL は MNS 患者 31 人中 2 人、偽患者 28 人中 5 人で再発しました。 6か月の無不整脈生存率は、それぞれ90.0% vs 80.8%（ハザード比 2.15; 95%CI 0.42-11.1; P=0.36）であった。 PAC 数と患者報告の転帰には差異はありなかった。 MNS またはデバイス関連の重篤な有害事象は発生しなかった。 
+【結論】
+ AF アブレーション後のウェアラブル MNS は、心房性不整脈イベントの再発の減少と関連していました。 このパイロット研究は、適切な検出力試験での確認を保証します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2514,7 +2716,16 @@
     <t>10.1016/j.hrthm.2026.09.007 doi</t>
   </si>
   <si>
-    <t>背景: 緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質です。 ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません。 目的: この研究は、CV 解析の新しい方法を評価することを目的としています。 方法: この単一施設の後ろ向き研究には、右心室電気解剖学的活性化マッピングを受けた連続 TOF 患者が含まれていました。 解剖学的峡部 3 にわたる CV は、自動化された局所活性化時間速度ベクトル (LVV) 分析と従来の手動測定の両方を使用して評価されました。 主要アウトカムは、持続性単形性心室頻拍（VT; SMVT）の誘発性でした。 結果：合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）。 全体として、SMVTは23人（52.3％）の患者で誘発可能であり、そのうち12/14人（85.7％）はVT（臨床的VTの病歴）のカテーテルアブレーションのために紹介された患者、および11/30人（36.7％）は自然発生性VTを伴わないEPSのために紹介された患者であった。 LVV-CV は手動測定と強い相関関係を示しました (r = 0.81)。 Youden 指数に基づく LVV-CV の最適カットオフ値は 0.5 m/s でした。 AUC、感度、特異度は、LVV-CV を使用した場合はそれぞれ 0.81、0.96、0.71 でしたが、手動 CV 測定を使用した場合は 0.75、0.57、0.81 でした。 LVV 分析により、分類エラーの数が手動 CV 測定では 14 件 (31.8%) でしたが、LVV-CV を使用した場合は 7 件 (15.9%) に減少しました。 結論：TOF 患者の基質評価のための CV 測定に対するこの新規で再現性があり、使いやすい LVV ベースのアプローチは、LVV-CV が SMVT 誘導性に関連する SCAI を同定するために手動の CV 測定と比較して優れた識別性能を提供することを示唆しています。 より大きな集団でこのアプローチを評価するには、さらなる研究が必要です。</t>
+    <t xml:space="preserve">【背景】
+ 緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質です。 ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません。 
+【目的】
+ この研究は、CV 解析の新しい方法を評価することを目的としています。 
+【方法】
+ この単一施設の後ろ向き研究には、右心室電気解剖学的活性化マッピングを受けた連続 TOF 患者が含まれていました。 解剖学的峡部 3 にわたる CV は、自動化された局所活性化時間速度ベクトル (LVV) 分析と従来の手動測定の両方を使用して評価された。 主要アウトカムは、持続性単形性心室頻拍（VT; SMVT）の誘発性であった。 
+【結果】
+合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）。 全体として、SMVTは23人（52.3％）の患者で誘発可能であり、そのうち12/14人（85.7％）はVT（臨床的VTの病歴）のカテーテルアブレーションのために紹介された患者、および11/30人（36.7％）は自然発生性VTを伴わないEPSのために紹介された患者であった。 LVV-CV は手動測定と強い相関関係を示しました (r = 0.81)。 Youden 指数に基づく LVV-CV の最適カットオフ値は 0.5 m/s であった。 AUC、感度、特異度は、LVV-CV を使用した場合はそれぞれ 0.81、0.96、0.71 であったが、手動 CV 測定を使用した場合は 0.75、0.57、0.81 であった。 LVV 分析により、分類エラーの数が手動 CV 測定では 14 件 (31.8%) であったが、LVV-CV を使用した場合は 7 件 (15.9%) に減少しました。 
+【結論】
+TOF 患者の基質評価のための CV 測定に対するこの新規で再現性があり、使いやすい LVV ベースのアプローチは、LVV-CV が SMVT 誘導性に関連する SCAI を同定するために手動の CV 測定と比較して優れた識別性能を提供することを示唆しています。 より大きな集団でこのアプローチを評価するには、さらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2545,7 +2756,16 @@
     <t>10.1016/j.jacep.2026.07.018 doi</t>
   </si>
   <si>
-    <t>背景: ブルガダ症候群 (BrS) における運動中の前胸部 J ポイント上昇の強調の臨床的意義は依然として不明である。 目的: この研究は、大規模な単一施設の BrS コホートにおける運動中の J ポイント上昇の強調の有病率と予後的重要性を判断することを目的としました。 方法：この後ろ向き研究では、2000年1月1日から2025年10月31日まで運動負荷検査（EST）を受けた、BrS評価のために紹介された連続141人の患者（1型BrSパターンを有する95人-BrS1コホート、1型パターンを有さないが機能喪失型ナトリウム電位依存性チャネルαサブユニット5バリアントを有する46人-SCN5Aコホート）を対象とした。含まれています。 盲検の心臓専門医 2 名がすべての追跡結果を調査しました。 運動により増強される BrS 表現型は、運動中の V1/V2 における J ポイント上昇の 1 mm 以上の増加として定義されました。 心臓イベントには、不整脈性失神、心停止、および適切な植込み型除細動器ショックが含まれます。 未調整および調整済み分析には、Firth ペナルティ付きロジスティック回帰を使用しました。 結果: 全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。 表現型は連続検査で非常に再現性が高かった (追跡 EST の 88%)。 運動強化表現型は、心臓イベント全体とは関連しなかった（未調整 OR: 1.83 [0.84-3.99]; P = 0.13; 調整済み OR: 1.22 [0.47-3.21]; P = 0.69）。 しかし、性別、運動負荷、ベースラインのタイプ 1 パターンとは無関係に、労作誘発性の心臓イベントと強く関連していました (未調整 OR: 10.50 [2.94-37.50]; P &lt; 0.001; 調整済み OR: 10.04 [2.76-36.53]; P &lt; 0.001)。 SCN5A変異陽性患者において一貫した結果が認められた。 結論: 運動誘発性の J ポイント上昇の強調は、労作性心臓イベントのリスクがある BrS 患者のサブセットを再現性よく特定します。 これらの発見は、BrS に対する臨床診断または遺伝的感受性を持つ患者の評価に EST を含めることを裏付けており、運動関連のリスクカウンセリングに情報を提供する可能性があります。</t>
+    <t xml:space="preserve">【背景】
+ ブルガダ症候群 (BrS) における運動中の前胸部 J ポイント上昇の強調の臨床的意義は依然として不明である。 
+【目的】
+ この研究は、大規模な単一施設の BrS コホートにおける運動中の J ポイント上昇の強調の有病率と予後的重要性を判断することを目的としました。 
+【方法】
+この後ろ向き研究では、2000年1月1日から2025年10月31日まで運動負荷検査（EST）を受けた、BrS評価のために紹介された連続141人の患者（1型BrSパターンを有する95人-BrS1コホート、1型パターンを有さないが機能喪失型ナトリウム電位依存性チャネルαサブユニット5バリアントを有する46人-SCN5Aコホート）を対象とした。含まれています。 盲検の心臓専門医 2 名がすべての追跡結果を調査しました。 運動により増強される BrS 表現型は、運動中の V1/V2 における J ポイント上昇の 1 mm 以上の増加として定義されました。 心臓イベントには、不整脈性失神、心停止、および適切な植込み型除細動器ショックが含まれます。 未調整および調整済み分析には、Firth ペナルティ付きロジスティック回帰を使用しました。 
+【結果】
+ 全体として、41 人の患者 (29%) が運動が集中する BrS 表現型を示し、運動のピーク付近 (年齢から予測される最大心拍数の中央値 90%) を示しました。 表現型は連続検査で非常に再現性が高かった (追跡 EST の 88%)。 運動強化表現型は、心臓イベント全体とは関連しなかった（未調整 OR: 1.83 [0.84-3.99]; P = 0.13; 調整済み OR: 1.22 [0.47-3.21]; P = 0.69）。 しかし、性別、運動負荷、ベースラインのタイプ 1 パターンとは無関係に、労作誘発性の心臓イベントと強く関連していました (未調整 OR: 10.50 [2.94-37.50]; P &lt; 0.001; 調整済み OR: 10.04 [2.76-36.53]; P &lt; 0.001)。 SCN5A変異陽性患者において一貫した結果が認められた。 
+【結論】
+ 運動誘発性の J ポイント上昇の強調は、労作性心臓イベントのリスクがある BrS 患者のサブセットを再現性よく特定します。 これらの発見は、BrS に対する臨床診断または遺伝的感受性を持つ患者の評価に EST を含めることを裏付けており、運動関連のリスクカウンセリングに情報を提供する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2576,7 +2796,14 @@
     <t>10.1007/s10840-026-02427-2 doi</t>
   </si>
   <si>
-    <t>背景: メッシュ形状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難です。 この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。 方法：TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました。 機構の検証は、ex vivo ブタ心筋モデル (152 病変) を使用して実行されました。 結果: 1,423 件の高周波アプリケーションのうち、138 件が伝導ギャップ セグメント内にありました。 AID% は、非伝導ギャップ セグメントよりも伝導ギャップ セグメントの高周波アプリケーションの方が低かったが、その差はわずかでした (10.2 [8.3-12.2] % 対 10.9 [9.0-13.1] %, p = 0.002).  全体的な識別性能は限られていました (曲線下面積、0.58、95% 信頼区間、0.53 ～ 0.63)。 患者内クラスタリングを説明する混合効果ロジスティック回帰では、AID% &lt;10% は伝導ギャップセグメントにおける高周波の適用と有意な関連はありませんでした (オッズ比、1.560; 95% 信頼区間、0.970-2.500; p = 0.065)。一方、平均高周波出力は有意でした。 ex vivo 研究では、ターゲット AID% が固定された条件下であっても、病変の特徴は高周波出力、接触力、持続時間に応じて変化しました。 結論: AID% は、複数のアブレーション パラメータの影響を受ける、高周波送達に対する複合インピーダンス ベースの組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件による病変特性のばらつきは、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。 平均インピーダンス低下パーセンテージ (AID%) は、複数のアブレーション パラメーターの影響を受ける、高周波送達に対する複合インピーダンスに基づく組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。</t>
+    <t xml:space="preserve">【背景】
+ メッシュ形状の柔軟な灌注チップ アブレーション カテーテル (TactiFlex) を使用した、高周波適用中の心筋組織反応のリアルタイム モニタリングは依然として困難です。 この研究では、新しいアブレーションパラメータである平均インピーダンス低下パーセンテージ（AID%）の動態と、伝導ギャップおよび病変特性との関連性を評価しました。 
+【方法】
+TactiFlex を使用して初回肺静脈隔離を受けた 30 人の患者における 1,423 回の高周波適用を遡及的に分析し、AID% と伝導ギャップセグメント内の高周波適用との関係を調べました。 機構の検証は、ex vivo ブタ心筋モデル (152 病変) を使用して実行されました。 
+【結果】
+ 1,423 件の高周波アプリケーションのうち、138 件が伝導ギャップ セグメント内にあった。 AID% は、非伝導ギャップ セグメントよりも伝導ギャップ セグメントの高周波アプリケーションの方が低かったが、その差はわずかであった (10.2 [8.3-12.2] % 対 10.9 [9.0-13.1] %, p = 0.002).  全体的な識別性能は限られていました (曲線下面積、0.58、95% 信頼区間、0.53 ～ 0.63)。 患者内クラスタリングを説明する混合効果ロジスティック回帰では、AID% &lt;10% は伝導ギャップセグメントにおける高周波の適用と有意な関連はありなかった (オッズ比、1.560; 95% 信頼区間、0.970-2.500; p = 0.065)。一方、平均高周波出力は有意であった。 ex vivo 研究では、ターゲット AID% が固定された条件下であっても、病変の特徴は高周波出力、接触力、持続時間に応じて変化しました。 
+【結論】
+ AID% は、複数のアブレーション パラメータの影響を受ける、高周波送達に対する複合インピーダンス ベースの組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件による病変特性のばらつきは、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。 平均インピーダンス低下パーセンテージ (AID%) は、複数のアブレーション パラメーターの影響を受ける、高周波送達に対する複合インピーダンスに基づく組織応答を反映します。 伝導ギャップセグメントを識別する能力が限られていることと、高周波送達条件全体にわたる病変特性の変動性は、AID% を独立した病変品質の指標としてではなく、組織反応のマーカーとして解釈する必要があることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2605,7 +2832,15 @@
     <t>10.1007/s10840-026-02434-3 doi</t>
   </si>
   <si>
-    <t>背景と目的: パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療にますます使用されています。 RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった。 方法：症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。 PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。 患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。 結果: 研究コホート全体ですべてのエンドポイントが達成されました。 SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%でした。 1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) でした。 二次有効性エンドポイントは、3か月間のPVIが82%、6か月間のAFが94%（34/36人の患者）でなかった。 研究中、PFA 用量は 3 つのコホートで調整されました。 「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありませんでした。 結論: 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
+    <t xml:space="preserve">背景と
+【目的】
+ パルスフィールドアブレーション (PFA) は、心房細動 (AF) 患者の治療にますます使用されています。 RESET-AFは、新規のシングルショットPFAシステム（米国カリフォルニア州タスティンのElePulse、CRC EP）を使用したAFアブレーションの単群ファーストインヒューマン臨床試験であり、試験登録ACTRN12622001523796（登録日2022年12月8日）であった。 
+【方法】
+症候性発作性心房細動（n = 22）および持続性心房細動（n = 14）を有する連続登録患者36人（57±11歳、男性69％）において、このカテーテルを使用し、3Dマッピングに基づいて肺静脈隔離術（PVI）が実施された。 PVI の耐久性を確認するために、すべての患者が 3 か月後に再マッピングを受けました。 患者は6ヵ月後と12ヵ月後に臨床レビュー、ホルターモニタリング、心電図検査を受けて追跡調査されました。 主要な有効性と安全性のエンドポイントには、12か月後の再発性AFの頻度が50%以上、7日と30日後の重篤な有害事象（SAE）の頻度が50%以上、6か月間のAFの頻度が60%を超えたことが含まれた。 
+【結果】
+ 研究コホート全体ですべてのエンドポイントが達成されました。 SAE（保存的管理で回復した腎障害）は1件あり、総SAE率は2.8%であった。 1 人の患者は 12 か月時点で追跡不能となり、主要有効性評価項目は 92% (患者 35 人中 32 人) であった。 二次有効性エンドポイントは、3か月間のPVIが82%、6か月間のAFが94%（34/36人の患者）でなかった。 研究中、PFA 用量は 3 つのコホートで調整されました。 「最適化されたサブセット」は、SAE がなく、6 か月および 12 か月の時点で 100% の PVI 耐久性と AF がありなかった。 
+【結論】
+ 発作性および持続性 AF のアブレーションのための新しい PFA カテーテル システムのこの研究は、あらかじめ決められた一次および二次臨床エンドポイントをすべて達成しました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND AND AIMS:
@@ -2634,7 +2869,16 @@
     <t>10.1016/j.jacep.2026.09.001 doi</t>
   </si>
   <si>
-    <t>背景: シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません。 既存の焦点 PFA 技術では、個別のアブレーションが可能ですが、複数の心臓および呼吸サイクルにわたってエネルギーを送達する必要があるため、持続的なカテーテルの安定性が重要となり、処置の効率が低下する可能性があります。 目的: 著者らは、「瞬間的な」ポイントバイポイントアブレーション用に設計された新しいサブ秒パルスフィールド波形を送出する焦点 PFA カテーテルを評価しようとしました。 方法: 8.5-F 力感知 PFA カテーテルは、QRS 同期された単一の高電圧 (≥10 kV; &lt;200 ms) パルス場印加を提供します。 3 つの連続した波形/電極構成コホートが評価されました。 PVI は、インピーダンスに基づいたカテーテルの位置特定を伴う従来の電気解剖学的マッピングによって誘導されました。 サブセットはPFA後の脳磁気共鳴画像検査を受けました。 〜90日後の侵襲的再マッピングにより、病変の耐久性を評価しました。 結果: 35 人の患者が波形 A (n = 15)、B (n = 5)、または C (n = 15) で PFA を受けました。 急性 PVI はすべての患者で達成され、患者あたり 39 (IQR: 35-45) の PF 病変が必要で、経過アブレーション時間の中央値は 13 (IQR: 10-15) 分でした。 32 人の患者の再マッピングでは、波形の進化に伴う PVI 耐久性の漸進的な改善が実証されました。波形 C は静脈あたり 94.2% の PVI 耐久性を達成しました。 脳磁気共鳴画像法 (n = 14) では、拡散強調画像法 (DWI)+/流体減衰反転回復法 (FLAIR)+ 病変は認められず、DWI+/FLAIR- 病変が 2 件 (14%) ありました。 主要な安全性事象、ハプトグロビン枯渇、または急性腎障害はありませんでした。 12 か月間心房性不整脈が発生しなかった率は 73.9% (95% CI: 60.6% ～ 90.2%) でした。 結論: 1 秒未満の高電圧焦点 PFA により、長時間のカテーテルの安定性を必要とせずに、効率的なポイントごとのアブレーションと個別の病変セットが可能になりました。 これらのファーストインヒューマンデータは、瞬間的な焦点の PFA ワークフローの継続的な臨床開発をサポートします。 臨床試験: 政府：（FIELD-PULSE 研究; 心房細動患者におけるフィールドフォースアブレーションシステムの安全性と実現可能性を評価するための、市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589）。</t>
+    <t xml:space="preserve">【背景】
+ シングルショットパルスフィールドアブレーション (PFA) カテーテルは、その効率性から肺静脈隔離 (PVI) に広く使用されていますが、柔軟な病変セットにはあまり適していません。 既存の焦点 PFA 技術では、個別のアブレーションが可能ですが、複数の心臓および呼吸サイクルにわたってエネルギーを送達する必要があるため、持続的なカテーテルの安定性が重要となり、処置の効率が低下する可能性があります。 
+【目的】
+ 著者らは、「瞬間的な」ポイントバイポイントアブレーション用に設計された新しいサブ秒パルスフィールド波形を送出する焦点 PFA カテーテルを評価しようとしました。 
+【方法】
+ 8.5-F 力感知 PFA カテーテルは、QRS 同期された単一の高電圧 (≥10 kV; &lt;200 ms) パルス場印加を提供します。 3 つの連続した波形/電極構成コホートが評価された。 PVI は、インピーダンスに基づいたカテーテルの位置特定を伴う従来の電気解剖学的マッピングによって誘導されました。 サブセットはPFA後の脳磁気共鳴画像検査を受けました。 〜90日後の侵襲的再マッピングにより、病変の耐久性を評価しました。 
+【結果】
+ 35 人の患者が波形 A (n = 15)、B (n = 5)、または C (n = 15) で PFA を受けました。 急性 PVI はすべての患者で達成され、患者あたり 39 (IQR: 35-45) の PF 病変が必要で、経過アブレーション時間の中央値は 13 (IQR: 10-15) 分であった。 32 人の患者の再マッピングでは、波形の進化に伴う PVI 耐久性の漸進的な改善が実証されました。波形 C は静脈あたり 94.2% の PVI 耐久性を達成しました。 脳磁気共鳴画像法 (n = 14) では、拡散強調画像法 (DWI)+/流体減衰反転回復法 (FLAIR)+ 病変は認められず、DWI+/FLAIR- 病変が 2 件 (14%) あった。 主要な安全性事象、ハプトグロビン枯渇、または急性腎障害はありなかった。 12 か月間心房性不整脈が発生しなかった率は 73.9% (95% CI: 60.6% ～ 90.2%) であった。 
+【結論】
+ 1 秒未満の高電圧焦点 PFA により、長時間のカテーテルの安定性を必要とせずに、効率的なポイントごとのアブレーションと個別の病変セットが可能になりました。 これらのファーストインヒューマンデータは、瞬間的な焦点の PFA ワークフローの継続的な臨床開発をサポートします。 臨床試験: 政府：（FIELD-PULSE 研究; 心房細動患者におけるフィールドフォースアブレーションシステムの安全性と実現可能性を評価するための、市販前、ファーストインヒューマン、パイロット、介入、臨床研究; NCT06452589）。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2667,7 +2911,16 @@
     <t>10.1016/j.hrthm.2026.09.006 doi</t>
   </si>
   <si>
-    <t>背景: 高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率 &lt; 75%、貫壁性 &lt; 60% という一貫性のない心筋ターゲティングが生じます。 目的：我々は、肥大型心筋症（HCM）における深心室頻拍（VT）アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドするためのHIUカテーテルとリアルタイム接触センシング法を設計した。 われわれは、接触感知誘導型 HIU (CSG-HIU) が、豚の終末期モデルにおいて、標準 HIU (Std-HIU) よりも大きく、より深く、より多くの貫壁性病変を生成すると仮説を立てました。 方法: トランスデューサーの寸法 (5x6 mm) と周波数 (5 MHz) は 3D 音響シミュレーションから選択されました。 3 つの接触検知モダリティ (パルスエコー、およびトランスデューサー側微小電極を介した双極または単極インピーダンス) が ex vivo で検証されました。 次に、心室中隔の Std-HIU (n=10) と CSG-HIU (n=13) のアブレーションを比較する前向きの in vivo ブタ研究で最良の方法が使用されました。 結果: 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました。 In-vivo と Std-HIU、CSG-HIU では、体積が大きくなり (2071±1231 vs. 568±890 mm、p=0.005）、より深い病変（15±3 vs. 6±6 mm、p&lt;0.001)、ブタの 69 対 20% で貫壁性 (p=0.030)。 持続的な房室ブロック、心室中隔欠損症、手術による死亡は発生しませんでした。 結論: リアルタイム双極性インピーダンス CSG-HIU は歴史的な方向制限を克服し、100% の病変効率とより予測可能な貫壁性を達成します。</t>
+    <t xml:space="preserve">【背景】
+ 高密度超音波 (HIU) アブレーションは深部心筋病変を生じさせる可能性がありますが、指向性のある横向きのトランスデューサーの向きによって制限されており、病変効率 &lt; 75%、貫壁性 &lt; 60% という一貫性のない心筋ターゲティングが生じます。 
+【目的】
+我々は、肥大型心筋症（HCM）における深心室頻拍（VT）アブレーションと中隔縮小療法が可能なデバイスを目指して、エネルギー送達をガイドするためのHIUカテーテルとリアルタイム接触センシング法を設計した。 われわれは、接触感知誘導型 HIU (CSG-HIU) が、豚の終末期モデルにおいて、標準 HIU (Std-HIU) よりも大きく、より深く、より多くの貫壁性病変を生成すると仮説を立てました。 
+【方法】
+ トランスデューサーの寸法 (5x6 mm) と周波数 (5 MHz) は 3D 音響シミュレーションから選択されました。 3 つの接触検知モダリティ (パルスエコー、およびトランスデューサー側微小電極を介した双極または単極インピーダンス) が ex vivo で検証されました。 次に、心室中隔の Std-HIU (n=10) と CSG-HIU (n=13) のアブレーションを比較する前向きの in vivo ブタ研究で最良の方法が使用されました。 
+【結果】
+ 生体外の双極性インピーダンスは、600 Ω の閾値で 100% の感度と安定した接触の特異性を示し、最も良好なパフォーマンスを示しました。 In-vivo と Std-HIU、CSG-HIU では、体積が大きくなり (2071±1231 vs. 568±890 mm、p=0.005）、より深い病変（15±3 vs. 6±6 mm、p&lt;0.001)、ブタの 69 対 20% で貫壁性 (p=0.030)。 持続的な房室ブロック、心室中隔欠損症、手術による死亡は発生しなかった。 
+【結論】
+ リアルタイム双極性インピーダンス CSG-HIU は歴史的な方向制限を克服し、100% の病変効率とより予測可能な貫壁性を達成します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2698,7 +2951,16 @@
     <t>10.1016/j.hrthm.2026.08.047 doi</t>
   </si>
   <si>
-    <t>背景: 植込み型除細動器は、主に電気信号に基づいて治療を誘導します。 血行動態センシングは、不整脈の直接的な生理学的影響に関する補足的な情報を提供する可能性があります。 目的: この研究では、血行動態センシング、電気センシング、心室ペーシングを統合した 3 次元胸骨下ショックリードの緊急の実現可能性と性能を評価しました。 方法: この前向きファーストインヒト実現可能性研究には、心臓手術または心外膜心室頻拍 (VT) アブレーションを受ける 5 人の患者が登録されました。 専用送達システムを使用した経皮剣状突起下アプローチにより、胸骨下ショックリードを一時的に配置しました。 リードの留置と取り外し、有害事象、同期センサー信号、表面心電図、胸骨下の電位図、およびペーシング閾値が評価されました。 結果: リードの留置と抜去は、デバイスまたは処置に関連した急性有害事象もなく、すべての患者で成功しました。 5 人の患者全員で解釈可能な血行動態信号が得られ、心電図との安定した拍動ごとの時間的対応と、洞調律、心房細動、VT、および心室細動にわたる明確な律動関連パターンが示されました。 147 の VT エピソードすべてに、解釈可能な血行動態指数の記録が含まれていました。 血行動態指数は VT 中に急激に減少し、不整脈の終了後に回復しました。 VT、心室細動、洞調律の間の移行中に、血行動態指数の対応する変化が観察されました。 心室捕捉は、5 人の患者全員で 11 ～ 17 V (平均 13.8 V)、0.5 ミリ秒で達成されました。 結論: この多機能胸骨下リードの急性留置は実現可能であり、急性心室捕捉による血行力学および電気センシングの統合が可能になりました。 これらの発見は、生理学に基づいた血管外植込み型除細動器システムのさらなる開発に対する人間による予備的な支援を提供します。血行力学センシングアルゴリズムの慢性的なパフォーマンスと臨床検証にはさらなる研究が必要です。</t>
+    <t xml:space="preserve">【背景】
+ 植込み型除細動器は、主に電気信号に基づいて治療を誘導します。 血行動態センシングは、不整脈の直接的な生理学的影響に関する補足的な情報を提供する可能性があります。 
+【目的】
+ この研究では、血行動態センシング、電気センシング、心室ペーシングを統合した 3 次元胸骨下ショックリードの緊急の実現可能性と性能を評価しました。 
+【方法】
+ この前向きファーストインヒト実現可能性研究には、心臓手術または心外膜心室頻拍 (VT) アブレーションを受ける 5 人の患者が登録されました。 専用送達システムを使用した経皮剣状突起下アプローチにより、胸骨下ショックリードを一時的に配置しました。 リードの留置と取り外し、有害事象、同期センサー信号、表面心電図、胸骨下の電位図、およびペーシング閾値が評価された。 
+【結果】
+ リードの留置と抜去は、デバイスまたは処置に関連した急性有害事象もなく、すべての患者で成功しました。 5 人の患者全員で解釈可能な血行動態信号が得られ、心電図との安定した拍動ごとの時間的対応と、洞調律、心房細動、VT、および心室細動にわたる明確な律動関連パターンが示された。 147 の VT エピソードすべてに、解釈可能な血行動態指数の記録が含まれていました。 血行動態指数は VT 中に急激に減少し、不整脈の終了後に回復しました。 VT、心室細動、洞調律の間の移行中に、血行動態指数の対応する変化が観察された。 心室捕捉は、5 人の患者全員で 11 ～ 17 V (平均 13.8 V)、0.5 ミリ秒で達成されました。 
+【結論】
+ この多機能胸骨下リードの急性留置は実現可能であり、急性心室捕捉による血行力学および電気センシングの統合が可能になりました。 これらの発見は、生理学に基づいた血管外植込み型除細動器システムのさらなる開発に対する人間による予備的な支援を提供します。血行力学センシングアルゴリズムの慢性的なパフォーマンスと臨床検証にはさらなる研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2729,7 +2991,16 @@
     <t>10.1007/s10840-026-02442-3 doi</t>
   </si>
   <si>
-    <t>背景: カテーテルアブレーションは、小児および先天性心疾患 (CHD) 患者の頻脈性不整脈に対する効果的かつ安全な治療法であることが証明されています。 これらの人々におけるカテーテルアブレーションの使用に関する国際登録はありますが、その中にはラテンアメリカ諸国は含まれていません。 目的: カテーテルアブレーション処置を受けている小児および先天性心疾患患者の臨床的特徴を評価すること。 取得されるデータには、不整脈の種類、技術、成功率、合併症、再発率が含まれます。 材料と方法: 記述的かつ分析的な遡及的観察研究が実施されました。 6 か月間利用できるクローズド コード化されたオンライン フォームが使用されました。 ラテンアメリカで小児電気生理学を実践し、以前の LAHSR の調査で特定された電気生理学者全員が、ラテンアメリカ心調律協会 (LAHRS) 電子メディア ( https://lahrs.org/ ) を通じて参加するよう招待されました。 参加は強制ではなく、経済的または物質的な財によって奨励されるものではなく、データの使用についてのインフォームドコンセントが必要でした。 2017年から2021年まで、年齢に関係なく、18歳未満の小児またはCHD患者を対象に、連続電気生理学的カテーテル処置が行われた。 結果: ラテンアメリカ 8 か国から 20 名の医師が参加しました。 合計1,778件の手術が報告され、53％が男性、平均年齢は12.4±5.1歳、8.5％が先天性心疾患を患っていた。 患者の 87% でアブレーションが試みられ、そのうちの 68% では非灌流先端高周波カテーテルが使用され、29% では 3D マッピング システムが使用されました。 98% のケースで最も一般的に使用されたエネルギー源は高周波でした。 最も頻度の高い基質は副経路で 69.5% (61% が明示的)、次いで房室結節リエントリーが 16.5%、異所性心房頻脈が 4% でした。 さらに、心房粗動が 3.8%、心室頻拍が 3.8%、心室性期外収縮が 1.2% 発生しました。 症例の 93% でアブレーションは直ちに成功したと考えられます。 平均総処置時間は 92.1 ± 36.8 分、平均総透視時間は 16.3 ± 9.4 分でした。 合併症率は 1.8% で、3 人の患者 (0.2%) には完全な房室ブロックが含まれていました。 死亡例は報告されていない。 再発率は8.5%でした。 結論: ラテンアメリカにおけるカテーテルアブレーションの、小児および先天性心疾患のみを対象としたこの初の遡及的登録では、高い成功率と低い合併症発生率が観察されました。 これは他の緯度で以前に報告された登録と一致しており、このグループの患者にとってアブレーションが効果的で安全な治療法であることが証明されています。</t>
+    <t xml:space="preserve">【背景】
+ カテーテルアブレーションは、小児および先天性心疾患 (CHD) 患者の頻脈性不整脈に対する効果的かつ安全な治療法であることが証明されています。 これらの人々におけるカテーテルアブレーションの使用に関する国際登録はありますが、その中にはラテンアメリカ諸国は含まれていません。 
+【目的】
+ カテーテルアブレーション処置を受けている小児および先天性心疾患患者の臨床的特徴を評価すること。 取得されるデータには、不整脈の種類、技術、成功率、合併症、再発率が含まれます。 材料と
+【方法】
+ 記述的かつ分析的な遡及的観察研究が実施されました。 6 か月間利用できるクローズド コード化されたオンライン フォームが使用されました。 ラテンアメリカで小児電気生理学を実践し、以前の LAHSR の調査で特定された電気生理学者全員が、ラテンアメリカ心調律協会 (LAHRS) 電子メディア ( https://lahrs.org/ ) を通じて参加するよう招待されました。 参加は強制ではなく、経済的または物質的な財によって奨励されるものではなく、データの使用についてのインフォームドコンセントが必要であった。 2017年から2021年まで、年齢に関係なく、18歳未満の小児またはCHD患者を対象に、連続電気生理学的カテーテル処置が行われた。 
+【結果】
+ ラテンアメリカ 8 か国から 20 名の医師が参加しました。 合計1,778件の手術が報告され、53％が男性、平均年齢は12.4±5.1歳、8.5％が先天性心疾患を患っていた。 患者の 87% でアブレーションが試みられ、そのうちの 68% では非灌流先端高周波カテーテルが使用され、29% では 3D マッピング システムが使用されました。 98% のケースで最も一般的に使用されたエネルギー源は高周波であった。 最も頻度の高い基質は副経路で 69.5% (61% が明示的)、次いで房室結節リエントリーが 16.5%、異所性心房頻脈が 4% であった。 さらに、心房粗動が 3.8%、心室頻拍が 3.8%、心室性期外収縮が 1.2% 発生しました。 症例の 93% でアブレーションは直ちに成功したと考えられます。 平均総処置時間は 92.1 ± 36.8 分、平均総透視時間は 16.3 ± 9.4 分であった。 合併症率は 1.8% で、3 人の患者 (0.2%) には完全な房室ブロックが含まれていました。 死亡例は報告されていない。 再発率は8.5%であった。 
+【結論】
+ ラテンアメリカにおけるカテーテルアブレーションの、小児および先天性心疾患のみを対象としたこの初の遡及的登録では、高い成功率と低い合併症発生率が観察された。 これは他の緯度で以前に報告された登録と一致しており、このグループの患者にとってアブレーションが効果的で安全な治療法であることが証明されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2760,7 +3031,14 @@
     <t>10.1111/jce.70512 doi</t>
   </si>
   <si>
-    <t>目的: 定位性不整脈放射線アブレーション (STAR) は、難治性心室頻拍に対する有望な非侵襲的治療法です。 STAR に走査陽子線を使用すると、正確に集束された高線量の電離放射線が可能になります。 ターゲットの動きを効果的に緩和することは安全性にとって重要ですが、ビームスキャンと心肺動作との間の複雑な相互作用のため、依然として困難です。 われわれは、ゲート走査陽子線を心室心筋標的に正確に照射する安全性と実現可能性を評価し、呼吸器（シングル）ゲートと心肺（デュアル）ゲート陽子線の病変転帰を比較した。 方法: 6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました。 その後、走査陽子線を使用したシングルゲートまたはデュアルゲート送達で治療されました。 治療反応は、ベースライン時および照射後 14 ～ 15 週間目に、心エコー検査、血液分析、陽電子放射断層撮影 (PET)-CT によって評価されました。 終了時に病変を評価し、組織を病理組織学のために採取した。 結果: フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。 照射領域は、すべての動物において、PET-CT では in vivo で、また ex vivo の剖検では予想された位置で識別可能でした。 視覚的病変の貫壁性は組織学によって確認された。 病変サイズは、デュアルゲート動物では予想される体積からそれほど遠くありませんでしたが、シングルゲート動物では大きかった（グループ間の比較では p = 0.3、各アームで N = 2）。 結論: 結果により、ワークフローの実現可能性が確認されました。 デュアルゲート照射は、標的体積外の心筋への放射線被ばくの減少と、病変のサイズが計画されたものに近づくことに関連していた。</t>
+    <t xml:space="preserve">【目的】
+ 定位性不整脈放射線アブレーション (STAR) は、難治性心室頻拍に対する有望な非侵襲的治療法です。 STAR に走査陽子線を使用すると、正確に集束された高線量の電離放射線が可能になります。 ターゲットの動きを効果的に緩和することは安全性にとって重要ですが、ビームスキャンと心肺動作との間の複雑な相互作用のため、依然として困難です。 われわれは、ゲート走査陽子線を心室心筋標的に正確に照射する安全性と実現可能性を評価し、呼吸器（シングル）ゲートと心肺（デュアル）ゲート陽子線の病変転帰を比較した。 
+【方法】
+ 6 頭のブタ (最初の 2 頭はプロトコルのテストとして使用) は、治療計画のために左心室自由壁の心筋標的に 35 Gy の単回分割線量でベースライン CT を受けました。 その後、走査陽子線を使用したシングルゲートまたはデュアルゲート送達で治療されました。 治療反応は、ベースライン時および照射後 14 ～ 15 週間目に、心エコー検査、血液分析、陽電子放射断層撮影 (PET)-CT によって評価された。 終了時に病変を評価し、組織を病理組織学のために採取した。 
+【結果】
+ フラクショナル モーションの平均ターゲット拡張は、シングル ゲートと比較してデュアルの方が低かった (16% ～ 23% 対 48% ～ 72%、各アームで N = 2)。 照射領域は、すべての動物において、PET-CT では in vivo で、また ex vivo の剖検では予想された位置で識別可能であった。 視覚的病変の貫壁性は組織学によって確認された。 病変サイズは、デュアルゲート動物では予想される体積からそれほど遠くありなかったが、シングルゲート動物では大きかった（グループ間の比較では p = 0.3、各アームで N = 2）。 
+【結論】
+ 結果により、ワークフローの実現可能性が確認されました。 デュアルゲート照射は、標的体積外の心筋への放射線被ばくの減少と、病変のサイズが計画されたものに近づくことに関連していた。</t>
   </si>
   <si>
     <t xml:space="preserve">AIMS:
@@ -2789,7 +3067,16 @@
     <t>10.1016/j.hrthm.2026.06.042 doi</t>
   </si>
   <si>
-    <t>背景: 慢性心臓植込み型電子機器リードの経静脈的抜去は、線維性癒着や処置上のリスクによって課題が生じています。 新しい技術は、安全性と有効性の向上を目指しています。 高周波機械振動システムは、癒着を破壊することを目的としています。 目的: この研究は、前臨床適正実験基準ヒツジモデルにおける新しい振動補助リード抽出システムの初期の安全性、性能、および使いやすさを評価することを目的としました。 方法： 2 年以上（範囲 2.9 ～ 5.25 年）埋め込まれた 9 本のリードを、X 線透視下で振動システムを使用して 6 頭の羊から抜き取った。 リードの内腔は、カスタマイズされたロッキング スタイレットを送達するために使用されました。 スタイレットを使用してリードに振動エネルギーを与え、1 匹あたり最大 20 分間適用しました。 評価には、手術の成功、リードの完全性、手術中のモニタリング、3日間の臨床フォローアップ、臨床検査、剖検、および病理組織学（心臓、肺、中心静脈）が含まれます。 結果: 補助ツールなしで手術の成功 (リード除去) は 100% でした。すべての症例で癒着剥離に外部切断シースは必要ありませんでした。 リードの解放は、9 つ​​のリードのうち 8 つで約 1 分以内に発生しました。 主要な安全性評価項目は満たされました：中心静脈または心筋穿孔がないこと、および肺塞栓症がないこと。 血圧低下、重大な不整脈、三尖弁逆流の悪化は発生しませんでした。 1 つのリード骨折 (9 件中 1 件) では、軽度の局所的な心筋壊死を伴う遠位スクリューの残存 (&lt;1 cm) が発生しました。 アンカーデバイスの誤動作により、2 件のケースで処置中の交換が必要になりました。 結論: このヒツジモデルでは、慢性心臓植込み型電子機器リードの振動支援による抜去は実現可能であり、主要な安全性エンドポイントを満たし、顕著な急性安全性プロファイルを示しました。 この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出を特徴としており、潜在的に危険な外部切断シースの要件を回避することに成功しました。 リードの破損とアンカーの機能不全は、さらなる技術評価と臨床試験の余地があることを示しています。</t>
+    <t xml:space="preserve">【背景】
+ 慢性心臓植込み型電子機器リードの経静脈的抜去は、線維性癒着や処置上のリスクによって課題が生じています。 新しい技術は、安全性と有効性の向上を目指しています。 高周波機械振動システムは、癒着を破壊することを目的としています。 
+【目的】
+ この研究は、前臨床適正実験基準ヒツジモデルにおける新しい振動補助リード抽出システムの初期の安全性、性能、および使いやすさを評価することを目的としました。 
+【方法】
+ 2 年以上（範囲 2.9 ～ 5.25 年）埋め込まれた 9 本のリードを、X 線透視下で振動システムを使用して 6 頭の羊から抜き取った。 リードの内腔は、カスタマイズされたロッキング スタイレットを送達するために使用されました。 スタイレットを使用してリードに振動エネルギーを与え、1 匹あたり最大 20 分間適用しました。 評価には、手術の成功、リードの完全性、手術中のモニタリング、3日間の臨床フォローアップ、臨床検査、剖検、および病理組織学（心臓、肺、中心静脈）が含まれます。 
+【結果】
+ 補助ツールなしで手術の成功 (リード除去) は 100% であった。すべての症例で癒着剥離に外部切断シースは必要ありなかった。 リードの解放は、9 つ​​のリードのうち 8 つで約 1 分以内に発生しました。 主要な安全性評価項目は満たされました：中心静脈または心筋穿孔がないこと、および肺塞栓症がないこと。 血圧低下、重大な不整脈、三尖弁逆流の悪化は発生しなかった。 1 つのリード骨折 (9 件中 1 件) では、軽度の局所的な心筋壊死を伴う遠位スクリューの残存 (&lt;1 cm) が発生しました。 アンカーデバイスの誤動作により、2 件のケースで処置中の交換が必要になりました。 
+【結論】
+ このヒツジモデルでは、慢性心臓植込み型電子機器リードの振動支援による抜去は実現可能であり、主要な安全性エンドポイントを満たし、顕著な急性安全性プロファイルを示しました。 この手順は、顕著な技術的単純さと内部ルーメンを介した迅速なリード放出を特徴としており、潜在的に危険な外部切断シースの要件を回避することに成功しました。 リードの破損とアンカーの機能不全は、さらなる技術評価と臨床試験の余地があることを示しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2820,7 +3107,16 @@
     <t>10.1111/jce.70503 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティです。 ただし、心室性不整脈 (VA) に対するその性能に関するデータは依然として限られています。 目的: 現実世界の米国多施設登録における複雑な VA に対する PFA の実現可能性、安全性、有効性を評価すること。 方法：この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けている連続患者が含まれていた（2024年4月から2025年7月まで）。 主要な実現可能性の成果は、意図した標的基質への PFA 損傷の送達の成功でした。 主な有効性アウトカムには、急性処置の成功が含まれます。植込み型除細動器（ICD）ショックまたは複数回の抗頻脈ペーシング療法を必要とする持続的な心室頻拍再発。 PVC 負荷が 80% 以上削減されます。 安全性の結果には、処置上の合併症、弁機能、血栓塞栓性イベント、腎機能、伝導障害が含まれます。 結果: 26 人の患者が含まれた (PVC 13 人、VT 13 人)。 すべての VT アブレーション (69.2% が完了、30.8% が部分的) および 92.3% の PVC アブレーションで急性成功が達成されました。 合併症は患者の 11.5% で発生しました (一過性 LBBB [n = 1] および血管合併症 [n = 2])。 血栓塞栓性イベント、心臓内血栓、または急性腎損傷は観察されませんでした。 僧帽弁装置付近の病変は、既存の弁膜症患者を含め、僧帽弁逆流を悪化させませんでした。 中央値365日の追跡調査の後、1人の患者がICDショックを必要とするVT再発を経験した。 VT アブレーション後の推定無再発生存率は 12 か月時点で 61.5% でした。 PVC 患者の 58.3% が 80% 以上の負担軽減を達成しました。 結論: VA に対する PFA は実行可能であり、非常に効果的であり、処置に関連した合併症の発生率は低いと考えられます。 急性の成功率は高かったものの、長期的な結果は VT アブレーションでは許容範囲であり、PVC アブレーションでは比較的穏やかであり、技術とエネルギー供給戦略の継続的な改良の必要性が強調されました。 大規模な前向き研究が保証されています。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールドアブレーション (PFA) は、心房性不整脈アブレーションにおける安全性が証明されている新興の非熱的アブレーションモダリティです。 ただし、心室性不整脈 (VA) に対するその性能に関するデータは依然として限られています。 
+【目的】
+ 現実世界の米国多施設登録における複雑な VA に対する PFA の実現可能性、安全性、有効性を評価すること。 
+【方法】
+この後ろ向き研究には、メイヨークリニックの3つのセンターで心室頻拍（VT）または心室性期外収縮（PVC）のPFAを受けている連続患者が含まれていた（2024年4月から2025年7月まで）。 主要な実現可能性の成果は、意図した標的基質への PFA 損傷の送達の成功であった。 主な有効性アウトカムには、急性処置の成功が含まれます。植込み型除細動器（ICD）ショックまたは複数回の抗頻脈ペーシング療法を必要とする持続的な心室頻拍再発。 PVC 負荷が 80% 以上削減されます。 安全性の結果には、処置上の合併症、弁機能、血栓塞栓性イベント、腎機能、伝導障害が含まれます。 
+【結果】
+ 26 人の患者が含まれた (PVC 13 人、VT 13 人)。 すべての VT アブレーション (69.2% が完了、30.8% が部分的) および 92.3% の PVC アブレーションで急性成功が達成されました。 合併症は患者の 11.5% で発生しました (一過性 LBBB [n = 1] および血管合併症 [n = 2])。 血栓塞栓性イベント、心臓内血栓、または急性腎損傷は観察されなかった。 僧帽弁装置付近の病変は、既存の弁膜症患者を含め、僧帽弁逆流を悪化させなかった。 中央値365日の追跡調査の後、1人の患者がICDショックを必要とするVT再発を経験した。 VT アブレーション後の推定無再発生存率は 12 か月時点で 61.5% であった。 PVC 患者の 58.3% が 80% 以上の負担軽減を達成しました。 
+【結論】
+ VA に対する PFA は実行可能であり、非常に効果的であり、処置に関連した合併症の発生率は低いと考えられます。 急性の成功率は高かったものの、長期的な結果は VT アブレーションでは許容範囲であり、PVC アブレーションでは比較的穏やかであり、技術とエネルギー供給戦略の継続的な改良の必要性が強調されました。 大規模な前向き研究が保証されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2851,7 +3147,16 @@
     <t>10.1016/j.hrthm.2026.09.026 doi</t>
   </si>
   <si>
-    <t>背景: 星状神経節遮断は、心臓への交感神経の流れを減少させることにより、難治性の心室不整脈を一時的に制御します。 しかし、現在の経皮的アプローチは効果の持続時間が短いために制限されており、より侵襲的な永久交感神経切除術を行わずに、より長期間持続する交感神経調節が必要とされています。 目的: 誘発された心臓交感神経反応の軽減における星状神経節凍結神経溶解性アブレーションの有効性と持続性を判断すること。 方法：ヨークシャー豚6頭で急性冷凍アブレーション研究を実施し、ユカタンミニ豚10頭で慢性研究を実施した（冷凍アブレーション7頭、偽対照3頭）。 急性研究では、高速スキャンサイクリックボルタンメトリーを使用して血行力学的反応と心筋ノルエピネフリン放出を評価しました。 慢性研究では、右星状神経節凍結神経溶解療法後の 1 か月間の生理学的、電気生理学的、神経化学的、および組織学的影響を評価しました。 結果： 低温神経溶解性星状神経節アブレーションは、急性期と慢性期の両方で誘発された心臓交感神経反応を減弱させた。 アブレーションから 1 か月後、交感神経の減衰は持続し、心室再分極に対する顕著な治療効果を伴っていました。 交感神経の減衰は解剖学的に切除部位に限定されたままであり、星状神経節の T1 成分のみを標的とするだけで、誘発された交感神経の心臓効果の大部分を除去するのに十分でした。 結論：低温神経溶解性星状神経節アブレーションは、持続性のある心臓交感神経調節を効果的に提供し、難治性心室不整脈に対する有望な中期治療を提供する。</t>
+    <t xml:space="preserve">【背景】
+ 星状神経節遮断は、心臓への交感神経の流れを減少させることにより、難治性の心室不整脈を一時的に制御します。 しかし、現在の経皮的アプローチは効果の持続時間が短いために制限されており、より侵襲的な永久交感神経切除術を行わずに、より長期間持続する交感神経調節が必要とされています。 
+【目的】
+ 誘発された心臓交感神経反応の軽減における星状神経節凍結神経溶解性アブレーションの有効性と持続性を判断すること。 
+【方法】
+ヨークシャー豚6頭で急性冷凍アブレーション研究を実施し、ユカタンミニ豚10頭で慢性研究を実施した（冷凍アブレーション7頭、偽対照3頭）。 急性研究では、高速スキャンサイクリックボルタンメトリーを使用して血行力学的反応と心筋ノルエピネフリン放出を評価しました。 慢性研究では、右星状神経節凍結神経溶解療法後の 1 か月間の生理学的、電気生理学的、神経化学的、および組織学的影響を評価しました。 
+【結果】
+ 低温神経溶解性星状神経節アブレーションは、急性期と慢性期の両方で誘発された心臓交感神経反応を減弱させた。 アブレーションから 1 か月後、交感神経の減衰は持続し、心室再分極に対する顕著な治療効果を伴っていました。 交感神経の減衰は解剖学的に切除部位に限定されたままであり、星状神経節の T1 成分のみを標的とするだけで、誘発された交感神経の心臓効果の大部分を除去するのに十分であった。 
+【結論】
+低温神経溶解性星状神経節アブレーションは、持続性のある心臓交感神経調節を効果的に提供し、難治性心室不整脈に対する有望な中期治療を提供する。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2879,7 +3184,11 @@
     <t>10.1111/jce.70511 doi</t>
   </si>
   <si>
-    <t>はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性があります。 我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。 方法と結果：我々は、Affera システムによる原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。 アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標が欠けているため、座標 (x、y、z) とバイポーラ電圧は CARTO 3 から抽出されました。 線維輪および左心耳を除く、エネルギー送達部位の外側のアブレーション前後のポイントは、2 mm の相互最近傍基準を使用して空間的に一致しました。 これにより、3772 ペアが得られました。 双極性電圧はケースごとに平均化されました。 平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました。 結論: Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
+    <t xml:space="preserve">はじめに: ほとんどのパルスフィールドアブレーション (PFA) システムとは異なり、Affera (Medtronic) は格子先端カテーテルと皮膚リターンパッチの間に単極エネルギーを供給し、より広範囲の電場を生成する可能性があります。 我々は、これによりアブレーション領域を超えて電圧が減衰する可能性があると仮説を立て、空間的に一致したアブレーション前およびアブレーション後のマップを使用してこれをテストしました。 方法と
+【結果】
+我々は、Affera システムによる原発性心房細動アブレーションを受けた連続 5 人の患者を遡及的に研究しました。 アブレーション前およびアブレーション直後の電圧マップは、CARTO 3 および OCTARAY (Biosense Webster) を使用して、右心房ペーシング中に同一の設定で生成されました。 Affera には空間マッチングのためのポイントレベルの 3D 座標が欠けているため、座標 (x、y、z) とバイポーラ電圧は CARTO 3 から抽出されました。 線維輪および左心耳を除く、エネルギー送達部位の外側のアブレーション前後のポイントは、2 mm の相互最近傍基準を使用して空間的に一致しました。 これにより、3772 ペアが得られた。 双極性電圧はケースごとに平均化されました。 平均双極電圧はすべての場合で 1.01 ± 0.61 から 0.56 ± 0.29 mV に減少し、40.2% の減少を示しました (95% CI、24.6%-55.8%、p = 0.044)。 距離階層化分析では、残留双極電圧（事後/事前×100）は、アブレーションゾーンの直後で最も低く、最も近いアプリケーションタグ中心からの距離に応じて徐々に増加し（10〜15 mmで16.5%、25〜30 mmで57.8%、すべてp&lt;0.001）、約30 mmを超えると数値的にベースラインと同等になりました。 
+【結論】
+ Affera ベースの単極アブレーションは急性双極電圧減衰を引き起こし、病変セットに隣接する非アブレーション心筋層にまで広がりましたが、距離とともに減少し、主に適用部位の約 30 mm 以内に限定されました。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -2903,7 +3212,14 @@
     <t>10.1111/jce.70515 doi</t>
   </si>
   <si>
-    <t>背景: ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。 しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。 方法：我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。 急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。 学習段階は、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。 結果: 学習曲線が観察され、最初の 20 回の手術中に不完全な病変形成が最も減少しました。 不完全な病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。 手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズでした。 より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しませんでした。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。 結論: PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。 LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。 体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
+    <t xml:space="preserve">【背景】
+ ペンタスプライン パルスフィールド アブレーション (PFA) は、持続性心房細動 (AF) における肺静脈隔離 (PVI) および後壁隔離 (PWI) の新しい治療法として登場しました。 しかし、PVI + PWI の組み合わせに関連する学習曲線と、急性病変の完全性に対する解剖学的要因の寄与は不完全に定義されたままです。 
+【方法】
+我々は、蛍光透視法および心臓内心エコー検査下での PFA を受けている持続性 AF 患者 182 名を連続して分析した。 急性不完全病変は、体系的な再マッピング後に追加の PFA 適用を必要とする残留伝導として定義されました。 学習段階は、セグメント化されたロジスティック回帰と逐次ブロック分析を使用して特定されました。 多変数モデルは、処置期、左心房容積 (LAV)、および後壁の形状を評価しました。 
+【結果】
+ 学習曲線が観察され、最初の 20 回の手術中に不完全な病変形成が最も減少しました。 不完全な病変は症例 1 ～ 20 の 55% (初期段階)、症例 21 ～ 160 の 32% (中間相)、症例 161 以上の 4.8% (後期) で発生しました。 手術段階は不完全病変の主な決定要因であり、初期段階と中期段階ではそれぞれ約 24 倍と 9 倍高いオッズであった。 より大きな LAV は、適度な独立した関連性 (OR 1.009/mL) を示しましたが、後壁の形状は独立した関連性を示しなかった。 中期の不整脈再発は各期で差はなかったが、後期では追跡期間が短かった。 
+【結論】
+ PVI + PWI を使用したペンタスプライン PFA 中の病変完全性は、処置の経験が増えるにつれて徐々に改善します。 LAV が大きいと不完全な病変形成に若干寄与する可能性がありますが、処置の経験が主な役割を果たすと思われます。 体系的な電気解剖学的再マッピングは、かなりの手術経験が蓄積された後でも、不完全な病変を特定して修正するために依然として重要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2929,7 +3245,16 @@
     <t>10.1016/j.hrthm.2026.09.044 doi</t>
   </si>
   <si>
-    <t>背景: QT延長症候群の多くの人々は、重要性が不確かな変異体として分類されるミスセンス変異体を保有しています。 臨床室実験からの機能的証拠は遺伝子診断の改善に役立ちますが、臨床解釈の枠組みで使用する前に適切な検証が必要です。 目的: KCNH2 変異体の 2 つの機能データセットを比較すること: K11.1 チャネルが細胞表面に到達する量を測定するハイスループット アッセイと、HEK293 細胞のカリウム電流レベルを測定する自動パッチ クランプです。 方法: 自動パッチクランプの結果は、病原性および良性の KCNH2 バリアントの参照セットを使用して尤度比に変換されました。 次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。 結果: 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られました。 残りの 103 個の変異はアッセイ間で異なり、49 個は正常な機能証拠と異常な機能的証拠の間でシフトし、54 個は機能的証拠のカテゴリーと不確定な結果の間でシフトしました。 両方のアッセイで強い異常証拠が割り当てられた変異体のうち、54 個は ClinVar には存在しませんでした。 111 個の未解決または矛盾する ClinVar バリアントのうち、92 個は、強力な機能的証拠を裏付けとなる計算および集団頻度の証拠と組み合わせると、おそらく病原性の分類に十分な証拠の組み合わせを満たすと考えられます。 結論: 尤度比キャリブレーションにより、MAVE データと自動パッチクランプ データを同じ臨床解釈フレームワーク内で比較できます。 これらの機能的データセットを組み合わせると、QT 延長症候群における KCNH2 バリアントのより透明性の高い解釈をサポートできます。</t>
+    <t xml:space="preserve">【背景】
+ QT延長症候群の多くの人々は、重要性が不確かな変異体として分類されるミスセンス変異体を保有しています。 臨床室実験からの機能的証拠は遺伝子診断の改善に役立ちますが、臨床解釈の枠組みで使用する前に適切な検証が必要です。 
+【目的】
+ KCNH2 変異体の 2 つの機能データセットを比較すること: K11.1 チャネルが細胞表面に到達する量を測定するハイスループット アッセイと、HEK293 細胞のカリウム電流レベルを測定する自動パッチ クランプです。 
+【方法】
+ 自動パッチクランプの結果は、病原性および良性の KCNH2 バリアントの参照セットを使用して尤度比に変換されました。 次に、これらの値を ACMG/AMP 機能証拠カテゴリーにマッピングし、QT 延長症候群の人で見つかった 495 個の一塩基 KCNH2 バリアントについて以前に校正された MAVE 証拠と比較しました。 
+【結果】
+ 全体として、495 種類のバリエーションのうち 392 種類 (79%) で、MAVE と自動パッチ クランプの間で一致する解釈が得られた。 残りの 103 個の変異はアッセイ間で異なり、49 個は正常な機能証拠と異常な機能的証拠の間でシフトし、54 個は機能的証拠のカテゴリーと不確定な結果の間でシフトしました。 両方のアッセイで強い異常証拠が割り当てられた変異体のうち、54 個は ClinVar には存在しなかった。 111 個の未解決または矛盾する ClinVar バリアントのうち、92 個は、強力な機能的証拠を裏付けとなる計算および集団頻度の証拠と組み合わせると、おそらく病原性の分類に十分な証拠の組み合わせを満たすと考えられます。 
+【結論】
+ 尤度比キャリブレーションにより、MAVE データと自動パッチクランプ データを同じ臨床解釈フレームワーク内で比較できます。 これらの機能的データセットを組み合わせると、QT 延長症候群における KCNH2 バリアントのより透明性の高い解釈をサポートできます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2957,7 +3282,16 @@
     <t>10.1007/s10840-026-02443-2 doi</t>
   </si>
   <si>
-    <t>背景: 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。 最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。 これに関連して、MAC がアブレーションの有効性を損なうことなく処置効率の利点を提供するかどうかは、十分に特徴づけられていません。 目的: 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。 方法：我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。 各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 で対応付けられ、39 人の年齢が一致した対照が得られました。 6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。 次に、グループ比較が行われました。 さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。 結果: 総室内時間 (103.5 ± 20.0 vs. 126.2±33.1分; p = 0.0004)、手順前のセットアップ時間 (33.4 ± 10.0 vs. 50.3±28.0分。 p = 0.0007）、および処置後のターンオーバー時間（14.8 ± 9.3 vs. 21.4 ± 8.3 分。 p = 0.0030) は MAC の方が有意に短かったです。 コア処置時間 (55.3 ± 20.5 vs. 55.3 ± 23.9 分）、経中隔から LA シースアウトまでの時間（34.2 ± 12.9 対 35.7 ± 18.5 分）はグループ間で有意な差はありませんでした（両方とも p ≥ 0.62）。 アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 vs. 24.2 ± 15.5 分。 p = 0.036)。 施行された切除病変の総数 (17.6 ± 5.1 vs. 18.8 ± 7.2、p = 0.68）および急性処置成功（39/39 [100%] vs. 39/39 [100%]) は MAC と GA の間で同様であり、どちらのグループにも処置上の合併症はありませんでした。 MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られました。 結論： AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありませんでした。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
+    <t xml:space="preserve">【背景】
+ 米国では、パルスフィールドアブレーション(PFA)システムが骨格筋の刺激と不快感を引き起こすため、米国では全身麻酔(GA)が心房細動(AF)カテーテルアブレーションの鎮静戦略として好まれており、より軽い鎮静下では耐えられないことが挙げられます。 最近導入されたバルーンインバスケット (BiB) PFA システム (VOLT) は、筋肉への刺激と痛みが少ないことが報告されており、GA の代わりに監視麻酔治療 (MAC) が可能になる可能性があります。 これに関連して、MAC がアブレーションの有効性を損なうことなく処置効率の利点を提供するかどうかは、十分に特徴づけられていません。 
+【目的】
+ 年齢に合わせたデザインを使用して、AF に対して BiB PFA (VOLT) を受けている患者において MAC と GA の間で処置のタイミング、アブレーションの有効性、安全性を比較すること。 
+【方法】
+我々は、2施設の電気生理学レジストリから、連続する39例のMAC症例とVOLT BiB PFAを受けた83例のGA症例のプールを遡及的に分析した。 各 MAC 患者は、利用可能な最も近い年齢の GA 患者と 1:1 で対応付けられ、39 人の年齢が一致した対照が得られた。 6 つの異なる時間間隔が収集されました: 総室時間、処置前のセットアップ時間、中心処置時間、処置後のターンオーバー時間、経中隔から左心房 (LA) へのシースアウト (滞留) 時間、およびアブレーション カテーテルの滞留時間。 施行された全切除病変数、急性手術の成功（4 本すべての肺静脈の分離）、および手術の合併症も比較されました。 次に、グループ比較が行われた。 さらに、公開されている EP/手順スイートの 1 分あたりのコスト見積もりを使用して、観察された総室内時間の違いに関連する EP 検査施設のコスト削減とスケジュールの機会コストも決定されました。 
+【結果】
+ 総室内時間 (103.5 ± 20.0 vs. 126.2±33.1分; p = 0.0004)、手順前のセットアップ時間 (33.4 ± 10.0 vs. 50.3±28.0分。 p = 0.0007）、および処置後のターンオーバー時間（14.8 ± 9.3 vs. 21.4 ± 8.3 分。 p = 0.0030) は MAC の方が有意に短かったです。 コア処置時間 (55.3 ± 20.5 vs. 55.3 ± 23.9 分）、経中隔から LA シースアウトまでの時間（34.2 ± 12.9 対 35.7 ± 18.5 分）はグループ間で有意な差はありなかった（両方とも p ≥ 0.62）。 アブレーションカテーテルの滞留時間は、MAC の方が若干長くなりました (27.7 ± 11.9 vs. 24.2 ± 15.5 分。 p = 0.036)。 施行された切除病変の総数 (17.6 ± 5.1 vs. 18.8 ± 7.2、p = 0.68）および急性処置成功（39/39 [100%] vs. 39/39 [100%]) は MAC と GA の間で同様であり、どちらのグループにも処置上の合併症はありなかった。 MAC 症例 1 例 (2.6%) は、気道分泌物による咳のため、処置の途中で全身麻酔に変更されました。 公表されている EP/手続きスイートの 1 分あたりのコスト見積もり (29 ドルから 60 ドル/分) を、観測された合計在室時間の 22.7 分の削減に適用すると、MAC は 1 件あたりの設備コストの推定 658 ドルから 1,362 ドルの節約に関連しており、追加のケースのスケジュール設定による潜在的な機会費用の利点が見られた。 
+【結論】
+ AF に対して BiB PFA (VOLT) を受けた年齢を一致させたコホートでは、MAC は GA よりも総室時間、処置前のセットアップ時間、および処置後のターンオーバー時間の短縮と関連しており、アブレーション病変の送達、急性成功、または合併症には差がありなかった。 MAC による麻酔関連の時間の節約は、アブレーション処置自体ではなく、部屋のロジスティクスに集中しているようで、この小規模コホートでは急性処置の結果に検出可能な差はなく、MAC が BiB PFA に対する GA に代わる合理的な代替品として支持されています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -2998,7 +3332,16 @@
     <t>10.1016/j.hrthm.2026.09.032 doi</t>
   </si>
   <si>
-    <t>背景: 身体運動と不整脈原性右室心筋症 (ARVC) との関連性にもかかわらず、患者に対する運動の安全性と適合性に関するデータは存在しない。 目的: 病原性プラコフィリン-2 変異を持つ ARVC 患者におけるさまざまな運動中の心室性期外収縮 (PVC) の発生率と複雑さ、および心臓代謝負荷を定量化すること。 方法: 明確な ARVC を持つ 25 人の参加者 (女性 9 人/男性 16 人) が、心肺機能をモニタリングしながらさまざまな運動を実施しました。 抵抗運動には両足スクワットと片側二頭筋カールが含まれ、持久運動には心拍数 (HR) 80、100、120 bpm でのウォーキングとサイクリングが含まれます。 各アクティビティの後には 10 分間の回復時間が続きました。 結果: 回復期の初期では、活発な運動期と比較して PVC の負担が 2 倍以上 (p &lt; 0.001)、PVC の形態が 3 つ以上発生しました (52 対 84%、p = 0.03)。 片側の上腕二頭筋カールのみが、安静時と比較して PVC 負担を増加させませんでした (p = 0.361)。 レジスタンスエクササイズは、同等の努力レベルでより低い心臓負荷と不整脈負荷を組み合わせたものです。 運動強度の分類では、同じタスクでも使用する指標によって「軽い」から「高い」まで大きな変動が見られました。 結論: PKP-2 ARVC における運動による不整脈の負担を適切に評価するには、早期回復モニタリングが不可欠です。 筋肉量の少ない運動は、PVC 負荷と心臓負荷 (不整脈のリスクと病気の進行の代用マーカー) が最も低いことが示されたため、この集団に運動を処方するための有望な道筋となります。 ARVC の運動強度ガイドラインは十分に明確ではないため、改善する必要があります。</t>
+    <t xml:space="preserve">【背景】
+ 身体運動と不整脈原性右室心筋症 (ARVC) との関連性にもかかわらず、患者に対する運動の安全性と適合性に関するデータは存在しない。 
+【目的】
+ 病原性プラコフィリン-2 変異を持つ ARVC 患者におけるさまざまな運動中の心室性期外収縮 (PVC) の発生率と複雑さ、および心臓代謝負荷を定量化すること。 
+【方法】
+ 明確な ARVC を持つ 25 人の参加者 (女性 9 人/男性 16 人) が、心肺機能をモニタリングしながらさまざまな運動を実施しました。 抵抗運動には両足スクワットと片側二頭筋カールが含まれ、持久運動には心拍数 (HR) 80、100、120 bpm でのウォーキングとサイクリングが含まれます。 各アクティビティの後には 10 分間の回復時間が続きました。 
+【結果】
+ 回復期の初期では、活発な運動期と比較して PVC の負担が 2 倍以上 (p &lt; 0.001)、PVC の形態が 3 つ以上発生しました (52 対 84%、p = 0.03)。 片側の上腕二頭筋カールのみが、安静時と比較して PVC 負担を増加させなかった (p = 0.361)。 レジスタンスエクササイズは、同等の努力レベルでより低い心臓負荷と不整脈負荷を組み合わせたものです。 運動強度の分類では、同じタスクでも使用する指標によって「軽い」から「高い」まで大きな変動が見られた。 
+【結論】
+ PKP-2 ARVC における運動による不整脈の負担を適切に評価するには、早期回復モニタリングが不可欠です。 筋肉量の少ない運動は、PVC 負荷と心臓負荷 (不整脈のリスクと病気の進行の代用マーカー) が最も低いことが示されたため、この集団に運動を処方するための有望な道筋となります。 ARVC の運動強度ガイドラインは十分に明確ではないため、改善する必要があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3091,7 +3434,12 @@
     <t>10.1093/europace/euag270 doi</t>
   </si>
   <si>
-    <t>目的: 心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まっています。 心臓は脂質含有量が高いことで知られており、脂質代謝の障害や異常は心血管疾患と関連していることがよくあります。 この研究は、AFにおける脂質の調節的役割を調査することを目的としています。 方法と結果: ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。 スフィンゴミエリンの外因性補給は、マウスにおける Ach-CaCl2 および Ang II 誘発性の AF、線維症、炎症を大幅に軽減しました。 さらに、スフィンゴミエリンレベルの低下は、AF条件下でのスフィンゴミエリンホスホジエステラーゼ（SMPD）の活性の増加に起因すると考えられました。 機構的には、RNA-Seq解析により、スフィンゴミエリンがAF誘発性のRap1シグナル伝達経路の活性化を阻害することが実証され、この所見は生体内でのRAP1の過剰発現とノックダウンによって裏付けられた。 結論：これらの発見は、まとめると、Rap1シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよびSMPD阻害剤の治療的可能性を強調し、それによってスフィンゴミエリン代謝の標的化が実行可能かつ新規な心房細動治療戦略として確立されることを示している。</t>
+    <t xml:space="preserve">【目的】
+ 心房細動 (AF) は、世界的に最も蔓延している不整脈の 1 つとして浮上しており、その発生率は継続的に増加しており、それにより公衆衛生上の重大な懸念事項にまで高まっています。 心臓は脂質含有量が高いことで知られており、脂質代謝の障害や異常は心血管疾患と関連していることがよくあります。 この研究は、AFにおける脂質の調節的役割を調査することを目的としています。 方法と
+【結果】
+ ツリーベースのアンサンブル学習支援リピドミクスを使用して、スフィンゴミエリンが重要な差次的代謝産物として同定され、AF 患者では大幅に減少していることが判明しました。 スフィンゴミエリンの外因性補給は、マウスにおける Ach-CaCl2 および Ang II 誘発性の AF、線維症、炎症を大幅に軽減しました。 さらに、スフィンゴミエリンレベルの低下は、AF条件下でのスフィンゴミエリンホスホジエステラーゼ（SMPD）の活性の増加に起因すると考えられました。 機構的には、RNA-Seq解析により、スフィンゴミエリンがAF誘発性のRap1シグナル伝達経路の活性化を阻害することが実証され、この所見は生体内でのRAP1の過剰発現とノックダウンによって裏付けられた。 
+【結論】
+これらの発見は、まとめると、Rap1シグナル伝達経路の阻害を通じて心房細動を軽減するスフィンゴミエリンおよびSMPD阻害剤の治療的可能性を強調し、それによってスフィンゴミエリン代謝の標的化が実行可能かつ新規な心房細動治療戦略として確立されることを示している。</t>
   </si>
   <si>
     <t xml:space="preserve">AIMS:
@@ -3115,7 +3463,7 @@
     <t>10.1007/s10840-026-02441-4 doi</t>
   </si>
   <si>
-    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。 我々は、左心室頻脈アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。 逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウスジョーダン) を使用して達成されました。 この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されませんでした。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大します。</t>
+    <t>パルスフィールドアブレーション (PFA) は心室アブレーションに使用されることが増えています。 我々は、左心室頻脈アブレーションに対する逆行性大動脈アプローチによる可変ループ円形 PFA カテーテル (Varipulse、Biosense Webster, Inc.、カリフォルニア州アーバイン) の使用を説明する新しい症例を紹介します。 逆行性大動脈アクセスは、僧帽弁装置による挟み込みを避けるために可変ループ PFA カテーテルの安全な抜去と操作を可能にする長いシース (Ventrax システム、Merit Medical、ユタ州サウスジョーダン) を使用して達成されました。 この処置は合併症なく完了し、3 か月の追跡調査を通じて VT の再発は観察されなかった。 この症例は、このアプローチの実現可能性を強調し、この統合された PFA プラットフォームの潜在的な用途を、現在の心房細動アブレーションの適応を超えて拡大します。</t>
   </si>
   <si>
     <t>Pulsed field ablation (PFA) has been increasingly used for ventricular ablation. We present a novel case describing use of a variable-loop circular PFA catheter (Varipulse, Biosense Webster, Inc., Irvine, CA, USA) via a retrograde aortic approach for left ventricular ventricular tachycardia ablation. Retrograde aortic access was achieved using a long sheath (Ventrax system, Merit Medical, South Jordan, UT) permitting safe unsheathing and manipulation of the variable-loop PFA catheter to avoid entrapment with the mitral valve apparatus. The procedure was completed without complication and no VT recurrence was observed over 3 months follow-up. This case highlights the feasibility of this approach and expands the potential applications of this integrated PFA platform beyond its current indication for atrial fibrillation ablation.</t>
@@ -3134,7 +3482,16 @@
     <t>10.1016/j.hrthm.2026.09.023 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、高い心筋選択性を備えた新しい非熱的アブレーションモダリティです。 しかし、隣接する神経構造の刺激と一過性の機能不全は依然として重要なオフターゲット効果です。 目的: 単一二相性エレクトロポレーション パルスに曝露された横隔神経と迷走神経の興奮、伝導抑制、回復に対するパルス パラメーターの影響を定義すること。 方法: 4 チャンネルの複合活動電位 (CAP) 記録を可能にする多電極チャンバーを使用して、生体外のブタの横隔神経と迷走神経を研究しました。 パルス振幅、パルス幅 (0.5 ～ 10 μs)、および相間遅延 (0.5 ～ 1000 μs) を系統的に変化させました。 刺激閾値と伝導抑制が定量化され、経時的に回復が評価されました。 横隔神経のインシリコモデルは、電場分布を推定し、機構の解釈をサポートするために開発されました。 結果: パルス幅と相間遅延が減少すると、刺激閾値が増加しました。 無髄線維は有髄線維よりも 6.8 ～ 8.3 倍高い電圧を必要としました。 伝導抑制はパルスパラメータに強く依存しており、パルス幅が長く、振幅が大きいほど伝導抑制が大きくなります。 高振幅パルスは完全ではあるが可逆的な伝導抑制を引き起こし、CAP の回復は 30 分以内に 80% を超えました。 モデリングでは、電極付近の電場勾配の上昇が示され、神経周膜内の特に高い電場の大きさが予測され、この構造がパルス送達の初期段階で影響を受ける可能性があることが示唆されました。 結論: 単一の PFA パルスは、パラメーター依存的に、摘出されたブタの横隔神経と迷走神経において神経興奮と可逆的な伝導抑制の両方を誘発しました。 これらの発見は、PFA 関連の神経効果に対する機構的な洞察を提供し、近くの自律神経の刺激が徐脈や冠状動脈けいれんなどの臨床観察に潜在的に寄与する可能性があることを示唆しています。 定量的な変換には、臨床的に代表的なカテーテルの形状と完全なパルス列が必要です。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールドアブレーション (PFA) は、高い心筋選択性を備えた新しい非熱的アブレーションモダリティです。 しかし、隣接する神経構造の刺激と一過性の機能不全は依然として重要なオフターゲット効果です。 
+【目的】
+ 単一二相性エレクトロポレーション パルスに曝露された横隔神経と迷走神経の興奮、伝導抑制、回復に対するパルス パラメーターの影響を定義すること。 
+【方法】
+ 4 チャンネルの複合活動電位 (CAP) 記録を可能にする多電極チャンバーを使用して、生体外のブタの横隔神経と迷走神経を研究しました。 パルス振幅、パルス幅 (0.5 ～ 10 μs)、および相間遅延 (0.5 ～ 1000 μs) を系統的に変化させました。 刺激閾値と伝導抑制が定量化され、経時的に回復が評価された。 横隔神経のインシリコモデルは、電場分布を推定し、機構の解釈をサポートするために開発されました。 
+【結果】
+ パルス幅と相間遅延が減少すると、刺激閾値が増加しました。 無髄線維は有髄線維よりも 6.8 ～ 8.3 倍高い電圧を必要としました。 伝導抑制はパルスパラメータに強く依存しており、パルス幅が長く、振幅が大きいほど伝導抑制が大きくなります。 高振幅パルスは完全ではあるが可逆的な伝導抑制を引き起こし、CAP の回復は 30 分以内に 80% を超えました。 モデリングでは、電極付近の電場勾配の上昇が示され、神経周膜内の特に高い電場の大きさが予測され、この構造がパルス送達の初期段階で影響を受ける可能性があることが示唆されました。 
+【結論】
+ 単一の PFA パルスは、パラメーター依存的に、摘出されたブタの横隔神経と迷走神経において神経興奮と可逆的な伝導抑制の両方を誘発しました。 これらの発見は、PFA 関連の神経効果に対する機構的な洞察を提供し、近くの自律神経の刺激が徐脈や冠状動脈けいれんなどの臨床観察に潜在的に寄与する可能性があることを示唆しています。 定量的な変換には、臨床的に代表的なカテーテルの形状と完全なパルス列が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3218,7 +3575,16 @@
     <t>10.1016/j.hrthm.2026.09.017 doi</t>
   </si>
   <si>
-    <t>背景: 心外膜脂肪組織 (EAT) は、心房リモデリングを誘発するという仮説が立てられています。 しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません。 心房線維症が心外膜から心内膜に進行する可能性があることを考慮すると、単極電圧は初期リモデリングのより感度の高いマーカーである可能性があります。 目的: 早期心房リモデリング患者における左心房 (LA) EAT、局所単極および双極電圧、アブレーション後の不整脈再発との関係を評価すること。 方法: 連続した患者はインデックス AF アブレーションの前に高解像度 LA 電気解剖学的マッピングを受けました。 双極性低電圧（≤0.5mV）領域が5％以上の患者は除外された。 LAおよび局所的な単極性瘢痕は、健康な対照コホートにおける5パーセンタイルのカットポイントによって定義されました。 EATは術前のCTでセグメント化されました。 各電圧点について、3 ボクセル内の EAT の存在が決定されました。 多変数モデリングを使用して、非瘢痕点における電圧の予測因子を特定しました。 心房性不整脈の再発は12か月の追跡調査で評価されました。 結果: 50 人の患者 (56±11 歳、78% が発作性) が含まれました。 単極電圧のカットポイントにより、双極電圧が保存されていたポイントのさらに 9.2% が傷跡として特定されました。 EAT の存在は、局所双極性電圧の有意な予測因子でした (p=0.010)。 この EAT と電圧の関係は、EAT の存在によって単極性 (p=0.027) と双極性 (p=0.007) の両方の電圧が予測される後壁で最も顕著でした。 後部:LA EAT 比は、発作性 AF 患者における心房性不整脈再発の唯一の独立した予測因子でした。 結論: EAT は、心房基質の発達、特に後壁において初期の原因となる可能性のある役割を果たしています。 単極電圧マッピングは、初期の心房基質を特定する際に付加価値を提供する可能性があります。</t>
+    <t xml:space="preserve">【背景】
+ 心外膜脂肪組織 (EAT) は、心房リモデリングを誘発するという仮説が立てられています。 しかし、EAT と初期心房基質の間の空間的関係を評価した先行研究はありません。 心房線維症が心外膜から心内膜に進行する可能性があることを考慮すると、単極電圧は初期リモデリングのより感度の高いマーカーである可能性があります。 
+【目的】
+ 早期心房リモデリング患者における左心房 (LA) EAT、局所単極および双極電圧、アブレーション後の不整脈再発との関係を評価すること。 
+【方法】
+ 連続した患者はインデックス AF アブレーションの前に高解像度 LA 電気解剖学的マッピングを受けました。 双極性低電圧（≤0.5mV）領域が5％以上の患者は除外された。 LAおよび局所的な単極性瘢痕は、健康な対照コホートにおける5パーセンタイルのカットポイントによって定義されました。 EATは術前のCTでセグメント化されました。 各電圧点について、3 ボクセル内の EAT の存在が決定されました。 多変数モデリングを使用して、非瘢痕点における電圧の予測因子を特定しました。 心房性不整脈の再発は12か月の追跡調査で評価された。 
+【結果】
+ 50 人の患者 (56±11 歳、78% が発作性) が含まれました。 単極電圧のカットポイントにより、双極電圧が保存されていたポイントのさらに 9.2% が傷跡として特定されました。 EAT の存在は、局所双極性電圧の有意な予測因子であった (p=0.010)。 この EAT と電圧の関係は、EAT の存在によって単極性 (p=0.027) と双極性 (p=0.007) の両方の電圧が予測される後壁で最も顕著であった。 後部:LA EAT 比は、発作性 AF 患者における心房性不整脈再発の唯一の独立した予測因子であった。 
+【結論】
+ EAT は、心房基質の発達、特に後壁において初期の原因となる可能性のある役割を果たしています。 単極電圧マッピングは、初期の心房基質を特定する際に付加価値を提供する可能性があります。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3304,7 +3670,12 @@
     <t>10.1111/jce.70498 doi</t>
   </si>
   <si>
-    <t>背景: 高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題です。 パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではありません。 ここでは、難治性 VT 患者に対する FARAPOINT 焦点 PFA の米国での最初の経験について説明します。 方法と結果：我々は、2025年7月から2026年5月までに、単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。 すべての患者は薬剤抵抗性の持続性単形性 VT を患っていた。 年齢中央値は77歳で、虚血性心筋症と非虚血性心筋症が混在していた。 10 人中 6 人は、以前に少なくとも 1 回カテーテルアブレーションに失敗したことがありました。 急性非誘発性は、正式なアブレーション後刺激試験を受けた9人の患者全員で達成されました。 処置上の合併症は発生しませんでした。 中央値95.5日の追跡期間中、10人の患者のうち4人で持続性VTが再発した。 繰り返しアブレーションを受けた患者も、機械的循環補助を必要とした患者も、死亡した患者もいませんでした。 結論：この米国での最初の実験では、難治性心室頻拍と、困難な基質を含む以前のアブレーション失敗を伴う高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に有効でした。 これらの観察を拡大するには、前向き多施設研究が必要です。</t>
+    <t xml:space="preserve">【背景】
+ 高周波 (RF) アブレーションが失敗した後の薬剤抵抗性の心室頻拍 (VT) は依然として臨床上の課題です。 パルスフィールドアブレーション（PFA）は心室用途に拡大していますが、VTにおける焦点パルスフィールド専用カテーテルに関する米国の経験は乏しく、パルスフィールドプラットフォームはメーカー間で同等ではない。 ここでは、難治性 VT 患者に対する FARAPOINT 焦点 PFA の米国での最初の経験について説明します。 方法と
+【結果】
+我々は、2025年7月から2026年5月までに、単一のVAヘルスケアシステムでFARAPOINT（ボストンサイエンティフィック）焦点PFAカテーテルを用いたVTアブレーションを受けた連続10人の患者を遡及的に検討した。 すべての患者は薬剤抵抗性の持続性単形性 VT を患っていた。 年齢中央値は77歳で、虚血性心筋症と非虚血性心筋症が混在していた。 10 人中 6 人は、以前に少なくとも 1 回カテーテルアブレーションに失敗したことがあった。 急性非誘発性は、正式なアブレーション後刺激試験を受けた9人の患者全員で達成されました。 処置上の合併症は発生しなかった。 中央値95.5日の追跡期間中、10人の患者のうち4人で持続性VTが再発した。 繰り返しアブレーションを受けた患者も、機械的循環補助を必要とした患者も、死亡した患者もいなかった。 
+【結論】
+この米国での最初の実験では、難治性心室頻拍と、困難な基質を含む以前のアブレーション失敗を伴う高リスクコホート内の虚血性心筋症患者に対して、FARAPOINT は安全であり、非常に有効であった。 これらの観察を拡大するには、前向き多施設研究が必要です。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3328,7 +3699,13 @@
     <t>10.1111/jce.70491 doi</t>
   </si>
   <si>
-    <t>はじめに: 電位図のピークツーピーク電圧は、心房壁の構造とマッピング構成によって異なります。 コンピューター断層撮影法から得られた心房壁の厚さ、心筋内脂肪、心筋の筋肉の厚さと、全極、双極、および単極マッピングで得られた心電図電圧との関係を評価しました。 方法：心房細動または非定型心房粗動アブレーション中に左心房マッピングを受けた連続患者を遡及的に含めた。 術前の造影 CT を ADAS 3D で処理して、左心房壁の厚さと心筋内脂肪浸潤を定量化し、そこから心筋の筋肉の厚さを導き出しました。 高密度の電気解剖学的マップが CT と空間的に同時登録されました。 解剖学的パラメーターとピークツーピーク電圧の間の関連性を、リズムの安定性によって階層化して評価しました。 結果: 20 人の患者が含まれました。 安定したリズムでは、左心房壁の厚さはすべての構成で電圧と正の相関があり、単極 (β = 0.38) と全極 (β = 0.23) で最も強くなります。 双極性マッピング (β = 0.13) (BP-UP p &lt; 0.0001; BP-OT p &lt; 0.01)。 心筋内脂肪は、双極性（β = -0.14）および単極性（β = -0.01; p ≤ 0.02）と比較して、全極性（β = -0.39）と最も強い逆相関を示しました。 脂肪を除いた後、筋肉の厚さはOT (β = 0.30)およびUP (β = 0.30)と正の相関があり、BPを上回りました(β = 0.14; p &lt; 0.0001)。 不安定なリズムでは、関連性は減弱されましたが、OT は脂肪 (β = -0.20) と筋肉の厚さ (β = 0.11) に対して最も反応し続けました (両方とも p &lt; 0.01)。 結論: 心筋の筋肉の厚さは局所心房電圧の主な決定要因ですが、心筋内の脂肪は電圧の減衰に寄与します。 OT は、特に調律が不安定な場合に、心房壁組成の最も一貫した評価を提供します。</t>
+    <t xml:space="preserve">はじめに: 電位図のピークツーピーク電圧は、心房壁の構造とマッピング構成によって異なります。 コンピューター断層撮影法から得られた心房壁の厚さ、心筋内脂肪、心筋の筋肉の厚さと、全極、双極、および単極マッピングで得られた心電図電圧との関係を評価しました。 
+【方法】
+心房細動または非定型心房粗動アブレーション中に左心房マッピングを受けた連続患者を遡及的に含めた。 術前の造影 CT を ADAS 3D で処理して、左心房壁の厚さと心筋内脂肪浸潤を定量化し、そこから心筋の筋肉の厚さを導き出しました。 高密度の電気解剖学的マップが CT と空間的に同時登録されました。 解剖学的パラメーターとピークツーピーク電圧の間の関連性を、リズムの安定性によって階層化して評価しました。 
+【結果】
+ 20 人の患者が含まれました。 安定したリズムでは、左心房壁の厚さはすべての構成で電圧と正の相関があり、単極 (β = 0.38) と全極 (β = 0.23) で最も強くなります。 双極性マッピング (β = 0.13) (BP-UP p &lt; 0.0001; BP-OT p &lt; 0.01)。 心筋内脂肪は、双極性（β = -0.14）および単極性（β = -0.01; p ≤ 0.02）と比較して、全極性（β = -0.39）と最も強い逆相関を示しました。 脂肪を除いた後、筋肉の厚さはOT (β = 0.30)およびUP (β = 0.30)と正の相関があり、BPを上回りました(β = 0.14; p &lt; 0.0001)。 不安定なリズムでは、関連性は減弱されましたが、OT は脂肪 (β = -0.20) と筋肉の厚さ (β = 0.11) に対して最も反応し続けました (両方とも p &lt; 0.01)。 
+【結論】
+ 心筋の筋肉の厚さは局所心房電圧の主な決定要因ですが、心筋内の脂肪は電圧の減衰に寄与します。 OT は、特に調律が不安定な場合に、心房壁組成の最も一貫した評価を提供します。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3354,7 +3731,12 @@
     <t>10.1111/jce.70492 doi</t>
   </si>
   <si>
-    <t>背景: 医原性空気同伴は、パルスフィールドアブレーション (PFA) において予防可能な塞栓の危険性です。 大口径 PFA シースを介したカテーテル挿入のマッピングは脆弱なステップである可能性がありますが、カテーテルの形状と液体で密封された挿入の役割は不明です。 方法と結果: ex vivo 生理食塩水タンク モデルでは、生理食塩水注入のみ、連続手動吸引、またはカスタム アダプター シンクを使用した液体密封挿入を使用して、ORION ミニバスケットと SPIRAL 円形マッピング カテーテルを FARADRIVE 操縦可能シースを通して挿入しました。 主要評価項目は、10 回の挿入の各試行後に遠位で回収された肉眼的な空気でした。試験は分析の単位であり、0.2 mL が定量的に報告可能な最小量でした。 60 件の試験 (600 件の挿入) において、緩和戦略は空気連行に大きな影響を与えました (Kruskal-Wallis p &lt; 0.001)。 生理食塩水注入のみでは、ORION は SPIRAL よりも多くの空気を生成しました (23.86 ± 3.63 vs. 10 回の挿入あたり 7.20 ± 2.09 mL。 2.39 vs. 1 回の挿入につき 0.72 mL。調整済み p &lt; 0.001)。 手動吸引により、エントレインメントは 10 挿入あたり 3.96 ± 1.01 および 1.02 ± 0.45 mL (挿入あたり 0.40 および 0.10 mL) に減少しましたが、残留空気は残りました。 液体封入挿入では、どの試験でも視覚的に検出可能または定量的に測定可能な肉眼で見える空気は観察されませんでした。 結論: 空気の同伴は、マッピングカテーテルの形状と緩和戦略によって異なります。 時間を決めて手動で吸引すると、測定可能な空気が大幅に減少しましたが、ゼロにはなりませんでした。 液体密封挿入は、この ex vivo モデル内で測定可能な肉眼で見える空気を伴わず、生理学的圧力条件下および臨床 PFA ワークフローでのさらなる評価が正当化されました。</t>
+    <t xml:space="preserve">【背景】
+ 医原性空気同伴は、パルスフィールドアブレーション (PFA) において予防可能な塞栓の危険性です。 大口径 PFA シースを介したカテーテル挿入のマッピングは脆弱なステップである可能性がありますが、カテーテルの形状と液体で密封された挿入の役割は不明です。 方法と
+【結果】
+ ex vivo 生理食塩水タンク モデルでは、生理食塩水注入のみ、連続手動吸引、またはカスタム アダプター シンクを使用した液体密封挿入を使用して、ORION ミニバスケットと SPIRAL 円形マッピング カテーテルを FARADRIVE 操縦可能シースを通して挿入しました。 主要評価項目は、10 回の挿入の各試行後に遠位で回収された肉眼的な空気であった。試験は分析の単位であり、0.2 mL が定量的に報告可能な最小量であった。 60 件の試験 (600 件の挿入) において、緩和戦略は空気連行に大きな影響を与えました (Kruskal-Wallis p &lt; 0.001)。 生理食塩水注入のみでは、ORION は SPIRAL よりも多くの空気を生成しました (23.86 ± 3.63 vs. 10 回の挿入あたり 7.20 ± 2.09 mL。 2.39 vs. 1 回の挿入につき 0.72 mL。調整済み p &lt; 0.001)。 手動吸引により、エントレインメントは 10 挿入あたり 3.96 ± 1.01 および 1.02 ± 0.45 mL (挿入あたり 0.40 および 0.10 mL) に減少しましたが、残留空気は残りました。 液体封入挿入では、どの試験でも視覚的に検出可能または定量的に測定可能な肉眼で見える空気は観察されなかった。 
+【結論】
+ 空気の同伴は、マッピングカテーテルの形状と緩和戦略によって異なります。 時間を決めて手動で吸引すると、測定可能な空気が大幅に減少しましたが、ゼロにはなりなかった。 液体密封挿入は、この ex vivo モデル内で測定可能な肉眼で見える空気を伴わず、生理学的圧力条件下および臨床 PFA ワークフローでのさらなる評価が正当化されました。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3378,7 +3760,13 @@
     <t>10.1007/s10840-026-02422-7 doi</t>
   </si>
   <si>
-    <t>はじめに: カテーテル アブレーションにおける持続的な結果には、貫壁性病変を達成することが重要です。 心電図振幅の減少とペーシング閾値の変化は有用なパラメーターとして報告されていますが、最適な電極構成とカットオフ値は不明のままです。 この前臨床研究では、QDOT MICRO カテーテルを使用した経壁性の予測における従来の微小電極構成の有効性を評価しました。 方法: 14 頭のブタに高周波アブレーションを実施し、131 個の心房病変を作成しました。 ペーシング閾値と電位図の振幅は、従来の双極、微小電極双極、単極の 3 つの構成を使用してアブレーションの前後で測定されました。 病変の貫壁性は組織学的に決定された。 予測精度を評価するために、受信機の動作特性分析が実施されました。 結果: すべての構成の中で、従来のバイポーラ (A1-A2) が最も高い予測値を示しました。 アブレーション後の双極性振幅は経壁性病変では低くなり (AUC 0.777、0.86mV)、振幅減少は大きくなりました (64.4% 対 64.4%)。 40.5%, AUC 0.682).  ペーシング閾値はアブレーション後に大幅に増加し、貫壁性病変ではより高くなりました。 A1-A2 構成は、貫壁性の予測精度が最も高かった (AUC 0.880、カットオフ 3.4 V)。 微小電極は一貫性のないパターンを示し、最適な構成が選択された場合でも、従来の双極測定よりも精度が低いままでした。 さらに、R 波 (双極性) および S 波 (単極性) の消失を含む形態学的変化は、限られた的中率を示しました (それぞれ AUC ≤ 0.77 および ≤ 0.56)。 結論: 従来の双極電極は、電位図の振幅とペーシング閾値による経壁性の評価において、微小電極構成よりも優れた性能を発揮しました。 QDOT-MICRO カテーテルを使用したチップツーリング双極ペーシングは、3.4 V を最適なしきい値として、心房病変の貫壁性を最も効果的に評価します。</t>
+    <t xml:space="preserve">はじめに: カテーテル アブレーションにおける持続的な結果には、貫壁性病変を達成することが重要です。 心電図振幅の減少とペーシング閾値の変化は有用なパラメーターとして報告されていますが、最適な電極構成とカットオフ値は不明のままです。 この前臨床研究では、QDOT MICRO カテーテルを使用した経壁性の予測における従来の微小電極構成の有効性を評価しました。 
+【方法】
+ 14 頭のブタに高周波アブレーションを実施し、131 個の心房病変を作成しました。 ペーシング閾値と電位図の振幅は、従来の双極、微小電極双極、単極の 3 つの構成を使用してアブレーションの前後で測定されました。 病変の貫壁性は組織学的に決定された。 予測精度を評価するために、受信機の動作特性分析が実施されました。 
+【結果】
+ すべての構成の中で、従来のバイポーラ (A1-A2) が最も高い予測値を示しました。 アブレーション後の双極性振幅は経壁性病変では低くなり (AUC 0.777、0.86mV)、振幅減少は大きくなりました (64.4% 対 64.4%)。 40.5%, AUC 0.682).  ペーシング閾値はアブレーション後に大幅に増加し、貫壁性病変ではより高くなりました。 A1-A2 構成は、貫壁性の予測精度が最も高かった (AUC 0.880、カットオフ 3.4 V)。 微小電極は一貫性のないパターンを示し、最適な構成が選択された場合でも、従来の双極測定よりも精度が低いままであった。 さらに、R 波 (双極性) および S 波 (単極性) の消失を含む形態学的変化は、限られた的中率を示しました (それぞれ AUC ≤ 0.77 および ≤ 0.56)。 
+【結論】
+ 従来の双極電極は、電位図の振幅とペーシング閾値による経壁性の評価において、微小電極構成よりも優れた性能を発揮しました。 QDOT-MICRO カテーテルを使用したチップツーリング双極ペーシングは、3.4 V を最適なしきい値として、心房病変の貫壁性を最も効果的に評価します。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3404,7 +3792,14 @@
     <t>10.1111/jce.70489 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションの有望なエネルギー源として浮上しています。 この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。 方法: AF を患う連続オールカマー患者は、深い鎮静下でバルーンインバスケット PFA カテーテルを使用して PFA を受けました。 Pear ワークフローは、2 段階の PVI プロトコルで構成されていました。(1) 最初の PV 血管造影によってガイドされ、回転展開によって PV 閉塞と病変の重なりを確認する 4 つの前庭部 PFA アプリケーション、続いて (2) PV スリーブをターゲットとした 2 つの遠位洋ナシ型バルーン アプリケーション。 インピーダンスベースの接触評価を備えた三次元電気解剖学的マッピングが利用されました。 手順パラメータ、急性有効性、および安全性が分析されました。 結果: 50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録されました。 すべての PV が正常に分離されました。 処置時間と蛍光透視検査時間の中央値はそれぞれ50分（IQR 41-50）と7.2分（IQR 5.8-11.4）で、研究期間を通じて大きな変化はなかった（50対IQR）。 患者 1 ～ 25 および 26 ～ 50 についてはそれぞれ 47 分、p = 0.26)。 追加のアブレーションが 4 人の患者に実行され、同時に左心耳閉鎖が 3 人に実行されました。 重篤な合併症も軽微な合併症も発生しませんでした。 一過性の横隔神経気絶が 2 人の患者で観察され、処置が完了する前に解消されました。 結論：Pear の 2 ステップ戦略により、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI が可能になります。このカテーテルは、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供します。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールドアブレーション (PFA) は、心房細動 (AF) カテーテルアブレーションの有望なエネルギー源として浮上しています。 この研究は、肺静脈隔離 (PVI)、ペア ワークフローのための 2 リング バルーンとペア戦略を使用した新しいバルーン イン バスケット PFA カテーテルの採用とワークフローの最適化について説明することを目的としました。 
+【方法】
+ AF を患う連続オールカマー患者は、深い鎮静下でバルーンインバスケット PFA カテーテルを使用して PFA を受けました。 Pear ワークフローは、2 段階の PVI プロトコルで構成されていました。(1) 最初の PV 血管造影によってガイドされ、回転展開によって PV 閉塞と病変の重なりを確認する 4 つの前庭部 PFA アプリケーション、続いて (2) PV スリーブをターゲットとした 2 つの遠位洋ナシ型バルーン アプリケーション。 インピーダンスベースの接触評価を備えた三次元電気解剖学的マッピングが利用されました。 手順パラメータ、急性有効性、および安全性が分析されました。 
+【結果】
+ 50 人の患者 (発作性 AF 62%、女性 42%、平均年齢 68 ± 10 歳) が登録されました。 すべての PV が正常に分離されました。 処置時間と蛍光透視検査時間の中央値はそれぞれ50分（IQR 41-50）と7.2分（IQR 5.8-11.4）で、研究期間を通じて大きな変化はなかった（50対IQR）。 患者 1 ～ 25 および 26 ～ 50 についてはそれぞれ 47 分、p = 0.26)。 追加のアブレーションが 4 人の患者に実行され、同時に左心耳閉鎖が 3 人に実行されました。 重篤な合併症も軽微な合併症も発生しなかった。 一過性の横隔神経気絶が 2 人の患者で観察され、処置が完了する前に解消されました。 
+【結論】
+Pear の 2 ステップ戦略により、バルーンインバスケット PFA カテーテルを使用した迅速、効率的、安全な PVI が可能になります。このカテーテルは、解剖学的に基づいた設計にもかかわらず、最小限の学習曲線で統合されたマッピングを通じて手順の多用途性を提供します。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3430,7 +3825,13 @@
     <t>10.1111/jce.70469 doi</t>
   </si>
   <si>
-    <t>はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる場合があります。 われわれは、失神、動悸、原因性脳卒中、またはブルガダ症候群のために移植された患者間で、ILRで検出された不整脈の時間依存的な診断率と臨床的関連性が異な​​るかどうかを評価した。 目的：この研究は、臨床適応症全体にわたるILRの時間依存的な診断率を定義し、早期診断と後期診断で臨床管理への影響が異なるかどうかを評価することを目的としました。 方法と結果：我々は、イタリアの5つのセンターで原因不明の失神、動悸、原因不明の脳卒中、またはブルガダ症候群でILR移植を受けている連続患者1734人を遡及的に分析した。 対象となる診断は、インプラントの適応症に応じて定義されました。失神に対する一時停止、動悸に対する上室性頻拍または心房細動、原因性脳卒中に対する心房細動、およびブルガダ症候群に対する心室頻拍または一時停止です。 追跡期間の中央値は34か月でした。 最大限に選択されたランク統計により、初期診断と後期診断を分ける全体的な閾値は 26 か月であることが特定されました。一方、適応症別の最適な診断期間は、失神では 14 か月、動悸では 13 か月、原因性脳卒中では 16 か月、ブルガダ症候群では 55 か月でした。 失神と動悸では、ほとんどの実用的な診断は早期に行われ、診断効率は 26 か月後に著しく低下し、後期の所見は指標の提示とあまり明確に関連していないことがよくありました。 原因性脳卒中では、心房細動の検出は初期に最も頻繁に検出されましたが、その後の抗血栓管理の変更につながる可能性があり、長期モニタリングに対する個別の「グレーゾーン」アプローチを裏付けています。 対照的に、ブルガダ症候群では、長期間の追跡調査を通じて持続的な診断率が示され、遅発性心室性不整脈または休止は、植込み型除細動器の植込みやデバイスの種類の選択など、予後および治療に大きな影響を及ぼしました。 結論: ILR モニタリングの価値は、時間と症状に大きく依存します。 早期の追跡調査で明らかになっていない場合、失神や動悸に関しては、長期にわたる定期的なモニタリングや再移植の増加価値は限られていると思われるが、ブルガダ症候群では長期にわたる監視が依然として正当化される可能性があり、原因性脳卒中後には個別化されるべきである。 これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしています。</t>
+    <t xml:space="preserve">はじめに: 植込み型ループレコーダー (ILR) モニタリングの最適な期間は依然として不確実であり、植込みの適応症に応じて異なる場合があります。 われわれは、失神、動悸、原因性脳卒中、またはブルガダ症候群のために移植された患者間で、ILRで検出された不整脈の時間依存的な診断率と臨床的関連性が異な​​るかどうかを評価した。 
+【目的】
+この研究は、臨床適応症全体にわたるILRの時間依存的な診断率を定義し、早期診断と後期診断で臨床管理への影響が異なるかどうかを評価することを目的としました。 方法と
+【結果】
+我々は、イタリアの5つのセンターで原因不明の失神、動悸、原因不明の脳卒中、またはブルガダ症候群でILR移植を受けている連続患者1734人を遡及的に分析した。 対象となる診断は、インプラントの適応症に応じて定義されました。失神に対する一時停止、動悸に対する上室性頻拍または心房細動、原因性脳卒中に対する心房細動、およびブルガダ症候群に対する心室頻拍または一時停止です。 追跡期間の中央値は34か月であった。 最大限に選択されたランク統計により、初期診断と後期診断を分ける全体的な閾値は 26 か月であることが特定されました。一方、適応症別の最適な診断期間は、失神では 14 か月、動悸では 13 か月、原因性脳卒中では 16 か月、ブルガダ症候群では 55 か月であった。 失神と動悸では、ほとんどの実用的な診断は早期に行われ、診断効率は 26 か月後に著しく低下し、後期の所見は指標の提示とあまり明確に関連していないことがよくあった。 原因性脳卒中では、心房細動の検出は初期に最も頻繁に検出されましたが、その後の抗血栓管理の変更につながる可能性があり、長期モニタリングに対する個別の「グレーゾーン」アプローチを裏付けています。 対照的に、ブルガダ症候群では、長期間の追跡調査を通じて持続的な診断率が示され、遅発性心室性不整脈または休止は、植込み型除細動器の植込みやデバイスの種類の選択など、予後および治療に大きな影響を及ぼしました。 
+【結論】
+ ILR モニタリングの価値は、時間と症状に大きく依存します。 早期の追跡調査で明らかになっていない場合、失神や動悸に関しては、長期にわたる定期的なモニタリングや再移植の増加価値は限られていると思われるが、ブルガダ症候群では長期にわたる監視が依然として正当化される可能性があり、原因性脳卒中後には個別化されるべきである。 これらの観察結果は、デバイスの寿命のみに基づいた一律のアプローチではなく、適応症主導型の ILR フォローアップ戦略をサポートしています。</t>
   </si>
   <si>
     <t xml:space="preserve">INTRODUCTION:
@@ -3475,7 +3876,7 @@
     <t>10.1016/j.hrthm.2026.07.012 doi</t>
   </si>
   <si>
-    <t>抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではありません。この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定しています。また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供します。</t>
+    <t>抗不整脈薬は、心拍リズム障害のある患者にとって重要な治療選択肢となり得ますが、抗不整脈薬の使用に関連する試験ではすべての患者およびシナリオが代表されているわけではない。この心拍リズム協会の科学的声明は、少なくとも部分的には研究が十分に進んでいないために、ほとんどガイダンスが存在しない一般的な臨床シナリオを特定しています。また、利用可能な証拠と経験豊富な臨床医の多様なグループの臨床能力を調達し、可能な限り実践的なアドバイスを提供し、各推奨事項の理論的根拠も提供します。</t>
   </si>
   <si>
     <t>Antiarrhythmic drugs can be an important treatment option for patients with heart rhythm disorders, but not all patients and scenarios are represented in trials related to antiarrhythmic drug use. This Heart Rhythm Society scientific statement identifies common clinical scenarios for which little guidance exists, at least partly because they are understudied. It also provides as much practical advice as possible, sourcing available evidence and the clinical proficiency of a diverse group of experienced clinicians, and provides the rationale for each recommendation.</t>
@@ -3494,7 +3895,16 @@
     <t>10.1016/j.hrthm.2026.08.052 doi</t>
   </si>
   <si>
-    <t>背景: 心房性不整脈はファロー四徴症 (TOF) 修復後によく見られますが、心室中隔欠損 (VSD) 修復後にはまれです。 術後の要因が寄与している可能性もありますが、術前の電気生理学的差異も、この異なる不整脈リスクの根底にある可能性があります。 目的: この研究の目的は、TOF の小児患者と VSD の小児患者の間で術前の心房電気生理学を比較することでした。 方法: TOF の小児 26 名と VSD の小児 41 名の心房 (右心房、左心房 [LA]、肺静脈 [PV]、およびバックマン束) で術中の心外膜マッピングを実施しました。 電位電圧と形態、および伝導特性が分析されました。 結果: TOF患者ではVSD患者よりもLA拡張の有病率が低いにもかかわらず(29% vs 81%、P = 0.004)、TOFはLAとPVの電位が低かった(LA: 3.4 ± 1.7 mV vs 5.3 ± 2.5 mV; PV: 1.8 [1.1-5.6] mV vs 4.7) [1.4-8.9] mV、両方 P &lt; 0.01) より低電圧領域が多い (LA: 12.9% [0.0%-53.7%] vs 4.4% [0.0%-29.0%]; PV: 23.9% [3.6%-47.0%] vs 7.0% [0.0%-35.9%]、両方 P &lt; 0.01)、伝導ブロックの有病率が高い (LA: 0.6% [0.0%-6.5%] vs 0.0% [0.0%-1.2%]、P &lt; 0.001)、および 2 つの偏向を含む電位 (短い二重電位: LA、12.1% [0.5%-41.8%] vs 8.8% [1.3%-18.9%]、P = 0.032;長い二重ポテンシャル: LA、0.1% [0.0%-13.8%] vs 0.0% [0.0%-2.2%]、P = 0.034)。 結論: TOF の小児患者は、VSD の患者よりも、特に LA と PV で心房電気生理学的異常が多く、これらの部位での心房電気生理学的変化が TOF 患者でより顕著であることが示唆されます。</t>
+    <t xml:space="preserve">【背景】
+ 心房性不整脈はファロー四徴症 (TOF) 修復後によく見られますが、心室中隔欠損 (VSD) 修復後にはまれです。 術後の要因が寄与している可能性もありますが、術前の電気生理学的差異も、この異なる不整脈リスクの根底にある可能性があります。 
+【目的】
+ この研究の目的は、TOF の小児患者と VSD の小児患者の間で術前の心房電気生理学を比較することであった。 
+【方法】
+ TOF の小児 26 名と VSD の小児 41 名の心房 (右心房、左心房 [LA]、肺静脈 [PV]、およびバックマン束) で術中の心外膜マッピングを実施しました。 電位電圧と形態、および伝導特性が分析されました。 
+【結果】
+ TOF患者ではVSD患者よりもLA拡張の有病率が低いにもかかわらず(29% vs 81%、P = 0.004)、TOFはLAとPVの電位が低かった(LA: 3.4 ± 1.7 mV vs 5.3 ± 2.5 mV; PV: 1.8 [1.1-5.6] mV vs 4.7) [1.4-8.9] mV、両方 P &lt; 0.01) より低電圧領域が多い (LA: 12.9% [0.0%-53.7%] vs 4.4% [0.0%-29.0%]; PV: 23.9% [3.6%-47.0%] vs 7.0% [0.0%-35.9%]、両方 P &lt; 0.01)、伝導ブロックの有病率が高い (LA: 0.6% [0.0%-6.5%] vs 0.0% [0.0%-1.2%]、P &lt; 0.001)、および 2 つの偏向を含む電位 (短い二重電位: LA、12.1% [0.5%-41.8%] vs 8.8% [1.3%-18.9%]、P = 0.032;長い二重ポテンシャル: LA、0.1% [0.0%-13.8%] vs 0.0% [0.0%-2.2%]、P = 0.034)。 
+【結論】
+ TOF の小児患者は、VSD の患者よりも、特に LA と PV で心房電気生理学的異常が多く、これらの部位での心房電気生理学的変化が TOF 患者でより顕著であることが示唆されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3541,7 +3951,14 @@
     <t>10.1161/CIRCEP.125.014266 doi</t>
   </si>
   <si>
-    <t>背景: 持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。 我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。 方法：CUVIA-AF2研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。 一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。 活動電位持続時間回復曲線の最大傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。 すべてのマーカーは、6 つの肺静脈外領域にわたって評価されました。 安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。 結果: 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察されました。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。 安定したDFを伴う安定したPSは、1年間の追跡調査での高いAF再発と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。 安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。 結論: 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
+    <t xml:space="preserve">【背景】
+ 持続性心房細動 (AF) におけるドライバーを対象としたアブレーションの臨床転帰には一貫性がなく、AF ドライバーのダイナミクスを特徴付け、アブレーション戦略を導くための仮想心臓ベースのアプローチの必要性が強調されています。 我々は、大規模な持続性AFコホートからの仮想心臓モデルを使用して、AFアブレーション後の調律結果に関連する肺静脈外ドライバーの電気生理学的特徴を定義しました。 
+【方法】
+CUVIA-AF2研究（心房細動の仮想アブレーションガイド付きカテーテルアブレーションの臨床的有用性2）から得られた持続性心房細動患者165人を対象に、心臓コンピュータ断層撮影法と電気解剖学的マップを統合した左心房仮想心臓モデルを分析した。 34 秒の仮想 AF シミュレーション中に、安定した位相特異点 (PS) は、直径 10 mm 内で 2 秒以上持続する PS によって特定されました。 一時的な安定性を評価するために、主要周波数 (DF) を 3 回の連続する 6 秒間隔で評価しました。 活動電位持続時間回復曲線の最大傾きは、仮想ランプ ペーシング (200 ～ 120 ミリ秒) によって導出されました。 すべてのマーカーは、6 つの肺静脈外領域にわたって評価された。 安定した PS、DF、活動電位持続時間回復曲線の最大傾き、低電圧領域 (&lt;0.5 mV)、および 1 年間のリズム結果の間の関連性が分析されました。 
+【結果】
+ 肺静脈外領域での安定した PS が 124 人 (75%) の患者で観察された。このうち 43 人 (34.7%) は安定した DF を示し、81 人 (65.3%) は蛇行した DF を示しました。 仮想心臓モデルの領域解析では、安定した DF を伴う安定した PS を含む領域は、蛇行する DF を伴う安定した PS を有する領域よりも、活動電位持続時間回復曲線のより高い最大傾き (1.41±0.80 対 1.09±0.60; &lt;0.001) とより大きな局所仮想低電圧負荷 (2.96±3.23% 対 2.10±2.75%) を示しました。 安定したDFを伴う安定したPSは、1年間の追跡調査での高いAF再発と相関した(ログランク=0.002;調整後ハザード比、5.78[95%CI、2.18-15.3])。 安定した PS と DF を含む予測モデルは、再発予測の見かけの曲線下面積 0.765 を示しました。 
+【結論】
+ 仮想心臓モデルで同定された安定した PS と安定した DF は、有害なモデル由来の局所基質特徴とアブレーション後のより高い再発率に関連していた。 これらのマーカーの仮想心臓ベースの同定は、持続性 AF におけるアブレーション反応の予測を改善する可能性があり、前向きの検証が保証されます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3573,7 +3990,14 @@
     <t>10.1161/CIRCEP.125.014506 doi</t>
   </si>
   <si>
-    <t>背景: パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。 肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。 方法: フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 結果: 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動でした。 最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。 完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察されました。 耐久性のある PVI の割合は、PFA の適用数 (12 回の適用) とともに増加しました。 同様に、ルーフ/PW ブロック率は、16 を超えるアプリケーション (&lt;0.01) で 88% に増加しました。 僧帽弁峡部のブロック率は依然として低く (31%)、申請数と有意な相関はありませんでした。 結論：ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えて行われた場合、AF が観察される頻度は低くなりました。 耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。 ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
+    <t xml:space="preserve">【背景】
+ パルスフィールドアブレーション (PFA) は、心房細動 (AF) のアブレーションのための新規かつ急速に拡大しているエネルギーです。 肺静脈 (PV) の特性と PV 以外の PFA 適用と、やり直し手順中に観察される不整脈の再発または持続性病変の種類との関係は依然として不明です。 
+【方法】
+ フランス PFA 全国網羅的多中心レジストリのこのサブ研究では、最初の AF アブレーション処置中に提供された PFA アプリケーションに関する詳細なデータを収集しました。 3次元マッピングによるやり直し処置を受けた不整脈再発患者（n=145）について、再発の種類、持続的PV隔離（PVI）の割合、およびアブレーションライン上の完全ブロックの存在を分析した。 
+【結果】
+ 再発性不整脈は 58% が AF、28% が心房頻脈、8% が典型的な心房粗動であった。 最初のアブレーションが PV 外領域をターゲットとした場合 (45 対 71%; =0.01)、および直径 35 mm のカテーテルが PVI のみに使用された場合 (50 対 77%; =0.01)、AF は観察される頻度が低くなりました。 完全な耐久性のある PVI は患者の 42% (個別の PV ごとに 69% ～ 76%) で観察され、耐久性のある屋根/PW および僧帽弁峡部ブロックはそれぞれ症例の 62% と 31% で観察された。 耐久性のある PVI の割合は、PFA の適用数 (12 回の適用) とともに増加しました。 同様に、ルーフ/PW ブロック率は、16 を超えるアプリケーション (&lt;0.01) で 88% に増加しました。 僧帽弁峡部のブロック率は依然として低く (31%)、申請数と有意な相関はありなかった。 
+【結論】
+ペンタスプリン PFA カテーテルを使用した最初の AF アブレーション後にやり直し処置を受けた患者では、アブレーション病変が PV を越えて行われた場合、AF が観察される頻度は低くなりました。 耐久性のある PVI またはブロックの高い割合は、PV あたり 12 を超える PFA アプリケーション、屋根/PW では 16 を超える PFA アプリケーションで達成されました。 ペンタスプライン PFA カテーテルを使用した場合、僧帽弁峡部ブロックの長期耐久性は低かった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3646,7 +4070,14 @@
     <t>10.1161/CIRCEP.126.015042 doi</t>
   </si>
   <si>
-    <t>背景: 可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。 初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。 この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。 方法: 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。 被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。 各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループになりました。 安楽死させる前に、フォローアップの再マッピング手順のために切除後 28±2 日間動物をモニタリングした。 28±2日目に肉眼的剖検と組織病理学を実施した。 結果: すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% 観察されました。 左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。 Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されませんでした。 Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。 溶血および心筋損傷マーカーの変化はすべてのグループ間で同様でしたが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないと評価されましたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価されました。 結論: 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察されました。 Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありませんでした。 Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しませんでした。</t>
+    <t xml:space="preserve">【背景】
+ 可変ループ円形カテーテルは、心房細動治療のための安全で効果的なパルスフィールドアブレーションカテーテルであることが示されています。 初期波形 (Seq1) の商用発売後、電極表面温度とアブレーション送達時間 (20 ～ 3.8 秒) を短縮する新しい波形 (Seq2) が開発されました。 この研究では、2 つの洗浄速度と 2 つの投与条件にわたって、Seq1 と Seq2 の安全性と有効性を比較します。 
+【方法】
+ 24 頭のヨークシャー豚を可変ループ円形カテーテルを使用したパルスフィールド アブレーションで治療しました。 被験者は、3 つのパルス レシピ/灌注アーム (Seq1、Seq1、および Seq 2) に無作為に割り当てられました。 各グループを名目上の 1 倍の用量グループと 2 倍の用量グループに分割し、合計 6 つの研究グループになりました。 安楽死させる前に、フォローアップの再マッピング手順のために切除後 28±2 日間動物をモニタリングした。 28±2日目に肉眼的剖検と組織病理学を実施した。 
+【結果】
+ すべてのグループにおいて、側副傷害の証拠のない壁貫通、周囲の肺静脈病変によって示されるように、急性および慢性肺静脈隔離の有効性が 100% 観察された。 左心耳、LA屋根、および後壁における貫壁性は、すべてのグループにわたって75%〜100%であり、僧帽弁峡部には存在しなかった。 Seq2 または Seq1 ではカテーテル血栓/炭化物は観察されなかった。 Seq1 では、血栓/炭化物が 25% (1x) と 100% (2x) で発生しました。 溶血および心筋損傷マーカーの変化はすべてのグループ間で同様であったが、2x グループで顕著に増加しました。 心エコー検査では、Seq2 のマイクロバブルはほとんどまたはまったくないと評価されたが、Seq1 と Seq1 はほとんどが中程度またはシャワー程度と評価された。 
+【結論】
+ 両方の投与条件にわたって、Seq1、Seq2、および Seq1 を含むすべてのグループで一貫して耐久性のある肺静脈隔離が観察された。 Seq2 は、アブレーション送出時間の短縮 (3.8 秒)、カテーテル血栓形成ゼロ、および微小気泡の発生がほとんどありなかった。 Seq1 でのより高い洗浄流量もカテーテル血栓の形成を軽減しましたが、マイクロバブルの生成は減少しなかった。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3675,7 +4106,12 @@
     <t>10.1161/CIRCEP.126.014860 doi</t>
   </si>
   <si>
-    <t>背景: PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解されます。 このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となります。 QT間隔の延長、不整脈のリスク、心臓突然死も代謝性心疾患で増大しており、解糖系調節障害と電気生理学的機能障害との間にクロストークが存在するかどうかという疑問が生じている。 方法 そこで我々は、心筋細胞特異的 PFKFB2 ノックアウトマウスモデル (cKO) と同腹子が一致した対照を用いて、心臓電気生理学に対する PFKFB2 欠損の影響を評価した。 そのために、我々は、摂食状態および12時間の絶食後の心電図検査を採用し、ベースラインと急性刺激性ストレスの存在下の両方で生理機能を調べました。 不整脈のメカニズムをさらに調査するために、パッチクランプ電気生理学と、対照心臓およびcKO心臓から単離した心室心筋細胞におけるIonOptix Ca過渡測定を使用しました。 結果: cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。 これは、心室心筋細胞における Ca 再取り込みの障害と自発的 Ca 放出事象の増加によって起こりました。 後者は、cKO心臓の摂食状態で増強される翻訳後修飾であるO-GlcNAc化を介して上方制御された。 最終的に、これらの変化は cKO マウスの心室頻脈性不整脈を引き起こし、絶食状態に比べて摂食状態で増強されました。 結論: これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆しています。</t>
+    <t xml:space="preserve">【背景】
+ PFKFB2 の心臓アイソフォーム (ホスホフルクトキナーゼ-2/フルクトース 2,6-ビスホスファターゼ) は心臓の最も強力な解糖調節因子ですが、インスリンシグナル伝達がないと分解されます。 このため、インスリンシグナル伝達の障害が特徴である代謝性心疾患では、PFKFB2 欠損を理解することが重要となります。 QT間隔の延長、不整脈のリスク、心臓突然死も代謝性心疾患で増大しており、解糖系調節障害と電気生理学的機能障害との間にクロストークが存在するかどうかという疑問が生じている。 方法 そこで我々は、心筋細胞特異的 PFKFB2 ノックアウトマウスモデル (cKO) と同腹子が一致した対照を用いて、心臓電気生理学に対する PFKFB2 欠損の影響を評価した。 そのために、我々は、摂食状態および12時間の絶食後の心電図検査を採用し、ベースラインと急性刺激性ストレスの存在下の両方で生理機能を調べました。 不整脈のメカニズムをさらに調査するために、パッチクランプ電気生理学と、対照心臓およびcKO心臓から単離した心室心筋細胞におけるIonOptix Ca過渡測定を使用しました。 
+【結果】
+ cKO マウスの心臓は、QT および活動電位持続時間の延長を特徴とする長期の再分極を示しました。 これは、心室心筋細胞における Ca 再取り込みの障害と自発的 Ca 放出事象の増加によって起こりました。 後者は、cKO心臓の摂食状態で増強される翻訳後修飾であるO-GlcNAc化を介して上方制御された。 最終的に、これらの変化は cKO マウスの心室頻脈性不整脈を引き起こし、絶食状態に比べて摂食状態で増強されました。 
+【結論】
+ これらのデータは、十分なグルコース利用可能性の存在下では、ホスホフルクトキナーゼ結合における心臓の解糖調節異常が心臓の電気生理学的不安定性を促進するのに十分であることを示唆しています。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -3704,7 +4140,14 @@
     <t>10.1161/CIRCEP.125.014773 doi</t>
   </si>
   <si>
-    <t>背景: 心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られています。 この研究は、発作性心房細動アブレーションの臨床試験の計画に情報を提供することを第二の目的として、アブレーション有効性エンドポイント検出と追跡期間との関係を評価することを目的としています。 方法: 4 つの前向き研究からの患者レベルのデータが集約されました。 長期有効性エンドポイントは、(1) 3 か月のブランク期間と 12 か月の追跡調査 (現在)、および (2) 2 か月のブランク期間と 6 か月の追跡調査 (提案) で計算されました。 感度、特異度、一致度は、現在のエンドポイントと提案されたエンドポイントに基づいて各研究について計算されました。 線形近似法を使用して 6 か月生存推定値を 12 か月に外挿し、予測された 12 か月生存率を実際の 12 か月生存率と比較しました。 線形近似を使用して、新しいパフォーマンス目標が導出され、各研究の 6 か月生存率と比較されました。 結果: 現在のエンドポイントと提案されたエンドポイントの比較分析により、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証されました。 線形近似法により、4 つのプールされた研究の推定 12 か月生存率は 72.5% となり、これに対し、真の 12 か月生存率は 71.0% (-1.5% 誤差) でした。 各研究の真の 12 か月生存率と個別に比較した場合、推定 12 か月生存率には -3.6% から 0.3% の範囲の誤差が生じました。 6 か月のエンドポイントを使用する試験では、56.2% という新しいパフォーマンス目標が提案されています。 結論: 2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと合理的なレベルの一致を示しました。 過去の比較を可能にすることで、線形近似を使用して 6 か月生存率から 12 か月生存率を確実に推定できます。</t>
+    <t xml:space="preserve">【背景】
+ 心房細動アブレーションの試験における 6 か月の有効性エンドポイントの使用に関する証拠は限られています。 この研究は、発作性心房細動アブレーションの臨床試験の計画に情報を提供することを第二の目的として、アブレーション有効性エンドポイント検出と追跡期間との関係を評価することを目的としています。 
+【方法】
+ 4 つの前向き研究からの患者レベルのデータが集約されました。 長期有効性エンドポイントは、(1) 3 か月のブランク期間と 12 か月の追跡調査 (現在)、および (2) 2 か月のブランク期間と 6 か月の追跡調査 (提案) で計算されました。 感度、特異度、一致度は、現在のエンドポイントと提案されたエンドポイントに基づいて各研究について計算されました。 線形近似法を使用して 6 か月生存推定値を 12 か月に外挿し、予測された 12 か月生存率を実際の 12 か月生存率と比較しました。 線形近似を使用して、新しいパフォーマンス目標が導出され、各研究の 6 か月生存率と比較されました。 
+【結果】
+ 現在のエンドポイントと提案されたエンドポイントの比較分析により、最近の 4 つの臨床試験全体で 83% ～ 92% の範囲の一致と 57% ～ 76% の範囲の感度が実証されました。 線形近似法により、4 つのプールされた研究の推定 12 か月生存率は 72.5% となり、これに対し、真の 12 か月生存率は 71.0% (-1.5% 誤差) であった。 各研究の真の 12 か月生存率と個別に比較した場合、推定 12 か月生存率には -3.6% から 0.3% の範囲の誤差が生じました。 6 か月のエンドポイントを使用する試験では、56.2% という新しいパフォーマンス目標が提案されています。 
+【結論】
+ 2 か月のブランク期間を含む 6 か月の追跡期間という提案されたエンドポイントは、現在の 12 か月の有効性エンドポイントと合理的なレベルの一致を示しました。 過去の比較を可能にすることで、線形近似を使用して 6 か月生存率から 12 か月生存率を確実に推定できます。</t>
   </si>
   <si>
     <t xml:space="preserve">BACKGROUND:
@@ -4498,7 +4941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
         <v>4</v>
       </c>
@@ -4576,7 +5019,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="11" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="4">
         <v>7</v>
       </c>
@@ -4862,7 +5305,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="22" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
         <v>18</v>
       </c>
@@ -4888,7 +5331,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="23" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4">
         <v>19</v>
       </c>
@@ -4914,7 +5357,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="24" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
         <v>20</v>
       </c>
@@ -4966,7 +5409,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
         <v>22</v>
       </c>
@@ -4992,7 +5435,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="27" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="4">
         <v>23</v>
       </c>
@@ -5044,7 +5487,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="29" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="4">
         <v>25</v>
       </c>
@@ -5096,7 +5539,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="31" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="4">
         <v>27</v>
       </c>
@@ -5200,7 +5643,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="4">
         <v>31</v>
       </c>
@@ -5460,7 +5903,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="45" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="4">
         <v>41</v>
       </c>
@@ -5902,7 +6345,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="62" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="11">
         <v>58</v>
       </c>
@@ -6136,7 +6579,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="71" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" ht="212" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="4">
         <v>67</v>
       </c>
@@ -6188,7 +6631,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="73" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="4">
         <v>69</v>
       </c>
@@ -6214,7 +6657,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="74" ht="148" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="11">
         <v>70</v>
       </c>
@@ -6318,7 +6761,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="78" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="11">
         <v>74</v>
       </c>
@@ -6344,7 +6787,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="79" ht="220" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="4">
         <v>75</v>
       </c>
@@ -6685,7 +7128,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>470</v>
       </c>
@@ -6823,7 +7266,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>477</v>
       </c>
@@ -6961,7 +7404,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>484</v>
       </c>
@@ -7099,7 +7542,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>491</v>
       </c>
@@ -7237,7 +7680,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>498</v>
       </c>
@@ -7375,7 +7818,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>505</v>
       </c>
@@ -7513,7 +7956,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>512</v>
       </c>
@@ -7651,7 +8094,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>519</v>
       </c>
@@ -7789,7 +8232,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>526</v>
       </c>
@@ -7927,7 +8370,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="804" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>533</v>
       </c>
@@ -8065,7 +8508,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="576" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>412</v>
       </c>
@@ -8203,7 +8646,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>540</v>
       </c>
@@ -8341,7 +8784,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>547</v>
       </c>
@@ -8479,7 +8922,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>555</v>
       </c>
@@ -8617,7 +9060,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>562</v>
       </c>
@@ -8755,7 +9198,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>569</v>
       </c>
@@ -8893,7 +9336,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>576</v>
       </c>
@@ -9031,7 +9474,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>583</v>
       </c>
@@ -9169,7 +9612,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>590</v>
       </c>
@@ -9307,7 +9750,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>597</v>
       </c>
@@ -9445,7 +9888,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>604</v>
       </c>
@@ -9721,7 +10164,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="709" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>611</v>
       </c>
@@ -9859,7 +10302,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="785" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>618</v>
       </c>
@@ -9997,7 +10440,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="747" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>625</v>
       </c>
@@ -10135,7 +10578,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>632</v>
       </c>
@@ -10273,7 +10716,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="823" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>639</v>
       </c>
@@ -10411,7 +10854,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>646</v>
       </c>
@@ -10549,7 +10992,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>653</v>
       </c>
@@ -10687,7 +11130,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="823" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>660</v>
       </c>
@@ -10825,7 +11268,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>667</v>
       </c>
@@ -10963,7 +11406,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>674</v>
       </c>
@@ -11239,7 +11682,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>681</v>
       </c>
@@ -11377,7 +11820,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="310" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>688</v>
       </c>
@@ -11515,7 +11958,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>694</v>
       </c>
@@ -11653,7 +12096,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>700</v>
       </c>
@@ -11791,7 +12234,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>706</v>
       </c>
@@ -11929,7 +12372,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="804" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="1108" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>712</v>
       </c>
@@ -12205,7 +12648,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>722</v>
       </c>
@@ -12619,7 +13062,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>433</v>
       </c>
@@ -13171,7 +13614,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="310" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>748</v>
       </c>
@@ -13447,7 +13890,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>760</v>
       </c>
@@ -13999,7 +14442,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>783</v>
       </c>
@@ -14137,7 +14580,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="994" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>441</v>
       </c>
@@ -14827,7 +15270,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="329" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>807</v>
       </c>
@@ -14965,7 +15408,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>813</v>
       </c>
@@ -15103,7 +15546,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>819</v>
       </c>
@@ -15241,7 +15684,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="576" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>825</v>
       </c>
@@ -15379,7 +15822,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="424" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>831</v>
       </c>
@@ -15517,7 +15960,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>837</v>
       </c>
@@ -15655,7 +16098,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>449</v>
       </c>
@@ -16069,7 +16512,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="709" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>855</v>
       </c>
@@ -16345,7 +16788,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>867</v>
       </c>
@@ -16483,7 +16926,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>875</v>
       </c>
@@ -16897,7 +17340,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>896</v>
       </c>
@@ -17035,7 +17478,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="367" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>903</v>
       </c>
@@ -17173,7 +17616,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="747" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>456</v>
       </c>
@@ -17311,7 +17754,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>910</v>
       </c>
@@ -17587,7 +18030,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>463</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
@@ -204,7 +204,7 @@
     <t xml:space="preserve">【概要】パルスフィールド (PF) ベースの肺静脈隔離 (PVI) 後の心房性不整脈 (AA) 再発に対する左心房 (LA) の解剖学的特徴の影響は不明である (前向き研究 (Prospective) / N = 287例)
 【方法】2023年6月から2024年9月まで、三次施設でペンタスプラインPFカテーテルによるPVIを受ける患者を前向きに登録した。 AA再発は、ホルター心電図と症状に基づくモニタリングを用いて、3、6、12か
 【結果】患者287人（年齢中央値66歳、女性34％、発作性AF61％）のうち、98人（34％）がPVI後中央値6か月で再発を経験した。 調整回帰分析では、右上の PV の最小直径が大きく（1 mm 増加あたり OR 1.11、95% CI (1.0
-【結論】PF ベースの PVI はさまざまな LA 解剖学的構造に適していると思われますが、これらの解剖学的特徴の予後価値を考えるとさらなる研究が必要である</t>
+【結論】右上部および左下部 PV の特定の解剖学的特徴は、PF ベースの PVI 後の再発とに関連していた。</t>
   </si>
   <si>
     <t xml:space="preserve">前向き研究 (Prospective)
@@ -227,7 +227,7 @@
     <t xml:space="preserve">【概要】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません (前向き研究 (Prospective) / N = 50例)
 【方法】STAR Apollo™ マッピング システム (Rhythm AI Ltd) は、ランク付けされた信号の確率的軌道分析を適用して、AF を持続する領域を示す可能性のある反復的な活性化パターン (RPA) と初期活性化部位 (ESA) を特定する FDA 認可のテクノロジーである
 【結果】肺静脈隔離術 (PVI) 後に再発する持続性心房細動 (AF) に対するやり直しアブレーションは持続的な成功に限界があり、補助的な基質戦略では一貫して結果が改善されていません。方法：この前向き多施設観察研究では、過去1回のPVI後に再発した持続性AF患者（以前の肺静脈外アブレーションは除く）に、肺静脈の再隔離、STAR Apolloマッピング、および術者主導の補助的アブレーションが施された
-【結論】実現可能性と安全性の研究として設計されており、単一群であるため、これらのデータは STAR ガイダンスの漸進的な有効性を確立することはできません。心強いリズム結果は仮説を生み出すものであり、PV 再分離単独とのランダム化比較を裏付けるものである</t>
+【結論】以前の PVI 後の再発性持続性 AF では、STAR Apollo ガイド下やり直しアブレーションは実行可能かつ安全で、適度なマッピングステップが追加され、12 か月時点でほとんどの患者で洞調律と症状の改善にに関連していた。</t>
   </si>
   <si>
     <t xml:space="preserve">Heart Rhythm
@@ -254,7 +254,7 @@
     <t xml:space="preserve">【概要】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである (前向き研究 (Prospective) / N = 27例)
 【方法】終端クリスタ（CT）領域は右横隔神経の近くに位置し、異方性伝導および自然または機能的伝導ブロックを示す可能性があると同時に、潜在的な非肺静脈トリガー部位としても機能する
 【結果】はじめに: 肺静脈隔離は依然として心房細動 (AF) アブレーションの中心ですが、右心房基質の修正は不完全に定義されたままである。 CT 関連の伝導遅延またはブロックが 27 人の患者 (75.0%) で認めた
-【結論】これらの発見は、確実な実現可能性と電気解剖学的エンドポイントを確立する。病変の耐久性、不整脈の再発、臨床上の利益の増加についてはさらなる研究が必要である</t>
+【結論】CT ガイド下、SN 温存 CCL は格子先端 PFA を用いて再現性よく作製でき、臨床的に明らかな横隔神経麻痺を伴わずに初回通過双方向横伝導ブロックを生成する。</t>
   </si>
   <si>
     <t xml:space="preserve">J Cardiovasc Electrophysiol
@@ -752,7 +752,7 @@
     <t xml:space="preserve">【概要】緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質である (観察研究・その他 / N = 44例)
 【方法】ただし、最適な伝導速度 (CV) 閾値と測定のための最良のアプローチはまだ決定されていません
 【結果】緩徐伝導解剖学的峡部 (SCAI) は、ファロー四徴症 (TOF) における心室性不整脈 (VA) の主な基質である。結果：合計44人の患者が含まれた（平均年齢44.6±13.8歳、56.8％が男性）
-【結論】より大きな集団でこのアプローチを評価するには、さらなる研究が必要である</t>
+【結論】TOF 患者の基質評価のための CV 測定に対するこの新規で再現性があり、使いやすい LVV ベースのアプローチは、LVV-CV が SMVT 誘導性に関連する SCAI を同定するために手動の CV 測定と比較して優れた識別性能を提供することを示唆している。</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -878,7 +878,7 @@
     <t xml:space="preserve">【概要】植込み型除細動器は、主に電気信号に基づいて治療を誘導しる (観察研究・その他 / N = 5例)
 【方法】血行動態センシングは、不整脈の直接的な生理学的影響に関する補足的な情報を提供する可能性がありる
 【結果】この研究では、血行動態センシング、電気センシング、心室ペーシングを統合した 3 次元胸骨下ショックリードの緊急の実現可能性と性能を評価しました。結果: リードの留置と抜去は、デバイスまたは処置に関連した急性有害事象もなく、すべての患者で成功しました
-【結論】これらの発見は、生理学に基づいた血管外植込み型除細動器システムのさらなる開発に対する人間による予備的な支援を提供しる。血行力学センシングアルゴリズムの慢性的なパフォーマンスと臨床検証にはさらなる研究が必要である</t>
+【結論】この多機能胸骨下リードの急性留置は実現可能であり、急性心室捕捉による血行力学および電気センシングの統合が可能になりました。</t>
   </si>
   <si>
     <t xml:space="preserve">観察研究・その他
@@ -4993,7 +4993,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" ht="196" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
         <v>6</v>
       </c>
@@ -5591,7 +5591,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="33" ht="132" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="4">
         <v>29</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="39" ht="180" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" ht="164" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="4">
         <v>35</v>
       </c>

--- a/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
+++ b/outputs/Catheter_Ablation_Papers_2026-09-30.xlsx
@@ -7128,7 +7128,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>470</v>
       </c>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>477</v>
       </c>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>484</v>
       </c>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>491</v>
       </c>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>498</v>
       </c>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>505</v>
       </c>
@@ -7956,7 +7956,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>512</v>
       </c>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>519</v>
       </c>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>526</v>
       </c>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="804" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>533</v>
       </c>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>412</v>
       </c>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>540</v>
       </c>
@@ -8784,7 +8784,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>547</v>
       </c>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>555</v>
       </c>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>562</v>
       </c>
@@ -9198,7 +9198,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>569</v>
       </c>
@@ -9336,7 +9336,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>576</v>
       </c>
@@ -9474,7 +9474,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>583</v>
       </c>
@@ -9612,7 +9612,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>590</v>
       </c>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>597</v>
       </c>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>604</v>
       </c>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="709" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>611</v>
       </c>
@@ -10302,7 +10302,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="785" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>618</v>
       </c>
@@ -10440,7 +10440,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="747" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>625</v>
       </c>
@@ -10578,7 +10578,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>632</v>
       </c>
@@ -10716,7 +10716,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="823" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>639</v>
       </c>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>646</v>
       </c>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>653</v>
       </c>
@@ -11130,7 +11130,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="823" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>660</v>
       </c>
@@ -11268,7 +11268,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>667</v>
       </c>
@@ -11406,7 +11406,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="728" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>674</v>
       </c>
@@ -11682,7 +11682,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>681</v>
       </c>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>688</v>
       </c>
@@ -11958,7 +11958,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>694</v>
       </c>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="614" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>700</v>
       </c>
@@ -12234,7 +12234,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>706</v>
       </c>
@@ -12372,7 +12372,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="1108" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="937" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>712</v>
       </c>
@@ -12648,7 +12648,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="652" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>722</v>
       </c>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>433</v>
       </c>
@@ -13614,7 +13614,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="481" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="386" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>748</v>
       </c>
@@ -13890,7 +13890,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>760</v>
       </c>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>783</v>
       </c>
@@ -14580,7 +14580,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="994" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="823" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>441</v>
       </c>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="405" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>807</v>
       </c>
@@ -15408,7 +15408,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>813</v>
       </c>
@@ -15546,7 +15546,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>819</v>
       </c>
@@ -15684,7 +15684,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="576" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="462" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>825</v>
       </c>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>831</v>
       </c>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>837</v>
       </c>
@@ -16098,7 +16098,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="595" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="519" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>449</v>
       </c>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="709" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>855</v>
       </c>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="766" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>867</v>
       </c>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>875</v>
       </c>
@@ -17340,7 +17340,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="690" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="557" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>896</v>
       </c>
@@ -17478,7 +17478,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="538" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="443" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>903</v>
       </c>
@@ -17616,7 +17616,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="747" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="576" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>456</v>
       </c>
@@ -17754,7 +17754,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="633" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>910</v>
       </c>
@@ -18030,7 +18030,7 @@
       </c>
       <c r="B16" s="24"/>
     </row>
-    <row r="17" ht="671" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" ht="500" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>463</v>
       </c>
